--- a/content/climate/XRO/XRO_RelENSO_fcst.xlsx
+++ b/content/climate/XRO/XRO_RelENSO_fcst.xlsx
@@ -17,9 +17,6 @@
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
 <sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="72" uniqueCount="72">
   <si>
-    <t>init</t>
-  </si>
-  <si>
     <t>2021-01</t>
   </si>
   <si>
@@ -216,6 +213,9 @@
   </si>
   <si>
     <t>2026-06</t>
+  </si>
+  <si>
+    <t>2026-07</t>
   </si>
   <si>
     <t>Readme</t>
@@ -592,7 +592,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:U67"/>
+  <dimension ref="A1:U68"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="2" max="21" width="10.7109375" style="1" customWidth="1"/>
@@ -665,4292 +665,4357 @@
     </row>
     <row r="2" spans="1:21">
       <c r="A2" s="2" t="s">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="B2" s="1">
         <v>-1.078</v>
       </c>
       <c r="C2" s="1">
-        <v>-0.99</v>
+        <v>-0.993</v>
       </c>
       <c r="D2" s="1">
-        <v>-0.875</v>
+        <v>-0.87</v>
       </c>
       <c r="E2" s="1">
-        <v>-0.79</v>
+        <v>-0.78</v>
       </c>
       <c r="F2" s="1">
-        <v>-0.664</v>
+        <v>-0.644</v>
       </c>
       <c r="G2" s="1">
-        <v>-0.487</v>
+        <v>-0.45</v>
       </c>
       <c r="H2" s="1">
-        <v>-0.349</v>
+        <v>-0.294</v>
       </c>
       <c r="I2" s="1">
-        <v>-0.302</v>
+        <v>-0.234</v>
       </c>
       <c r="J2" s="1">
-        <v>-0.342</v>
+        <v>-0.256</v>
       </c>
       <c r="K2" s="1">
-        <v>-0.431</v>
+        <v>-0.32</v>
       </c>
       <c r="L2" s="1">
-        <v>-0.511</v>
+        <v>-0.363</v>
       </c>
       <c r="M2" s="1">
-        <v>-0.53</v>
+        <v>-0.351</v>
       </c>
       <c r="N2" s="1">
-        <v>-0.446</v>
+        <v>-0.311</v>
       </c>
       <c r="O2" s="1">
-        <v>-0.357</v>
+        <v>-0.259</v>
       </c>
       <c r="P2" s="1">
-        <v>-0.322</v>
+        <v>-0.225</v>
       </c>
       <c r="Q2" s="1">
-        <v>-0.294</v>
+        <v>-0.181</v>
       </c>
       <c r="R2" s="1">
-        <v>-0.206</v>
+        <v>-0.079</v>
       </c>
       <c r="S2" s="1">
-        <v>-0.03</v>
+        <v>0.046</v>
       </c>
       <c r="T2" s="1">
-        <v>0.121</v>
+        <v>0.148</v>
       </c>
       <c r="U2" s="1">
-        <v>0.206</v>
+        <v>0.228</v>
       </c>
     </row>
     <row r="3" spans="1:21">
       <c r="A3" s="2" t="s">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="B3" s="1">
         <v>-0.907</v>
       </c>
       <c r="C3" s="1">
-        <v>-0.851</v>
+        <v>-0.849</v>
       </c>
       <c r="D3" s="1">
-        <v>-0.757</v>
+        <v>-0.751</v>
       </c>
       <c r="E3" s="1">
-        <v>-0.63</v>
+        <v>-0.636</v>
       </c>
       <c r="F3" s="1">
-        <v>-0.5</v>
+        <v>-0.504</v>
       </c>
       <c r="G3" s="1">
-        <v>-0.415</v>
+        <v>-0.412</v>
       </c>
       <c r="H3" s="1">
-        <v>-0.403</v>
+        <v>-0.393</v>
       </c>
       <c r="I3" s="1">
-        <v>-0.475</v>
+        <v>-0.417</v>
       </c>
       <c r="J3" s="1">
-        <v>-0.58</v>
+        <v>-0.462</v>
       </c>
       <c r="K3" s="1">
-        <v>-0.667</v>
+        <v>-0.528</v>
       </c>
       <c r="L3" s="1">
-        <v>-0.68</v>
+        <v>-0.536</v>
       </c>
       <c r="M3" s="1">
-        <v>-0.617</v>
+        <v>-0.464</v>
       </c>
       <c r="N3" s="1">
-        <v>-0.545</v>
+        <v>-0.376</v>
       </c>
       <c r="O3" s="1">
-        <v>-0.5</v>
+        <v>-0.315</v>
       </c>
       <c r="P3" s="1">
-        <v>-0.442</v>
+        <v>-0.266</v>
       </c>
       <c r="Q3" s="1">
-        <v>-0.312</v>
+        <v>-0.159</v>
       </c>
       <c r="R3" s="1">
-        <v>-0.115</v>
+        <v>-0.012</v>
       </c>
       <c r="S3" s="1">
-        <v>0.07199999999999999</v>
+        <v>0.125</v>
       </c>
       <c r="T3" s="1">
-        <v>0.21</v>
+        <v>0.243</v>
       </c>
       <c r="U3" s="1">
-        <v>0.324</v>
+        <v>0.314</v>
       </c>
     </row>
     <row r="4" spans="1:21">
       <c r="A4" s="2" t="s">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="B4" s="1">
         <v>-0.681</v>
       </c>
       <c r="C4" s="1">
-        <v>-0.649</v>
+        <v>-0.653</v>
       </c>
       <c r="D4" s="1">
-        <v>-0.5659999999999999</v>
+        <v>-0.581</v>
       </c>
       <c r="E4" s="1">
-        <v>-0.424</v>
+        <v>-0.44</v>
       </c>
       <c r="F4" s="1">
-        <v>-0.289</v>
+        <v>-0.306</v>
       </c>
       <c r="G4" s="1">
-        <v>-0.232</v>
+        <v>-0.235</v>
       </c>
       <c r="H4" s="1">
-        <v>-0.258</v>
+        <v>-0.227</v>
       </c>
       <c r="I4" s="1">
-        <v>-0.343</v>
+        <v>-0.261</v>
       </c>
       <c r="J4" s="1">
-        <v>-0.424</v>
+        <v>-0.307</v>
       </c>
       <c r="K4" s="1">
-        <v>-0.444</v>
+        <v>-0.315</v>
       </c>
       <c r="L4" s="1">
-        <v>-0.413</v>
+        <v>-0.269</v>
       </c>
       <c r="M4" s="1">
-        <v>-0.362</v>
+        <v>-0.217</v>
       </c>
       <c r="N4" s="1">
-        <v>-0.301</v>
+        <v>-0.188</v>
       </c>
       <c r="O4" s="1">
-        <v>-0.246</v>
+        <v>-0.148</v>
       </c>
       <c r="P4" s="1">
-        <v>-0.153</v>
+        <v>-0.056</v>
       </c>
       <c r="Q4" s="1">
-        <v>-0.028</v>
+        <v>0.079</v>
       </c>
       <c r="R4" s="1">
-        <v>0.063</v>
+        <v>0.194</v>
       </c>
       <c r="S4" s="1">
-        <v>0.129</v>
+        <v>0.252</v>
       </c>
       <c r="T4" s="1">
-        <v>0.178</v>
+        <v>0.291</v>
       </c>
       <c r="U4" s="1">
-        <v>0.206</v>
+        <v>0.337</v>
       </c>
     </row>
     <row r="5" spans="1:21">
       <c r="A5" s="2" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="B5" s="1">
         <v>-0.741</v>
       </c>
       <c r="C5" s="1">
-        <v>-0.661</v>
+        <v>-0.673</v>
       </c>
       <c r="D5" s="1">
-        <v>-0.533</v>
+        <v>-0.546</v>
       </c>
       <c r="E5" s="1">
         <v>-0.44</v>
       </c>
       <c r="F5" s="1">
-        <v>-0.406</v>
+        <v>-0.398</v>
       </c>
       <c r="G5" s="1">
-        <v>-0.445</v>
+        <v>-0.419</v>
       </c>
       <c r="H5" s="1">
-        <v>-0.525</v>
+        <v>-0.49</v>
       </c>
       <c r="I5" s="1">
-        <v>-0.581</v>
+        <v>-0.572</v>
       </c>
       <c r="J5" s="1">
-        <v>-0.5649999999999999</v>
+        <v>-0.574</v>
       </c>
       <c r="K5" s="1">
-        <v>-0.483</v>
+        <v>-0.491</v>
       </c>
       <c r="L5" s="1">
-        <v>-0.426</v>
+        <v>-0.419</v>
       </c>
       <c r="M5" s="1">
-        <v>-0.389</v>
+        <v>-0.362</v>
       </c>
       <c r="N5" s="1">
-        <v>-0.318</v>
+        <v>-0.28</v>
       </c>
       <c r="O5" s="1">
-        <v>-0.201</v>
+        <v>-0.14</v>
       </c>
       <c r="P5" s="1">
-        <v>-0.06</v>
+        <v>0.011</v>
       </c>
       <c r="Q5" s="1">
-        <v>0.075</v>
+        <v>0.14</v>
       </c>
       <c r="R5" s="1">
-        <v>0.173</v>
+        <v>0.221</v>
       </c>
       <c r="S5" s="1">
-        <v>0.207</v>
+        <v>0.278</v>
       </c>
       <c r="T5" s="1">
-        <v>0.243</v>
+        <v>0.353</v>
       </c>
       <c r="U5" s="1">
-        <v>0.291</v>
+        <v>0.422</v>
       </c>
     </row>
     <row r="6" spans="1:21">
       <c r="A6" s="2" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="B6" s="1">
         <v>-0.448</v>
       </c>
       <c r="C6" s="1">
-        <v>-0.418</v>
+        <v>-0.42</v>
       </c>
       <c r="D6" s="1">
-        <v>-0.382</v>
+        <v>-0.383</v>
       </c>
       <c r="E6" s="1">
-        <v>-0.373</v>
+        <v>-0.398</v>
       </c>
       <c r="F6" s="1">
-        <v>-0.43</v>
+        <v>-0.465</v>
       </c>
       <c r="G6" s="1">
-        <v>-0.54</v>
+        <v>-0.543</v>
       </c>
       <c r="H6" s="1">
-        <v>-0.656</v>
+        <v>-0.638</v>
       </c>
       <c r="I6" s="1">
-        <v>-0.72</v>
+        <v>-0.6889999999999999</v>
       </c>
       <c r="J6" s="1">
-        <v>-0.678</v>
+        <v>-0.644</v>
       </c>
       <c r="K6" s="1">
-        <v>-0.6</v>
+        <v>-0.553</v>
       </c>
       <c r="L6" s="1">
-        <v>-0.526</v>
+        <v>-0.47</v>
       </c>
       <c r="M6" s="1">
-        <v>-0.451</v>
+        <v>-0.39</v>
       </c>
       <c r="N6" s="1">
-        <v>-0.324</v>
+        <v>-0.27</v>
       </c>
       <c r="O6" s="1">
-        <v>-0.155</v>
+        <v>-0.101</v>
       </c>
       <c r="P6" s="1">
-        <v>-0.015</v>
+        <v>0.033</v>
       </c>
       <c r="Q6" s="1">
-        <v>0.08400000000000001</v>
+        <v>0.109</v>
       </c>
       <c r="R6" s="1">
-        <v>0.146</v>
+        <v>0.148</v>
       </c>
       <c r="S6" s="1">
-        <v>0.16</v>
+        <v>0.177</v>
       </c>
       <c r="T6" s="1">
-        <v>0.168</v>
+        <v>0.227</v>
       </c>
       <c r="U6" s="1">
-        <v>0.196</v>
+        <v>0.277</v>
       </c>
     </row>
     <row r="7" spans="1:21">
       <c r="A7" s="2" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="B7" s="1">
         <v>-0.277</v>
       </c>
       <c r="C7" s="1">
-        <v>-0.305</v>
+        <v>-0.321</v>
       </c>
       <c r="D7" s="1">
-        <v>-0.364</v>
+        <v>-0.381</v>
       </c>
       <c r="E7" s="1">
-        <v>-0.445</v>
+        <v>-0.463</v>
       </c>
       <c r="F7" s="1">
-        <v>-0.5629999999999999</v>
+        <v>-0.586</v>
       </c>
       <c r="G7" s="1">
-        <v>-0.719</v>
+        <v>-0.72</v>
       </c>
       <c r="H7" s="1">
-        <v>-0.828</v>
+        <v>-0.822</v>
       </c>
       <c r="I7" s="1">
-        <v>-0.822</v>
+        <v>-0.8110000000000001</v>
       </c>
       <c r="J7" s="1">
-        <v>-0.745</v>
+        <v>-0.737</v>
       </c>
       <c r="K7" s="1">
-        <v>-0.623</v>
+        <v>-0.649</v>
       </c>
       <c r="L7" s="1">
-        <v>-0.496</v>
+        <v>-0.533</v>
       </c>
       <c r="M7" s="1">
-        <v>-0.373</v>
+        <v>-0.402</v>
       </c>
       <c r="N7" s="1">
-        <v>-0.24</v>
+        <v>-0.243</v>
       </c>
       <c r="O7" s="1">
-        <v>-0.114</v>
+        <v>-0.107</v>
       </c>
       <c r="P7" s="1">
-        <v>-0.04</v>
+        <v>-0.035</v>
       </c>
       <c r="Q7" s="1">
-        <v>-0.004</v>
+        <v>-0.003</v>
       </c>
       <c r="R7" s="1">
-        <v>0.004</v>
+        <v>-0.012</v>
       </c>
       <c r="S7" s="1">
-        <v>0.029</v>
+        <v>-0.018</v>
       </c>
       <c r="T7" s="1">
+        <v>0.025</v>
+      </c>
+      <c r="U7" s="1">
         <v>0.07199999999999999</v>
-      </c>
-      <c r="U7" s="1">
-        <v>0.117</v>
       </c>
     </row>
     <row r="8" spans="1:21">
       <c r="A8" s="2" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="B8" s="1">
         <v>-0.452</v>
       </c>
       <c r="C8" s="1">
-        <v>-0.532</v>
+        <v>-0.544</v>
       </c>
       <c r="D8" s="1">
-        <v>-0.659</v>
+        <v>-0.6840000000000001</v>
       </c>
       <c r="E8" s="1">
-        <v>-0.794</v>
+        <v>-0.837</v>
       </c>
       <c r="F8" s="1">
-        <v>-0.953</v>
+        <v>-1.011</v>
       </c>
       <c r="G8" s="1">
-        <v>-1.08</v>
+        <v>-1.137</v>
       </c>
       <c r="H8" s="1">
-        <v>-1.094</v>
+        <v>-1.123</v>
       </c>
       <c r="I8" s="1">
-        <v>-0.971</v>
+        <v>-0.999</v>
       </c>
       <c r="J8" s="1">
-        <v>-0.833</v>
+        <v>-0.844</v>
       </c>
       <c r="K8" s="1">
-        <v>-0.706</v>
+        <v>-0.6870000000000001</v>
       </c>
       <c r="L8" s="1">
-        <v>-0.538</v>
+        <v>-0.522</v>
       </c>
       <c r="M8" s="1">
-        <v>-0.377</v>
+        <v>-0.349</v>
       </c>
       <c r="N8" s="1">
-        <v>-0.25</v>
+        <v>-0.181</v>
       </c>
       <c r="O8" s="1">
-        <v>-0.176</v>
+        <v>-0.063</v>
       </c>
       <c r="P8" s="1">
-        <v>-0.147</v>
+        <v>-0.005</v>
       </c>
       <c r="Q8" s="1">
-        <v>-0.137</v>
+        <v>0.014</v>
       </c>
       <c r="R8" s="1">
-        <v>-0.148</v>
+        <v>0.049</v>
       </c>
       <c r="S8" s="1">
-        <v>-0.131</v>
+        <v>0.117</v>
       </c>
       <c r="T8" s="1">
-        <v>-0.079</v>
+        <v>0.164</v>
       </c>
       <c r="U8" s="1">
-        <v>-0.056</v>
+        <v>0.168</v>
       </c>
     </row>
     <row r="9" spans="1:21">
       <c r="A9" s="2" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="B9" s="1">
         <v>-0.641</v>
       </c>
       <c r="C9" s="1">
-        <v>-0.713</v>
+        <v>-0.712</v>
       </c>
       <c r="D9" s="1">
-        <v>-0.885</v>
+        <v>-0.888</v>
       </c>
       <c r="E9" s="1">
-        <v>-1.117</v>
+        <v>-1.115</v>
       </c>
       <c r="F9" s="1">
-        <v>-1.306</v>
+        <v>-1.295</v>
       </c>
       <c r="G9" s="1">
-        <v>-1.321</v>
+        <v>-1.314</v>
       </c>
       <c r="H9" s="1">
-        <v>-1.194</v>
+        <v>-1.181</v>
       </c>
       <c r="I9" s="1">
-        <v>-1.046</v>
+        <v>-1.014</v>
       </c>
       <c r="J9" s="1">
-        <v>-0.899</v>
+        <v>-0.85</v>
       </c>
       <c r="K9" s="1">
-        <v>-0.699</v>
+        <v>-0.663</v>
       </c>
       <c r="L9" s="1">
-        <v>-0.466</v>
+        <v>-0.458</v>
       </c>
       <c r="M9" s="1">
-        <v>-0.268</v>
+        <v>-0.286</v>
       </c>
       <c r="N9" s="1">
-        <v>-0.161</v>
+        <v>-0.181</v>
       </c>
       <c r="O9" s="1">
-        <v>-0.13</v>
+        <v>-0.164</v>
       </c>
       <c r="P9" s="1">
-        <v>-0.144</v>
+        <v>-0.172</v>
       </c>
       <c r="Q9" s="1">
-        <v>-0.165</v>
+        <v>-0.169</v>
       </c>
       <c r="R9" s="1">
-        <v>-0.12</v>
+        <v>-0.124</v>
       </c>
       <c r="S9" s="1">
-        <v>-0.043</v>
+        <v>-0.057</v>
       </c>
       <c r="T9" s="1">
-        <v>-0.011</v>
+        <v>-0.047</v>
       </c>
       <c r="U9" s="1">
-        <v>-0.001</v>
+        <v>-0.051</v>
       </c>
     </row>
     <row r="10" spans="1:21">
       <c r="A10" s="2" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="B10" s="1">
         <v>-0.646</v>
       </c>
       <c r="C10" s="1">
-        <v>-0.744</v>
+        <v>-0.762</v>
       </c>
       <c r="D10" s="1">
-        <v>-0.9379999999999999</v>
+        <v>-0.974</v>
       </c>
       <c r="E10" s="1">
-        <v>-1.107</v>
+        <v>-1.142</v>
       </c>
       <c r="F10" s="1">
-        <v>-1.135</v>
+        <v>-1.169</v>
       </c>
       <c r="G10" s="1">
-        <v>-1.018</v>
+        <v>-1.061</v>
       </c>
       <c r="H10" s="1">
-        <v>-0.869</v>
+        <v>-0.919</v>
       </c>
       <c r="I10" s="1">
-        <v>-0.74</v>
+        <v>-0.778</v>
       </c>
       <c r="J10" s="1">
-        <v>-0.6</v>
+        <v>-0.63</v>
       </c>
       <c r="K10" s="1">
-        <v>-0.459</v>
+        <v>-0.481</v>
       </c>
       <c r="L10" s="1">
-        <v>-0.347</v>
+        <v>-0.351</v>
       </c>
       <c r="M10" s="1">
-        <v>-0.278</v>
+        <v>-0.28</v>
       </c>
       <c r="N10" s="1">
-        <v>-0.286</v>
+        <v>-0.267</v>
       </c>
       <c r="O10" s="1">
-        <v>-0.349</v>
+        <v>-0.296</v>
       </c>
       <c r="P10" s="1">
-        <v>-0.392</v>
+        <v>-0.329</v>
       </c>
       <c r="Q10" s="1">
-        <v>-0.376</v>
+        <v>-0.298</v>
       </c>
       <c r="R10" s="1">
-        <v>-0.302</v>
+        <v>-0.239</v>
       </c>
       <c r="S10" s="1">
-        <v>-0.239</v>
+        <v>-0.19</v>
       </c>
       <c r="T10" s="1">
-        <v>-0.212</v>
+        <v>-0.157</v>
       </c>
       <c r="U10" s="1">
-        <v>-0.177</v>
+        <v>-0.139</v>
       </c>
     </row>
     <row r="11" spans="1:21">
       <c r="A11" s="2" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="B11" s="1">
         <v>-1.17</v>
       </c>
       <c r="C11" s="1">
-        <v>-1.306</v>
+        <v>-1.321</v>
       </c>
       <c r="D11" s="1">
-        <v>-1.498</v>
+        <v>-1.521</v>
       </c>
       <c r="E11" s="1">
-        <v>-1.509</v>
+        <v>-1.522</v>
       </c>
       <c r="F11" s="1">
-        <v>-1.353</v>
+        <v>-1.346</v>
       </c>
       <c r="G11" s="1">
-        <v>-1.152</v>
+        <v>-1.138</v>
       </c>
       <c r="H11" s="1">
-        <v>-0.964</v>
+        <v>-0.95</v>
       </c>
       <c r="I11" s="1">
-        <v>-0.752</v>
+        <v>-0.74</v>
       </c>
       <c r="J11" s="1">
-        <v>-0.497</v>
+        <v>-0.49</v>
       </c>
       <c r="K11" s="1">
-        <v>-0.276</v>
+        <v>-0.28</v>
       </c>
       <c r="L11" s="1">
-        <v>-0.141</v>
+        <v>-0.18</v>
       </c>
       <c r="M11" s="1">
-        <v>-0.06900000000000001</v>
+        <v>-0.166</v>
       </c>
       <c r="N11" s="1">
-        <v>-0.042</v>
+        <v>-0.174</v>
       </c>
       <c r="O11" s="1">
-        <v>-0.011</v>
+        <v>-0.162</v>
       </c>
       <c r="P11" s="1">
-        <v>0.06</v>
+        <v>-0.107</v>
       </c>
       <c r="Q11" s="1">
-        <v>0.145</v>
+        <v>-0.037</v>
       </c>
       <c r="R11" s="1">
-        <v>0.177</v>
+        <v>-0.004</v>
       </c>
       <c r="S11" s="1">
-        <v>0.123</v>
+        <v>-0.024</v>
       </c>
       <c r="T11" s="1">
-        <v>0.067</v>
+        <v>-0.04</v>
       </c>
       <c r="U11" s="1">
-        <v>0.067</v>
+        <v>0.004</v>
       </c>
     </row>
     <row r="12" spans="1:21">
       <c r="A12" s="2" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="B12" s="1">
         <v>-1.218</v>
       </c>
       <c r="C12" s="1">
-        <v>-1.269</v>
+        <v>-1.272</v>
       </c>
       <c r="D12" s="1">
-        <v>-1.266</v>
+        <v>-1.26</v>
       </c>
       <c r="E12" s="1">
-        <v>-1.143</v>
+        <v>-1.156</v>
       </c>
       <c r="F12" s="1">
-        <v>-0.98</v>
+        <v>-1.005</v>
       </c>
       <c r="G12" s="1">
-        <v>-0.8110000000000001</v>
+        <v>-0.828</v>
       </c>
       <c r="H12" s="1">
-        <v>-0.6</v>
+        <v>-0.62</v>
       </c>
       <c r="I12" s="1">
-        <v>-0.358</v>
+        <v>-0.381</v>
       </c>
       <c r="J12" s="1">
-        <v>-0.177</v>
+        <v>-0.185</v>
       </c>
       <c r="K12" s="1">
-        <v>-0.07099999999999999</v>
+        <v>-0.079</v>
       </c>
       <c r="L12" s="1">
-        <v>-0.033</v>
+        <v>-0.03</v>
       </c>
       <c r="M12" s="1">
-        <v>-0.034</v>
+        <v>-0.001</v>
       </c>
       <c r="N12" s="1">
-        <v>-0.005</v>
+        <v>0.022</v>
       </c>
       <c r="O12" s="1">
-        <v>0.07199999999999999</v>
+        <v>0.082</v>
       </c>
       <c r="P12" s="1">
-        <v>0.149</v>
+        <v>0.14</v>
       </c>
       <c r="Q12" s="1">
-        <v>0.177</v>
+        <v>0.158</v>
       </c>
       <c r="R12" s="1">
-        <v>0.137</v>
+        <v>0.138</v>
       </c>
       <c r="S12" s="1">
-        <v>0.08400000000000001</v>
+        <v>0.099</v>
       </c>
       <c r="T12" s="1">
-        <v>0.077</v>
+        <v>0.073</v>
       </c>
       <c r="U12" s="1">
-        <v>0.08</v>
+        <v>0.089</v>
       </c>
     </row>
     <row r="13" spans="1:21">
       <c r="A13" s="2" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B13" s="1">
         <v>-1.227</v>
       </c>
       <c r="C13" s="1">
-        <v>-1.154</v>
+        <v>-1.147</v>
       </c>
       <c r="D13" s="1">
-        <v>-1.008</v>
+        <v>-0.977</v>
       </c>
       <c r="E13" s="1">
-        <v>-0.867</v>
+        <v>-0.849</v>
       </c>
       <c r="F13" s="1">
-        <v>-0.705</v>
+        <v>-0.721</v>
       </c>
       <c r="G13" s="1">
-        <v>-0.494</v>
+        <v>-0.489</v>
       </c>
       <c r="H13" s="1">
-        <v>-0.278</v>
+        <v>-0.203</v>
       </c>
       <c r="I13" s="1">
-        <v>-0.094</v>
+        <v>0.008999999999999999</v>
       </c>
       <c r="J13" s="1">
-        <v>0.032</v>
+        <v>0.117</v>
       </c>
       <c r="K13" s="1">
-        <v>0.1</v>
+        <v>0.189</v>
       </c>
       <c r="L13" s="1">
-        <v>0.161</v>
+        <v>0.268</v>
       </c>
       <c r="M13" s="1">
-        <v>0.229</v>
+        <v>0.366</v>
       </c>
       <c r="N13" s="1">
-        <v>0.34</v>
+        <v>0.464</v>
       </c>
       <c r="O13" s="1">
-        <v>0.42</v>
+        <v>0.534</v>
       </c>
       <c r="P13" s="1">
-        <v>0.427</v>
+        <v>0.509</v>
       </c>
       <c r="Q13" s="1">
-        <v>0.372</v>
+        <v>0.435</v>
       </c>
       <c r="R13" s="1">
-        <v>0.282</v>
+        <v>0.359</v>
       </c>
       <c r="S13" s="1">
-        <v>0.232</v>
+        <v>0.302</v>
       </c>
       <c r="T13" s="1">
-        <v>0.229</v>
+        <v>0.289</v>
       </c>
       <c r="U13" s="1">
-        <v>0.244</v>
+        <v>0.257</v>
       </c>
     </row>
     <row r="14" spans="1:21">
       <c r="A14" s="2" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="B14" s="1">
         <v>-1.152</v>
       </c>
       <c r="C14" s="1">
-        <v>-1.046</v>
+        <v>-1.056</v>
       </c>
       <c r="D14" s="1">
-        <v>-0.905</v>
+        <v>-0.924</v>
       </c>
       <c r="E14" s="1">
-        <v>-0.799</v>
+        <v>-0.823</v>
       </c>
       <c r="F14" s="1">
-        <v>-0.62</v>
+        <v>-0.666</v>
       </c>
       <c r="G14" s="1">
-        <v>-0.378</v>
+        <v>-0.431</v>
       </c>
       <c r="H14" s="1">
-        <v>-0.174</v>
+        <v>-0.215</v>
       </c>
       <c r="I14" s="1">
-        <v>-0.059</v>
+        <v>-0.09</v>
       </c>
       <c r="J14" s="1">
-        <v>-0.012</v>
+        <v>-0.046</v>
       </c>
       <c r="K14" s="1">
-        <v>0.006</v>
+        <v>-0.033</v>
       </c>
       <c r="L14" s="1">
-        <v>0.062</v>
+        <v>0.013</v>
       </c>
       <c r="M14" s="1">
-        <v>0.185</v>
+        <v>0.112</v>
       </c>
       <c r="N14" s="1">
-        <v>0.284</v>
+        <v>0.214</v>
       </c>
       <c r="O14" s="1">
-        <v>0.313</v>
+        <v>0.251</v>
       </c>
       <c r="P14" s="1">
-        <v>0.261</v>
+        <v>0.222</v>
       </c>
       <c r="Q14" s="1">
-        <v>0.199</v>
+        <v>0.169</v>
       </c>
       <c r="R14" s="1">
-        <v>0.182</v>
+        <v>0.162</v>
       </c>
       <c r="S14" s="1">
-        <v>0.195</v>
+        <v>0.216</v>
       </c>
       <c r="T14" s="1">
-        <v>0.204</v>
+        <v>0.271</v>
       </c>
       <c r="U14" s="1">
-        <v>0.204</v>
+        <v>0.286</v>
       </c>
     </row>
     <row r="15" spans="1:21">
       <c r="A15" s="2" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="B15" s="1">
         <v>-1.011</v>
       </c>
       <c r="C15" s="1">
-        <v>-0.954</v>
+        <v>-0.968</v>
       </c>
       <c r="D15" s="1">
-        <v>-0.869</v>
+        <v>-0.89</v>
       </c>
       <c r="E15" s="1">
-        <v>-0.722</v>
+        <v>-0.729</v>
       </c>
       <c r="F15" s="1">
-        <v>-0.47</v>
+        <v>-0.469</v>
       </c>
       <c r="G15" s="1">
-        <v>-0.226</v>
+        <v>-0.224</v>
       </c>
       <c r="H15" s="1">
-        <v>-0.07099999999999999</v>
+        <v>-0.096</v>
       </c>
       <c r="I15" s="1">
-        <v>0</v>
+        <v>-0.065</v>
       </c>
       <c r="J15" s="1">
-        <v>0.038</v>
+        <v>-0.06</v>
       </c>
       <c r="K15" s="1">
-        <v>0.11</v>
+        <v>-0.015</v>
       </c>
       <c r="L15" s="1">
-        <v>0.222</v>
+        <v>0.101</v>
       </c>
       <c r="M15" s="1">
-        <v>0.326</v>
+        <v>0.212</v>
       </c>
       <c r="N15" s="1">
-        <v>0.353</v>
+        <v>0.249</v>
       </c>
       <c r="O15" s="1">
-        <v>0.306</v>
+        <v>0.217</v>
       </c>
       <c r="P15" s="1">
-        <v>0.254</v>
+        <v>0.155</v>
       </c>
       <c r="Q15" s="1">
-        <v>0.218</v>
+        <v>0.141</v>
       </c>
       <c r="R15" s="1">
-        <v>0.231</v>
+        <v>0.186</v>
       </c>
       <c r="S15" s="1">
-        <v>0.268</v>
+        <v>0.241</v>
       </c>
       <c r="T15" s="1">
-        <v>0.296</v>
+        <v>0.282</v>
       </c>
       <c r="U15" s="1">
-        <v>0.324</v>
+        <v>0.303</v>
       </c>
     </row>
     <row r="16" spans="1:21">
       <c r="A16" s="2" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="B16" s="1">
         <v>-1.278</v>
       </c>
       <c r="C16" s="1">
-        <v>-1.222</v>
+        <v>-1.223</v>
       </c>
       <c r="D16" s="1">
-        <v>-1.037</v>
+        <v>-1.047</v>
       </c>
       <c r="E16" s="1">
-        <v>-0.749</v>
+        <v>-0.788</v>
       </c>
       <c r="F16" s="1">
-        <v>-0.476</v>
+        <v>-0.544</v>
       </c>
       <c r="G16" s="1">
-        <v>-0.323</v>
+        <v>-0.386</v>
       </c>
       <c r="H16" s="1">
-        <v>-0.311</v>
+        <v>-0.357</v>
       </c>
       <c r="I16" s="1">
-        <v>-0.35</v>
+        <v>-0.408</v>
       </c>
       <c r="J16" s="1">
-        <v>-0.368</v>
+        <v>-0.456</v>
       </c>
       <c r="K16" s="1">
-        <v>-0.297</v>
+        <v>-0.412</v>
       </c>
       <c r="L16" s="1">
-        <v>-0.164</v>
+        <v>-0.277</v>
       </c>
       <c r="M16" s="1">
-        <v>-0.063</v>
+        <v>-0.191</v>
       </c>
       <c r="N16" s="1">
-        <v>-0.042</v>
+        <v>-0.19</v>
       </c>
       <c r="O16" s="1">
-        <v>-0.038</v>
+        <v>-0.188</v>
       </c>
       <c r="P16" s="1">
-        <v>0.037</v>
+        <v>-0.08500000000000001</v>
       </c>
       <c r="Q16" s="1">
-        <v>0.195</v>
+        <v>0.105</v>
       </c>
       <c r="R16" s="1">
-        <v>0.361</v>
+        <v>0.29</v>
       </c>
       <c r="S16" s="1">
-        <v>0.458</v>
+        <v>0.427</v>
       </c>
       <c r="T16" s="1">
-        <v>0.524</v>
+        <v>0.538</v>
       </c>
       <c r="U16" s="1">
-        <v>0.597</v>
+        <v>0.647</v>
       </c>
     </row>
     <row r="17" spans="1:21">
       <c r="A17" s="2" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="B17" s="1">
         <v>-1.291</v>
       </c>
       <c r="C17" s="1">
-        <v>-1.195</v>
+        <v>-1.19</v>
       </c>
       <c r="D17" s="1">
-        <v>-0.963</v>
+        <v>-0.925</v>
       </c>
       <c r="E17" s="1">
-        <v>-0.725</v>
+        <v>-0.667</v>
       </c>
       <c r="F17" s="1">
-        <v>-0.611</v>
+        <v>-0.536</v>
       </c>
       <c r="G17" s="1">
-        <v>-0.647</v>
+        <v>-0.547</v>
       </c>
       <c r="H17" s="1">
-        <v>-0.785</v>
+        <v>-0.6830000000000001</v>
       </c>
       <c r="I17" s="1">
-        <v>-0.907</v>
+        <v>-0.8139999999999999</v>
       </c>
       <c r="J17" s="1">
-        <v>-0.877</v>
+        <v>-0.758</v>
       </c>
       <c r="K17" s="1">
-        <v>-0.708</v>
+        <v>-0.578</v>
       </c>
       <c r="L17" s="1">
-        <v>-0.5659999999999999</v>
+        <v>-0.45</v>
       </c>
       <c r="M17" s="1">
-        <v>-0.535</v>
+        <v>-0.413</v>
       </c>
       <c r="N17" s="1">
-        <v>-0.495</v>
+        <v>-0.378</v>
       </c>
       <c r="O17" s="1">
-        <v>-0.32</v>
+        <v>-0.235</v>
       </c>
       <c r="P17" s="1">
-        <v>-0.028</v>
+        <v>0.034</v>
       </c>
       <c r="Q17" s="1">
-        <v>0.266</v>
+        <v>0.323</v>
       </c>
       <c r="R17" s="1">
-        <v>0.476</v>
+        <v>0.544</v>
       </c>
       <c r="S17" s="1">
-        <v>0.641</v>
+        <v>0.726</v>
       </c>
       <c r="T17" s="1">
-        <v>0.791</v>
+        <v>0.925</v>
       </c>
       <c r="U17" s="1">
-        <v>0.947</v>
+        <v>1.124</v>
       </c>
     </row>
     <row r="18" spans="1:21">
       <c r="A18" s="2" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="B18" s="1">
         <v>-1.16</v>
       </c>
       <c r="C18" s="1">
-        <v>-0.999</v>
+        <v>-1.005</v>
       </c>
       <c r="D18" s="1">
-        <v>-0.768</v>
+        <v>-0.764</v>
       </c>
       <c r="E18" s="1">
-        <v>-0.664</v>
+        <v>-0.669</v>
       </c>
       <c r="F18" s="1">
-        <v>-0.711</v>
+        <v>-0.742</v>
       </c>
       <c r="G18" s="1">
-        <v>-0.869</v>
+        <v>-0.928</v>
       </c>
       <c r="H18" s="1">
-        <v>-1.033</v>
+        <v>-1.106</v>
       </c>
       <c r="I18" s="1">
-        <v>-1.034</v>
+        <v>-1.119</v>
       </c>
       <c r="J18" s="1">
-        <v>-0.877</v>
+        <v>-0.951</v>
       </c>
       <c r="K18" s="1">
-        <v>-0.736</v>
+        <v>-0.797</v>
       </c>
       <c r="L18" s="1">
-        <v>-0.67</v>
+        <v>-0.748</v>
       </c>
       <c r="M18" s="1">
-        <v>-0.598</v>
+        <v>-0.681</v>
       </c>
       <c r="N18" s="1">
-        <v>-0.39</v>
+        <v>-0.471</v>
       </c>
       <c r="O18" s="1">
-        <v>-0.054</v>
+        <v>-0.143</v>
       </c>
       <c r="P18" s="1">
-        <v>0.255</v>
+        <v>0.176</v>
       </c>
       <c r="Q18" s="1">
-        <v>0.468</v>
+        <v>0.396</v>
       </c>
       <c r="R18" s="1">
-        <v>0.635</v>
+        <v>0.55</v>
       </c>
       <c r="S18" s="1">
-        <v>0.806</v>
+        <v>0.6860000000000001</v>
       </c>
       <c r="T18" s="1">
-        <v>0.986</v>
+        <v>0.805</v>
       </c>
       <c r="U18" s="1">
-        <v>1.135</v>
+        <v>0.897</v>
       </c>
     </row>
     <row r="19" spans="1:21">
       <c r="A19" s="2" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="B19" s="1">
         <v>-0.786</v>
       </c>
       <c r="C19" s="1">
-        <v>-0.673</v>
+        <v>-0.6879999999999999</v>
       </c>
       <c r="D19" s="1">
-        <v>-0.588</v>
+        <v>-0.608</v>
       </c>
       <c r="E19" s="1">
-        <v>-0.6840000000000001</v>
+        <v>-0.68</v>
       </c>
       <c r="F19" s="1">
-        <v>-0.874</v>
+        <v>-0.856</v>
       </c>
       <c r="G19" s="1">
-        <v>-1.036</v>
+        <v>-0.993</v>
       </c>
       <c r="H19" s="1">
-        <v>-1.042</v>
+        <v>-0.99</v>
       </c>
       <c r="I19" s="1">
-        <v>-0.91</v>
+        <v>-0.861</v>
       </c>
       <c r="J19" s="1">
-        <v>-0.798</v>
+        <v>-0.741</v>
       </c>
       <c r="K19" s="1">
-        <v>-0.75</v>
+        <v>-0.701</v>
       </c>
       <c r="L19" s="1">
-        <v>-0.665</v>
+        <v>-0.633</v>
       </c>
       <c r="M19" s="1">
-        <v>-0.441</v>
+        <v>-0.429</v>
       </c>
       <c r="N19" s="1">
-        <v>-0.126</v>
+        <v>-0.111</v>
       </c>
       <c r="O19" s="1">
-        <v>0.158</v>
+        <v>0.196</v>
       </c>
       <c r="P19" s="1">
-        <v>0.354</v>
+        <v>0.409</v>
       </c>
       <c r="Q19" s="1">
-        <v>0.486</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="R19" s="1">
-        <v>0.592</v>
+        <v>0.6889999999999999</v>
       </c>
       <c r="S19" s="1">
-        <v>0.715</v>
+        <v>0.8080000000000001</v>
       </c>
       <c r="T19" s="1">
-        <v>0.86</v>
+        <v>0.929</v>
       </c>
       <c r="U19" s="1">
-        <v>0.922</v>
+        <v>0.983</v>
       </c>
     </row>
     <row r="20" spans="1:21">
       <c r="A20" s="2" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="B20" s="1">
         <v>-0.644</v>
       </c>
       <c r="C20" s="1">
-        <v>-0.669</v>
+        <v>-0.657</v>
       </c>
       <c r="D20" s="1">
-        <v>-0.779</v>
+        <v>-0.767</v>
       </c>
       <c r="E20" s="1">
-        <v>-0.978</v>
+        <v>-0.956</v>
       </c>
       <c r="F20" s="1">
-        <v>-1.174</v>
+        <v>-1.117</v>
       </c>
       <c r="G20" s="1">
-        <v>-1.197</v>
+        <v>-1.112</v>
       </c>
       <c r="H20" s="1">
-        <v>-1.043</v>
+        <v>-0.955</v>
       </c>
       <c r="I20" s="1">
-        <v>-0.896</v>
+        <v>-0.791</v>
       </c>
       <c r="J20" s="1">
-        <v>-0.827</v>
+        <v>-0.708</v>
       </c>
       <c r="K20" s="1">
-        <v>-0.734</v>
+        <v>-0.632</v>
       </c>
       <c r="L20" s="1">
-        <v>-0.455</v>
+        <v>-0.399</v>
       </c>
       <c r="M20" s="1">
-        <v>-0.019</v>
+        <v>-0.012</v>
       </c>
       <c r="N20" s="1">
-        <v>0.389</v>
+        <v>0.387</v>
       </c>
       <c r="O20" s="1">
-        <v>0.6850000000000001</v>
+        <v>0.68</v>
       </c>
       <c r="P20" s="1">
-        <v>0.922</v>
+        <v>0.895</v>
       </c>
       <c r="Q20" s="1">
-        <v>1.145</v>
+        <v>1.124</v>
       </c>
       <c r="R20" s="1">
-        <v>1.373</v>
+        <v>1.353</v>
       </c>
       <c r="S20" s="1">
-        <v>1.567</v>
+        <v>1.527</v>
       </c>
       <c r="T20" s="1">
-        <v>1.64</v>
+        <v>1.579</v>
       </c>
       <c r="U20" s="1">
-        <v>1.552</v>
+        <v>1.478</v>
       </c>
     </row>
     <row r="21" spans="1:21">
       <c r="A21" s="2" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="B21" s="1">
         <v>-0.909</v>
       </c>
       <c r="C21" s="1">
-        <v>-1.009</v>
+        <v>-0.997</v>
       </c>
       <c r="D21" s="1">
-        <v>-1.23</v>
+        <v>-1.223</v>
       </c>
       <c r="E21" s="1">
-        <v>-1.449</v>
+        <v>-1.437</v>
       </c>
       <c r="F21" s="1">
-        <v>-1.504</v>
+        <v>-1.46</v>
       </c>
       <c r="G21" s="1">
-        <v>-1.337</v>
+        <v>-1.286</v>
       </c>
       <c r="H21" s="1">
-        <v>-1.141</v>
+        <v>-1.091</v>
       </c>
       <c r="I21" s="1">
-        <v>-1.064</v>
+        <v>-0.98</v>
       </c>
       <c r="J21" s="1">
-        <v>-0.976</v>
+        <v>-0.851</v>
       </c>
       <c r="K21" s="1">
-        <v>-0.712</v>
+        <v>-0.57</v>
       </c>
       <c r="L21" s="1">
-        <v>-0.272</v>
+        <v>-0.124</v>
       </c>
       <c r="M21" s="1">
-        <v>0.181</v>
+        <v>0.321</v>
       </c>
       <c r="N21" s="1">
-        <v>0.511</v>
+        <v>0.66</v>
       </c>
       <c r="O21" s="1">
-        <v>0.767</v>
+        <v>0.9340000000000001</v>
       </c>
       <c r="P21" s="1">
-        <v>1.014</v>
+        <v>1.21</v>
       </c>
       <c r="Q21" s="1">
-        <v>1.272</v>
+        <v>1.493</v>
       </c>
       <c r="R21" s="1">
-        <v>1.495</v>
+        <v>1.722</v>
       </c>
       <c r="S21" s="1">
-        <v>1.606</v>
+        <v>1.793</v>
       </c>
       <c r="T21" s="1">
-        <v>1.546</v>
+        <v>1.669</v>
       </c>
       <c r="U21" s="1">
-        <v>1.33</v>
+        <v>1.392</v>
       </c>
     </row>
     <row r="22" spans="1:21">
       <c r="A22" s="2" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="B22" s="1">
         <v>-1.019</v>
       </c>
       <c r="C22" s="1">
-        <v>-1.141</v>
+        <v>-1.132</v>
       </c>
       <c r="D22" s="1">
-        <v>-1.341</v>
+        <v>-1.295</v>
       </c>
       <c r="E22" s="1">
-        <v>-1.354</v>
+        <v>-1.294</v>
       </c>
       <c r="F22" s="1">
-        <v>-1.158</v>
+        <v>-1.112</v>
       </c>
       <c r="G22" s="1">
-        <v>-0.973</v>
+        <v>-0.918</v>
       </c>
       <c r="H22" s="1">
-        <v>-0.889</v>
+        <v>-0.831</v>
       </c>
       <c r="I22" s="1">
-        <v>-0.787</v>
+        <v>-0.746</v>
       </c>
       <c r="J22" s="1">
-        <v>-0.514</v>
+        <v>-0.512</v>
       </c>
       <c r="K22" s="1">
-        <v>-0.105</v>
+        <v>-0.102</v>
       </c>
       <c r="L22" s="1">
-        <v>0.29</v>
+        <v>0.293</v>
       </c>
       <c r="M22" s="1">
-        <v>0.584</v>
+        <v>0.5620000000000001</v>
       </c>
       <c r="N22" s="1">
-        <v>0.827</v>
+        <v>0.776</v>
       </c>
       <c r="O22" s="1">
-        <v>1.082</v>
+        <v>0.996</v>
       </c>
       <c r="P22" s="1">
-        <v>1.337</v>
+        <v>1.224</v>
       </c>
       <c r="Q22" s="1">
-        <v>1.553</v>
+        <v>1.432</v>
       </c>
       <c r="R22" s="1">
-        <v>1.644</v>
+        <v>1.535</v>
       </c>
       <c r="S22" s="1">
-        <v>1.542</v>
+        <v>1.463</v>
       </c>
       <c r="T22" s="1">
-        <v>1.275</v>
+        <v>1.224</v>
       </c>
       <c r="U22" s="1">
-        <v>0.951</v>
+        <v>0.921</v>
       </c>
     </row>
     <row r="23" spans="1:21">
       <c r="A23" s="2" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="B23" s="1">
         <v>-0.985</v>
       </c>
       <c r="C23" s="1">
-        <v>-1.045</v>
+        <v>-1.048</v>
       </c>
       <c r="D23" s="1">
-        <v>-1.028</v>
+        <v>-1.06</v>
       </c>
       <c r="E23" s="1">
-        <v>-0.868</v>
+        <v>-0.914</v>
       </c>
       <c r="F23" s="1">
-        <v>-0.718</v>
+        <v>-0.769</v>
       </c>
       <c r="G23" s="1">
-        <v>-0.629</v>
+        <v>-0.708</v>
       </c>
       <c r="H23" s="1">
-        <v>-0.519</v>
+        <v>-0.615</v>
       </c>
       <c r="I23" s="1">
-        <v>-0.288</v>
+        <v>-0.376</v>
       </c>
       <c r="J23" s="1">
-        <v>0.054</v>
+        <v>-0.039</v>
       </c>
       <c r="K23" s="1">
-        <v>0.37</v>
+        <v>0.283</v>
       </c>
       <c r="L23" s="1">
-        <v>0.599</v>
+        <v>0.5</v>
       </c>
       <c r="M23" s="1">
-        <v>0.781</v>
+        <v>0.654</v>
       </c>
       <c r="N23" s="1">
-        <v>0.971</v>
+        <v>0.829</v>
       </c>
       <c r="O23" s="1">
-        <v>1.164</v>
+        <v>1.053</v>
       </c>
       <c r="P23" s="1">
-        <v>1.298</v>
+        <v>1.261</v>
       </c>
       <c r="Q23" s="1">
-        <v>1.346</v>
+        <v>1.37</v>
       </c>
       <c r="R23" s="1">
-        <v>1.263</v>
+        <v>1.32</v>
       </c>
       <c r="S23" s="1">
-        <v>1.06</v>
+        <v>1.12</v>
       </c>
       <c r="T23" s="1">
-        <v>0.799</v>
+        <v>0.862</v>
       </c>
       <c r="U23" s="1">
-        <v>0.546</v>
+        <v>0.593</v>
       </c>
     </row>
     <row r="24" spans="1:21">
       <c r="A24" s="2" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="B24" s="1">
         <v>-1.166</v>
       </c>
       <c r="C24" s="1">
-        <v>-1.086</v>
+        <v>-1.102</v>
       </c>
       <c r="D24" s="1">
-        <v>-0.906</v>
+        <v>-0.9330000000000001</v>
       </c>
       <c r="E24" s="1">
-        <v>-0.758</v>
+        <v>-0.781</v>
       </c>
       <c r="F24" s="1">
-        <v>-0.6830000000000001</v>
+        <v>-0.6870000000000001</v>
       </c>
       <c r="G24" s="1">
-        <v>-0.5580000000000001</v>
+        <v>-0.549</v>
       </c>
       <c r="H24" s="1">
-        <v>-0.318</v>
+        <v>-0.286</v>
       </c>
       <c r="I24" s="1">
-        <v>0.031</v>
+        <v>0.074</v>
       </c>
       <c r="J24" s="1">
-        <v>0.383</v>
+        <v>0.419</v>
       </c>
       <c r="K24" s="1">
-        <v>0.634</v>
+        <v>0.672</v>
       </c>
       <c r="L24" s="1">
-        <v>0.826</v>
+        <v>0.892</v>
       </c>
       <c r="M24" s="1">
-        <v>1.029</v>
+        <v>1.117</v>
       </c>
       <c r="N24" s="1">
-        <v>1.232</v>
+        <v>1.359</v>
       </c>
       <c r="O24" s="1">
-        <v>1.394</v>
+        <v>1.566</v>
       </c>
       <c r="P24" s="1">
-        <v>1.454</v>
+        <v>1.641</v>
       </c>
       <c r="Q24" s="1">
-        <v>1.35</v>
+        <v>1.537</v>
       </c>
       <c r="R24" s="1">
-        <v>1.133</v>
+        <v>1.289</v>
       </c>
       <c r="S24" s="1">
-        <v>0.863</v>
+        <v>0.965</v>
       </c>
       <c r="T24" s="1">
-        <v>0.571</v>
+        <v>0.615</v>
       </c>
       <c r="U24" s="1">
-        <v>0.301</v>
+        <v>0.3</v>
       </c>
     </row>
     <row r="25" spans="1:21">
       <c r="A25" s="2" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="B25" s="1">
         <v>-1.026</v>
       </c>
       <c r="C25" s="1">
-        <v>-0.93</v>
+        <v>-0.917</v>
       </c>
       <c r="D25" s="1">
-        <v>-0.785</v>
+        <v>-0.748</v>
       </c>
       <c r="E25" s="1">
-        <v>-0.665</v>
+        <v>-0.614</v>
       </c>
       <c r="F25" s="1">
-        <v>-0.487</v>
+        <v>-0.446</v>
       </c>
       <c r="G25" s="1">
-        <v>-0.201</v>
+        <v>-0.153</v>
       </c>
       <c r="H25" s="1">
-        <v>0.155</v>
+        <v>0.191</v>
       </c>
       <c r="I25" s="1">
-        <v>0.467</v>
+        <v>0.487</v>
       </c>
       <c r="J25" s="1">
-        <v>0.6899999999999999</v>
+        <v>0.722</v>
       </c>
       <c r="K25" s="1">
-        <v>0.894</v>
+        <v>0.953</v>
       </c>
       <c r="L25" s="1">
-        <v>1.133</v>
+        <v>1.223</v>
       </c>
       <c r="M25" s="1">
-        <v>1.385</v>
+        <v>1.487</v>
       </c>
       <c r="N25" s="1">
-        <v>1.588</v>
+        <v>1.661</v>
       </c>
       <c r="O25" s="1">
-        <v>1.661</v>
+        <v>1.678</v>
       </c>
       <c r="P25" s="1">
-        <v>1.554</v>
+        <v>1.538</v>
       </c>
       <c r="Q25" s="1">
-        <v>1.307</v>
+        <v>1.252</v>
       </c>
       <c r="R25" s="1">
-        <v>0.973</v>
+        <v>0.888</v>
       </c>
       <c r="S25" s="1">
-        <v>0.606</v>
+        <v>0.521</v>
       </c>
       <c r="T25" s="1">
-        <v>0.292</v>
+        <v>0.187</v>
       </c>
       <c r="U25" s="1">
-        <v>0.067</v>
+        <v>-0.064</v>
       </c>
     </row>
     <row r="26" spans="1:21">
       <c r="A26" s="2" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="B26" s="1">
         <v>-0.848</v>
       </c>
       <c r="C26" s="1">
-        <v>-0.781</v>
+        <v>-0.772</v>
       </c>
       <c r="D26" s="1">
-        <v>-0.665</v>
+        <v>-0.607</v>
       </c>
       <c r="E26" s="1">
-        <v>-0.489</v>
+        <v>-0.411</v>
       </c>
       <c r="F26" s="1">
-        <v>-0.204</v>
+        <v>-0.138</v>
       </c>
       <c r="G26" s="1">
-        <v>0.132</v>
+        <v>0.174</v>
       </c>
       <c r="H26" s="1">
-        <v>0.425</v>
+        <v>0.44</v>
       </c>
       <c r="I26" s="1">
-        <v>0.636</v>
+        <v>0.659</v>
       </c>
       <c r="J26" s="1">
-        <v>0.821</v>
+        <v>0.858</v>
       </c>
       <c r="K26" s="1">
-        <v>1.03</v>
+        <v>1.074</v>
       </c>
       <c r="L26" s="1">
-        <v>1.26</v>
+        <v>1.301</v>
       </c>
       <c r="M26" s="1">
-        <v>1.447</v>
+        <v>1.477</v>
       </c>
       <c r="N26" s="1">
-        <v>1.502</v>
+        <v>1.535</v>
       </c>
       <c r="O26" s="1">
-        <v>1.416</v>
+        <v>1.417</v>
       </c>
       <c r="P26" s="1">
-        <v>1.217</v>
+        <v>1.163</v>
       </c>
       <c r="Q26" s="1">
-        <v>0.9340000000000001</v>
+        <v>0.868</v>
       </c>
       <c r="R26" s="1">
-        <v>0.625</v>
+        <v>0.556</v>
       </c>
       <c r="S26" s="1">
-        <v>0.336</v>
+        <v>0.262</v>
       </c>
       <c r="T26" s="1">
-        <v>0.12</v>
+        <v>0.037</v>
       </c>
       <c r="U26" s="1">
-        <v>-0.026</v>
+        <v>-0.101</v>
       </c>
     </row>
     <row r="27" spans="1:21">
       <c r="A27" s="2" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="B27" s="1">
         <v>-0.646</v>
       </c>
       <c r="C27" s="1">
-        <v>-0.537</v>
+        <v>-0.543</v>
       </c>
       <c r="D27" s="1">
-        <v>-0.328</v>
+        <v>-0.344</v>
       </c>
       <c r="E27" s="1">
-        <v>-0.08500000000000001</v>
+        <v>-0.096</v>
       </c>
       <c r="F27" s="1">
-        <v>0.158</v>
+        <v>0.163</v>
       </c>
       <c r="G27" s="1">
-        <v>0.36</v>
+        <v>0.353</v>
       </c>
       <c r="H27" s="1">
-        <v>0.522</v>
+        <v>0.481</v>
       </c>
       <c r="I27" s="1">
-        <v>0.68</v>
+        <v>0.6</v>
       </c>
       <c r="J27" s="1">
-        <v>0.841</v>
+        <v>0.734</v>
       </c>
       <c r="K27" s="1">
-        <v>1.02</v>
+        <v>0.887</v>
       </c>
       <c r="L27" s="1">
-        <v>1.144</v>
+        <v>0.979</v>
       </c>
       <c r="M27" s="1">
-        <v>1.136</v>
+        <v>0.961</v>
       </c>
       <c r="N27" s="1">
-        <v>1.001</v>
+        <v>0.873</v>
       </c>
       <c r="O27" s="1">
-        <v>0.792</v>
+        <v>0.723</v>
       </c>
       <c r="P27" s="1">
-        <v>0.5649999999999999</v>
+        <v>0.538</v>
       </c>
       <c r="Q27" s="1">
-        <v>0.338</v>
+        <v>0.351</v>
       </c>
       <c r="R27" s="1">
-        <v>0.103</v>
+        <v>0.156</v>
       </c>
       <c r="S27" s="1">
-        <v>-0.106</v>
+        <v>-0.01</v>
       </c>
       <c r="T27" s="1">
-        <v>-0.252</v>
+        <v>-0.127</v>
       </c>
       <c r="U27" s="1">
-        <v>-0.331</v>
+        <v>-0.188</v>
       </c>
     </row>
     <row r="28" spans="1:21">
       <c r="A28" s="2" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="B28" s="1">
         <v>-0.262</v>
       </c>
       <c r="C28" s="1">
-        <v>-0.17</v>
+        <v>-0.165</v>
       </c>
       <c r="D28" s="1">
-        <v>0.028</v>
+        <v>0.045</v>
       </c>
       <c r="E28" s="1">
-        <v>0.251</v>
+        <v>0.288</v>
       </c>
       <c r="F28" s="1">
-        <v>0.447</v>
+        <v>0.5</v>
       </c>
       <c r="G28" s="1">
-        <v>0.585</v>
+        <v>0.646</v>
       </c>
       <c r="H28" s="1">
-        <v>0.704</v>
+        <v>0.764</v>
       </c>
       <c r="I28" s="1">
-        <v>0.843</v>
+        <v>0.88</v>
       </c>
       <c r="J28" s="1">
-        <v>0.95</v>
+        <v>1.007</v>
       </c>
       <c r="K28" s="1">
-        <v>1.014</v>
+        <v>1.09</v>
       </c>
       <c r="L28" s="1">
-        <v>0.994</v>
+        <v>1.038</v>
       </c>
       <c r="M28" s="1">
-        <v>0.877</v>
+        <v>0.881</v>
       </c>
       <c r="N28" s="1">
-        <v>0.707</v>
+        <v>0.6840000000000001</v>
       </c>
       <c r="O28" s="1">
-        <v>0.485</v>
+        <v>0.46</v>
       </c>
       <c r="P28" s="1">
-        <v>0.213</v>
+        <v>0.218</v>
       </c>
       <c r="Q28" s="1">
-        <v>-0.076</v>
+        <v>-0.065</v>
       </c>
       <c r="R28" s="1">
-        <v>-0.307</v>
+        <v>-0.31</v>
       </c>
       <c r="S28" s="1">
-        <v>-0.456</v>
+        <v>-0.468</v>
       </c>
       <c r="T28" s="1">
-        <v>-0.546</v>
+        <v>-0.555</v>
       </c>
       <c r="U28" s="1">
-        <v>-0.624</v>
+        <v>-0.623</v>
       </c>
     </row>
     <row r="29" spans="1:21">
       <c r="A29" s="2" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="B29" s="1">
         <v>-0.299</v>
       </c>
       <c r="C29" s="1">
-        <v>-0.154</v>
+        <v>-0.18</v>
       </c>
       <c r="D29" s="1">
-        <v>0.114</v>
+        <v>0.053</v>
       </c>
       <c r="E29" s="1">
-        <v>0.367</v>
+        <v>0.299</v>
       </c>
       <c r="F29" s="1">
-        <v>0.576</v>
+        <v>0.503</v>
       </c>
       <c r="G29" s="1">
-        <v>0.739</v>
+        <v>0.664</v>
       </c>
       <c r="H29" s="1">
-        <v>0.882</v>
+        <v>0.774</v>
       </c>
       <c r="I29" s="1">
-        <v>0.996</v>
+        <v>0.85</v>
       </c>
       <c r="J29" s="1">
-        <v>1.043</v>
+        <v>0.883</v>
       </c>
       <c r="K29" s="1">
-        <v>0.986</v>
+        <v>0.826</v>
       </c>
       <c r="L29" s="1">
-        <v>0.823</v>
+        <v>0.699</v>
       </c>
       <c r="M29" s="1">
-        <v>0.63</v>
+        <v>0.531</v>
       </c>
       <c r="N29" s="1">
-        <v>0.418</v>
+        <v>0.334</v>
       </c>
       <c r="O29" s="1">
-        <v>0.137</v>
+        <v>0.1</v>
       </c>
       <c r="P29" s="1">
-        <v>-0.186</v>
+        <v>-0.176</v>
       </c>
       <c r="Q29" s="1">
-        <v>-0.448</v>
+        <v>-0.419</v>
       </c>
       <c r="R29" s="1">
-        <v>-0.608</v>
+        <v>-0.581</v>
       </c>
       <c r="S29" s="1">
-        <v>-0.694</v>
+        <v>-0.68</v>
       </c>
       <c r="T29" s="1">
-        <v>-0.786</v>
+        <v>-0.757</v>
       </c>
       <c r="U29" s="1">
-        <v>-0.927</v>
+        <v>-0.875</v>
       </c>
     </row>
     <row r="30" spans="1:21">
       <c r="A30" s="2" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="B30" s="1">
         <v>0.07099999999999999</v>
       </c>
       <c r="C30" s="1">
-        <v>0.191</v>
+        <v>0.197</v>
       </c>
       <c r="D30" s="1">
-        <v>0.364</v>
+        <v>0.365</v>
       </c>
       <c r="E30" s="1">
-        <v>0.49</v>
+        <v>0.471</v>
       </c>
       <c r="F30" s="1">
-        <v>0.597</v>
+        <v>0.551</v>
       </c>
       <c r="G30" s="1">
-        <v>0.662</v>
+        <v>0.611</v>
       </c>
       <c r="H30" s="1">
-        <v>0.701</v>
+        <v>0.657</v>
       </c>
       <c r="I30" s="1">
-        <v>0.71</v>
+        <v>0.648</v>
       </c>
       <c r="J30" s="1">
-        <v>0.668</v>
+        <v>0.571</v>
       </c>
       <c r="K30" s="1">
-        <v>0.551</v>
+        <v>0.447</v>
       </c>
       <c r="L30" s="1">
-        <v>0.428</v>
+        <v>0.331</v>
       </c>
       <c r="M30" s="1">
-        <v>0.292</v>
+        <v>0.21</v>
       </c>
       <c r="N30" s="1">
-        <v>0.079</v>
+        <v>0.04</v>
       </c>
       <c r="O30" s="1">
-        <v>-0.178</v>
+        <v>-0.184</v>
       </c>
       <c r="P30" s="1">
-        <v>-0.401</v>
+        <v>-0.402</v>
       </c>
       <c r="Q30" s="1">
-        <v>-0.5610000000000001</v>
+        <v>-0.5659999999999999</v>
       </c>
       <c r="R30" s="1">
-        <v>-0.655</v>
+        <v>-0.668</v>
       </c>
       <c r="S30" s="1">
-        <v>-0.737</v>
+        <v>-0.767</v>
       </c>
       <c r="T30" s="1">
         <v>-0.888</v>
       </c>
       <c r="U30" s="1">
-        <v>-1.051</v>
+        <v>-0.994</v>
       </c>
     </row>
     <row r="31" spans="1:21">
       <c r="A31" s="2" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="B31" s="1">
         <v>0.378</v>
       </c>
       <c r="C31" s="1">
-        <v>0.505</v>
+        <v>0.515</v>
       </c>
       <c r="D31" s="1">
-        <v>0.672</v>
+        <v>0.707</v>
       </c>
       <c r="E31" s="1">
-        <v>0.786</v>
+        <v>0.857</v>
       </c>
       <c r="F31" s="1">
-        <v>0.903</v>
+        <v>0.958</v>
       </c>
       <c r="G31" s="1">
-        <v>1.018</v>
+        <v>1.042</v>
       </c>
       <c r="H31" s="1">
-        <v>1.067</v>
+        <v>1.091</v>
       </c>
       <c r="I31" s="1">
-        <v>0.992</v>
+        <v>1.021</v>
       </c>
       <c r="J31" s="1">
-        <v>0.836</v>
+        <v>0.86</v>
       </c>
       <c r="K31" s="1">
-        <v>0.639</v>
+        <v>0.661</v>
       </c>
       <c r="L31" s="1">
-        <v>0.379</v>
+        <v>0.413</v>
       </c>
       <c r="M31" s="1">
-        <v>0.039</v>
+        <v>0.08799999999999999</v>
       </c>
       <c r="N31" s="1">
-        <v>-0.324</v>
+        <v>-0.281</v>
       </c>
       <c r="O31" s="1">
-        <v>-0.631</v>
+        <v>-0.574</v>
       </c>
       <c r="P31" s="1">
-        <v>-0.829</v>
+        <v>-0.77</v>
       </c>
       <c r="Q31" s="1">
-        <v>-0.945</v>
+        <v>-0.891</v>
       </c>
       <c r="R31" s="1">
-        <v>-1.076</v>
+        <v>-1.008</v>
       </c>
       <c r="S31" s="1">
-        <v>-1.265</v>
+        <v>-1.201</v>
       </c>
       <c r="T31" s="1">
-        <v>-1.443</v>
+        <v>-1.377</v>
       </c>
       <c r="U31" s="1">
-        <v>-1.438</v>
+        <v>-1.373</v>
       </c>
     </row>
     <row r="32" spans="1:21">
       <c r="A32" s="2" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="B32" s="1">
         <v>0.501</v>
       </c>
       <c r="C32" s="1">
-        <v>0.596</v>
+        <v>0.597</v>
       </c>
       <c r="D32" s="1">
-        <v>0.749</v>
+        <v>0.754</v>
       </c>
       <c r="E32" s="1">
-        <v>0.884</v>
+        <v>0.865</v>
       </c>
       <c r="F32" s="1">
-        <v>0.963</v>
+        <v>0.913</v>
       </c>
       <c r="G32" s="1">
-        <v>0.9389999999999999</v>
+        <v>0.893</v>
       </c>
       <c r="H32" s="1">
-        <v>0.828</v>
+        <v>0.764</v>
       </c>
       <c r="I32" s="1">
-        <v>0.6860000000000001</v>
+        <v>0.599</v>
       </c>
       <c r="J32" s="1">
-        <v>0.521</v>
+        <v>0.431</v>
       </c>
       <c r="K32" s="1">
-        <v>0.336</v>
+        <v>0.236</v>
       </c>
       <c r="L32" s="1">
-        <v>0.108</v>
+        <v>-0.018</v>
       </c>
       <c r="M32" s="1">
-        <v>-0.208</v>
+        <v>-0.335</v>
       </c>
       <c r="N32" s="1">
-        <v>-0.503</v>
+        <v>-0.614</v>
       </c>
       <c r="O32" s="1">
-        <v>-0.674</v>
+        <v>-0.785</v>
       </c>
       <c r="P32" s="1">
-        <v>-0.775</v>
+        <v>-0.897</v>
       </c>
       <c r="Q32" s="1">
-        <v>-0.882</v>
+        <v>-0.999</v>
       </c>
       <c r="R32" s="1">
-        <v>-1.024</v>
+        <v>-1.169</v>
       </c>
       <c r="S32" s="1">
-        <v>-1.165</v>
+        <v>-1.346</v>
       </c>
       <c r="T32" s="1">
-        <v>-1.164</v>
+        <v>-1.339</v>
       </c>
       <c r="U32" s="1">
-        <v>-1.013</v>
+        <v>-1.153</v>
       </c>
     </row>
     <row r="33" spans="1:21">
       <c r="A33" s="2" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="B33" s="1">
         <v>0.785</v>
       </c>
       <c r="C33" s="1">
-        <v>0.907</v>
+        <v>0.889</v>
       </c>
       <c r="D33" s="1">
-        <v>1.079</v>
+        <v>1.036</v>
       </c>
       <c r="E33" s="1">
-        <v>1.18</v>
+        <v>1.12</v>
       </c>
       <c r="F33" s="1">
-        <v>1.186</v>
+        <v>1.128</v>
       </c>
       <c r="G33" s="1">
-        <v>1.075</v>
+        <v>1.023</v>
       </c>
       <c r="H33" s="1">
-        <v>0.883</v>
+        <v>0.836</v>
       </c>
       <c r="I33" s="1">
-        <v>0.656</v>
+        <v>0.619</v>
       </c>
       <c r="J33" s="1">
-        <v>0.402</v>
+        <v>0.373</v>
       </c>
       <c r="K33" s="1">
-        <v>0.053</v>
+        <v>0.047</v>
       </c>
       <c r="L33" s="1">
-        <v>-0.35</v>
+        <v>-0.326</v>
       </c>
       <c r="M33" s="1">
-        <v>-0.6929999999999999</v>
+        <v>-0.636</v>
       </c>
       <c r="N33" s="1">
-        <v>-0.891</v>
+        <v>-0.793</v>
       </c>
       <c r="O33" s="1">
-        <v>-0.983</v>
+        <v>-0.868</v>
       </c>
       <c r="P33" s="1">
-        <v>-1.088</v>
+        <v>-0.977</v>
       </c>
       <c r="Q33" s="1">
-        <v>-1.276</v>
+        <v>-1.16</v>
       </c>
       <c r="R33" s="1">
-        <v>-1.476</v>
+        <v>-1.35</v>
       </c>
       <c r="S33" s="1">
-        <v>-1.51</v>
+        <v>-1.377</v>
       </c>
       <c r="T33" s="1">
-        <v>-1.318</v>
+        <v>-1.215</v>
       </c>
       <c r="U33" s="1">
-        <v>-1.068</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="34" spans="1:21">
       <c r="A34" s="2" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="B34" s="1">
         <v>1.057</v>
       </c>
       <c r="C34" s="1">
-        <v>1.135</v>
+        <v>1.141</v>
       </c>
       <c r="D34" s="1">
-        <v>1.248</v>
+        <v>1.245</v>
       </c>
       <c r="E34" s="1">
-        <v>1.267</v>
+        <v>1.244</v>
       </c>
       <c r="F34" s="1">
-        <v>1.136</v>
+        <v>1.13</v>
       </c>
       <c r="G34" s="1">
-        <v>0.921</v>
+        <v>0.9379999999999999</v>
       </c>
       <c r="H34" s="1">
-        <v>0.6860000000000001</v>
+        <v>0.706</v>
       </c>
       <c r="I34" s="1">
-        <v>0.411</v>
+        <v>0.43</v>
       </c>
       <c r="J34" s="1">
-        <v>0.059</v>
+        <v>0.08</v>
       </c>
       <c r="K34" s="1">
-        <v>-0.364</v>
+        <v>-0.343</v>
       </c>
       <c r="L34" s="1">
-        <v>-0.733</v>
+        <v>-0.695</v>
       </c>
       <c r="M34" s="1">
-        <v>-0.9409999999999999</v>
+        <v>-0.889</v>
       </c>
       <c r="N34" s="1">
-        <v>-1.034</v>
+        <v>-0.997</v>
       </c>
       <c r="O34" s="1">
-        <v>-1.138</v>
+        <v>-1.124</v>
       </c>
       <c r="P34" s="1">
-        <v>-1.325</v>
+        <v>-1.314</v>
       </c>
       <c r="Q34" s="1">
-        <v>-1.517</v>
+        <v>-1.492</v>
       </c>
       <c r="R34" s="1">
-        <v>-1.52</v>
+        <v>-1.486</v>
       </c>
       <c r="S34" s="1">
-        <v>-1.303</v>
+        <v>-1.278</v>
       </c>
       <c r="T34" s="1">
-        <v>-1.025</v>
+        <v>-1.014</v>
       </c>
       <c r="U34" s="1">
-        <v>-0.829</v>
+        <v>-0.803</v>
       </c>
     </row>
     <row r="35" spans="1:21">
       <c r="A35" s="2" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="B35" s="1">
         <v>1.079</v>
       </c>
       <c r="C35" s="1">
-        <v>1.177</v>
+        <v>1.158</v>
       </c>
       <c r="D35" s="1">
-        <v>1.278</v>
+        <v>1.232</v>
       </c>
       <c r="E35" s="1">
-        <v>1.22</v>
+        <v>1.156</v>
       </c>
       <c r="F35" s="1">
-        <v>1.022</v>
+        <v>0.972</v>
       </c>
       <c r="G35" s="1">
-        <v>0.769</v>
+        <v>0.725</v>
       </c>
       <c r="H35" s="1">
-        <v>0.485</v>
+        <v>0.466</v>
       </c>
       <c r="I35" s="1">
-        <v>0.128</v>
+        <v>0.16</v>
       </c>
       <c r="J35" s="1">
-        <v>-0.257</v>
+        <v>-0.196</v>
       </c>
       <c r="K35" s="1">
-        <v>-0.569</v>
+        <v>-0.518</v>
       </c>
       <c r="L35" s="1">
-        <v>-0.751</v>
+        <v>-0.726</v>
       </c>
       <c r="M35" s="1">
-        <v>-0.85</v>
+        <v>-0.839</v>
       </c>
       <c r="N35" s="1">
-        <v>-0.9419999999999999</v>
+        <v>-0.9370000000000001</v>
       </c>
       <c r="O35" s="1">
-        <v>-1.095</v>
+        <v>-1.102</v>
       </c>
       <c r="P35" s="1">
-        <v>-1.253</v>
+        <v>-1.269</v>
       </c>
       <c r="Q35" s="1">
-        <v>-1.255</v>
+        <v>-1.267</v>
       </c>
       <c r="R35" s="1">
-        <v>-1.077</v>
+        <v>-1.092</v>
       </c>
       <c r="S35" s="1">
-        <v>-0.875</v>
+        <v>-0.871</v>
       </c>
       <c r="T35" s="1">
-        <v>-0.727</v>
+        <v>-0.715</v>
       </c>
       <c r="U35" s="1">
-        <v>-0.648</v>
+        <v>-0.626</v>
       </c>
     </row>
     <row r="36" spans="1:21">
       <c r="A36" s="2" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="B36" s="1">
         <v>1.339</v>
       </c>
       <c r="C36" s="1">
-        <v>1.314</v>
+        <v>1.308</v>
       </c>
       <c r="D36" s="1">
-        <v>1.185</v>
+        <v>1.168</v>
       </c>
       <c r="E36" s="1">
-        <v>0.961</v>
+        <v>0.9370000000000001</v>
       </c>
       <c r="F36" s="1">
-        <v>0.708</v>
+        <v>0.696</v>
       </c>
       <c r="G36" s="1">
-        <v>0.426</v>
+        <v>0.412</v>
       </c>
       <c r="H36" s="1">
-        <v>0.083</v>
+        <v>0.043</v>
       </c>
       <c r="I36" s="1">
-        <v>-0.308</v>
+        <v>-0.337</v>
       </c>
       <c r="J36" s="1">
-        <v>-0.652</v>
+        <v>-0.655</v>
       </c>
       <c r="K36" s="1">
-        <v>-0.868</v>
+        <v>-0.846</v>
       </c>
       <c r="L36" s="1">
-        <v>-0.968</v>
+        <v>-0.9370000000000001</v>
       </c>
       <c r="M36" s="1">
-        <v>-1.081</v>
+        <v>-1.043</v>
       </c>
       <c r="N36" s="1">
-        <v>-1.253</v>
+        <v>-1.21</v>
       </c>
       <c r="O36" s="1">
-        <v>-1.42</v>
+        <v>-1.353</v>
       </c>
       <c r="P36" s="1">
-        <v>-1.427</v>
+        <v>-1.346</v>
       </c>
       <c r="Q36" s="1">
-        <v>-1.232</v>
+        <v>-1.165</v>
       </c>
       <c r="R36" s="1">
-        <v>-0.979</v>
+        <v>-0.925</v>
       </c>
       <c r="S36" s="1">
-        <v>-0.784</v>
+        <v>-0.739</v>
       </c>
       <c r="T36" s="1">
-        <v>-0.668</v>
+        <v>-0.621</v>
       </c>
       <c r="U36" s="1">
-        <v>-0.628</v>
+        <v>-0.5639999999999999</v>
       </c>
     </row>
     <row r="37" spans="1:21">
       <c r="A37" s="2" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="B37" s="1">
         <v>1.432</v>
       </c>
       <c r="C37" s="1">
-        <v>1.317</v>
+        <v>1.323</v>
       </c>
       <c r="D37" s="1">
-        <v>1.05</v>
+        <v>1.059</v>
       </c>
       <c r="E37" s="1">
-        <v>0.736</v>
+        <v>0.773</v>
       </c>
       <c r="F37" s="1">
-        <v>0.372</v>
+        <v>0.418</v>
       </c>
       <c r="G37" s="1">
-        <v>-0.05</v>
+        <v>-0.02</v>
       </c>
       <c r="H37" s="1">
-        <v>-0.483</v>
+        <v>-0.477</v>
       </c>
       <c r="I37" s="1">
-        <v>-0.845</v>
+        <v>-0.848</v>
       </c>
       <c r="J37" s="1">
-        <v>-1.054</v>
+        <v>-1.063</v>
       </c>
       <c r="K37" s="1">
-        <v>-1.16</v>
+        <v>-1.174</v>
       </c>
       <c r="L37" s="1">
-        <v>-1.296</v>
+        <v>-1.3</v>
       </c>
       <c r="M37" s="1">
-        <v>-1.508</v>
+        <v>-1.514</v>
       </c>
       <c r="N37" s="1">
-        <v>-1.708</v>
+        <v>-1.736</v>
       </c>
       <c r="O37" s="1">
-        <v>-1.693</v>
+        <v>-1.736</v>
       </c>
       <c r="P37" s="1">
-        <v>-1.469</v>
+        <v>-1.502</v>
       </c>
       <c r="Q37" s="1">
-        <v>-1.199</v>
+        <v>-1.214</v>
       </c>
       <c r="R37" s="1">
-        <v>-0.992</v>
+        <v>-1.001</v>
       </c>
       <c r="S37" s="1">
-        <v>-0.86</v>
+        <v>-0.836</v>
       </c>
       <c r="T37" s="1">
-        <v>-0.764</v>
+        <v>-0.724</v>
       </c>
       <c r="U37" s="1">
-        <v>-0.704</v>
+        <v>-0.6860000000000001</v>
       </c>
     </row>
     <row r="38" spans="1:21">
       <c r="A38" s="2" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="B38" s="1">
         <v>1.107</v>
       </c>
       <c r="C38" s="1">
-        <v>1.004</v>
+        <v>0.997</v>
       </c>
       <c r="D38" s="1">
-        <v>0.747</v>
+        <v>0.738</v>
       </c>
       <c r="E38" s="1">
-        <v>0.397</v>
+        <v>0.388</v>
       </c>
       <c r="F38" s="1">
-        <v>-0.003</v>
+        <v>-0.006</v>
       </c>
       <c r="G38" s="1">
-        <v>-0.409</v>
+        <v>-0.418</v>
       </c>
       <c r="H38" s="1">
-        <v>-0.764</v>
+        <v>-0.776</v>
       </c>
       <c r="I38" s="1">
-        <v>-0.972</v>
+        <v>-0.979</v>
       </c>
       <c r="J38" s="1">
-        <v>-1.079</v>
+        <v>-1.077</v>
       </c>
       <c r="K38" s="1">
-        <v>-1.223</v>
+        <v>-1.191</v>
       </c>
       <c r="L38" s="1">
-        <v>-1.429</v>
+        <v>-1.383</v>
       </c>
       <c r="M38" s="1">
-        <v>-1.625</v>
+        <v>-1.569</v>
       </c>
       <c r="N38" s="1">
-        <v>-1.617</v>
+        <v>-1.56</v>
       </c>
       <c r="O38" s="1">
-        <v>-1.385</v>
+        <v>-1.33</v>
       </c>
       <c r="P38" s="1">
-        <v>-1.12</v>
+        <v>-1.054</v>
       </c>
       <c r="Q38" s="1">
-        <v>-0.916</v>
+        <v>-0.855</v>
       </c>
       <c r="R38" s="1">
-        <v>-0.762</v>
+        <v>-0.74</v>
       </c>
       <c r="S38" s="1">
-        <v>-0.651</v>
+        <v>-0.68</v>
       </c>
       <c r="T38" s="1">
-        <v>-0.575</v>
+        <v>-0.639</v>
       </c>
       <c r="U38" s="1">
-        <v>-0.54</v>
+        <v>-0.607</v>
       </c>
     </row>
     <row r="39" spans="1:21">
       <c r="A39" s="2" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="B39" s="1">
         <v>0.907</v>
       </c>
       <c r="C39" s="1">
-        <v>0.777</v>
+        <v>0.771</v>
       </c>
       <c r="D39" s="1">
-        <v>0.476</v>
+        <v>0.457</v>
       </c>
       <c r="E39" s="1">
-        <v>0.06</v>
+        <v>0.045</v>
       </c>
       <c r="F39" s="1">
-        <v>-0.418</v>
+        <v>-0.434</v>
       </c>
       <c r="G39" s="1">
-        <v>-0.8159999999999999</v>
+        <v>-0.837</v>
       </c>
       <c r="H39" s="1">
-        <v>-1.037</v>
+        <v>-1.069</v>
       </c>
       <c r="I39" s="1">
-        <v>-1.142</v>
+        <v>-1.185</v>
       </c>
       <c r="J39" s="1">
-        <v>-1.241</v>
+        <v>-1.287</v>
       </c>
       <c r="K39" s="1">
-        <v>-1.428</v>
+        <v>-1.466</v>
       </c>
       <c r="L39" s="1">
-        <v>-1.626</v>
+        <v>-1.657</v>
       </c>
       <c r="M39" s="1">
-        <v>-1.6</v>
+        <v>-1.643</v>
       </c>
       <c r="N39" s="1">
-        <v>-1.353</v>
+        <v>-1.395</v>
       </c>
       <c r="O39" s="1">
-        <v>-1.096</v>
+        <v>-1.125</v>
       </c>
       <c r="P39" s="1">
-        <v>-0.908</v>
+        <v>-0.917</v>
       </c>
       <c r="Q39" s="1">
-        <v>-0.769</v>
+        <v>-0.794</v>
       </c>
       <c r="R39" s="1">
-        <v>-0.705</v>
+        <v>-0.734</v>
       </c>
       <c r="S39" s="1">
-        <v>-0.695</v>
+        <v>-0.724</v>
       </c>
       <c r="T39" s="1">
-        <v>-0.71</v>
+        <v>-0.752</v>
       </c>
       <c r="U39" s="1">
-        <v>-0.759</v>
+        <v>-0.8120000000000001</v>
       </c>
     </row>
     <row r="40" spans="1:21">
       <c r="A40" s="2" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="B40" s="1">
         <v>0.713</v>
       </c>
       <c r="C40" s="1">
-        <v>0.519</v>
+        <v>0.527</v>
       </c>
       <c r="D40" s="1">
-        <v>0.109</v>
+        <v>0.128</v>
       </c>
       <c r="E40" s="1">
-        <v>-0.374</v>
+        <v>-0.335</v>
       </c>
       <c r="F40" s="1">
-        <v>-0.781</v>
+        <v>-0.729</v>
       </c>
       <c r="G40" s="1">
-        <v>-1.02</v>
+        <v>-0.962</v>
       </c>
       <c r="H40" s="1">
-        <v>-1.144</v>
+        <v>-1.081</v>
       </c>
       <c r="I40" s="1">
-        <v>-1.252</v>
+        <v>-1.173</v>
       </c>
       <c r="J40" s="1">
-        <v>-1.404</v>
+        <v>-1.348</v>
       </c>
       <c r="K40" s="1">
-        <v>-1.58</v>
+        <v>-1.547</v>
       </c>
       <c r="L40" s="1">
-        <v>-1.601</v>
+        <v>-1.541</v>
       </c>
       <c r="M40" s="1">
-        <v>-1.385</v>
+        <v>-1.319</v>
       </c>
       <c r="N40" s="1">
-        <v>-1.09</v>
+        <v>-1.053</v>
       </c>
       <c r="O40" s="1">
-        <v>-0.875</v>
+        <v>-0.868</v>
       </c>
       <c r="P40" s="1">
-        <v>-0.758</v>
+        <v>-0.794</v>
       </c>
       <c r="Q40" s="1">
-        <v>-0.725</v>
+        <v>-0.798</v>
       </c>
       <c r="R40" s="1">
-        <v>-0.731</v>
+        <v>-0.825</v>
       </c>
       <c r="S40" s="1">
-        <v>-0.755</v>
+        <v>-0.871</v>
       </c>
       <c r="T40" s="1">
-        <v>-0.795</v>
+        <v>-0.9429999999999999</v>
       </c>
       <c r="U40" s="1">
-        <v>-0.862</v>
+        <v>-1.043</v>
       </c>
     </row>
     <row r="41" spans="1:21">
       <c r="A41" s="2" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="B41" s="1">
         <v>0.257</v>
       </c>
       <c r="C41" s="1">
-        <v>0.068</v>
+        <v>0.054</v>
       </c>
       <c r="D41" s="1">
-        <v>-0.319</v>
+        <v>-0.326</v>
       </c>
       <c r="E41" s="1">
-        <v>-0.6899999999999999</v>
+        <v>-0.656</v>
       </c>
       <c r="F41" s="1">
-        <v>-0.931</v>
+        <v>-0.85</v>
       </c>
       <c r="G41" s="1">
-        <v>-1.059</v>
+        <v>-0.97</v>
       </c>
       <c r="H41" s="1">
-        <v>-1.181</v>
+        <v>-1.09</v>
       </c>
       <c r="I41" s="1">
-        <v>-1.358</v>
+        <v>-1.263</v>
       </c>
       <c r="J41" s="1">
-        <v>-1.503</v>
+        <v>-1.425</v>
       </c>
       <c r="K41" s="1">
-        <v>-1.481</v>
+        <v>-1.408</v>
       </c>
       <c r="L41" s="1">
-        <v>-1.286</v>
+        <v>-1.197</v>
       </c>
       <c r="M41" s="1">
-        <v>-1.05</v>
+        <v>-0.95</v>
       </c>
       <c r="N41" s="1">
-        <v>-0.873</v>
+        <v>-0.767</v>
       </c>
       <c r="O41" s="1">
-        <v>-0.777</v>
+        <v>-0.678</v>
       </c>
       <c r="P41" s="1">
-        <v>-0.739</v>
+        <v>-0.659</v>
       </c>
       <c r="Q41" s="1">
-        <v>-0.723</v>
+        <v>-0.67</v>
       </c>
       <c r="R41" s="1">
-        <v>-0.727</v>
+        <v>-0.7</v>
       </c>
       <c r="S41" s="1">
-        <v>-0.769</v>
+        <v>-0.755</v>
       </c>
       <c r="T41" s="1">
-        <v>-0.853</v>
+        <v>-0.857</v>
       </c>
       <c r="U41" s="1">
-        <v>-0.971</v>
+        <v>-0.989</v>
       </c>
     </row>
     <row r="42" spans="1:21">
       <c r="A42" s="2" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="B42" s="1">
         <v>-0.42</v>
       </c>
       <c r="C42" s="1">
-        <v>-0.621</v>
+        <v>-0.624</v>
       </c>
       <c r="D42" s="1">
         <v>-0.926</v>
       </c>
       <c r="E42" s="1">
-        <v>-1.122</v>
+        <v>-1.118</v>
       </c>
       <c r="F42" s="1">
-        <v>-1.25</v>
+        <v>-1.22</v>
       </c>
       <c r="G42" s="1">
-        <v>-1.38</v>
+        <v>-1.331</v>
       </c>
       <c r="H42" s="1">
-        <v>-1.576</v>
+        <v>-1.519</v>
       </c>
       <c r="I42" s="1">
-        <v>-1.711</v>
+        <v>-1.685</v>
       </c>
       <c r="J42" s="1">
-        <v>-1.618</v>
+        <v>-1.632</v>
       </c>
       <c r="K42" s="1">
-        <v>-1.354</v>
+        <v>-1.391</v>
       </c>
       <c r="L42" s="1">
-        <v>-1.103</v>
+        <v>-1.148</v>
       </c>
       <c r="M42" s="1">
-        <v>-0.913</v>
+        <v>-0.975</v>
       </c>
       <c r="N42" s="1">
-        <v>-0.744</v>
+        <v>-0.84</v>
       </c>
       <c r="O42" s="1">
-        <v>-0.62</v>
+        <v>-0.735</v>
       </c>
       <c r="P42" s="1">
-        <v>-0.5580000000000001</v>
+        <v>-0.68</v>
       </c>
       <c r="Q42" s="1">
-        <v>-0.5580000000000001</v>
+        <v>-0.665</v>
       </c>
       <c r="R42" s="1">
-        <v>-0.604</v>
+        <v>-0.704</v>
       </c>
       <c r="S42" s="1">
-        <v>-0.6840000000000001</v>
+        <v>-0.8080000000000001</v>
       </c>
       <c r="T42" s="1">
-        <v>-0.779</v>
+        <v>-0.9340000000000001</v>
       </c>
       <c r="U42" s="1">
-        <v>-0.8179999999999999</v>
+        <v>-0.994</v>
       </c>
     </row>
     <row r="43" spans="1:21">
       <c r="A43" s="2" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="B43" s="1">
         <v>-0.289</v>
       </c>
       <c r="C43" s="1">
-        <v>-0.432</v>
+        <v>-0.431</v>
       </c>
       <c r="D43" s="1">
-        <v>-0.629</v>
+        <v>-0.617</v>
       </c>
       <c r="E43" s="1">
-        <v>-0.762</v>
+        <v>-0.737</v>
       </c>
       <c r="F43" s="1">
-        <v>-0.872</v>
+        <v>-0.878</v>
       </c>
       <c r="G43" s="1">
-        <v>-1.01</v>
+        <v>-1.013</v>
       </c>
       <c r="H43" s="1">
-        <v>-1.108</v>
+        <v>-1.088</v>
       </c>
       <c r="I43" s="1">
-        <v>-1.052</v>
+        <v>-1.036</v>
       </c>
       <c r="J43" s="1">
-        <v>-0.866</v>
+        <v>-0.871</v>
       </c>
       <c r="K43" s="1">
-        <v>-0.706</v>
+        <v>-0.674</v>
       </c>
       <c r="L43" s="1">
-        <v>-0.609</v>
+        <v>-0.54</v>
       </c>
       <c r="M43" s="1">
-        <v>-0.5669999999999999</v>
+        <v>-0.5</v>
       </c>
       <c r="N43" s="1">
-        <v>-0.5669999999999999</v>
+        <v>-0.507</v>
       </c>
       <c r="O43" s="1">
-        <v>-0.5629999999999999</v>
+        <v>-0.542</v>
       </c>
       <c r="P43" s="1">
-        <v>-0.573</v>
+        <v>-0.5659999999999999</v>
       </c>
       <c r="Q43" s="1">
-        <v>-0.622</v>
+        <v>-0.612</v>
       </c>
       <c r="R43" s="1">
-        <v>-0.716</v>
+        <v>-0.6860000000000001</v>
       </c>
       <c r="S43" s="1">
-        <v>-0.829</v>
+        <v>-0.768</v>
       </c>
       <c r="T43" s="1">
-        <v>-0.901</v>
+        <v>-0.819</v>
       </c>
       <c r="U43" s="1">
-        <v>-0.848</v>
+        <v>-0.774</v>
       </c>
     </row>
     <row r="44" spans="1:21">
       <c r="A44" s="2" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="B44" s="1">
         <v>-0.374</v>
       </c>
       <c r="C44" s="1">
-        <v>-0.424</v>
+        <v>-0.439</v>
       </c>
       <c r="D44" s="1">
-        <v>-0.499</v>
+        <v>-0.542</v>
       </c>
       <c r="E44" s="1">
-        <v>-0.5659999999999999</v>
+        <v>-0.659</v>
       </c>
       <c r="F44" s="1">
-        <v>-0.678</v>
+        <v>-0.777</v>
       </c>
       <c r="G44" s="1">
-        <v>-0.781</v>
+        <v>-0.848</v>
       </c>
       <c r="H44" s="1">
-        <v>-0.759</v>
+        <v>-0.793</v>
       </c>
       <c r="I44" s="1">
-        <v>-0.641</v>
+        <v>-0.647</v>
       </c>
       <c r="J44" s="1">
-        <v>-0.54</v>
+        <v>-0.517</v>
       </c>
       <c r="K44" s="1">
-        <v>-0.483</v>
+        <v>-0.463</v>
       </c>
       <c r="L44" s="1">
-        <v>-0.441</v>
+        <v>-0.476</v>
       </c>
       <c r="M44" s="1">
-        <v>-0.436</v>
+        <v>-0.51</v>
       </c>
       <c r="N44" s="1">
-        <v>-0.456</v>
+        <v>-0.547</v>
       </c>
       <c r="O44" s="1">
-        <v>-0.476</v>
+        <v>-0.584</v>
       </c>
       <c r="P44" s="1">
-        <v>-0.497</v>
+        <v>-0.66</v>
       </c>
       <c r="Q44" s="1">
-        <v>-0.575</v>
+        <v>-0.755</v>
       </c>
       <c r="R44" s="1">
-        <v>-0.668</v>
+        <v>-0.847</v>
       </c>
       <c r="S44" s="1">
-        <v>-0.694</v>
+        <v>-0.902</v>
       </c>
       <c r="T44" s="1">
-        <v>-0.64</v>
+        <v>-0.834</v>
       </c>
       <c r="U44" s="1">
-        <v>-0.549</v>
+        <v>-0.6929999999999999</v>
       </c>
     </row>
     <row r="45" spans="1:21">
       <c r="A45" s="2" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="B45" s="1">
         <v>-0.515</v>
       </c>
       <c r="C45" s="1">
-        <v>-0.5639999999999999</v>
+        <v>-0.5600000000000001</v>
       </c>
       <c r="D45" s="1">
+        <v>-0.66</v>
+      </c>
+      <c r="E45" s="1">
+        <v>-0.774</v>
+      </c>
+      <c r="F45" s="1">
+        <v>-0.868</v>
+      </c>
+      <c r="G45" s="1">
+        <v>-0.854</v>
+      </c>
+      <c r="H45" s="1">
+        <v>-0.72</v>
+      </c>
+      <c r="I45" s="1">
+        <v>-0.5649999999999999</v>
+      </c>
+      <c r="J45" s="1">
+        <v>-0.498</v>
+      </c>
+      <c r="K45" s="1">
+        <v>-0.54</v>
+      </c>
+      <c r="L45" s="1">
+        <v>-0.603</v>
+      </c>
+      <c r="M45" s="1">
+        <v>-0.649</v>
+      </c>
+      <c r="N45" s="1">
         <v>-0.704</v>
       </c>
-      <c r="E45" s="1">
-        <v>-0.869</v>
-      </c>
-      <c r="F45" s="1">
-        <v>-0.983</v>
-      </c>
-      <c r="G45" s="1">
-        <v>-0.951</v>
-      </c>
-      <c r="H45" s="1">
-        <v>-0.8070000000000001</v>
-      </c>
-      <c r="I45" s="1">
-        <v>-0.678</v>
-      </c>
-      <c r="J45" s="1">
-        <v>-0.619</v>
-      </c>
-      <c r="K45" s="1">
-        <v>-0.613</v>
-      </c>
-      <c r="L45" s="1">
-        <v>-0.643</v>
-      </c>
-      <c r="M45" s="1">
-        <v>-0.662</v>
-      </c>
-      <c r="N45" s="1">
-        <v>-0.666</v>
-      </c>
       <c r="O45" s="1">
-        <v>-0.712</v>
+        <v>-0.761</v>
       </c>
       <c r="P45" s="1">
-        <v>-0.786</v>
+        <v>-0.839</v>
       </c>
       <c r="Q45" s="1">
-        <v>-0.875</v>
+        <v>-0.96</v>
       </c>
       <c r="R45" s="1">
-        <v>-0.9370000000000001</v>
+        <v>-1.036</v>
       </c>
       <c r="S45" s="1">
-        <v>-0.897</v>
+        <v>-0.977</v>
       </c>
       <c r="T45" s="1">
-        <v>-0.791</v>
+        <v>-0.848</v>
       </c>
       <c r="U45" s="1">
-        <v>-0.68</v>
+        <v>-0.72</v>
       </c>
     </row>
     <row r="46" spans="1:21">
       <c r="A46" s="2" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="B46" s="1">
         <v>-0.82</v>
       </c>
       <c r="C46" s="1">
-        <v>-0.894</v>
+        <v>-0.879</v>
       </c>
       <c r="D46" s="1">
-        <v>-1.055</v>
+        <v>-1.02</v>
       </c>
       <c r="E46" s="1">
-        <v>-1.165</v>
+        <v>-1.129</v>
       </c>
       <c r="F46" s="1">
-        <v>-1.125</v>
+        <v>-1.094</v>
       </c>
       <c r="G46" s="1">
-        <v>-0.95</v>
+        <v>-0.93</v>
       </c>
       <c r="H46" s="1">
-        <v>-0.764</v>
+        <v>-0.746</v>
       </c>
       <c r="I46" s="1">
-        <v>-0.645</v>
+        <v>-0.638</v>
       </c>
       <c r="J46" s="1">
-        <v>-0.58</v>
+        <v>-0.605</v>
       </c>
       <c r="K46" s="1">
-        <v>-0.546</v>
+        <v>-0.602</v>
       </c>
       <c r="L46" s="1">
-        <v>-0.554</v>
+        <v>-0.618</v>
       </c>
       <c r="M46" s="1">
-        <v>-0.587</v>
+        <v>-0.649</v>
       </c>
       <c r="N46" s="1">
-        <v>-0.629</v>
+        <v>-0.707</v>
       </c>
       <c r="O46" s="1">
-        <v>-0.721</v>
+        <v>-0.823</v>
       </c>
       <c r="P46" s="1">
-        <v>-0.826</v>
+        <v>-0.959</v>
       </c>
       <c r="Q46" s="1">
-        <v>-0.869</v>
+        <v>-1.043</v>
       </c>
       <c r="R46" s="1">
-        <v>-0.796</v>
+        <v>-0.992</v>
       </c>
       <c r="S46" s="1">
-        <v>-0.651</v>
+        <v>-0.854</v>
       </c>
       <c r="T46" s="1">
-        <v>-0.533</v>
+        <v>-0.726</v>
       </c>
       <c r="U46" s="1">
-        <v>-0.448</v>
+        <v>-0.618</v>
       </c>
     </row>
     <row r="47" spans="1:21">
       <c r="A47" s="2" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="B47" s="1">
         <v>-1.017</v>
       </c>
       <c r="C47" s="1">
-        <v>-1.089</v>
+        <v>-1.09</v>
       </c>
       <c r="D47" s="1">
-        <v>-1.165</v>
+        <v>-1.158</v>
       </c>
       <c r="E47" s="1">
-        <v>-1.081</v>
+        <v>-1.07</v>
       </c>
       <c r="F47" s="1">
-        <v>-0.871</v>
+        <v>-0.867</v>
       </c>
       <c r="G47" s="1">
-        <v>-0.6830000000000001</v>
+        <v>-0.699</v>
       </c>
       <c r="H47" s="1">
-        <v>-0.5620000000000001</v>
+        <v>-0.6</v>
       </c>
       <c r="I47" s="1">
-        <v>-0.49</v>
+        <v>-0.543</v>
       </c>
       <c r="J47" s="1">
-        <v>-0.463</v>
+        <v>-0.523</v>
       </c>
       <c r="K47" s="1">
-        <v>-0.454</v>
+        <v>-0.528</v>
       </c>
       <c r="L47" s="1">
-        <v>-0.468</v>
+        <v>-0.539</v>
       </c>
       <c r="M47" s="1">
-        <v>-0.511</v>
+        <v>-0.5580000000000001</v>
       </c>
       <c r="N47" s="1">
-        <v>-0.5679999999999999</v>
+        <v>-0.627</v>
       </c>
       <c r="O47" s="1">
-        <v>-0.62</v>
+        <v>-0.71</v>
       </c>
       <c r="P47" s="1">
-        <v>-0.635</v>
+        <v>-0.727</v>
       </c>
       <c r="Q47" s="1">
-        <v>-0.5590000000000001</v>
+        <v>-0.671</v>
       </c>
       <c r="R47" s="1">
-        <v>-0.457</v>
+        <v>-0.5570000000000001</v>
       </c>
       <c r="S47" s="1">
-        <v>-0.389</v>
+        <v>-0.444</v>
       </c>
       <c r="T47" s="1">
-        <v>-0.318</v>
+        <v>-0.366</v>
       </c>
       <c r="U47" s="1">
-        <v>-0.208</v>
+        <v>-0.284</v>
       </c>
     </row>
     <row r="48" spans="1:21">
       <c r="A48" s="2" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="B48" s="1">
         <v>-0.8</v>
       </c>
       <c r="C48" s="1">
-        <v>-0.837</v>
+        <v>-0.847</v>
       </c>
       <c r="D48" s="1">
-        <v>-0.8070000000000001</v>
+        <v>-0.833</v>
       </c>
       <c r="E48" s="1">
-        <v>-0.662</v>
+        <v>-0.6860000000000001</v>
       </c>
       <c r="F48" s="1">
-        <v>-0.511</v>
+        <v>-0.517</v>
       </c>
       <c r="G48" s="1">
-        <v>-0.442</v>
+        <v>-0.431</v>
       </c>
       <c r="H48" s="1">
-        <v>-0.464</v>
+        <v>-0.437</v>
       </c>
       <c r="I48" s="1">
-        <v>-0.528</v>
+        <v>-0.491</v>
       </c>
       <c r="J48" s="1">
-        <v>-0.582</v>
+        <v>-0.5610000000000001</v>
       </c>
       <c r="K48" s="1">
-        <v>-0.62</v>
+        <v>-0.623</v>
       </c>
       <c r="L48" s="1">
-        <v>-0.678</v>
+        <v>-0.6830000000000001</v>
       </c>
       <c r="M48" s="1">
-        <v>-0.755</v>
+        <v>-0.762</v>
       </c>
       <c r="N48" s="1">
-        <v>-0.849</v>
+        <v>-0.863</v>
       </c>
       <c r="O48" s="1">
-        <v>-0.891</v>
+        <v>-0.928</v>
       </c>
       <c r="P48" s="1">
-        <v>-0.835</v>
+        <v>-0.873</v>
       </c>
       <c r="Q48" s="1">
-        <v>-0.715</v>
+        <v>-0.744</v>
       </c>
       <c r="R48" s="1">
-        <v>-0.6</v>
+        <v>-0.633</v>
       </c>
       <c r="S48" s="1">
-        <v>-0.512</v>
+        <v>-0.542</v>
       </c>
       <c r="T48" s="1">
-        <v>-0.402</v>
+        <v>-0.413</v>
       </c>
       <c r="U48" s="1">
-        <v>-0.248</v>
+        <v>-0.253</v>
       </c>
     </row>
     <row r="49" spans="1:21">
       <c r="A49" s="2" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="B49" s="1">
         <v>-1.138</v>
       </c>
       <c r="C49" s="1">
-        <v>-1.082</v>
+        <v>-1.087</v>
       </c>
       <c r="D49" s="1">
-        <v>-0.924</v>
+        <v>-0.923</v>
       </c>
       <c r="E49" s="1">
-        <v>-0.756</v>
+        <v>-0.76</v>
       </c>
       <c r="F49" s="1">
-        <v>-0.659</v>
+        <v>-0.674</v>
       </c>
       <c r="G49" s="1">
-        <v>-0.639</v>
+        <v>-0.637</v>
       </c>
       <c r="H49" s="1">
         <v>-0.629</v>
       </c>
       <c r="I49" s="1">
+        <v>-0.638</v>
+      </c>
+      <c r="J49" s="1">
+        <v>-0.655</v>
+      </c>
+      <c r="K49" s="1">
+        <v>-0.722</v>
+      </c>
+      <c r="L49" s="1">
+        <v>-0.825</v>
+      </c>
+      <c r="M49" s="1">
+        <v>-0.905</v>
+      </c>
+      <c r="N49" s="1">
+        <v>-0.931</v>
+      </c>
+      <c r="O49" s="1">
+        <v>-0.85</v>
+      </c>
+      <c r="P49" s="1">
+        <v>-0.724</v>
+      </c>
+      <c r="Q49" s="1">
         <v>-0.607</v>
       </c>
-      <c r="J49" s="1">
-        <v>-0.618</v>
-      </c>
-      <c r="K49" s="1">
-        <v>-0.6840000000000001</v>
-      </c>
-      <c r="L49" s="1">
-        <v>-0.784</v>
-      </c>
-      <c r="M49" s="1">
-        <v>-0.927</v>
-      </c>
-      <c r="N49" s="1">
-        <v>-1.017</v>
-      </c>
-      <c r="O49" s="1">
-        <v>-0.963</v>
-      </c>
-      <c r="P49" s="1">
-        <v>-0.846</v>
-      </c>
-      <c r="Q49" s="1">
-        <v>-0.738</v>
-      </c>
       <c r="R49" s="1">
-        <v>-0.637</v>
+        <v>-0.486</v>
       </c>
       <c r="S49" s="1">
-        <v>-0.477</v>
+        <v>-0.347</v>
       </c>
       <c r="T49" s="1">
-        <v>-0.274</v>
+        <v>-0.175</v>
       </c>
       <c r="U49" s="1">
-        <v>-0.106</v>
+        <v>-0.033</v>
       </c>
     </row>
     <row r="50" spans="1:21">
       <c r="A50" s="2" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="B50" s="1">
         <v>-1.279</v>
       </c>
       <c r="C50" s="1">
-        <v>-1.112</v>
+        <v>-1.121</v>
       </c>
       <c r="D50" s="1">
-        <v>-0.869</v>
+        <v>-0.892</v>
       </c>
       <c r="E50" s="1">
-        <v>-0.71</v>
+        <v>-0.74</v>
       </c>
       <c r="F50" s="1">
-        <v>-0.622</v>
+        <v>-0.679</v>
       </c>
       <c r="G50" s="1">
-        <v>-0.601</v>
+        <v>-0.669</v>
       </c>
       <c r="H50" s="1">
-        <v>-0.628</v>
+        <v>-0.68</v>
       </c>
       <c r="I50" s="1">
-        <v>-0.677</v>
+        <v>-0.736</v>
       </c>
       <c r="J50" s="1">
-        <v>-0.725</v>
+        <v>-0.8129999999999999</v>
       </c>
       <c r="K50" s="1">
-        <v>-0.8169999999999999</v>
+        <v>-0.896</v>
       </c>
       <c r="L50" s="1">
-        <v>-0.928</v>
+        <v>-1.002</v>
       </c>
       <c r="M50" s="1">
-        <v>-0.96</v>
+        <v>-1.054</v>
       </c>
       <c r="N50" s="1">
-        <v>-0.886</v>
+        <v>-0.987</v>
       </c>
       <c r="O50" s="1">
-        <v>-0.738</v>
+        <v>-0.853</v>
       </c>
       <c r="P50" s="1">
-        <v>-0.606</v>
+        <v>-0.722</v>
       </c>
       <c r="Q50" s="1">
-        <v>-0.505</v>
+        <v>-0.6</v>
       </c>
       <c r="R50" s="1">
-        <v>-0.376</v>
+        <v>-0.457</v>
       </c>
       <c r="S50" s="1">
-        <v>-0.197</v>
+        <v>-0.288</v>
       </c>
       <c r="T50" s="1">
-        <v>-0.039</v>
+        <v>-0.134</v>
       </c>
       <c r="U50" s="1">
-        <v>0.048</v>
+        <v>-0.034</v>
       </c>
     </row>
     <row r="51" spans="1:21">
       <c r="A51" s="2" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="B51" s="1">
         <v>-0.914</v>
       </c>
       <c r="C51" s="1">
-        <v>-0.768</v>
+        <v>-0.79</v>
       </c>
       <c r="D51" s="1">
-        <v>-0.612</v>
+        <v>-0.639</v>
       </c>
       <c r="E51" s="1">
-        <v>-0.543</v>
+        <v>-0.595</v>
       </c>
       <c r="F51" s="1">
-        <v>-0.521</v>
+        <v>-0.602</v>
       </c>
       <c r="G51" s="1">
-        <v>-0.523</v>
+        <v>-0.621</v>
       </c>
       <c r="H51" s="1">
-        <v>-0.526</v>
+        <v>-0.639</v>
       </c>
       <c r="I51" s="1">
-        <v>-0.542</v>
+        <v>-0.646</v>
       </c>
       <c r="J51" s="1">
-        <v>-0.577</v>
+        <v>-0.6879999999999999</v>
       </c>
       <c r="K51" s="1">
-        <v>-0.631</v>
+        <v>-0.763</v>
       </c>
       <c r="L51" s="1">
-        <v>-0.6870000000000001</v>
+        <v>-0.8159999999999999</v>
       </c>
       <c r="M51" s="1">
-        <v>-0.662</v>
+        <v>-0.794</v>
       </c>
       <c r="N51" s="1">
-        <v>-0.574</v>
+        <v>-0.681</v>
       </c>
       <c r="O51" s="1">
-        <v>-0.479</v>
+        <v>-0.5659999999999999</v>
       </c>
       <c r="P51" s="1">
-        <v>-0.404</v>
+        <v>-0.488</v>
       </c>
       <c r="Q51" s="1">
-        <v>-0.31</v>
+        <v>-0.412</v>
       </c>
       <c r="R51" s="1">
-        <v>-0.199</v>
+        <v>-0.289</v>
       </c>
       <c r="S51" s="1">
-        <v>-0.118</v>
+        <v>-0.181</v>
       </c>
       <c r="T51" s="1">
-        <v>-0.044</v>
+        <v>-0.115</v>
       </c>
       <c r="U51" s="1">
-        <v>-0.011</v>
+        <v>-0.08799999999999999</v>
       </c>
     </row>
     <row r="52" spans="1:21">
       <c r="A52" s="2" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="B52" s="1">
         <v>-0.346</v>
       </c>
       <c r="C52" s="1">
-        <v>-0.322</v>
+        <v>-0.31</v>
       </c>
       <c r="D52" s="1">
-        <v>-0.262</v>
+        <v>-0.3</v>
       </c>
       <c r="E52" s="1">
-        <v>-0.231</v>
+        <v>-0.328</v>
       </c>
       <c r="F52" s="1">
-        <v>-0.267</v>
+        <v>-0.344</v>
       </c>
       <c r="G52" s="1">
-        <v>-0.31</v>
+        <v>-0.344</v>
       </c>
       <c r="H52" s="1">
+        <v>-0.35</v>
+      </c>
+      <c r="I52" s="1">
+        <v>-0.376</v>
+      </c>
+      <c r="J52" s="1">
+        <v>-0.407</v>
+      </c>
+      <c r="K52" s="1">
+        <v>-0.41</v>
+      </c>
+      <c r="L52" s="1">
+        <v>-0.367</v>
+      </c>
+      <c r="M52" s="1">
         <v>-0.32</v>
       </c>
-      <c r="I52" s="1">
-        <v>-0.348</v>
-      </c>
-      <c r="J52" s="1">
-        <v>-0.395</v>
-      </c>
-      <c r="K52" s="1">
-        <v>-0.411</v>
-      </c>
-      <c r="L52" s="1">
-        <v>-0.37</v>
-      </c>
-      <c r="M52" s="1">
-        <v>-0.298</v>
-      </c>
       <c r="N52" s="1">
-        <v>-0.268</v>
+        <v>-0.28</v>
       </c>
       <c r="O52" s="1">
-        <v>-0.249</v>
+        <v>-0.252</v>
       </c>
       <c r="P52" s="1">
-        <v>-0.225</v>
+        <v>-0.227</v>
       </c>
       <c r="Q52" s="1">
-        <v>-0.209</v>
+        <v>-0.197</v>
       </c>
       <c r="R52" s="1">
-        <v>-0.185</v>
+        <v>-0.165</v>
       </c>
       <c r="S52" s="1">
-        <v>-0.163</v>
+        <v>-0.138</v>
       </c>
       <c r="T52" s="1">
-        <v>-0.164</v>
+        <v>-0.135</v>
       </c>
       <c r="U52" s="1">
-        <v>-0.17</v>
+        <v>-0.165</v>
       </c>
     </row>
     <row r="53" spans="1:21">
       <c r="A53" s="2" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="B53" s="1">
         <v>-0.489</v>
       </c>
       <c r="C53" s="1">
-        <v>-0.454</v>
+        <v>-0.448</v>
       </c>
       <c r="D53" s="1">
-        <v>-0.409</v>
+        <v>-0.385</v>
       </c>
       <c r="E53" s="1">
-        <v>-0.362</v>
+        <v>-0.345</v>
       </c>
       <c r="F53" s="1">
-        <v>-0.326</v>
+        <v>-0.339</v>
       </c>
       <c r="G53" s="1">
-        <v>-0.302</v>
+        <v>-0.346</v>
       </c>
       <c r="H53" s="1">
-        <v>-0.295</v>
+        <v>-0.34</v>
       </c>
       <c r="I53" s="1">
-        <v>-0.285</v>
+        <v>-0.348</v>
       </c>
       <c r="J53" s="1">
-        <v>-0.242</v>
+        <v>-0.358</v>
       </c>
       <c r="K53" s="1">
-        <v>-0.173</v>
+        <v>-0.308</v>
       </c>
       <c r="L53" s="1">
-        <v>-0.096</v>
+        <v>-0.241</v>
       </c>
       <c r="M53" s="1">
-        <v>-0.057</v>
+        <v>-0.197</v>
       </c>
       <c r="N53" s="1">
-        <v>-0.047</v>
+        <v>-0.175</v>
       </c>
       <c r="O53" s="1">
-        <v>-0.038</v>
+        <v>-0.153</v>
       </c>
       <c r="P53" s="1">
-        <v>-0.03</v>
+        <v>-0.1</v>
       </c>
       <c r="Q53" s="1">
-        <v>-0.02</v>
+        <v>-0.046</v>
       </c>
       <c r="R53" s="1">
-        <v>-0.006</v>
+        <v>-0.01</v>
       </c>
       <c r="S53" s="1">
-        <v>0.004</v>
+        <v>0.029</v>
       </c>
       <c r="T53" s="1">
-        <v>0.017</v>
+        <v>0.044</v>
       </c>
       <c r="U53" s="1">
-        <v>0.02</v>
+        <v>0.061</v>
       </c>
     </row>
     <row r="54" spans="1:21">
       <c r="A54" s="2" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="B54" s="1">
         <v>-0.375</v>
       </c>
       <c r="C54" s="1">
+        <v>-0.393</v>
+      </c>
+      <c r="D54" s="1">
+        <v>-0.404</v>
+      </c>
+      <c r="E54" s="1">
+        <v>-0.394</v>
+      </c>
+      <c r="F54" s="1">
+        <v>-0.41</v>
+      </c>
+      <c r="G54" s="1">
+        <v>-0.471</v>
+      </c>
+      <c r="H54" s="1">
+        <v>-0.52</v>
+      </c>
+      <c r="I54" s="1">
+        <v>-0.52</v>
+      </c>
+      <c r="J54" s="1">
+        <v>-0.472</v>
+      </c>
+      <c r="K54" s="1">
         <v>-0.385</v>
       </c>
-      <c r="D54" s="1">
-        <v>-0.4</v>
-      </c>
-      <c r="E54" s="1">
-        <v>-0.409</v>
-      </c>
-      <c r="F54" s="1">
-        <v>-0.428</v>
-      </c>
-      <c r="G54" s="1">
-        <v>-0.443</v>
-      </c>
-      <c r="H54" s="1">
-        <v>-0.473</v>
-      </c>
-      <c r="I54" s="1">
-        <v>-0.476</v>
-      </c>
-      <c r="J54" s="1">
-        <v>-0.4</v>
-      </c>
-      <c r="K54" s="1">
-        <v>-0.306</v>
-      </c>
       <c r="L54" s="1">
-        <v>-0.24</v>
+        <v>-0.301</v>
       </c>
       <c r="M54" s="1">
-        <v>-0.195</v>
+        <v>-0.247</v>
       </c>
       <c r="N54" s="1">
-        <v>-0.156</v>
+        <v>-0.213</v>
       </c>
       <c r="O54" s="1">
-        <v>-0.094</v>
+        <v>-0.177</v>
       </c>
       <c r="P54" s="1">
-        <v>-0.022</v>
+        <v>-0.122</v>
       </c>
       <c r="Q54" s="1">
-        <v>0.034</v>
+        <v>-0.07099999999999999</v>
       </c>
       <c r="R54" s="1">
-        <v>0.059</v>
+        <v>-0.05</v>
       </c>
       <c r="S54" s="1">
-        <v>0.09</v>
+        <v>-0.031</v>
       </c>
       <c r="T54" s="1">
-        <v>0.121</v>
+        <v>-0.031</v>
       </c>
       <c r="U54" s="1">
-        <v>0.151</v>
+        <v>-0.025</v>
       </c>
     </row>
     <row r="55" spans="1:21">
       <c r="A55" s="2" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="B55" s="1">
         <v>-0.279</v>
       </c>
       <c r="C55" s="1">
-        <v>-0.329</v>
+        <v>-0.335</v>
       </c>
       <c r="D55" s="1">
-        <v>-0.373</v>
+        <v>-0.414</v>
       </c>
       <c r="E55" s="1">
-        <v>-0.403</v>
+        <v>-0.443</v>
       </c>
       <c r="F55" s="1">
-        <v>-0.448</v>
+        <v>-0.451</v>
       </c>
       <c r="G55" s="1">
-        <v>-0.483</v>
+        <v>-0.485</v>
       </c>
       <c r="H55" s="1">
-        <v>-0.498</v>
+        <v>-0.513</v>
       </c>
       <c r="I55" s="1">
-        <v>-0.467</v>
+        <v>-0.482</v>
       </c>
       <c r="J55" s="1">
-        <v>-0.396</v>
+        <v>-0.423</v>
       </c>
       <c r="K55" s="1">
-        <v>-0.336</v>
+        <v>-0.354</v>
       </c>
       <c r="L55" s="1">
-        <v>-0.269</v>
+        <v>-0.288</v>
       </c>
       <c r="M55" s="1">
-        <v>-0.194</v>
+        <v>-0.233</v>
       </c>
       <c r="N55" s="1">
-        <v>-0.138</v>
+        <v>-0.182</v>
       </c>
       <c r="O55" s="1">
-        <v>-0.08400000000000001</v>
+        <v>-0.113</v>
       </c>
       <c r="P55" s="1">
-        <v>-0.05</v>
+        <v>-0.045</v>
       </c>
       <c r="Q55" s="1">
-        <v>-0.035</v>
+        <v>0.003</v>
       </c>
       <c r="R55" s="1">
-        <v>-0.004</v>
+        <v>0.02</v>
       </c>
       <c r="S55" s="1">
-        <v>0.02</v>
+        <v>0.039</v>
       </c>
       <c r="T55" s="1">
-        <v>0.022</v>
+        <v>0.06900000000000001</v>
       </c>
       <c r="U55" s="1">
-        <v>0.042</v>
+        <v>0.104</v>
       </c>
     </row>
     <row r="56" spans="1:21">
       <c r="A56" s="2" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="B56" s="1">
         <v>-0.378</v>
       </c>
       <c r="C56" s="1">
-        <v>-0.438</v>
+        <v>-0.426</v>
       </c>
       <c r="D56" s="1">
-        <v>-0.505</v>
+        <v>-0.503</v>
       </c>
       <c r="E56" s="1">
-        <v>-0.571</v>
+        <v>-0.583</v>
       </c>
       <c r="F56" s="1">
-        <v>-0.667</v>
+        <v>-0.67</v>
       </c>
       <c r="G56" s="1">
-        <v>-0.726</v>
+        <v>-0.725</v>
       </c>
       <c r="H56" s="1">
-        <v>-0.6889999999999999</v>
+        <v>-0.6919999999999999</v>
       </c>
       <c r="I56" s="1">
-        <v>-0.581</v>
+        <v>-0.584</v>
       </c>
       <c r="J56" s="1">
-        <v>-0.472</v>
+        <v>-0.478</v>
       </c>
       <c r="K56" s="1">
-        <v>-0.382</v>
+        <v>-0.397</v>
       </c>
       <c r="L56" s="1">
-        <v>-0.299</v>
+        <v>-0.345</v>
       </c>
       <c r="M56" s="1">
-        <v>-0.251</v>
+        <v>-0.317</v>
       </c>
       <c r="N56" s="1">
-        <v>-0.217</v>
+        <v>-0.301</v>
       </c>
       <c r="O56" s="1">
-        <v>-0.182</v>
+        <v>-0.261</v>
       </c>
       <c r="P56" s="1">
-        <v>-0.153</v>
+        <v>-0.246</v>
       </c>
       <c r="Q56" s="1">
-        <v>-0.136</v>
+        <v>-0.303</v>
       </c>
       <c r="R56" s="1">
-        <v>-0.131</v>
+        <v>-0.385</v>
       </c>
       <c r="S56" s="1">
-        <v>-0.131</v>
+        <v>-0.447</v>
       </c>
       <c r="T56" s="1">
-        <v>-0.12</v>
+        <v>-0.461</v>
       </c>
       <c r="U56" s="1">
-        <v>-0.118</v>
+        <v>-0.423</v>
       </c>
     </row>
     <row r="57" spans="1:21">
       <c r="A57" s="2" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="B57" s="1">
         <v>-0.6</v>
       </c>
       <c r="C57" s="1">
-        <v>-0.649</v>
+        <v>-0.633</v>
       </c>
       <c r="D57" s="1">
-        <v>-0.742</v>
+        <v>-0.696</v>
       </c>
       <c r="E57" s="1">
-        <v>-0.843</v>
+        <v>-0.792</v>
       </c>
       <c r="F57" s="1">
-        <v>-0.908</v>
+        <v>-0.864</v>
       </c>
       <c r="G57" s="1">
-        <v>-0.863</v>
+        <v>-0.8149999999999999</v>
       </c>
       <c r="H57" s="1">
-        <v>-0.723</v>
+        <v>-0.675</v>
       </c>
       <c r="I57" s="1">
-        <v>-0.576</v>
+        <v>-0.53</v>
       </c>
       <c r="J57" s="1">
-        <v>-0.456</v>
+        <v>-0.416</v>
       </c>
       <c r="K57" s="1">
-        <v>-0.348</v>
+        <v>-0.319</v>
       </c>
       <c r="L57" s="1">
-        <v>-0.255</v>
+        <v>-0.251</v>
       </c>
       <c r="M57" s="1">
-        <v>-0.171</v>
+        <v>-0.195</v>
       </c>
       <c r="N57" s="1">
-        <v>-0.108</v>
+        <v>-0.159</v>
       </c>
       <c r="O57" s="1">
-        <v>-0.074</v>
+        <v>-0.144</v>
       </c>
       <c r="P57" s="1">
-        <v>-0.063</v>
+        <v>-0.155</v>
       </c>
       <c r="Q57" s="1">
-        <v>-0.07000000000000001</v>
+        <v>-0.179</v>
       </c>
       <c r="R57" s="1">
-        <v>-0.073</v>
+        <v>-0.182</v>
       </c>
       <c r="S57" s="1">
-        <v>-0.062</v>
+        <v>-0.158</v>
       </c>
       <c r="T57" s="1">
-        <v>-0.051</v>
+        <v>-0.131</v>
       </c>
       <c r="U57" s="1">
-        <v>-0.048</v>
+        <v>-0.121</v>
       </c>
     </row>
     <row r="58" spans="1:21">
       <c r="A58" s="2" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="B58" s="1">
         <v>-0.732</v>
       </c>
       <c r="C58" s="1">
-        <v>-0.789</v>
+        <v>-0.772</v>
       </c>
       <c r="D58" s="1">
-        <v>-0.916</v>
+        <v>-0.887</v>
       </c>
       <c r="E58" s="1">
-        <v>-0.997</v>
+        <v>-0.97</v>
       </c>
       <c r="F58" s="1">
-        <v>-0.9429999999999999</v>
+        <v>-0.92</v>
       </c>
       <c r="G58" s="1">
-        <v>-0.797</v>
+        <v>-0.802</v>
       </c>
       <c r="H58" s="1">
-        <v>-0.631</v>
+        <v>-0.6820000000000001</v>
       </c>
       <c r="I58" s="1">
-        <v>-0.483</v>
+        <v>-0.5590000000000001</v>
       </c>
       <c r="J58" s="1">
-        <v>-0.378</v>
+        <v>-0.451</v>
       </c>
       <c r="K58" s="1">
-        <v>-0.275</v>
+        <v>-0.344</v>
       </c>
       <c r="L58" s="1">
-        <v>-0.172</v>
+        <v>-0.257</v>
       </c>
       <c r="M58" s="1">
-        <v>-0.093</v>
+        <v>-0.208</v>
       </c>
       <c r="N58" s="1">
-        <v>-0.035</v>
+        <v>-0.198</v>
       </c>
       <c r="O58" s="1">
-        <v>-0.004</v>
+        <v>-0.209</v>
       </c>
       <c r="P58" s="1">
-        <v>-0.004</v>
+        <v>-0.229</v>
       </c>
       <c r="Q58" s="1">
-        <v>0.002</v>
+        <v>-0.228</v>
       </c>
       <c r="R58" s="1">
-        <v>0.039</v>
+        <v>-0.202</v>
       </c>
       <c r="S58" s="1">
-        <v>0.056</v>
+        <v>-0.167</v>
       </c>
       <c r="T58" s="1">
-        <v>0.053</v>
+        <v>-0.155</v>
       </c>
       <c r="U58" s="1">
-        <v>0.046</v>
+        <v>-0.144</v>
       </c>
     </row>
     <row r="59" spans="1:21">
       <c r="A59" s="2" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="B59" s="1">
         <v>-0.826</v>
       </c>
       <c r="C59" s="1">
-        <v>-0.844</v>
+        <v>-0.86</v>
       </c>
       <c r="D59" s="1">
-        <v>-0.858</v>
+        <v>-0.883</v>
       </c>
       <c r="E59" s="1">
-        <v>-0.798</v>
+        <v>-0.804</v>
       </c>
       <c r="F59" s="1">
-        <v>-0.681</v>
+        <v>-0.67</v>
       </c>
       <c r="G59" s="1">
-        <v>-0.555</v>
+        <v>-0.542</v>
       </c>
       <c r="H59" s="1">
-        <v>-0.425</v>
+        <v>-0.428</v>
       </c>
       <c r="I59" s="1">
-        <v>-0.319</v>
+        <v>-0.283</v>
       </c>
       <c r="J59" s="1">
-        <v>-0.244</v>
+        <v>-0.12</v>
       </c>
       <c r="K59" s="1">
-        <v>-0.169</v>
+        <v>-0.004</v>
       </c>
       <c r="L59" s="1">
-        <v>-0.111</v>
+        <v>0.06900000000000001</v>
       </c>
       <c r="M59" s="1">
-        <v>-0.075</v>
+        <v>0.123</v>
       </c>
       <c r="N59" s="1">
-        <v>-0.054</v>
+        <v>0.183</v>
       </c>
       <c r="O59" s="1">
-        <v>-0.02</v>
+        <v>0.257</v>
       </c>
       <c r="P59" s="1">
-        <v>0.022</v>
+        <v>0.322</v>
       </c>
       <c r="Q59" s="1">
-        <v>0.055</v>
+        <v>0.338</v>
       </c>
       <c r="R59" s="1">
-        <v>0.066</v>
+        <v>0.326</v>
       </c>
       <c r="S59" s="1">
-        <v>0.059</v>
+        <v>0.302</v>
       </c>
       <c r="T59" s="1">
-        <v>0.034</v>
+        <v>0.225</v>
       </c>
       <c r="U59" s="1">
-        <v>0.01</v>
+        <v>0.153</v>
       </c>
     </row>
     <row r="60" spans="1:21">
       <c r="A60" s="2" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="B60" s="1">
         <v>-0.914</v>
       </c>
       <c r="C60" s="1">
-        <v>-0.881</v>
+        <v>-0.887</v>
       </c>
       <c r="D60" s="1">
-        <v>-0.751</v>
+        <v>-0.768</v>
       </c>
       <c r="E60" s="1">
-        <v>-0.591</v>
+        <v>-0.616</v>
       </c>
       <c r="F60" s="1">
-        <v>-0.46</v>
+        <v>-0.485</v>
       </c>
       <c r="G60" s="1">
-        <v>-0.339</v>
+        <v>-0.373</v>
       </c>
       <c r="H60" s="1">
-        <v>-0.192</v>
+        <v>-0.258</v>
       </c>
       <c r="I60" s="1">
-        <v>-0.049</v>
+        <v>-0.107</v>
       </c>
       <c r="J60" s="1">
-        <v>0.048</v>
+        <v>0.019</v>
       </c>
       <c r="K60" s="1">
-        <v>0.101</v>
+        <v>0.091</v>
       </c>
       <c r="L60" s="1">
-        <v>0.148</v>
+        <v>0.128</v>
       </c>
       <c r="M60" s="1">
-        <v>0.216</v>
+        <v>0.162</v>
       </c>
       <c r="N60" s="1">
-        <v>0.29</v>
+        <v>0.232</v>
       </c>
       <c r="O60" s="1">
-        <v>0.363</v>
+        <v>0.302</v>
       </c>
       <c r="P60" s="1">
-        <v>0.391</v>
+        <v>0.326</v>
       </c>
       <c r="Q60" s="1">
-        <v>0.367</v>
+        <v>0.315</v>
       </c>
       <c r="R60" s="1">
-        <v>0.32</v>
+        <v>0.275</v>
       </c>
       <c r="S60" s="1">
-        <v>0.247</v>
+        <v>0.207</v>
       </c>
       <c r="T60" s="1">
-        <v>0.16</v>
+        <v>0.141</v>
       </c>
       <c r="U60" s="1">
-        <v>0.091</v>
+        <v>0.081</v>
       </c>
     </row>
     <row r="61" spans="1:21">
       <c r="A61" s="2" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="B61" s="1">
         <v>-0.903</v>
       </c>
       <c r="C61" s="1">
-        <v>-0.784</v>
+        <v>-0.802</v>
       </c>
       <c r="D61" s="1">
-        <v>-0.596</v>
+        <v>-0.631</v>
       </c>
       <c r="E61" s="1">
-        <v>-0.452</v>
+        <v>-0.477</v>
       </c>
       <c r="F61" s="1">
-        <v>-0.318</v>
+        <v>-0.349</v>
       </c>
       <c r="G61" s="1">
-        <v>-0.183</v>
+        <v>-0.214</v>
       </c>
       <c r="H61" s="1">
-        <v>-0.041</v>
+        <v>-0.048</v>
       </c>
       <c r="I61" s="1">
-        <v>0.093</v>
+        <v>0.109</v>
       </c>
       <c r="J61" s="1">
-        <v>0.192</v>
+        <v>0.229</v>
       </c>
       <c r="K61" s="1">
-        <v>0.28</v>
+        <v>0.323</v>
       </c>
       <c r="L61" s="1">
-        <v>0.385</v>
+        <v>0.397</v>
       </c>
       <c r="M61" s="1">
-        <v>0.503</v>
+        <v>0.521</v>
       </c>
       <c r="N61" s="1">
-        <v>0.618</v>
+        <v>0.648</v>
       </c>
       <c r="O61" s="1">
-        <v>0.6820000000000001</v>
+        <v>0.709</v>
       </c>
       <c r="P61" s="1">
-        <v>0.658</v>
+        <v>0.675</v>
       </c>
       <c r="Q61" s="1">
-        <v>0.5570000000000001</v>
+        <v>0.5659999999999999</v>
       </c>
       <c r="R61" s="1">
-        <v>0.41</v>
+        <v>0.429</v>
       </c>
       <c r="S61" s="1">
-        <v>0.289</v>
+        <v>0.303</v>
       </c>
       <c r="T61" s="1">
-        <v>0.168</v>
+        <v>0.205</v>
       </c>
       <c r="U61" s="1">
-        <v>0.062</v>
+        <v>0.148</v>
       </c>
     </row>
     <row r="62" spans="1:21">
       <c r="A62" s="2" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="B62" s="1">
         <v>-0.882</v>
       </c>
       <c r="C62" s="1">
-        <v>-0.741</v>
+        <v>-0.754</v>
       </c>
       <c r="D62" s="1">
-        <v>-0.584</v>
+        <v>-0.589</v>
       </c>
       <c r="E62" s="1">
-        <v>-0.491</v>
+        <v>-0.477</v>
       </c>
       <c r="F62" s="1">
-        <v>-0.342</v>
+        <v>-0.311</v>
       </c>
       <c r="G62" s="1">
-        <v>-0.146</v>
+        <v>-0.117</v>
       </c>
       <c r="H62" s="1">
-        <v>0.047</v>
+        <v>0.045</v>
       </c>
       <c r="I62" s="1">
-        <v>0.184</v>
+        <v>0.193</v>
       </c>
       <c r="J62" s="1">
-        <v>0.273</v>
+        <v>0.325</v>
       </c>
       <c r="K62" s="1">
-        <v>0.372</v>
+        <v>0.443</v>
       </c>
       <c r="L62" s="1">
-        <v>0.483</v>
+        <v>0.592</v>
       </c>
       <c r="M62" s="1">
-        <v>0.599</v>
+        <v>0.739</v>
       </c>
       <c r="N62" s="1">
-        <v>0.657</v>
+        <v>0.806</v>
       </c>
       <c r="O62" s="1">
-        <v>0.63</v>
+        <v>0.769</v>
       </c>
       <c r="P62" s="1">
-        <v>0.556</v>
+        <v>0.652</v>
       </c>
       <c r="Q62" s="1">
-        <v>0.432</v>
+        <v>0.508</v>
       </c>
       <c r="R62" s="1">
-        <v>0.312</v>
+        <v>0.358</v>
       </c>
       <c r="S62" s="1">
-        <v>0.218</v>
+        <v>0.22</v>
       </c>
       <c r="T62" s="1">
-        <v>0.142</v>
+        <v>0.13</v>
       </c>
       <c r="U62" s="1">
-        <v>0.09</v>
+        <v>0.093</v>
       </c>
     </row>
     <row r="63" spans="1:21">
       <c r="A63" s="2" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="B63" s="1">
         <v>-0.657</v>
       </c>
       <c r="C63" s="1">
-        <v>-0.5610000000000001</v>
+        <v>-0.579</v>
       </c>
       <c r="D63" s="1">
-        <v>-0.407</v>
+        <v>-0.434</v>
       </c>
       <c r="E63" s="1">
-        <v>-0.22</v>
+        <v>-0.259</v>
       </c>
       <c r="F63" s="1">
-        <v>-0.007</v>
+        <v>-0.055</v>
       </c>
       <c r="G63" s="1">
-        <v>0.171</v>
+        <v>0.145</v>
       </c>
       <c r="H63" s="1">
-        <v>0.287</v>
+        <v>0.308</v>
       </c>
       <c r="I63" s="1">
-        <v>0.397</v>
+        <v>0.457</v>
       </c>
       <c r="J63" s="1">
-        <v>0.536</v>
+        <v>0.615</v>
       </c>
       <c r="K63" s="1">
-        <v>0.705</v>
+        <v>0.798</v>
       </c>
       <c r="L63" s="1">
-        <v>0.854</v>
+        <v>0.948</v>
       </c>
       <c r="M63" s="1">
-        <v>0.922</v>
+        <v>0.986</v>
       </c>
       <c r="N63" s="1">
-        <v>0.89</v>
+        <v>0.923</v>
       </c>
       <c r="O63" s="1">
-        <v>0.749</v>
+        <v>0.783</v>
       </c>
       <c r="P63" s="1">
-        <v>0.5580000000000001</v>
+        <v>0.587</v>
       </c>
       <c r="Q63" s="1">
         <v>0.363</v>
       </c>
       <c r="R63" s="1">
-        <v>0.151</v>
+        <v>0.138</v>
       </c>
       <c r="S63" s="1">
-        <v>-0.015</v>
+        <v>-0.051</v>
       </c>
       <c r="T63" s="1">
-        <v>-0.101</v>
+        <v>-0.183</v>
       </c>
       <c r="U63" s="1">
-        <v>-0.146</v>
+        <v>-0.274</v>
       </c>
     </row>
     <row r="64" spans="1:21">
       <c r="A64" s="2" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="B64" s="1">
         <v>-0.388</v>
       </c>
       <c r="C64" s="1">
-        <v>-0.29</v>
+        <v>-0.269</v>
       </c>
       <c r="D64" s="1">
-        <v>-0.078</v>
+        <v>-0.039</v>
       </c>
       <c r="E64" s="1">
-        <v>0.162</v>
+        <v>0.202</v>
       </c>
       <c r="F64" s="1">
-        <v>0.369</v>
+        <v>0.423</v>
       </c>
       <c r="G64" s="1">
-        <v>0.543</v>
+        <v>0.599</v>
       </c>
       <c r="H64" s="1">
-        <v>0.713</v>
+        <v>0.783</v>
       </c>
       <c r="I64" s="1">
-        <v>0.918</v>
+        <v>1.028</v>
       </c>
       <c r="J64" s="1">
-        <v>1.166</v>
+        <v>1.314</v>
       </c>
       <c r="K64" s="1">
-        <v>1.393</v>
+        <v>1.553</v>
       </c>
       <c r="L64" s="1">
-        <v>1.491</v>
+        <v>1.627</v>
       </c>
       <c r="M64" s="1">
-        <v>1.408</v>
+        <v>1.541</v>
       </c>
       <c r="N64" s="1">
-        <v>1.181</v>
+        <v>1.317</v>
       </c>
       <c r="O64" s="1">
-        <v>0.886</v>
+        <v>0.971</v>
       </c>
       <c r="P64" s="1">
-        <v>0.577</v>
+        <v>0.591</v>
       </c>
       <c r="Q64" s="1">
-        <v>0.287</v>
+        <v>0.253</v>
       </c>
       <c r="R64" s="1">
-        <v>0.058</v>
+        <v>0.005</v>
       </c>
       <c r="S64" s="1">
-        <v>-0.083</v>
+        <v>-0.159</v>
       </c>
       <c r="T64" s="1">
-        <v>-0.158</v>
+        <v>-0.242</v>
       </c>
       <c r="U64" s="1">
-        <v>-0.211</v>
+        <v>-0.293</v>
       </c>
     </row>
     <row r="65" spans="1:21">
       <c r="A65" s="2" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="B65" s="1">
         <v>0.044</v>
       </c>
       <c r="C65" s="1">
-        <v>0.206</v>
+        <v>0.199</v>
       </c>
       <c r="D65" s="1">
-        <v>0.483</v>
+        <v>0.49</v>
       </c>
       <c r="E65" s="1">
-        <v>0.754</v>
+        <v>0.771</v>
       </c>
       <c r="F65" s="1">
-        <v>1.009</v>
+        <v>1.008</v>
       </c>
       <c r="G65" s="1">
-        <v>1.282</v>
+        <v>1.27</v>
       </c>
       <c r="H65" s="1">
-        <v>1.636</v>
+        <v>1.626</v>
       </c>
       <c r="I65" s="1">
-        <v>2.07</v>
+        <v>2.027</v>
       </c>
       <c r="J65" s="1">
-        <v>2.429</v>
+        <v>2.345</v>
       </c>
       <c r="K65" s="1">
-        <v>2.564</v>
+        <v>2.455</v>
       </c>
       <c r="L65" s="1">
-        <v>2.419</v>
+        <v>2.309</v>
       </c>
       <c r="M65" s="1">
-        <v>1.981</v>
+        <v>1.924</v>
       </c>
       <c r="N65" s="1">
-        <v>1.387</v>
+        <v>1.381</v>
       </c>
       <c r="O65" s="1">
-        <v>0.788</v>
+        <v>0.8129999999999999</v>
       </c>
       <c r="P65" s="1">
-        <v>0.25</v>
+        <v>0.293</v>
       </c>
       <c r="Q65" s="1">
-        <v>-0.145</v>
+        <v>-0.112</v>
       </c>
       <c r="R65" s="1">
-        <v>-0.39</v>
+        <v>-0.335</v>
       </c>
       <c r="S65" s="1">
-        <v>-0.52</v>
+        <v>-0.436</v>
       </c>
       <c r="T65" s="1">
-        <v>-0.602</v>
+        <v>-0.494</v>
       </c>
       <c r="U65" s="1">
-        <v>-0.678</v>
+        <v>-0.547</v>
       </c>
     </row>
     <row r="66" spans="1:21">
       <c r="A66" s="2" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="B66" s="1">
         <v>0.635</v>
       </c>
       <c r="C66" s="1">
-        <v>0.778</v>
+        <v>0.754</v>
       </c>
       <c r="D66" s="1">
-        <v>1.017</v>
+        <v>0.959</v>
       </c>
       <c r="E66" s="1">
-        <v>1.283</v>
+        <v>1.168</v>
       </c>
       <c r="F66" s="1">
-        <v>1.566</v>
+        <v>1.424</v>
       </c>
       <c r="G66" s="1">
-        <v>1.879</v>
+        <v>1.735</v>
       </c>
       <c r="H66" s="1">
-        <v>2.206</v>
+        <v>2.065</v>
       </c>
       <c r="I66" s="1">
-        <v>2.443</v>
+        <v>2.31</v>
       </c>
       <c r="J66" s="1">
-        <v>2.514</v>
+        <v>2.356</v>
       </c>
       <c r="K66" s="1">
-        <v>2.357</v>
+        <v>2.16</v>
       </c>
       <c r="L66" s="1">
-        <v>1.948</v>
+        <v>1.756</v>
       </c>
       <c r="M66" s="1">
-        <v>1.37</v>
+        <v>1.247</v>
       </c>
       <c r="N66" s="1">
-        <v>0.789</v>
+        <v>0.715</v>
       </c>
       <c r="O66" s="1">
-        <v>0.276</v>
+        <v>0.251</v>
       </c>
       <c r="P66" s="1">
-        <v>-0.118</v>
+        <v>-0.096</v>
       </c>
       <c r="Q66" s="1">
-        <v>-0.357</v>
+        <v>-0.306</v>
       </c>
       <c r="R66" s="1">
-        <v>-0.481</v>
+        <v>-0.392</v>
       </c>
       <c r="S66" s="1">
-        <v>-0.533</v>
+        <v>-0.437</v>
       </c>
       <c r="T66" s="1">
-        <v>-0.588</v>
+        <v>-0.484</v>
       </c>
       <c r="U66" s="1">
-        <v>-0.643</v>
+        <v>-0.526</v>
       </c>
     </row>
     <row r="67" spans="1:21">
       <c r="A67" s="2" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="B67" s="1">
         <v>0.9429999999999999</v>
       </c>
       <c r="C67" s="1">
-        <v>1.106</v>
+        <v>1.141</v>
       </c>
       <c r="D67" s="1">
-        <v>1.41</v>
+        <v>1.472</v>
       </c>
       <c r="E67" s="1">
-        <v>1.726</v>
+        <v>1.805</v>
       </c>
       <c r="F67" s="1">
-        <v>2.073</v>
+        <v>2.143</v>
       </c>
       <c r="G67" s="1">
-        <v>2.409</v>
+        <v>2.446</v>
       </c>
       <c r="H67" s="1">
-        <v>2.627</v>
+        <v>2.644</v>
       </c>
       <c r="I67" s="1">
-        <v>2.657</v>
+        <v>2.658</v>
       </c>
       <c r="J67" s="1">
-        <v>2.439</v>
+        <v>2.463</v>
       </c>
       <c r="K67" s="1">
-        <v>1.969</v>
+        <v>2.036</v>
       </c>
       <c r="L67" s="1">
-        <v>1.357</v>
+        <v>1.424</v>
       </c>
       <c r="M67" s="1">
-        <v>0.752</v>
+        <v>0.781</v>
       </c>
       <c r="N67" s="1">
-        <v>0.206</v>
+        <v>0.186</v>
       </c>
       <c r="O67" s="1">
-        <v>-0.212</v>
+        <v>-0.255</v>
       </c>
       <c r="P67" s="1">
-        <v>-0.441</v>
+        <v>-0.491</v>
       </c>
       <c r="Q67" s="1">
-        <v>-0.547</v>
+        <v>-0.597</v>
       </c>
       <c r="R67" s="1">
-        <v>-0.616</v>
+        <v>-0.653</v>
       </c>
       <c r="S67" s="1">
-        <v>-0.699</v>
+        <v>-0.743</v>
       </c>
       <c r="T67" s="1">
-        <v>-0.798</v>
+        <v>-0.846</v>
       </c>
       <c r="U67" s="1">
-        <v>-0.8110000000000001</v>
+        <v>-0.8179999999999999</v>
+      </c>
+    </row>
+    <row r="68" spans="1:21">
+      <c r="A68" s="2" t="s">
+        <v>66</v>
+      </c>
+      <c r="B68" s="1">
+        <v>1.429</v>
+      </c>
+      <c r="C68" s="1">
+        <v>1.676</v>
+      </c>
+      <c r="D68" s="1">
+        <v>2.138</v>
+      </c>
+      <c r="E68" s="1">
+        <v>2.626</v>
+      </c>
+      <c r="F68" s="1">
+        <v>3.032</v>
+      </c>
+      <c r="G68" s="1">
+        <v>3.28</v>
+      </c>
+      <c r="H68" s="1">
+        <v>3.299</v>
+      </c>
+      <c r="I68" s="1">
+        <v>3.004</v>
+      </c>
+      <c r="J68" s="1">
+        <v>2.366</v>
+      </c>
+      <c r="K68" s="1">
+        <v>1.548</v>
+      </c>
+      <c r="L68" s="1">
+        <v>0.757</v>
+      </c>
+      <c r="M68" s="1">
+        <v>0.037</v>
+      </c>
+      <c r="N68" s="1">
+        <v>-0.505</v>
+      </c>
+      <c r="O68" s="1">
+        <v>-0.777</v>
+      </c>
+      <c r="P68" s="1">
+        <v>-0.882</v>
+      </c>
+      <c r="Q68" s="1">
+        <v>-0.952</v>
+      </c>
+      <c r="R68" s="1">
+        <v>-1.091</v>
+      </c>
+      <c r="S68" s="1">
+        <v>-1.243</v>
+      </c>
+      <c r="T68" s="1">
+        <v>-1.218</v>
+      </c>
+      <c r="U68" s="1">
+        <v>-1.021</v>
       </c>
     </row>
   </sheetData>

--- a/content/climate/XRO/XRO_RelENSO_fcst.xlsx
+++ b/content/climate/XRO/XRO_RelENSO_fcst.xlsx
@@ -15,7 +15,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="72" uniqueCount="72">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="73" uniqueCount="73">
   <si>
     <t>2021-01</t>
   </si>
@@ -216,6 +216,9 @@
   </si>
   <si>
     <t>2026-07</t>
+  </si>
+  <si>
+    <t>2026-08</t>
   </si>
   <si>
     <t>Readme</t>
@@ -592,7 +595,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:U68"/>
+  <dimension ref="A1:U69"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="2" max="21" width="10.7109375" style="1" customWidth="1"/>
@@ -600,7 +603,7 @@
   <sheetData>
     <row r="1" spans="1:21">
       <c r="A1" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="B1" s="2">
         <v>0</v>
@@ -671,61 +674,61 @@
         <v>-1.078</v>
       </c>
       <c r="C2" s="1">
-        <v>-0.993</v>
+        <v>-0.992</v>
       </c>
       <c r="D2" s="1">
-        <v>-0.87</v>
+        <v>-0.866</v>
       </c>
       <c r="E2" s="1">
-        <v>-0.78</v>
+        <v>-0.753</v>
       </c>
       <c r="F2" s="1">
-        <v>-0.644</v>
+        <v>-0.612</v>
       </c>
       <c r="G2" s="1">
-        <v>-0.45</v>
+        <v>-0.446</v>
       </c>
       <c r="H2" s="1">
-        <v>-0.294</v>
+        <v>-0.298</v>
       </c>
       <c r="I2" s="1">
-        <v>-0.234</v>
+        <v>-0.239</v>
       </c>
       <c r="J2" s="1">
-        <v>-0.256</v>
+        <v>-0.276</v>
       </c>
       <c r="K2" s="1">
-        <v>-0.32</v>
+        <v>-0.358</v>
       </c>
       <c r="L2" s="1">
-        <v>-0.363</v>
+        <v>-0.428</v>
       </c>
       <c r="M2" s="1">
-        <v>-0.351</v>
+        <v>-0.429</v>
       </c>
       <c r="N2" s="1">
-        <v>-0.311</v>
+        <v>-0.366</v>
       </c>
       <c r="O2" s="1">
-        <v>-0.259</v>
+        <v>-0.281</v>
       </c>
       <c r="P2" s="1">
-        <v>-0.225</v>
+        <v>-0.26</v>
       </c>
       <c r="Q2" s="1">
-        <v>-0.181</v>
+        <v>-0.242</v>
       </c>
       <c r="R2" s="1">
-        <v>-0.079</v>
+        <v>-0.139</v>
       </c>
       <c r="S2" s="1">
-        <v>0.046</v>
+        <v>-0.01</v>
       </c>
       <c r="T2" s="1">
-        <v>0.148</v>
+        <v>0.125</v>
       </c>
       <c r="U2" s="1">
-        <v>0.228</v>
+        <v>0.253</v>
       </c>
     </row>
     <row r="3" spans="1:21">
@@ -736,61 +739,61 @@
         <v>-0.907</v>
       </c>
       <c r="C3" s="1">
-        <v>-0.849</v>
+        <v>-0.863</v>
       </c>
       <c r="D3" s="1">
-        <v>-0.751</v>
+        <v>-0.767</v>
       </c>
       <c r="E3" s="1">
-        <v>-0.636</v>
+        <v>-0.645</v>
       </c>
       <c r="F3" s="1">
-        <v>-0.504</v>
+        <v>-0.493</v>
       </c>
       <c r="G3" s="1">
-        <v>-0.412</v>
+        <v>-0.378</v>
       </c>
       <c r="H3" s="1">
-        <v>-0.393</v>
+        <v>-0.339</v>
       </c>
       <c r="I3" s="1">
-        <v>-0.417</v>
+        <v>-0.367</v>
       </c>
       <c r="J3" s="1">
-        <v>-0.462</v>
+        <v>-0.443</v>
       </c>
       <c r="K3" s="1">
-        <v>-0.528</v>
+        <v>-0.493</v>
       </c>
       <c r="L3" s="1">
-        <v>-0.536</v>
+        <v>-0.488</v>
       </c>
       <c r="M3" s="1">
-        <v>-0.464</v>
+        <v>-0.43</v>
       </c>
       <c r="N3" s="1">
-        <v>-0.376</v>
+        <v>-0.343</v>
       </c>
       <c r="O3" s="1">
-        <v>-0.315</v>
+        <v>-0.309</v>
       </c>
       <c r="P3" s="1">
-        <v>-0.266</v>
+        <v>-0.275</v>
       </c>
       <c r="Q3" s="1">
-        <v>-0.159</v>
+        <v>-0.158</v>
       </c>
       <c r="R3" s="1">
-        <v>-0.012</v>
+        <v>-0.003</v>
       </c>
       <c r="S3" s="1">
-        <v>0.125</v>
+        <v>0.132</v>
       </c>
       <c r="T3" s="1">
-        <v>0.243</v>
+        <v>0.24</v>
       </c>
       <c r="U3" s="1">
-        <v>0.314</v>
+        <v>0.319</v>
       </c>
     </row>
     <row r="4" spans="1:21">
@@ -801,61 +804,61 @@
         <v>-0.681</v>
       </c>
       <c r="C4" s="1">
-        <v>-0.653</v>
+        <v>-0.63</v>
       </c>
       <c r="D4" s="1">
-        <v>-0.581</v>
+        <v>-0.525</v>
       </c>
       <c r="E4" s="1">
-        <v>-0.44</v>
+        <v>-0.401</v>
       </c>
       <c r="F4" s="1">
-        <v>-0.306</v>
+        <v>-0.29</v>
       </c>
       <c r="G4" s="1">
-        <v>-0.235</v>
+        <v>-0.244</v>
       </c>
       <c r="H4" s="1">
-        <v>-0.227</v>
+        <v>-0.259</v>
       </c>
       <c r="I4" s="1">
-        <v>-0.261</v>
+        <v>-0.337</v>
       </c>
       <c r="J4" s="1">
-        <v>-0.307</v>
+        <v>-0.439</v>
       </c>
       <c r="K4" s="1">
-        <v>-0.315</v>
+        <v>-0.481</v>
       </c>
       <c r="L4" s="1">
-        <v>-0.269</v>
+        <v>-0.46</v>
       </c>
       <c r="M4" s="1">
-        <v>-0.217</v>
+        <v>-0.402</v>
       </c>
       <c r="N4" s="1">
-        <v>-0.188</v>
+        <v>-0.345</v>
       </c>
       <c r="O4" s="1">
-        <v>-0.148</v>
+        <v>-0.291</v>
       </c>
       <c r="P4" s="1">
-        <v>-0.056</v>
+        <v>-0.197</v>
       </c>
       <c r="Q4" s="1">
-        <v>0.079</v>
+        <v>-0.07000000000000001</v>
       </c>
       <c r="R4" s="1">
-        <v>0.194</v>
+        <v>0.041</v>
       </c>
       <c r="S4" s="1">
-        <v>0.252</v>
+        <v>0.122</v>
       </c>
       <c r="T4" s="1">
-        <v>0.291</v>
+        <v>0.197</v>
       </c>
       <c r="U4" s="1">
-        <v>0.337</v>
+        <v>0.26</v>
       </c>
     </row>
     <row r="5" spans="1:21">
@@ -866,61 +869,61 @@
         <v>-0.741</v>
       </c>
       <c r="C5" s="1">
-        <v>-0.673</v>
+        <v>-0.657</v>
       </c>
       <c r="D5" s="1">
-        <v>-0.546</v>
+        <v>-0.49</v>
       </c>
       <c r="E5" s="1">
-        <v>-0.44</v>
+        <v>-0.372</v>
       </c>
       <c r="F5" s="1">
-        <v>-0.398</v>
+        <v>-0.334</v>
       </c>
       <c r="G5" s="1">
-        <v>-0.419</v>
+        <v>-0.37</v>
       </c>
       <c r="H5" s="1">
-        <v>-0.49</v>
+        <v>-0.456</v>
       </c>
       <c r="I5" s="1">
-        <v>-0.572</v>
+        <v>-0.518</v>
       </c>
       <c r="J5" s="1">
-        <v>-0.574</v>
+        <v>-0.527</v>
       </c>
       <c r="K5" s="1">
-        <v>-0.491</v>
+        <v>-0.485</v>
       </c>
       <c r="L5" s="1">
-        <v>-0.419</v>
+        <v>-0.415</v>
       </c>
       <c r="M5" s="1">
-        <v>-0.362</v>
+        <v>-0.363</v>
       </c>
       <c r="N5" s="1">
-        <v>-0.28</v>
+        <v>-0.297</v>
       </c>
       <c r="O5" s="1">
-        <v>-0.14</v>
+        <v>-0.182</v>
       </c>
       <c r="P5" s="1">
-        <v>0.011</v>
+        <v>-0.022</v>
       </c>
       <c r="Q5" s="1">
-        <v>0.14</v>
+        <v>0.12</v>
       </c>
       <c r="R5" s="1">
-        <v>0.221</v>
+        <v>0.199</v>
       </c>
       <c r="S5" s="1">
-        <v>0.278</v>
+        <v>0.257</v>
       </c>
       <c r="T5" s="1">
-        <v>0.353</v>
+        <v>0.313</v>
       </c>
       <c r="U5" s="1">
-        <v>0.422</v>
+        <v>0.351</v>
       </c>
     </row>
     <row r="6" spans="1:21">
@@ -931,61 +934,61 @@
         <v>-0.448</v>
       </c>
       <c r="C6" s="1">
-        <v>-0.42</v>
+        <v>-0.393</v>
       </c>
       <c r="D6" s="1">
+        <v>-0.345</v>
+      </c>
+      <c r="E6" s="1">
+        <v>-0.378</v>
+      </c>
+      <c r="F6" s="1">
+        <v>-0.451</v>
+      </c>
+      <c r="G6" s="1">
+        <v>-0.534</v>
+      </c>
+      <c r="H6" s="1">
+        <v>-0.61</v>
+      </c>
+      <c r="I6" s="1">
+        <v>-0.632</v>
+      </c>
+      <c r="J6" s="1">
+        <v>-0.574</v>
+      </c>
+      <c r="K6" s="1">
+        <v>-0.499</v>
+      </c>
+      <c r="L6" s="1">
+        <v>-0.45</v>
+      </c>
+      <c r="M6" s="1">
         <v>-0.383</v>
       </c>
-      <c r="E6" s="1">
-        <v>-0.398</v>
-      </c>
-      <c r="F6" s="1">
-        <v>-0.465</v>
-      </c>
-      <c r="G6" s="1">
-        <v>-0.543</v>
-      </c>
-      <c r="H6" s="1">
-        <v>-0.638</v>
-      </c>
-      <c r="I6" s="1">
-        <v>-0.6889999999999999</v>
-      </c>
-      <c r="J6" s="1">
-        <v>-0.644</v>
-      </c>
-      <c r="K6" s="1">
-        <v>-0.553</v>
-      </c>
-      <c r="L6" s="1">
-        <v>-0.47</v>
-      </c>
-      <c r="M6" s="1">
-        <v>-0.39</v>
-      </c>
       <c r="N6" s="1">
-        <v>-0.27</v>
+        <v>-0.282</v>
       </c>
       <c r="O6" s="1">
-        <v>-0.101</v>
+        <v>-0.131</v>
       </c>
       <c r="P6" s="1">
-        <v>0.033</v>
+        <v>0.002</v>
       </c>
       <c r="Q6" s="1">
-        <v>0.109</v>
+        <v>0.083</v>
       </c>
       <c r="R6" s="1">
-        <v>0.148</v>
+        <v>0.131</v>
       </c>
       <c r="S6" s="1">
-        <v>0.177</v>
+        <v>0.161</v>
       </c>
       <c r="T6" s="1">
-        <v>0.227</v>
+        <v>0.205</v>
       </c>
       <c r="U6" s="1">
-        <v>0.277</v>
+        <v>0.265</v>
       </c>
     </row>
     <row r="7" spans="1:21">
@@ -996,61 +999,61 @@
         <v>-0.277</v>
       </c>
       <c r="C7" s="1">
-        <v>-0.321</v>
+        <v>-0.313</v>
       </c>
       <c r="D7" s="1">
-        <v>-0.381</v>
+        <v>-0.383</v>
       </c>
       <c r="E7" s="1">
-        <v>-0.463</v>
+        <v>-0.452</v>
       </c>
       <c r="F7" s="1">
-        <v>-0.586</v>
+        <v>-0.5659999999999999</v>
       </c>
       <c r="G7" s="1">
-        <v>-0.72</v>
+        <v>-0.704</v>
       </c>
       <c r="H7" s="1">
-        <v>-0.822</v>
+        <v>-0.783</v>
       </c>
       <c r="I7" s="1">
-        <v>-0.8110000000000001</v>
+        <v>-0.754</v>
       </c>
       <c r="J7" s="1">
-        <v>-0.737</v>
+        <v>-0.666</v>
       </c>
       <c r="K7" s="1">
-        <v>-0.649</v>
+        <v>-0.576</v>
       </c>
       <c r="L7" s="1">
-        <v>-0.533</v>
+        <v>-0.487</v>
       </c>
       <c r="M7" s="1">
-        <v>-0.402</v>
+        <v>-0.345</v>
       </c>
       <c r="N7" s="1">
-        <v>-0.243</v>
+        <v>-0.169</v>
       </c>
       <c r="O7" s="1">
-        <v>-0.107</v>
+        <v>-0.024</v>
       </c>
       <c r="P7" s="1">
-        <v>-0.035</v>
+        <v>0.081</v>
       </c>
       <c r="Q7" s="1">
-        <v>-0.003</v>
+        <v>0.137</v>
       </c>
       <c r="R7" s="1">
-        <v>-0.012</v>
+        <v>0.173</v>
       </c>
       <c r="S7" s="1">
-        <v>-0.018</v>
+        <v>0.231</v>
       </c>
       <c r="T7" s="1">
-        <v>0.025</v>
+        <v>0.285</v>
       </c>
       <c r="U7" s="1">
-        <v>0.07199999999999999</v>
+        <v>0.304</v>
       </c>
     </row>
     <row r="8" spans="1:21">
@@ -1061,61 +1064,61 @@
         <v>-0.452</v>
       </c>
       <c r="C8" s="1">
-        <v>-0.544</v>
+        <v>-0.538</v>
       </c>
       <c r="D8" s="1">
-        <v>-0.6840000000000001</v>
+        <v>-0.6889999999999999</v>
       </c>
       <c r="E8" s="1">
-        <v>-0.837</v>
+        <v>-0.854</v>
       </c>
       <c r="F8" s="1">
-        <v>-1.011</v>
+        <v>-1.049</v>
       </c>
       <c r="G8" s="1">
-        <v>-1.137</v>
+        <v>-1.214</v>
       </c>
       <c r="H8" s="1">
-        <v>-1.123</v>
+        <v>-1.21</v>
       </c>
       <c r="I8" s="1">
-        <v>-0.999</v>
+        <v>-1.07</v>
       </c>
       <c r="J8" s="1">
-        <v>-0.844</v>
+        <v>-0.914</v>
       </c>
       <c r="K8" s="1">
-        <v>-0.6870000000000001</v>
+        <v>-0.752</v>
       </c>
       <c r="L8" s="1">
-        <v>-0.522</v>
+        <v>-0.5600000000000001</v>
       </c>
       <c r="M8" s="1">
-        <v>-0.349</v>
+        <v>-0.341</v>
       </c>
       <c r="N8" s="1">
-        <v>-0.181</v>
+        <v>-0.15</v>
       </c>
       <c r="O8" s="1">
-        <v>-0.063</v>
+        <v>-0.031</v>
       </c>
       <c r="P8" s="1">
-        <v>-0.005</v>
+        <v>0.031</v>
       </c>
       <c r="Q8" s="1">
-        <v>0.014</v>
+        <v>0.08</v>
       </c>
       <c r="R8" s="1">
-        <v>0.049</v>
+        <v>0.117</v>
       </c>
       <c r="S8" s="1">
-        <v>0.117</v>
+        <v>0.153</v>
       </c>
       <c r="T8" s="1">
-        <v>0.164</v>
+        <v>0.196</v>
       </c>
       <c r="U8" s="1">
-        <v>0.168</v>
+        <v>0.212</v>
       </c>
     </row>
     <row r="9" spans="1:21">
@@ -1126,61 +1129,61 @@
         <v>-0.641</v>
       </c>
       <c r="C9" s="1">
-        <v>-0.712</v>
+        <v>-0.715</v>
       </c>
       <c r="D9" s="1">
-        <v>-0.888</v>
+        <v>-0.897</v>
       </c>
       <c r="E9" s="1">
-        <v>-1.115</v>
+        <v>-1.114</v>
       </c>
       <c r="F9" s="1">
-        <v>-1.295</v>
+        <v>-1.284</v>
       </c>
       <c r="G9" s="1">
-        <v>-1.314</v>
+        <v>-1.278</v>
       </c>
       <c r="H9" s="1">
-        <v>-1.181</v>
+        <v>-1.121</v>
       </c>
       <c r="I9" s="1">
-        <v>-1.014</v>
+        <v>-0.954</v>
       </c>
       <c r="J9" s="1">
-        <v>-0.85</v>
+        <v>-0.8070000000000001</v>
       </c>
       <c r="K9" s="1">
-        <v>-0.663</v>
+        <v>-0.619</v>
       </c>
       <c r="L9" s="1">
-        <v>-0.458</v>
+        <v>-0.382</v>
       </c>
       <c r="M9" s="1">
-        <v>-0.286</v>
+        <v>-0.194</v>
       </c>
       <c r="N9" s="1">
-        <v>-0.181</v>
+        <v>-0.089</v>
       </c>
       <c r="O9" s="1">
-        <v>-0.164</v>
+        <v>-0.052</v>
       </c>
       <c r="P9" s="1">
-        <v>-0.172</v>
+        <v>-0.046</v>
       </c>
       <c r="Q9" s="1">
-        <v>-0.169</v>
+        <v>-0.005</v>
       </c>
       <c r="R9" s="1">
-        <v>-0.124</v>
+        <v>0.058</v>
       </c>
       <c r="S9" s="1">
-        <v>-0.057</v>
+        <v>0.112</v>
       </c>
       <c r="T9" s="1">
-        <v>-0.047</v>
+        <v>0.131</v>
       </c>
       <c r="U9" s="1">
-        <v>-0.051</v>
+        <v>0.106</v>
       </c>
     </row>
     <row r="10" spans="1:21">
@@ -1191,61 +1194,61 @@
         <v>-0.646</v>
       </c>
       <c r="C10" s="1">
-        <v>-0.762</v>
+        <v>-0.727</v>
       </c>
       <c r="D10" s="1">
-        <v>-0.974</v>
+        <v>-0.924</v>
       </c>
       <c r="E10" s="1">
-        <v>-1.142</v>
+        <v>-1.102</v>
       </c>
       <c r="F10" s="1">
-        <v>-1.169</v>
+        <v>-1.126</v>
       </c>
       <c r="G10" s="1">
-        <v>-1.061</v>
+        <v>-1.037</v>
       </c>
       <c r="H10" s="1">
-        <v>-0.919</v>
+        <v>-0.901</v>
       </c>
       <c r="I10" s="1">
-        <v>-0.778</v>
+        <v>-0.754</v>
       </c>
       <c r="J10" s="1">
-        <v>-0.63</v>
+        <v>-0.618</v>
       </c>
       <c r="K10" s="1">
-        <v>-0.481</v>
+        <v>-0.473</v>
       </c>
       <c r="L10" s="1">
+        <v>-0.359</v>
+      </c>
+      <c r="M10" s="1">
+        <v>-0.309</v>
+      </c>
+      <c r="N10" s="1">
+        <v>-0.307</v>
+      </c>
+      <c r="O10" s="1">
+        <v>-0.376</v>
+      </c>
+      <c r="P10" s="1">
+        <v>-0.46</v>
+      </c>
+      <c r="Q10" s="1">
+        <v>-0.482</v>
+      </c>
+      <c r="R10" s="1">
+        <v>-0.426</v>
+      </c>
+      <c r="S10" s="1">
         <v>-0.351</v>
       </c>
-      <c r="M10" s="1">
-        <v>-0.28</v>
-      </c>
-      <c r="N10" s="1">
-        <v>-0.267</v>
-      </c>
-      <c r="O10" s="1">
-        <v>-0.296</v>
-      </c>
-      <c r="P10" s="1">
-        <v>-0.329</v>
-      </c>
-      <c r="Q10" s="1">
-        <v>-0.298</v>
-      </c>
-      <c r="R10" s="1">
-        <v>-0.239</v>
-      </c>
-      <c r="S10" s="1">
-        <v>-0.19</v>
-      </c>
       <c r="T10" s="1">
-        <v>-0.157</v>
+        <v>-0.294</v>
       </c>
       <c r="U10" s="1">
-        <v>-0.139</v>
+        <v>-0.245</v>
       </c>
     </row>
     <row r="11" spans="1:21">
@@ -1256,61 +1259,61 @@
         <v>-1.17</v>
       </c>
       <c r="C11" s="1">
-        <v>-1.321</v>
+        <v>-1.29</v>
       </c>
       <c r="D11" s="1">
-        <v>-1.521</v>
+        <v>-1.455</v>
       </c>
       <c r="E11" s="1">
-        <v>-1.522</v>
+        <v>-1.446</v>
       </c>
       <c r="F11" s="1">
-        <v>-1.346</v>
+        <v>-1.28</v>
       </c>
       <c r="G11" s="1">
-        <v>-1.138</v>
+        <v>-1.09</v>
       </c>
       <c r="H11" s="1">
-        <v>-0.95</v>
+        <v>-0.905</v>
       </c>
       <c r="I11" s="1">
-        <v>-0.74</v>
+        <v>-0.6899999999999999</v>
       </c>
       <c r="J11" s="1">
-        <v>-0.49</v>
+        <v>-0.439</v>
       </c>
       <c r="K11" s="1">
-        <v>-0.28</v>
+        <v>-0.225</v>
       </c>
       <c r="L11" s="1">
-        <v>-0.18</v>
+        <v>-0.105</v>
       </c>
       <c r="M11" s="1">
-        <v>-0.166</v>
+        <v>-0.057</v>
       </c>
       <c r="N11" s="1">
-        <v>-0.174</v>
+        <v>-0.039</v>
       </c>
       <c r="O11" s="1">
-        <v>-0.162</v>
+        <v>-0.025</v>
       </c>
       <c r="P11" s="1">
-        <v>-0.107</v>
+        <v>0.042</v>
       </c>
       <c r="Q11" s="1">
-        <v>-0.037</v>
+        <v>0.115</v>
       </c>
       <c r="R11" s="1">
-        <v>-0.004</v>
+        <v>0.137</v>
       </c>
       <c r="S11" s="1">
-        <v>-0.024</v>
+        <v>0.107</v>
       </c>
       <c r="T11" s="1">
-        <v>-0.04</v>
+        <v>0.063</v>
       </c>
       <c r="U11" s="1">
-        <v>0.004</v>
+        <v>0.057</v>
       </c>
     </row>
     <row r="12" spans="1:21">
@@ -1321,61 +1324,61 @@
         <v>-1.218</v>
       </c>
       <c r="C12" s="1">
-        <v>-1.272</v>
+        <v>-1.284</v>
       </c>
       <c r="D12" s="1">
-        <v>-1.26</v>
+        <v>-1.305</v>
       </c>
       <c r="E12" s="1">
-        <v>-1.156</v>
+        <v>-1.202</v>
       </c>
       <c r="F12" s="1">
-        <v>-1.005</v>
+        <v>-1.041</v>
       </c>
       <c r="G12" s="1">
-        <v>-0.828</v>
+        <v>-0.867</v>
       </c>
       <c r="H12" s="1">
-        <v>-0.62</v>
+        <v>-0.654</v>
       </c>
       <c r="I12" s="1">
-        <v>-0.381</v>
+        <v>-0.427</v>
       </c>
       <c r="J12" s="1">
-        <v>-0.185</v>
+        <v>-0.244</v>
       </c>
       <c r="K12" s="1">
-        <v>-0.079</v>
+        <v>-0.124</v>
       </c>
       <c r="L12" s="1">
-        <v>-0.03</v>
+        <v>-0.07000000000000001</v>
       </c>
       <c r="M12" s="1">
-        <v>-0.001</v>
+        <v>-0.039</v>
       </c>
       <c r="N12" s="1">
-        <v>0.022</v>
+        <v>0</v>
       </c>
       <c r="O12" s="1">
-        <v>0.082</v>
+        <v>0.058</v>
       </c>
       <c r="P12" s="1">
-        <v>0.14</v>
+        <v>0.105</v>
       </c>
       <c r="Q12" s="1">
-        <v>0.158</v>
+        <v>0.098</v>
       </c>
       <c r="R12" s="1">
-        <v>0.138</v>
+        <v>0.078</v>
       </c>
       <c r="S12" s="1">
-        <v>0.099</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="T12" s="1">
-        <v>0.073</v>
+        <v>0.081</v>
       </c>
       <c r="U12" s="1">
-        <v>0.089</v>
+        <v>0.13</v>
       </c>
     </row>
     <row r="13" spans="1:21">
@@ -1386,61 +1389,61 @@
         <v>-1.227</v>
       </c>
       <c r="C13" s="1">
-        <v>-1.147</v>
+        <v>-1.17</v>
       </c>
       <c r="D13" s="1">
-        <v>-0.977</v>
+        <v>-1.033</v>
       </c>
       <c r="E13" s="1">
-        <v>-0.849</v>
+        <v>-0.879</v>
       </c>
       <c r="F13" s="1">
-        <v>-0.721</v>
+        <v>-0.704</v>
       </c>
       <c r="G13" s="1">
-        <v>-0.489</v>
+        <v>-0.472</v>
       </c>
       <c r="H13" s="1">
-        <v>-0.203</v>
+        <v>-0.222</v>
       </c>
       <c r="I13" s="1">
-        <v>0.008999999999999999</v>
+        <v>-0.012</v>
       </c>
       <c r="J13" s="1">
-        <v>0.117</v>
+        <v>0.142</v>
       </c>
       <c r="K13" s="1">
-        <v>0.189</v>
+        <v>0.24</v>
       </c>
       <c r="L13" s="1">
-        <v>0.268</v>
+        <v>0.329</v>
       </c>
       <c r="M13" s="1">
-        <v>0.366</v>
+        <v>0.465</v>
       </c>
       <c r="N13" s="1">
-        <v>0.464</v>
+        <v>0.613</v>
       </c>
       <c r="O13" s="1">
-        <v>0.534</v>
+        <v>0.6870000000000001</v>
       </c>
       <c r="P13" s="1">
-        <v>0.509</v>
+        <v>0.667</v>
       </c>
       <c r="Q13" s="1">
-        <v>0.435</v>
+        <v>0.5629999999999999</v>
       </c>
       <c r="R13" s="1">
-        <v>0.359</v>
+        <v>0.442</v>
       </c>
       <c r="S13" s="1">
-        <v>0.302</v>
+        <v>0.332</v>
       </c>
       <c r="T13" s="1">
-        <v>0.289</v>
+        <v>0.265</v>
       </c>
       <c r="U13" s="1">
-        <v>0.257</v>
+        <v>0.232</v>
       </c>
     </row>
     <row r="14" spans="1:21">
@@ -1451,61 +1454,61 @@
         <v>-1.152</v>
       </c>
       <c r="C14" s="1">
-        <v>-1.056</v>
+        <v>-1.041</v>
       </c>
       <c r="D14" s="1">
-        <v>-0.924</v>
+        <v>-0.905</v>
       </c>
       <c r="E14" s="1">
-        <v>-0.823</v>
+        <v>-0.8110000000000001</v>
       </c>
       <c r="F14" s="1">
-        <v>-0.666</v>
+        <v>-0.637</v>
       </c>
       <c r="G14" s="1">
-        <v>-0.431</v>
+        <v>-0.387</v>
       </c>
       <c r="H14" s="1">
-        <v>-0.215</v>
+        <v>-0.18</v>
       </c>
       <c r="I14" s="1">
-        <v>-0.09</v>
+        <v>-0.062</v>
       </c>
       <c r="J14" s="1">
-        <v>-0.046</v>
+        <v>-0.021</v>
       </c>
       <c r="K14" s="1">
-        <v>-0.033</v>
+        <v>-0.001</v>
       </c>
       <c r="L14" s="1">
-        <v>0.013</v>
+        <v>0.041</v>
       </c>
       <c r="M14" s="1">
+        <v>0.108</v>
+      </c>
+      <c r="N14" s="1">
+        <v>0.18</v>
+      </c>
+      <c r="O14" s="1">
+        <v>0.205</v>
+      </c>
+      <c r="P14" s="1">
+        <v>0.166</v>
+      </c>
+      <c r="Q14" s="1">
         <v>0.112</v>
       </c>
-      <c r="N14" s="1">
-        <v>0.214</v>
-      </c>
-      <c r="O14" s="1">
-        <v>0.251</v>
-      </c>
-      <c r="P14" s="1">
-        <v>0.222</v>
-      </c>
-      <c r="Q14" s="1">
-        <v>0.169</v>
-      </c>
       <c r="R14" s="1">
-        <v>0.162</v>
+        <v>0.075</v>
       </c>
       <c r="S14" s="1">
-        <v>0.216</v>
+        <v>0.074</v>
       </c>
       <c r="T14" s="1">
-        <v>0.271</v>
+        <v>0.109</v>
       </c>
       <c r="U14" s="1">
-        <v>0.286</v>
+        <v>0.156</v>
       </c>
     </row>
     <row r="15" spans="1:21">
@@ -1516,61 +1519,61 @@
         <v>-1.011</v>
       </c>
       <c r="C15" s="1">
-        <v>-0.968</v>
+        <v>-0.956</v>
       </c>
       <c r="D15" s="1">
-        <v>-0.89</v>
+        <v>-0.859</v>
       </c>
       <c r="E15" s="1">
-        <v>-0.729</v>
+        <v>-0.71</v>
       </c>
       <c r="F15" s="1">
-        <v>-0.469</v>
+        <v>-0.448</v>
       </c>
       <c r="G15" s="1">
-        <v>-0.224</v>
+        <v>-0.201</v>
       </c>
       <c r="H15" s="1">
-        <v>-0.096</v>
+        <v>-0.08400000000000001</v>
       </c>
       <c r="I15" s="1">
-        <v>-0.065</v>
+        <v>-0.033</v>
       </c>
       <c r="J15" s="1">
-        <v>-0.06</v>
+        <v>-0.004</v>
       </c>
       <c r="K15" s="1">
-        <v>-0.015</v>
+        <v>0.07199999999999999</v>
       </c>
       <c r="L15" s="1">
-        <v>0.101</v>
+        <v>0.204</v>
       </c>
       <c r="M15" s="1">
-        <v>0.212</v>
+        <v>0.322</v>
       </c>
       <c r="N15" s="1">
-        <v>0.249</v>
+        <v>0.347</v>
       </c>
       <c r="O15" s="1">
-        <v>0.217</v>
+        <v>0.285</v>
       </c>
       <c r="P15" s="1">
-        <v>0.155</v>
+        <v>0.224</v>
       </c>
       <c r="Q15" s="1">
-        <v>0.141</v>
+        <v>0.221</v>
       </c>
       <c r="R15" s="1">
-        <v>0.186</v>
+        <v>0.271</v>
       </c>
       <c r="S15" s="1">
-        <v>0.241</v>
+        <v>0.325</v>
       </c>
       <c r="T15" s="1">
-        <v>0.282</v>
+        <v>0.356</v>
       </c>
       <c r="U15" s="1">
-        <v>0.303</v>
+        <v>0.399</v>
       </c>
     </row>
     <row r="16" spans="1:21">
@@ -1581,61 +1584,61 @@
         <v>-1.278</v>
       </c>
       <c r="C16" s="1">
-        <v>-1.223</v>
+        <v>-1.216</v>
       </c>
       <c r="D16" s="1">
-        <v>-1.047</v>
+        <v>-1.038</v>
       </c>
       <c r="E16" s="1">
-        <v>-0.788</v>
+        <v>-0.787</v>
       </c>
       <c r="F16" s="1">
-        <v>-0.544</v>
+        <v>-0.546</v>
       </c>
       <c r="G16" s="1">
-        <v>-0.386</v>
+        <v>-0.399</v>
       </c>
       <c r="H16" s="1">
-        <v>-0.357</v>
+        <v>-0.371</v>
       </c>
       <c r="I16" s="1">
-        <v>-0.408</v>
+        <v>-0.435</v>
       </c>
       <c r="J16" s="1">
-        <v>-0.456</v>
+        <v>-0.477</v>
       </c>
       <c r="K16" s="1">
-        <v>-0.412</v>
+        <v>-0.396</v>
       </c>
       <c r="L16" s="1">
-        <v>-0.277</v>
+        <v>-0.221</v>
       </c>
       <c r="M16" s="1">
-        <v>-0.191</v>
+        <v>-0.105</v>
       </c>
       <c r="N16" s="1">
-        <v>-0.19</v>
+        <v>-0.098</v>
       </c>
       <c r="O16" s="1">
-        <v>-0.188</v>
+        <v>-0.065</v>
       </c>
       <c r="P16" s="1">
-        <v>-0.08500000000000001</v>
+        <v>0.046</v>
       </c>
       <c r="Q16" s="1">
-        <v>0.105</v>
+        <v>0.222</v>
       </c>
       <c r="R16" s="1">
-        <v>0.29</v>
+        <v>0.408</v>
       </c>
       <c r="S16" s="1">
-        <v>0.427</v>
+        <v>0.54</v>
       </c>
       <c r="T16" s="1">
-        <v>0.538</v>
+        <v>0.659</v>
       </c>
       <c r="U16" s="1">
-        <v>0.647</v>
+        <v>0.785</v>
       </c>
     </row>
     <row r="17" spans="1:21">
@@ -1646,61 +1649,61 @@
         <v>-1.291</v>
       </c>
       <c r="C17" s="1">
-        <v>-1.19</v>
+        <v>-1.178</v>
       </c>
       <c r="D17" s="1">
-        <v>-0.925</v>
+        <v>-0.915</v>
       </c>
       <c r="E17" s="1">
-        <v>-0.667</v>
+        <v>-0.654</v>
       </c>
       <c r="F17" s="1">
-        <v>-0.536</v>
+        <v>-0.528</v>
       </c>
       <c r="G17" s="1">
-        <v>-0.547</v>
+        <v>-0.548</v>
       </c>
       <c r="H17" s="1">
-        <v>-0.6830000000000001</v>
+        <v>-0.659</v>
       </c>
       <c r="I17" s="1">
-        <v>-0.8139999999999999</v>
+        <v>-0.748</v>
       </c>
       <c r="J17" s="1">
-        <v>-0.758</v>
+        <v>-0.6860000000000001</v>
       </c>
       <c r="K17" s="1">
-        <v>-0.578</v>
+        <v>-0.525</v>
       </c>
       <c r="L17" s="1">
-        <v>-0.45</v>
+        <v>-0.411</v>
       </c>
       <c r="M17" s="1">
-        <v>-0.413</v>
+        <v>-0.384</v>
       </c>
       <c r="N17" s="1">
-        <v>-0.378</v>
+        <v>-0.355</v>
       </c>
       <c r="O17" s="1">
-        <v>-0.235</v>
+        <v>-0.228</v>
       </c>
       <c r="P17" s="1">
-        <v>0.034</v>
+        <v>0.025</v>
       </c>
       <c r="Q17" s="1">
-        <v>0.323</v>
+        <v>0.293</v>
       </c>
       <c r="R17" s="1">
-        <v>0.544</v>
+        <v>0.477</v>
       </c>
       <c r="S17" s="1">
-        <v>0.726</v>
+        <v>0.625</v>
       </c>
       <c r="T17" s="1">
-        <v>0.925</v>
+        <v>0.771</v>
       </c>
       <c r="U17" s="1">
-        <v>1.124</v>
+        <v>0.91</v>
       </c>
     </row>
     <row r="18" spans="1:21">
@@ -1711,61 +1714,61 @@
         <v>-1.16</v>
       </c>
       <c r="C18" s="1">
-        <v>-1.005</v>
+        <v>-0.993</v>
       </c>
       <c r="D18" s="1">
-        <v>-0.764</v>
+        <v>-0.75</v>
       </c>
       <c r="E18" s="1">
-        <v>-0.669</v>
+        <v>-0.67</v>
       </c>
       <c r="F18" s="1">
-        <v>-0.742</v>
+        <v>-0.76</v>
       </c>
       <c r="G18" s="1">
-        <v>-0.928</v>
+        <v>-0.965</v>
       </c>
       <c r="H18" s="1">
-        <v>-1.106</v>
+        <v>-1.143</v>
       </c>
       <c r="I18" s="1">
-        <v>-1.119</v>
+        <v>-1.159</v>
       </c>
       <c r="J18" s="1">
-        <v>-0.951</v>
+        <v>-1.012</v>
       </c>
       <c r="K18" s="1">
-        <v>-0.797</v>
+        <v>-0.848</v>
       </c>
       <c r="L18" s="1">
-        <v>-0.748</v>
+        <v>-0.782</v>
       </c>
       <c r="M18" s="1">
-        <v>-0.681</v>
+        <v>-0.711</v>
       </c>
       <c r="N18" s="1">
-        <v>-0.471</v>
+        <v>-0.511</v>
       </c>
       <c r="O18" s="1">
-        <v>-0.143</v>
+        <v>-0.169</v>
       </c>
       <c r="P18" s="1">
-        <v>0.176</v>
+        <v>0.163</v>
       </c>
       <c r="Q18" s="1">
-        <v>0.396</v>
+        <v>0.377</v>
       </c>
       <c r="R18" s="1">
-        <v>0.55</v>
+        <v>0.523</v>
       </c>
       <c r="S18" s="1">
-        <v>0.6860000000000001</v>
+        <v>0.663</v>
       </c>
       <c r="T18" s="1">
-        <v>0.805</v>
+        <v>0.8110000000000001</v>
       </c>
       <c r="U18" s="1">
-        <v>0.897</v>
+        <v>0.947</v>
       </c>
     </row>
     <row r="19" spans="1:21">
@@ -1776,61 +1779,61 @@
         <v>-0.786</v>
       </c>
       <c r="C19" s="1">
-        <v>-0.6879999999999999</v>
+        <v>-0.681</v>
       </c>
       <c r="D19" s="1">
-        <v>-0.608</v>
+        <v>-0.588</v>
       </c>
       <c r="E19" s="1">
-        <v>-0.68</v>
+        <v>-0.642</v>
       </c>
       <c r="F19" s="1">
-        <v>-0.856</v>
+        <v>-0.803</v>
       </c>
       <c r="G19" s="1">
-        <v>-0.993</v>
+        <v>-0.964</v>
       </c>
       <c r="H19" s="1">
-        <v>-0.99</v>
+        <v>-0.987</v>
       </c>
       <c r="I19" s="1">
-        <v>-0.861</v>
+        <v>-0.844</v>
       </c>
       <c r="J19" s="1">
-        <v>-0.741</v>
+        <v>-0.72</v>
       </c>
       <c r="K19" s="1">
-        <v>-0.701</v>
+        <v>-0.665</v>
       </c>
       <c r="L19" s="1">
-        <v>-0.633</v>
+        <v>-0.578</v>
       </c>
       <c r="M19" s="1">
-        <v>-0.429</v>
+        <v>-0.405</v>
       </c>
       <c r="N19" s="1">
-        <v>-0.111</v>
+        <v>-0.124</v>
       </c>
       <c r="O19" s="1">
-        <v>0.196</v>
+        <v>0.159</v>
       </c>
       <c r="P19" s="1">
-        <v>0.409</v>
+        <v>0.355</v>
       </c>
       <c r="Q19" s="1">
-        <v>0.5600000000000001</v>
+        <v>0.497</v>
       </c>
       <c r="R19" s="1">
-        <v>0.6889999999999999</v>
+        <v>0.627</v>
       </c>
       <c r="S19" s="1">
-        <v>0.8080000000000001</v>
+        <v>0.751</v>
       </c>
       <c r="T19" s="1">
-        <v>0.929</v>
+        <v>0.87</v>
       </c>
       <c r="U19" s="1">
-        <v>0.983</v>
+        <v>0.9360000000000001</v>
       </c>
     </row>
     <row r="20" spans="1:21">
@@ -1841,61 +1844,61 @@
         <v>-0.644</v>
       </c>
       <c r="C20" s="1">
-        <v>-0.657</v>
+        <v>-0.641</v>
       </c>
       <c r="D20" s="1">
-        <v>-0.767</v>
+        <v>-0.726</v>
       </c>
       <c r="E20" s="1">
-        <v>-0.956</v>
+        <v>-0.921</v>
       </c>
       <c r="F20" s="1">
-        <v>-1.117</v>
+        <v>-1.097</v>
       </c>
       <c r="G20" s="1">
-        <v>-1.112</v>
+        <v>-1.098</v>
       </c>
       <c r="H20" s="1">
-        <v>-0.955</v>
+        <v>-0.931</v>
       </c>
       <c r="I20" s="1">
         <v>-0.791</v>
       </c>
       <c r="J20" s="1">
-        <v>-0.708</v>
+        <v>-0.739</v>
       </c>
       <c r="K20" s="1">
-        <v>-0.632</v>
+        <v>-0.657</v>
       </c>
       <c r="L20" s="1">
-        <v>-0.399</v>
+        <v>-0.423</v>
       </c>
       <c r="M20" s="1">
-        <v>-0.012</v>
+        <v>-0.036</v>
       </c>
       <c r="N20" s="1">
-        <v>0.387</v>
+        <v>0.347</v>
       </c>
       <c r="O20" s="1">
-        <v>0.68</v>
+        <v>0.627</v>
       </c>
       <c r="P20" s="1">
-        <v>0.895</v>
+        <v>0.852</v>
       </c>
       <c r="Q20" s="1">
-        <v>1.124</v>
+        <v>1.082</v>
       </c>
       <c r="R20" s="1">
-        <v>1.353</v>
+        <v>1.321</v>
       </c>
       <c r="S20" s="1">
-        <v>1.527</v>
+        <v>1.499</v>
       </c>
       <c r="T20" s="1">
-        <v>1.579</v>
+        <v>1.549</v>
       </c>
       <c r="U20" s="1">
-        <v>1.478</v>
+        <v>1.437</v>
       </c>
     </row>
     <row r="21" spans="1:21">
@@ -1906,61 +1909,61 @@
         <v>-0.909</v>
       </c>
       <c r="C21" s="1">
-        <v>-0.997</v>
+        <v>-1.006</v>
       </c>
       <c r="D21" s="1">
-        <v>-1.223</v>
+        <v>-1.228</v>
       </c>
       <c r="E21" s="1">
-        <v>-1.437</v>
+        <v>-1.465</v>
       </c>
       <c r="F21" s="1">
-        <v>-1.46</v>
+        <v>-1.498</v>
       </c>
       <c r="G21" s="1">
-        <v>-1.286</v>
+        <v>-1.298</v>
       </c>
       <c r="H21" s="1">
-        <v>-1.091</v>
+        <v>-1.089</v>
       </c>
       <c r="I21" s="1">
-        <v>-0.98</v>
+        <v>-0.962</v>
       </c>
       <c r="J21" s="1">
-        <v>-0.851</v>
+        <v>-0.852</v>
       </c>
       <c r="K21" s="1">
-        <v>-0.57</v>
+        <v>-0.628</v>
       </c>
       <c r="L21" s="1">
-        <v>-0.124</v>
+        <v>-0.222</v>
       </c>
       <c r="M21" s="1">
-        <v>0.321</v>
+        <v>0.195</v>
       </c>
       <c r="N21" s="1">
-        <v>0.66</v>
+        <v>0.491</v>
       </c>
       <c r="O21" s="1">
-        <v>0.9340000000000001</v>
+        <v>0.722</v>
       </c>
       <c r="P21" s="1">
-        <v>1.21</v>
+        <v>0.9330000000000001</v>
       </c>
       <c r="Q21" s="1">
-        <v>1.493</v>
+        <v>1.142</v>
       </c>
       <c r="R21" s="1">
-        <v>1.722</v>
+        <v>1.317</v>
       </c>
       <c r="S21" s="1">
-        <v>1.793</v>
+        <v>1.387</v>
       </c>
       <c r="T21" s="1">
-        <v>1.669</v>
+        <v>1.333</v>
       </c>
       <c r="U21" s="1">
-        <v>1.392</v>
+        <v>1.141</v>
       </c>
     </row>
     <row r="22" spans="1:21">
@@ -1971,61 +1974,61 @@
         <v>-1.019</v>
       </c>
       <c r="C22" s="1">
-        <v>-1.132</v>
+        <v>-1.146</v>
       </c>
       <c r="D22" s="1">
-        <v>-1.295</v>
+        <v>-1.332</v>
       </c>
       <c r="E22" s="1">
-        <v>-1.294</v>
+        <v>-1.348</v>
       </c>
       <c r="F22" s="1">
-        <v>-1.112</v>
+        <v>-1.189</v>
       </c>
       <c r="G22" s="1">
-        <v>-0.918</v>
+        <v>-1.015</v>
       </c>
       <c r="H22" s="1">
-        <v>-0.831</v>
+        <v>-0.923</v>
       </c>
       <c r="I22" s="1">
-        <v>-0.746</v>
+        <v>-0.8159999999999999</v>
       </c>
       <c r="J22" s="1">
-        <v>-0.512</v>
+        <v>-0.554</v>
       </c>
       <c r="K22" s="1">
-        <v>-0.102</v>
+        <v>-0.144</v>
       </c>
       <c r="L22" s="1">
-        <v>0.293</v>
+        <v>0.254</v>
       </c>
       <c r="M22" s="1">
-        <v>0.5620000000000001</v>
+        <v>0.5679999999999999</v>
       </c>
       <c r="N22" s="1">
-        <v>0.776</v>
+        <v>0.8070000000000001</v>
       </c>
       <c r="O22" s="1">
-        <v>0.996</v>
+        <v>1.021</v>
       </c>
       <c r="P22" s="1">
-        <v>1.224</v>
+        <v>1.246</v>
       </c>
       <c r="Q22" s="1">
-        <v>1.432</v>
+        <v>1.419</v>
       </c>
       <c r="R22" s="1">
-        <v>1.535</v>
+        <v>1.487</v>
       </c>
       <c r="S22" s="1">
-        <v>1.463</v>
+        <v>1.406</v>
       </c>
       <c r="T22" s="1">
-        <v>1.224</v>
+        <v>1.16</v>
       </c>
       <c r="U22" s="1">
-        <v>0.921</v>
+        <v>0.844</v>
       </c>
     </row>
     <row r="23" spans="1:21">
@@ -2036,61 +2039,61 @@
         <v>-0.985</v>
       </c>
       <c r="C23" s="1">
-        <v>-1.048</v>
+        <v>-1.032</v>
       </c>
       <c r="D23" s="1">
-        <v>-1.06</v>
+        <v>-1.021</v>
       </c>
       <c r="E23" s="1">
-        <v>-0.914</v>
+        <v>-0.867</v>
       </c>
       <c r="F23" s="1">
-        <v>-0.769</v>
+        <v>-0.699</v>
       </c>
       <c r="G23" s="1">
-        <v>-0.708</v>
+        <v>-0.59</v>
       </c>
       <c r="H23" s="1">
-        <v>-0.615</v>
+        <v>-0.483</v>
       </c>
       <c r="I23" s="1">
-        <v>-0.376</v>
+        <v>-0.263</v>
       </c>
       <c r="J23" s="1">
-        <v>-0.039</v>
+        <v>0.047</v>
       </c>
       <c r="K23" s="1">
-        <v>0.283</v>
+        <v>0.333</v>
       </c>
       <c r="L23" s="1">
-        <v>0.5</v>
+        <v>0.531</v>
       </c>
       <c r="M23" s="1">
-        <v>0.654</v>
+        <v>0.662</v>
       </c>
       <c r="N23" s="1">
-        <v>0.829</v>
+        <v>0.786</v>
       </c>
       <c r="O23" s="1">
-        <v>1.053</v>
+        <v>0.9360000000000001</v>
       </c>
       <c r="P23" s="1">
-        <v>1.261</v>
+        <v>1.104</v>
       </c>
       <c r="Q23" s="1">
-        <v>1.37</v>
+        <v>1.198</v>
       </c>
       <c r="R23" s="1">
-        <v>1.32</v>
+        <v>1.136</v>
       </c>
       <c r="S23" s="1">
-        <v>1.12</v>
+        <v>0.971</v>
       </c>
       <c r="T23" s="1">
-        <v>0.862</v>
+        <v>0.75</v>
       </c>
       <c r="U23" s="1">
-        <v>0.593</v>
+        <v>0.535</v>
       </c>
     </row>
     <row r="24" spans="1:21">
@@ -2101,61 +2104,61 @@
         <v>-1.166</v>
       </c>
       <c r="C24" s="1">
-        <v>-1.102</v>
+        <v>-1.094</v>
       </c>
       <c r="D24" s="1">
-        <v>-0.9330000000000001</v>
+        <v>-0.9</v>
       </c>
       <c r="E24" s="1">
-        <v>-0.781</v>
+        <v>-0.731</v>
       </c>
       <c r="F24" s="1">
-        <v>-0.6870000000000001</v>
+        <v>-0.639</v>
       </c>
       <c r="G24" s="1">
-        <v>-0.549</v>
+        <v>-0.519</v>
       </c>
       <c r="H24" s="1">
-        <v>-0.286</v>
+        <v>-0.254</v>
       </c>
       <c r="I24" s="1">
-        <v>0.074</v>
+        <v>0.1</v>
       </c>
       <c r="J24" s="1">
-        <v>0.419</v>
+        <v>0.428</v>
       </c>
       <c r="K24" s="1">
-        <v>0.672</v>
+        <v>0.671</v>
       </c>
       <c r="L24" s="1">
-        <v>0.892</v>
+        <v>0.869</v>
       </c>
       <c r="M24" s="1">
-        <v>1.117</v>
+        <v>1.08</v>
       </c>
       <c r="N24" s="1">
-        <v>1.359</v>
+        <v>1.314</v>
       </c>
       <c r="O24" s="1">
-        <v>1.566</v>
+        <v>1.506</v>
       </c>
       <c r="P24" s="1">
-        <v>1.641</v>
+        <v>1.562</v>
       </c>
       <c r="Q24" s="1">
-        <v>1.537</v>
+        <v>1.467</v>
       </c>
       <c r="R24" s="1">
-        <v>1.289</v>
+        <v>1.232</v>
       </c>
       <c r="S24" s="1">
-        <v>0.965</v>
+        <v>0.926</v>
       </c>
       <c r="T24" s="1">
-        <v>0.615</v>
+        <v>0.608</v>
       </c>
       <c r="U24" s="1">
-        <v>0.3</v>
+        <v>0.343</v>
       </c>
     </row>
     <row r="25" spans="1:21">
@@ -2166,61 +2169,61 @@
         <v>-1.026</v>
       </c>
       <c r="C25" s="1">
-        <v>-0.917</v>
+        <v>-0.944</v>
       </c>
       <c r="D25" s="1">
-        <v>-0.748</v>
+        <v>-0.8</v>
       </c>
       <c r="E25" s="1">
-        <v>-0.614</v>
+        <v>-0.68</v>
       </c>
       <c r="F25" s="1">
-        <v>-0.446</v>
+        <v>-0.504</v>
       </c>
       <c r="G25" s="1">
-        <v>-0.153</v>
+        <v>-0.215</v>
       </c>
       <c r="H25" s="1">
-        <v>0.191</v>
+        <v>0.152</v>
       </c>
       <c r="I25" s="1">
-        <v>0.487</v>
+        <v>0.503</v>
       </c>
       <c r="J25" s="1">
-        <v>0.722</v>
+        <v>0.755</v>
       </c>
       <c r="K25" s="1">
-        <v>0.953</v>
+        <v>0.969</v>
       </c>
       <c r="L25" s="1">
-        <v>1.223</v>
+        <v>1.229</v>
       </c>
       <c r="M25" s="1">
-        <v>1.487</v>
+        <v>1.515</v>
       </c>
       <c r="N25" s="1">
-        <v>1.661</v>
+        <v>1.717</v>
       </c>
       <c r="O25" s="1">
-        <v>1.678</v>
+        <v>1.767</v>
       </c>
       <c r="P25" s="1">
-        <v>1.538</v>
+        <v>1.635</v>
       </c>
       <c r="Q25" s="1">
-        <v>1.252</v>
+        <v>1.346</v>
       </c>
       <c r="R25" s="1">
-        <v>0.888</v>
+        <v>0.982</v>
       </c>
       <c r="S25" s="1">
-        <v>0.521</v>
+        <v>0.605</v>
       </c>
       <c r="T25" s="1">
-        <v>0.187</v>
+        <v>0.285</v>
       </c>
       <c r="U25" s="1">
-        <v>-0.064</v>
+        <v>0.037</v>
       </c>
     </row>
     <row r="26" spans="1:21">
@@ -2231,61 +2234,61 @@
         <v>-0.848</v>
       </c>
       <c r="C26" s="1">
-        <v>-0.772</v>
+        <v>-0.755</v>
       </c>
       <c r="D26" s="1">
-        <v>-0.607</v>
+        <v>-0.619</v>
       </c>
       <c r="E26" s="1">
-        <v>-0.411</v>
+        <v>-0.429</v>
       </c>
       <c r="F26" s="1">
-        <v>-0.138</v>
+        <v>-0.135</v>
       </c>
       <c r="G26" s="1">
-        <v>0.174</v>
+        <v>0.19</v>
       </c>
       <c r="H26" s="1">
-        <v>0.44</v>
+        <v>0.491</v>
       </c>
       <c r="I26" s="1">
-        <v>0.659</v>
+        <v>0.744</v>
       </c>
       <c r="J26" s="1">
-        <v>0.858</v>
+        <v>0.98</v>
       </c>
       <c r="K26" s="1">
-        <v>1.074</v>
+        <v>1.246</v>
       </c>
       <c r="L26" s="1">
-        <v>1.301</v>
+        <v>1.502</v>
       </c>
       <c r="M26" s="1">
-        <v>1.477</v>
+        <v>1.693</v>
       </c>
       <c r="N26" s="1">
-        <v>1.535</v>
+        <v>1.737</v>
       </c>
       <c r="O26" s="1">
-        <v>1.417</v>
+        <v>1.615</v>
       </c>
       <c r="P26" s="1">
-        <v>1.163</v>
+        <v>1.359</v>
       </c>
       <c r="Q26" s="1">
-        <v>0.868</v>
+        <v>1.004</v>
       </c>
       <c r="R26" s="1">
-        <v>0.556</v>
+        <v>0.643</v>
       </c>
       <c r="S26" s="1">
-        <v>0.262</v>
+        <v>0.322</v>
       </c>
       <c r="T26" s="1">
-        <v>0.037</v>
+        <v>0.07199999999999999</v>
       </c>
       <c r="U26" s="1">
-        <v>-0.101</v>
+        <v>-0.08</v>
       </c>
     </row>
     <row r="27" spans="1:21">
@@ -2296,61 +2299,61 @@
         <v>-0.646</v>
       </c>
       <c r="C27" s="1">
-        <v>-0.543</v>
+        <v>-0.577</v>
       </c>
       <c r="D27" s="1">
-        <v>-0.344</v>
+        <v>-0.39</v>
       </c>
       <c r="E27" s="1">
-        <v>-0.096</v>
+        <v>-0.143</v>
       </c>
       <c r="F27" s="1">
-        <v>0.163</v>
+        <v>0.106</v>
       </c>
       <c r="G27" s="1">
-        <v>0.353</v>
+        <v>0.305</v>
       </c>
       <c r="H27" s="1">
-        <v>0.481</v>
+        <v>0.449</v>
       </c>
       <c r="I27" s="1">
-        <v>0.6</v>
+        <v>0.58</v>
       </c>
       <c r="J27" s="1">
-        <v>0.734</v>
+        <v>0.741</v>
       </c>
       <c r="K27" s="1">
-        <v>0.887</v>
+        <v>0.903</v>
       </c>
       <c r="L27" s="1">
-        <v>0.979</v>
+        <v>1.009</v>
       </c>
       <c r="M27" s="1">
-        <v>0.961</v>
+        <v>1.015</v>
       </c>
       <c r="N27" s="1">
-        <v>0.873</v>
+        <v>0.907</v>
       </c>
       <c r="O27" s="1">
-        <v>0.723</v>
+        <v>0.747</v>
       </c>
       <c r="P27" s="1">
-        <v>0.538</v>
+        <v>0.5659999999999999</v>
       </c>
       <c r="Q27" s="1">
-        <v>0.351</v>
+        <v>0.341</v>
       </c>
       <c r="R27" s="1">
-        <v>0.156</v>
+        <v>0.1</v>
       </c>
       <c r="S27" s="1">
-        <v>-0.01</v>
+        <v>-0.09</v>
       </c>
       <c r="T27" s="1">
-        <v>-0.127</v>
+        <v>-0.198</v>
       </c>
       <c r="U27" s="1">
-        <v>-0.188</v>
+        <v>-0.253</v>
       </c>
     </row>
     <row r="28" spans="1:21">
@@ -2361,61 +2364,61 @@
         <v>-0.262</v>
       </c>
       <c r="C28" s="1">
-        <v>-0.165</v>
+        <v>-0.174</v>
       </c>
       <c r="D28" s="1">
-        <v>0.045</v>
+        <v>0.049</v>
       </c>
       <c r="E28" s="1">
-        <v>0.288</v>
+        <v>0.268</v>
       </c>
       <c r="F28" s="1">
-        <v>0.5</v>
+        <v>0.45</v>
       </c>
       <c r="G28" s="1">
-        <v>0.646</v>
+        <v>0.592</v>
       </c>
       <c r="H28" s="1">
-        <v>0.764</v>
+        <v>0.714</v>
       </c>
       <c r="I28" s="1">
-        <v>0.88</v>
+        <v>0.871</v>
       </c>
       <c r="J28" s="1">
-        <v>1.007</v>
+        <v>1.019</v>
       </c>
       <c r="K28" s="1">
-        <v>1.09</v>
+        <v>1.097</v>
       </c>
       <c r="L28" s="1">
-        <v>1.038</v>
+        <v>1.079</v>
       </c>
       <c r="M28" s="1">
-        <v>0.881</v>
+        <v>0.971</v>
       </c>
       <c r="N28" s="1">
-        <v>0.6840000000000001</v>
+        <v>0.783</v>
       </c>
       <c r="O28" s="1">
-        <v>0.46</v>
+        <v>0.553</v>
       </c>
       <c r="P28" s="1">
-        <v>0.218</v>
+        <v>0.272</v>
       </c>
       <c r="Q28" s="1">
-        <v>-0.065</v>
+        <v>-0.003</v>
       </c>
       <c r="R28" s="1">
-        <v>-0.31</v>
+        <v>-0.233</v>
       </c>
       <c r="S28" s="1">
-        <v>-0.468</v>
+        <v>-0.37</v>
       </c>
       <c r="T28" s="1">
-        <v>-0.555</v>
+        <v>-0.431</v>
       </c>
       <c r="U28" s="1">
-        <v>-0.623</v>
+        <v>-0.518</v>
       </c>
     </row>
     <row r="29" spans="1:21">
@@ -2426,61 +2429,61 @@
         <v>-0.299</v>
       </c>
       <c r="C29" s="1">
-        <v>-0.18</v>
+        <v>-0.152</v>
       </c>
       <c r="D29" s="1">
-        <v>0.053</v>
+        <v>0.097</v>
       </c>
       <c r="E29" s="1">
-        <v>0.299</v>
+        <v>0.331</v>
       </c>
       <c r="F29" s="1">
-        <v>0.503</v>
+        <v>0.528</v>
       </c>
       <c r="G29" s="1">
-        <v>0.664</v>
+        <v>0.678</v>
       </c>
       <c r="H29" s="1">
-        <v>0.774</v>
+        <v>0.8070000000000001</v>
       </c>
       <c r="I29" s="1">
-        <v>0.85</v>
+        <v>0.891</v>
       </c>
       <c r="J29" s="1">
-        <v>0.883</v>
+        <v>0.914</v>
       </c>
       <c r="K29" s="1">
-        <v>0.826</v>
+        <v>0.857</v>
       </c>
       <c r="L29" s="1">
-        <v>0.699</v>
+        <v>0.754</v>
       </c>
       <c r="M29" s="1">
-        <v>0.531</v>
+        <v>0.605</v>
       </c>
       <c r="N29" s="1">
-        <v>0.334</v>
+        <v>0.405</v>
       </c>
       <c r="O29" s="1">
-        <v>0.1</v>
+        <v>0.162</v>
       </c>
       <c r="P29" s="1">
-        <v>-0.176</v>
+        <v>-0.138</v>
       </c>
       <c r="Q29" s="1">
-        <v>-0.419</v>
+        <v>-0.394</v>
       </c>
       <c r="R29" s="1">
-        <v>-0.581</v>
+        <v>-0.546</v>
       </c>
       <c r="S29" s="1">
-        <v>-0.68</v>
+        <v>-0.605</v>
       </c>
       <c r="T29" s="1">
-        <v>-0.757</v>
+        <v>-0.66</v>
       </c>
       <c r="U29" s="1">
-        <v>-0.875</v>
+        <v>-0.772</v>
       </c>
     </row>
     <row r="30" spans="1:21">
@@ -2491,61 +2494,61 @@
         <v>0.07099999999999999</v>
       </c>
       <c r="C30" s="1">
-        <v>0.197</v>
+        <v>0.202</v>
       </c>
       <c r="D30" s="1">
-        <v>0.365</v>
+        <v>0.386</v>
       </c>
       <c r="E30" s="1">
-        <v>0.471</v>
+        <v>0.499</v>
       </c>
       <c r="F30" s="1">
-        <v>0.551</v>
+        <v>0.576</v>
       </c>
       <c r="G30" s="1">
-        <v>0.611</v>
+        <v>0.651</v>
       </c>
       <c r="H30" s="1">
-        <v>0.657</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="I30" s="1">
-        <v>0.648</v>
+        <v>0.6840000000000001</v>
       </c>
       <c r="J30" s="1">
-        <v>0.571</v>
+        <v>0.64</v>
       </c>
       <c r="K30" s="1">
-        <v>0.447</v>
+        <v>0.538</v>
       </c>
       <c r="L30" s="1">
-        <v>0.331</v>
+        <v>0.402</v>
       </c>
       <c r="M30" s="1">
-        <v>0.21</v>
+        <v>0.249</v>
       </c>
       <c r="N30" s="1">
-        <v>0.04</v>
+        <v>0.078</v>
       </c>
       <c r="O30" s="1">
-        <v>-0.184</v>
+        <v>-0.129</v>
       </c>
       <c r="P30" s="1">
-        <v>-0.402</v>
+        <v>-0.326</v>
       </c>
       <c r="Q30" s="1">
-        <v>-0.5659999999999999</v>
+        <v>-0.475</v>
       </c>
       <c r="R30" s="1">
-        <v>-0.668</v>
+        <v>-0.573</v>
       </c>
       <c r="S30" s="1">
-        <v>-0.767</v>
+        <v>-0.648</v>
       </c>
       <c r="T30" s="1">
-        <v>-0.888</v>
+        <v>-0.753</v>
       </c>
       <c r="U30" s="1">
-        <v>-0.994</v>
+        <v>-0.853</v>
       </c>
     </row>
     <row r="31" spans="1:21">
@@ -2556,61 +2559,61 @@
         <v>0.378</v>
       </c>
       <c r="C31" s="1">
-        <v>0.515</v>
+        <v>0.527</v>
       </c>
       <c r="D31" s="1">
-        <v>0.707</v>
+        <v>0.717</v>
       </c>
       <c r="E31" s="1">
-        <v>0.857</v>
+        <v>0.832</v>
       </c>
       <c r="F31" s="1">
-        <v>0.958</v>
+        <v>0.931</v>
       </c>
       <c r="G31" s="1">
-        <v>1.042</v>
+        <v>1.021</v>
       </c>
       <c r="H31" s="1">
-        <v>1.091</v>
+        <v>1.071</v>
       </c>
       <c r="I31" s="1">
-        <v>1.021</v>
+        <v>1.03</v>
       </c>
       <c r="J31" s="1">
-        <v>0.86</v>
+        <v>0.891</v>
       </c>
       <c r="K31" s="1">
-        <v>0.661</v>
+        <v>0.6860000000000001</v>
       </c>
       <c r="L31" s="1">
-        <v>0.413</v>
+        <v>0.446</v>
       </c>
       <c r="M31" s="1">
-        <v>0.08799999999999999</v>
+        <v>0.163</v>
       </c>
       <c r="N31" s="1">
-        <v>-0.281</v>
+        <v>-0.17</v>
       </c>
       <c r="O31" s="1">
-        <v>-0.574</v>
+        <v>-0.463</v>
       </c>
       <c r="P31" s="1">
-        <v>-0.77</v>
+        <v>-0.653</v>
       </c>
       <c r="Q31" s="1">
-        <v>-0.891</v>
+        <v>-0.781</v>
       </c>
       <c r="R31" s="1">
-        <v>-1.008</v>
+        <v>-0.888</v>
       </c>
       <c r="S31" s="1">
-        <v>-1.201</v>
+        <v>-1.025</v>
       </c>
       <c r="T31" s="1">
-        <v>-1.377</v>
+        <v>-1.159</v>
       </c>
       <c r="U31" s="1">
-        <v>-1.373</v>
+        <v>-1.15</v>
       </c>
     </row>
     <row r="32" spans="1:21">
@@ -2621,61 +2624,61 @@
         <v>0.501</v>
       </c>
       <c r="C32" s="1">
-        <v>0.597</v>
+        <v>0.584</v>
       </c>
       <c r="D32" s="1">
-        <v>0.754</v>
+        <v>0.726</v>
       </c>
       <c r="E32" s="1">
-        <v>0.865</v>
+        <v>0.838</v>
       </c>
       <c r="F32" s="1">
-        <v>0.913</v>
+        <v>0.899</v>
       </c>
       <c r="G32" s="1">
-        <v>0.893</v>
+        <v>0.912</v>
       </c>
       <c r="H32" s="1">
-        <v>0.764</v>
+        <v>0.829</v>
       </c>
       <c r="I32" s="1">
-        <v>0.599</v>
+        <v>0.653</v>
       </c>
       <c r="J32" s="1">
-        <v>0.431</v>
+        <v>0.48</v>
       </c>
       <c r="K32" s="1">
-        <v>0.236</v>
+        <v>0.314</v>
       </c>
       <c r="L32" s="1">
-        <v>-0.018</v>
+        <v>0.062</v>
       </c>
       <c r="M32" s="1">
-        <v>-0.335</v>
+        <v>-0.259</v>
       </c>
       <c r="N32" s="1">
-        <v>-0.614</v>
+        <v>-0.538</v>
       </c>
       <c r="O32" s="1">
-        <v>-0.785</v>
+        <v>-0.697</v>
       </c>
       <c r="P32" s="1">
-        <v>-0.897</v>
+        <v>-0.782</v>
       </c>
       <c r="Q32" s="1">
-        <v>-0.999</v>
+        <v>-0.904</v>
       </c>
       <c r="R32" s="1">
-        <v>-1.169</v>
+        <v>-1.095</v>
       </c>
       <c r="S32" s="1">
-        <v>-1.346</v>
+        <v>-1.26</v>
       </c>
       <c r="T32" s="1">
-        <v>-1.339</v>
+        <v>-1.261</v>
       </c>
       <c r="U32" s="1">
-        <v>-1.153</v>
+        <v>-1.072</v>
       </c>
     </row>
     <row r="33" spans="1:21">
@@ -2686,61 +2689,61 @@
         <v>0.785</v>
       </c>
       <c r="C33" s="1">
-        <v>0.889</v>
+        <v>0.874</v>
       </c>
       <c r="D33" s="1">
-        <v>1.036</v>
+        <v>1.018</v>
       </c>
       <c r="E33" s="1">
-        <v>1.12</v>
+        <v>1.121</v>
       </c>
       <c r="F33" s="1">
-        <v>1.128</v>
+        <v>1.138</v>
       </c>
       <c r="G33" s="1">
-        <v>1.023</v>
+        <v>1.039</v>
       </c>
       <c r="H33" s="1">
-        <v>0.836</v>
+        <v>0.865</v>
       </c>
       <c r="I33" s="1">
-        <v>0.619</v>
+        <v>0.649</v>
       </c>
       <c r="J33" s="1">
-        <v>0.373</v>
+        <v>0.374</v>
       </c>
       <c r="K33" s="1">
-        <v>0.047</v>
+        <v>0.023</v>
       </c>
       <c r="L33" s="1">
-        <v>-0.326</v>
+        <v>-0.358</v>
       </c>
       <c r="M33" s="1">
-        <v>-0.636</v>
+        <v>-0.6840000000000001</v>
       </c>
       <c r="N33" s="1">
-        <v>-0.793</v>
+        <v>-0.877</v>
       </c>
       <c r="O33" s="1">
-        <v>-0.868</v>
+        <v>-0.971</v>
       </c>
       <c r="P33" s="1">
-        <v>-0.977</v>
+        <v>-1.076</v>
       </c>
       <c r="Q33" s="1">
-        <v>-1.16</v>
+        <v>-1.254</v>
       </c>
       <c r="R33" s="1">
-        <v>-1.35</v>
+        <v>-1.44</v>
       </c>
       <c r="S33" s="1">
-        <v>-1.377</v>
+        <v>-1.452</v>
       </c>
       <c r="T33" s="1">
-        <v>-1.215</v>
+        <v>-1.264</v>
       </c>
       <c r="U33" s="1">
-        <v>-1</v>
+        <v>-1.02</v>
       </c>
     </row>
     <row r="34" spans="1:21">
@@ -2751,61 +2754,61 @@
         <v>1.057</v>
       </c>
       <c r="C34" s="1">
-        <v>1.141</v>
+        <v>1.142</v>
       </c>
       <c r="D34" s="1">
-        <v>1.245</v>
+        <v>1.259</v>
       </c>
       <c r="E34" s="1">
-        <v>1.244</v>
+        <v>1.279</v>
       </c>
       <c r="F34" s="1">
-        <v>1.13</v>
+        <v>1.162</v>
       </c>
       <c r="G34" s="1">
-        <v>0.9379999999999999</v>
+        <v>0.948</v>
       </c>
       <c r="H34" s="1">
-        <v>0.706</v>
+        <v>0.704</v>
       </c>
       <c r="I34" s="1">
-        <v>0.43</v>
+        <v>0.422</v>
       </c>
       <c r="J34" s="1">
         <v>0.08</v>
       </c>
       <c r="K34" s="1">
-        <v>-0.343</v>
+        <v>-0.312</v>
       </c>
       <c r="L34" s="1">
-        <v>-0.695</v>
+        <v>-0.664</v>
       </c>
       <c r="M34" s="1">
-        <v>-0.889</v>
+        <v>-0.897</v>
       </c>
       <c r="N34" s="1">
-        <v>-0.997</v>
+        <v>-1.01</v>
       </c>
       <c r="O34" s="1">
-        <v>-1.124</v>
+        <v>-1.109</v>
       </c>
       <c r="P34" s="1">
-        <v>-1.314</v>
+        <v>-1.279</v>
       </c>
       <c r="Q34" s="1">
-        <v>-1.492</v>
+        <v>-1.456</v>
       </c>
       <c r="R34" s="1">
-        <v>-1.486</v>
+        <v>-1.454</v>
       </c>
       <c r="S34" s="1">
-        <v>-1.278</v>
+        <v>-1.253</v>
       </c>
       <c r="T34" s="1">
-        <v>-1.014</v>
+        <v>-1.011</v>
       </c>
       <c r="U34" s="1">
-        <v>-0.803</v>
+        <v>-0.837</v>
       </c>
     </row>
     <row r="35" spans="1:21">
@@ -2816,61 +2819,61 @@
         <v>1.079</v>
       </c>
       <c r="C35" s="1">
-        <v>1.158</v>
+        <v>1.171</v>
       </c>
       <c r="D35" s="1">
-        <v>1.232</v>
+        <v>1.25</v>
       </c>
       <c r="E35" s="1">
-        <v>1.156</v>
+        <v>1.203</v>
       </c>
       <c r="F35" s="1">
-        <v>0.972</v>
+        <v>1.047</v>
       </c>
       <c r="G35" s="1">
-        <v>0.725</v>
+        <v>0.8149999999999999</v>
       </c>
       <c r="H35" s="1">
-        <v>0.466</v>
+        <v>0.54</v>
       </c>
       <c r="I35" s="1">
-        <v>0.16</v>
+        <v>0.17</v>
       </c>
       <c r="J35" s="1">
-        <v>-0.196</v>
+        <v>-0.237</v>
       </c>
       <c r="K35" s="1">
-        <v>-0.518</v>
+        <v>-0.572</v>
       </c>
       <c r="L35" s="1">
-        <v>-0.726</v>
+        <v>-0.783</v>
       </c>
       <c r="M35" s="1">
-        <v>-0.839</v>
+        <v>-0.906</v>
       </c>
       <c r="N35" s="1">
-        <v>-0.9370000000000001</v>
+        <v>-1.009</v>
       </c>
       <c r="O35" s="1">
-        <v>-1.102</v>
+        <v>-1.162</v>
       </c>
       <c r="P35" s="1">
-        <v>-1.269</v>
+        <v>-1.326</v>
       </c>
       <c r="Q35" s="1">
-        <v>-1.267</v>
+        <v>-1.337</v>
       </c>
       <c r="R35" s="1">
-        <v>-1.092</v>
+        <v>-1.163</v>
       </c>
       <c r="S35" s="1">
-        <v>-0.871</v>
+        <v>-0.9340000000000001</v>
       </c>
       <c r="T35" s="1">
-        <v>-0.715</v>
+        <v>-0.763</v>
       </c>
       <c r="U35" s="1">
-        <v>-0.626</v>
+        <v>-0.649</v>
       </c>
     </row>
     <row r="36" spans="1:21">
@@ -2881,61 +2884,61 @@
         <v>1.339</v>
       </c>
       <c r="C36" s="1">
-        <v>1.308</v>
+        <v>1.303</v>
       </c>
       <c r="D36" s="1">
-        <v>1.168</v>
+        <v>1.163</v>
       </c>
       <c r="E36" s="1">
-        <v>0.9370000000000001</v>
+        <v>0.951</v>
       </c>
       <c r="F36" s="1">
-        <v>0.696</v>
+        <v>0.708</v>
       </c>
       <c r="G36" s="1">
-        <v>0.412</v>
+        <v>0.411</v>
       </c>
       <c r="H36" s="1">
-        <v>0.043</v>
+        <v>0.037</v>
       </c>
       <c r="I36" s="1">
-        <v>-0.337</v>
+        <v>-0.349</v>
       </c>
       <c r="J36" s="1">
-        <v>-0.655</v>
+        <v>-0.653</v>
       </c>
       <c r="K36" s="1">
-        <v>-0.846</v>
+        <v>-0.839</v>
       </c>
       <c r="L36" s="1">
-        <v>-0.9370000000000001</v>
+        <v>-0.965</v>
       </c>
       <c r="M36" s="1">
-        <v>-1.043</v>
+        <v>-1.08</v>
       </c>
       <c r="N36" s="1">
-        <v>-1.21</v>
+        <v>-1.249</v>
       </c>
       <c r="O36" s="1">
-        <v>-1.353</v>
+        <v>-1.394</v>
       </c>
       <c r="P36" s="1">
-        <v>-1.346</v>
+        <v>-1.368</v>
       </c>
       <c r="Q36" s="1">
-        <v>-1.165</v>
+        <v>-1.186</v>
       </c>
       <c r="R36" s="1">
-        <v>-0.925</v>
+        <v>-0.967</v>
       </c>
       <c r="S36" s="1">
-        <v>-0.739</v>
+        <v>-0.775</v>
       </c>
       <c r="T36" s="1">
-        <v>-0.621</v>
+        <v>-0.644</v>
       </c>
       <c r="U36" s="1">
-        <v>-0.5639999999999999</v>
+        <v>-0.575</v>
       </c>
     </row>
     <row r="37" spans="1:21">
@@ -2946,61 +2949,61 @@
         <v>1.432</v>
       </c>
       <c r="C37" s="1">
-        <v>1.323</v>
+        <v>1.325</v>
       </c>
       <c r="D37" s="1">
-        <v>1.059</v>
+        <v>1.087</v>
       </c>
       <c r="E37" s="1">
-        <v>0.773</v>
+        <v>0.788</v>
       </c>
       <c r="F37" s="1">
-        <v>0.418</v>
+        <v>0.434</v>
       </c>
       <c r="G37" s="1">
-        <v>-0.02</v>
+        <v>0.029</v>
       </c>
       <c r="H37" s="1">
-        <v>-0.477</v>
+        <v>-0.431</v>
       </c>
       <c r="I37" s="1">
-        <v>-0.848</v>
+        <v>-0.841</v>
       </c>
       <c r="J37" s="1">
-        <v>-1.063</v>
+        <v>-1.068</v>
       </c>
       <c r="K37" s="1">
-        <v>-1.174</v>
+        <v>-1.179</v>
       </c>
       <c r="L37" s="1">
-        <v>-1.3</v>
+        <v>-1.292</v>
       </c>
       <c r="M37" s="1">
-        <v>-1.514</v>
+        <v>-1.506</v>
       </c>
       <c r="N37" s="1">
         <v>-1.736</v>
       </c>
       <c r="O37" s="1">
-        <v>-1.736</v>
+        <v>-1.726</v>
       </c>
       <c r="P37" s="1">
-        <v>-1.502</v>
+        <v>-1.496</v>
       </c>
       <c r="Q37" s="1">
-        <v>-1.214</v>
+        <v>-1.223</v>
       </c>
       <c r="R37" s="1">
-        <v>-1.001</v>
+        <v>-0.989</v>
       </c>
       <c r="S37" s="1">
-        <v>-0.836</v>
+        <v>-0.826</v>
       </c>
       <c r="T37" s="1">
-        <v>-0.724</v>
+        <v>-0.714</v>
       </c>
       <c r="U37" s="1">
-        <v>-0.6860000000000001</v>
+        <v>-0.639</v>
       </c>
     </row>
     <row r="38" spans="1:21">
@@ -3011,61 +3014,61 @@
         <v>1.107</v>
       </c>
       <c r="C38" s="1">
-        <v>0.997</v>
+        <v>1.02</v>
       </c>
       <c r="D38" s="1">
-        <v>0.738</v>
+        <v>0.767</v>
       </c>
       <c r="E38" s="1">
-        <v>0.388</v>
+        <v>0.419</v>
       </c>
       <c r="F38" s="1">
-        <v>-0.006</v>
+        <v>-0.007</v>
       </c>
       <c r="G38" s="1">
-        <v>-0.418</v>
+        <v>-0.442</v>
       </c>
       <c r="H38" s="1">
-        <v>-0.776</v>
+        <v>-0.785</v>
       </c>
       <c r="I38" s="1">
-        <v>-0.979</v>
+        <v>-0.999</v>
       </c>
       <c r="J38" s="1">
-        <v>-1.077</v>
+        <v>-1.127</v>
       </c>
       <c r="K38" s="1">
-        <v>-1.191</v>
+        <v>-1.249</v>
       </c>
       <c r="L38" s="1">
-        <v>-1.383</v>
+        <v>-1.438</v>
       </c>
       <c r="M38" s="1">
-        <v>-1.569</v>
+        <v>-1.645</v>
       </c>
       <c r="N38" s="1">
-        <v>-1.56</v>
+        <v>-1.632</v>
       </c>
       <c r="O38" s="1">
-        <v>-1.33</v>
+        <v>-1.381</v>
       </c>
       <c r="P38" s="1">
-        <v>-1.054</v>
+        <v>-1.108</v>
       </c>
       <c r="Q38" s="1">
-        <v>-0.855</v>
+        <v>-0.916</v>
       </c>
       <c r="R38" s="1">
-        <v>-0.74</v>
+        <v>-0.778</v>
       </c>
       <c r="S38" s="1">
-        <v>-0.68</v>
+        <v>-0.6889999999999999</v>
       </c>
       <c r="T38" s="1">
-        <v>-0.639</v>
+        <v>-0.653</v>
       </c>
       <c r="U38" s="1">
-        <v>-0.607</v>
+        <v>-0.653</v>
       </c>
     </row>
     <row r="39" spans="1:21">
@@ -3079,58 +3082,58 @@
         <v>0.771</v>
       </c>
       <c r="D39" s="1">
-        <v>0.457</v>
+        <v>0.464</v>
       </c>
       <c r="E39" s="1">
-        <v>0.045</v>
+        <v>0.06</v>
       </c>
       <c r="F39" s="1">
-        <v>-0.434</v>
+        <v>-0.404</v>
       </c>
       <c r="G39" s="1">
-        <v>-0.837</v>
+        <v>-0.8080000000000001</v>
       </c>
       <c r="H39" s="1">
-        <v>-1.069</v>
+        <v>-1.059</v>
       </c>
       <c r="I39" s="1">
-        <v>-1.185</v>
+        <v>-1.18</v>
       </c>
       <c r="J39" s="1">
-        <v>-1.287</v>
+        <v>-1.304</v>
       </c>
       <c r="K39" s="1">
-        <v>-1.466</v>
+        <v>-1.501</v>
       </c>
       <c r="L39" s="1">
-        <v>-1.657</v>
+        <v>-1.673</v>
       </c>
       <c r="M39" s="1">
-        <v>-1.643</v>
+        <v>-1.648</v>
       </c>
       <c r="N39" s="1">
-        <v>-1.395</v>
+        <v>-1.423</v>
       </c>
       <c r="O39" s="1">
-        <v>-1.125</v>
+        <v>-1.152</v>
       </c>
       <c r="P39" s="1">
-        <v>-0.917</v>
+        <v>-0.954</v>
       </c>
       <c r="Q39" s="1">
-        <v>-0.794</v>
+        <v>-0.844</v>
       </c>
       <c r="R39" s="1">
-        <v>-0.734</v>
+        <v>-0.771</v>
       </c>
       <c r="S39" s="1">
-        <v>-0.724</v>
+        <v>-0.725</v>
       </c>
       <c r="T39" s="1">
-        <v>-0.752</v>
+        <v>-0.723</v>
       </c>
       <c r="U39" s="1">
-        <v>-0.8120000000000001</v>
+        <v>-0.764</v>
       </c>
     </row>
     <row r="40" spans="1:21">
@@ -3141,61 +3144,61 @@
         <v>0.713</v>
       </c>
       <c r="C40" s="1">
-        <v>0.527</v>
+        <v>0.524</v>
       </c>
       <c r="D40" s="1">
-        <v>0.128</v>
+        <v>0.123</v>
       </c>
       <c r="E40" s="1">
         <v>-0.335</v>
       </c>
       <c r="F40" s="1">
-        <v>-0.729</v>
+        <v>-0.722</v>
       </c>
       <c r="G40" s="1">
-        <v>-0.962</v>
+        <v>-0.959</v>
       </c>
       <c r="H40" s="1">
-        <v>-1.081</v>
+        <v>-1.07</v>
       </c>
       <c r="I40" s="1">
-        <v>-1.173</v>
+        <v>-1.198</v>
       </c>
       <c r="J40" s="1">
-        <v>-1.348</v>
+        <v>-1.407</v>
       </c>
       <c r="K40" s="1">
-        <v>-1.547</v>
+        <v>-1.602</v>
       </c>
       <c r="L40" s="1">
-        <v>-1.541</v>
+        <v>-1.595</v>
       </c>
       <c r="M40" s="1">
-        <v>-1.319</v>
+        <v>-1.366</v>
       </c>
       <c r="N40" s="1">
-        <v>-1.053</v>
+        <v>-1.089</v>
       </c>
       <c r="O40" s="1">
-        <v>-0.868</v>
+        <v>-0.879</v>
       </c>
       <c r="P40" s="1">
-        <v>-0.794</v>
+        <v>-0.786</v>
       </c>
       <c r="Q40" s="1">
-        <v>-0.798</v>
+        <v>-0.757</v>
       </c>
       <c r="R40" s="1">
-        <v>-0.825</v>
+        <v>-0.734</v>
       </c>
       <c r="S40" s="1">
-        <v>-0.871</v>
+        <v>-0.732</v>
       </c>
       <c r="T40" s="1">
-        <v>-0.9429999999999999</v>
+        <v>-0.753</v>
       </c>
       <c r="U40" s="1">
-        <v>-1.043</v>
+        <v>-0.8110000000000001</v>
       </c>
     </row>
     <row r="41" spans="1:21">
@@ -3206,61 +3209,61 @@
         <v>0.257</v>
       </c>
       <c r="C41" s="1">
-        <v>0.054</v>
+        <v>0.051</v>
       </c>
       <c r="D41" s="1">
-        <v>-0.326</v>
+        <v>-0.333</v>
       </c>
       <c r="E41" s="1">
-        <v>-0.656</v>
+        <v>-0.673</v>
       </c>
       <c r="F41" s="1">
-        <v>-0.85</v>
+        <v>-0.869</v>
       </c>
       <c r="G41" s="1">
-        <v>-0.97</v>
+        <v>-0.968</v>
       </c>
       <c r="H41" s="1">
-        <v>-1.09</v>
+        <v>-1.069</v>
       </c>
       <c r="I41" s="1">
-        <v>-1.263</v>
+        <v>-1.243</v>
       </c>
       <c r="J41" s="1">
-        <v>-1.425</v>
+        <v>-1.406</v>
       </c>
       <c r="K41" s="1">
-        <v>-1.408</v>
+        <v>-1.397</v>
       </c>
       <c r="L41" s="1">
-        <v>-1.197</v>
+        <v>-1.208</v>
       </c>
       <c r="M41" s="1">
-        <v>-0.95</v>
+        <v>-0.987</v>
       </c>
       <c r="N41" s="1">
-        <v>-0.767</v>
+        <v>-0.829</v>
       </c>
       <c r="O41" s="1">
+        <v>-0.73</v>
+      </c>
+      <c r="P41" s="1">
         <v>-0.678</v>
       </c>
-      <c r="P41" s="1">
-        <v>-0.659</v>
-      </c>
       <c r="Q41" s="1">
-        <v>-0.67</v>
+        <v>-0.681</v>
       </c>
       <c r="R41" s="1">
-        <v>-0.7</v>
+        <v>-0.708</v>
       </c>
       <c r="S41" s="1">
-        <v>-0.755</v>
+        <v>-0.76</v>
       </c>
       <c r="T41" s="1">
-        <v>-0.857</v>
+        <v>-0.869</v>
       </c>
       <c r="U41" s="1">
-        <v>-0.989</v>
+        <v>-1.012</v>
       </c>
     </row>
     <row r="42" spans="1:21">
@@ -3271,61 +3274,61 @@
         <v>-0.42</v>
       </c>
       <c r="C42" s="1">
-        <v>-0.624</v>
+        <v>-0.61</v>
       </c>
       <c r="D42" s="1">
-        <v>-0.926</v>
+        <v>-0.887</v>
       </c>
       <c r="E42" s="1">
-        <v>-1.118</v>
+        <v>-1.068</v>
       </c>
       <c r="F42" s="1">
-        <v>-1.22</v>
+        <v>-1.184</v>
       </c>
       <c r="G42" s="1">
-        <v>-1.331</v>
+        <v>-1.337</v>
       </c>
       <c r="H42" s="1">
-        <v>-1.519</v>
+        <v>-1.532</v>
       </c>
       <c r="I42" s="1">
-        <v>-1.685</v>
+        <v>-1.665</v>
       </c>
       <c r="J42" s="1">
-        <v>-1.632</v>
+        <v>-1.601</v>
       </c>
       <c r="K42" s="1">
-        <v>-1.391</v>
+        <v>-1.36</v>
       </c>
       <c r="L42" s="1">
-        <v>-1.148</v>
+        <v>-1.128</v>
       </c>
       <c r="M42" s="1">
-        <v>-0.975</v>
+        <v>-0.959</v>
       </c>
       <c r="N42" s="1">
-        <v>-0.84</v>
+        <v>-0.825</v>
       </c>
       <c r="O42" s="1">
-        <v>-0.735</v>
+        <v>-0.712</v>
       </c>
       <c r="P42" s="1">
-        <v>-0.68</v>
+        <v>-0.652</v>
       </c>
       <c r="Q42" s="1">
-        <v>-0.665</v>
+        <v>-0.648</v>
       </c>
       <c r="R42" s="1">
-        <v>-0.704</v>
+        <v>-0.678</v>
       </c>
       <c r="S42" s="1">
-        <v>-0.8080000000000001</v>
+        <v>-0.771</v>
       </c>
       <c r="T42" s="1">
-        <v>-0.9340000000000001</v>
+        <v>-0.898</v>
       </c>
       <c r="U42" s="1">
-        <v>-0.994</v>
+        <v>-0.9320000000000001</v>
       </c>
     </row>
     <row r="43" spans="1:21">
@@ -3336,61 +3339,61 @@
         <v>-0.289</v>
       </c>
       <c r="C43" s="1">
-        <v>-0.431</v>
+        <v>-0.435</v>
       </c>
       <c r="D43" s="1">
-        <v>-0.617</v>
+        <v>-0.63</v>
       </c>
       <c r="E43" s="1">
-        <v>-0.737</v>
+        <v>-0.735</v>
       </c>
       <c r="F43" s="1">
-        <v>-0.878</v>
+        <v>-0.835</v>
       </c>
       <c r="G43" s="1">
-        <v>-1.013</v>
+        <v>-0.965</v>
       </c>
       <c r="H43" s="1">
-        <v>-1.088</v>
+        <v>-1.073</v>
       </c>
       <c r="I43" s="1">
-        <v>-1.036</v>
+        <v>-1.043</v>
       </c>
       <c r="J43" s="1">
-        <v>-0.871</v>
+        <v>-0.862</v>
       </c>
       <c r="K43" s="1">
-        <v>-0.674</v>
+        <v>-0.701</v>
       </c>
       <c r="L43" s="1">
-        <v>-0.54</v>
+        <v>-0.616</v>
       </c>
       <c r="M43" s="1">
-        <v>-0.5</v>
+        <v>-0.574</v>
       </c>
       <c r="N43" s="1">
-        <v>-0.507</v>
+        <v>-0.58</v>
       </c>
       <c r="O43" s="1">
-        <v>-0.542</v>
+        <v>-0.614</v>
       </c>
       <c r="P43" s="1">
-        <v>-0.5659999999999999</v>
+        <v>-0.646</v>
       </c>
       <c r="Q43" s="1">
-        <v>-0.612</v>
+        <v>-0.697</v>
       </c>
       <c r="R43" s="1">
-        <v>-0.6860000000000001</v>
+        <v>-0.788</v>
       </c>
       <c r="S43" s="1">
-        <v>-0.768</v>
+        <v>-0.901</v>
       </c>
       <c r="T43" s="1">
-        <v>-0.819</v>
+        <v>-0.978</v>
       </c>
       <c r="U43" s="1">
-        <v>-0.774</v>
+        <v>-0.928</v>
       </c>
     </row>
     <row r="44" spans="1:21">
@@ -3401,61 +3404,61 @@
         <v>-0.374</v>
       </c>
       <c r="C44" s="1">
-        <v>-0.439</v>
+        <v>-0.414</v>
       </c>
       <c r="D44" s="1">
-        <v>-0.542</v>
+        <v>-0.493</v>
       </c>
       <c r="E44" s="1">
-        <v>-0.659</v>
+        <v>-0.59</v>
       </c>
       <c r="F44" s="1">
-        <v>-0.777</v>
+        <v>-0.706</v>
       </c>
       <c r="G44" s="1">
-        <v>-0.848</v>
+        <v>-0.793</v>
       </c>
       <c r="H44" s="1">
-        <v>-0.793</v>
+        <v>-0.753</v>
       </c>
       <c r="I44" s="1">
-        <v>-0.647</v>
+        <v>-0.611</v>
       </c>
       <c r="J44" s="1">
-        <v>-0.517</v>
+        <v>-0.48</v>
       </c>
       <c r="K44" s="1">
-        <v>-0.463</v>
+        <v>-0.437</v>
       </c>
       <c r="L44" s="1">
-        <v>-0.476</v>
+        <v>-0.456</v>
       </c>
       <c r="M44" s="1">
-        <v>-0.51</v>
+        <v>-0.487</v>
       </c>
       <c r="N44" s="1">
-        <v>-0.547</v>
+        <v>-0.513</v>
       </c>
       <c r="O44" s="1">
-        <v>-0.584</v>
+        <v>-0.512</v>
       </c>
       <c r="P44" s="1">
-        <v>-0.66</v>
+        <v>-0.532</v>
       </c>
       <c r="Q44" s="1">
-        <v>-0.755</v>
+        <v>-0.612</v>
       </c>
       <c r="R44" s="1">
-        <v>-0.847</v>
+        <v>-0.711</v>
       </c>
       <c r="S44" s="1">
-        <v>-0.902</v>
+        <v>-0.753</v>
       </c>
       <c r="T44" s="1">
-        <v>-0.834</v>
+        <v>-0.6899999999999999</v>
       </c>
       <c r="U44" s="1">
-        <v>-0.6929999999999999</v>
+        <v>-0.588</v>
       </c>
     </row>
     <row r="45" spans="1:21">
@@ -3466,61 +3469,61 @@
         <v>-0.515</v>
       </c>
       <c r="C45" s="1">
-        <v>-0.5600000000000001</v>
+        <v>-0.5649999999999999</v>
       </c>
       <c r="D45" s="1">
-        <v>-0.66</v>
+        <v>-0.659</v>
       </c>
       <c r="E45" s="1">
-        <v>-0.774</v>
+        <v>-0.786</v>
       </c>
       <c r="F45" s="1">
-        <v>-0.868</v>
+        <v>-0.89</v>
       </c>
       <c r="G45" s="1">
-        <v>-0.854</v>
+        <v>-0.852</v>
       </c>
       <c r="H45" s="1">
-        <v>-0.72</v>
+        <v>-0.7</v>
       </c>
       <c r="I45" s="1">
-        <v>-0.5649999999999999</v>
+        <v>-0.586</v>
       </c>
       <c r="J45" s="1">
-        <v>-0.498</v>
+        <v>-0.537</v>
       </c>
       <c r="K45" s="1">
-        <v>-0.54</v>
+        <v>-0.538</v>
       </c>
       <c r="L45" s="1">
-        <v>-0.603</v>
+        <v>-0.585</v>
       </c>
       <c r="M45" s="1">
-        <v>-0.649</v>
+        <v>-0.631</v>
       </c>
       <c r="N45" s="1">
-        <v>-0.704</v>
+        <v>-0.668</v>
       </c>
       <c r="O45" s="1">
-        <v>-0.761</v>
+        <v>-0.739</v>
       </c>
       <c r="P45" s="1">
-        <v>-0.839</v>
+        <v>-0.847</v>
       </c>
       <c r="Q45" s="1">
-        <v>-0.96</v>
+        <v>-0.986</v>
       </c>
       <c r="R45" s="1">
-        <v>-1.036</v>
+        <v>-1.077</v>
       </c>
       <c r="S45" s="1">
-        <v>-0.977</v>
+        <v>-1.02</v>
       </c>
       <c r="T45" s="1">
-        <v>-0.848</v>
+        <v>-0.864</v>
       </c>
       <c r="U45" s="1">
-        <v>-0.72</v>
+        <v>-0.734</v>
       </c>
     </row>
     <row r="46" spans="1:21">
@@ -3531,61 +3534,61 @@
         <v>-0.82</v>
       </c>
       <c r="C46" s="1">
-        <v>-0.879</v>
+        <v>-0.919</v>
       </c>
       <c r="D46" s="1">
-        <v>-1.02</v>
+        <v>-1.085</v>
       </c>
       <c r="E46" s="1">
-        <v>-1.129</v>
+        <v>-1.204</v>
       </c>
       <c r="F46" s="1">
-        <v>-1.094</v>
+        <v>-1.168</v>
       </c>
       <c r="G46" s="1">
-        <v>-0.93</v>
+        <v>-0.996</v>
       </c>
       <c r="H46" s="1">
-        <v>-0.746</v>
+        <v>-0.796</v>
       </c>
       <c r="I46" s="1">
-        <v>-0.638</v>
+        <v>-0.665</v>
       </c>
       <c r="J46" s="1">
-        <v>-0.605</v>
+        <v>-0.609</v>
       </c>
       <c r="K46" s="1">
-        <v>-0.602</v>
+        <v>-0.582</v>
       </c>
       <c r="L46" s="1">
-        <v>-0.618</v>
+        <v>-0.578</v>
       </c>
       <c r="M46" s="1">
-        <v>-0.649</v>
+        <v>-0.587</v>
       </c>
       <c r="N46" s="1">
-        <v>-0.707</v>
+        <v>-0.626</v>
       </c>
       <c r="O46" s="1">
-        <v>-0.823</v>
+        <v>-0.698</v>
       </c>
       <c r="P46" s="1">
-        <v>-0.959</v>
+        <v>-0.795</v>
       </c>
       <c r="Q46" s="1">
-        <v>-1.043</v>
+        <v>-0.825</v>
       </c>
       <c r="R46" s="1">
-        <v>-0.992</v>
+        <v>-0.745</v>
       </c>
       <c r="S46" s="1">
-        <v>-0.854</v>
+        <v>-0.641</v>
       </c>
       <c r="T46" s="1">
-        <v>-0.726</v>
+        <v>-0.5570000000000001</v>
       </c>
       <c r="U46" s="1">
-        <v>-0.618</v>
+        <v>-0.499</v>
       </c>
     </row>
     <row r="47" spans="1:21">
@@ -3596,61 +3599,61 @@
         <v>-1.017</v>
       </c>
       <c r="C47" s="1">
-        <v>-1.09</v>
+        <v>-1.061</v>
       </c>
       <c r="D47" s="1">
-        <v>-1.158</v>
+        <v>-1.117</v>
       </c>
       <c r="E47" s="1">
-        <v>-1.07</v>
+        <v>-1.041</v>
       </c>
       <c r="F47" s="1">
-        <v>-0.867</v>
+        <v>-0.865</v>
       </c>
       <c r="G47" s="1">
-        <v>-0.699</v>
+        <v>-0.6909999999999999</v>
       </c>
       <c r="H47" s="1">
-        <v>-0.6</v>
+        <v>-0.569</v>
       </c>
       <c r="I47" s="1">
-        <v>-0.543</v>
+        <v>-0.521</v>
       </c>
       <c r="J47" s="1">
-        <v>-0.523</v>
+        <v>-0.502</v>
       </c>
       <c r="K47" s="1">
-        <v>-0.528</v>
+        <v>-0.486</v>
       </c>
       <c r="L47" s="1">
-        <v>-0.539</v>
+        <v>-0.494</v>
       </c>
       <c r="M47" s="1">
-        <v>-0.5580000000000001</v>
+        <v>-0.527</v>
       </c>
       <c r="N47" s="1">
-        <v>-0.627</v>
+        <v>-0.595</v>
       </c>
       <c r="O47" s="1">
-        <v>-0.71</v>
+        <v>-0.66</v>
       </c>
       <c r="P47" s="1">
-        <v>-0.727</v>
+        <v>-0.655</v>
       </c>
       <c r="Q47" s="1">
-        <v>-0.671</v>
+        <v>-0.581</v>
       </c>
       <c r="R47" s="1">
-        <v>-0.5570000000000001</v>
+        <v>-0.491</v>
       </c>
       <c r="S47" s="1">
-        <v>-0.444</v>
+        <v>-0.436</v>
       </c>
       <c r="T47" s="1">
-        <v>-0.366</v>
+        <v>-0.376</v>
       </c>
       <c r="U47" s="1">
-        <v>-0.284</v>
+        <v>-0.261</v>
       </c>
     </row>
     <row r="48" spans="1:21">
@@ -3661,61 +3664,61 @@
         <v>-0.8</v>
       </c>
       <c r="C48" s="1">
-        <v>-0.847</v>
+        <v>-0.841</v>
       </c>
       <c r="D48" s="1">
-        <v>-0.833</v>
+        <v>-0.821</v>
       </c>
       <c r="E48" s="1">
-        <v>-0.6860000000000001</v>
+        <v>-0.6909999999999999</v>
       </c>
       <c r="F48" s="1">
-        <v>-0.517</v>
+        <v>-0.54</v>
       </c>
       <c r="G48" s="1">
-        <v>-0.431</v>
+        <v>-0.45</v>
       </c>
       <c r="H48" s="1">
-        <v>-0.437</v>
+        <v>-0.438</v>
       </c>
       <c r="I48" s="1">
-        <v>-0.491</v>
+        <v>-0.479</v>
       </c>
       <c r="J48" s="1">
-        <v>-0.5610000000000001</v>
+        <v>-0.521</v>
       </c>
       <c r="K48" s="1">
-        <v>-0.623</v>
+        <v>-0.579</v>
       </c>
       <c r="L48" s="1">
-        <v>-0.6830000000000001</v>
+        <v>-0.653</v>
       </c>
       <c r="M48" s="1">
-        <v>-0.762</v>
+        <v>-0.747</v>
       </c>
       <c r="N48" s="1">
-        <v>-0.863</v>
+        <v>-0.853</v>
       </c>
       <c r="O48" s="1">
         <v>-0.928</v>
       </c>
       <c r="P48" s="1">
-        <v>-0.873</v>
+        <v>-0.894</v>
       </c>
       <c r="Q48" s="1">
-        <v>-0.744</v>
+        <v>-0.772</v>
       </c>
       <c r="R48" s="1">
-        <v>-0.633</v>
+        <v>-0.664</v>
       </c>
       <c r="S48" s="1">
-        <v>-0.542</v>
+        <v>-0.578</v>
       </c>
       <c r="T48" s="1">
-        <v>-0.413</v>
+        <v>-0.466</v>
       </c>
       <c r="U48" s="1">
-        <v>-0.253</v>
+        <v>-0.305</v>
       </c>
     </row>
     <row r="49" spans="1:21">
@@ -3726,61 +3729,61 @@
         <v>-1.138</v>
       </c>
       <c r="C49" s="1">
-        <v>-1.087</v>
+        <v>-1.083</v>
       </c>
       <c r="D49" s="1">
-        <v>-0.923</v>
+        <v>-0.9340000000000001</v>
       </c>
       <c r="E49" s="1">
-        <v>-0.76</v>
+        <v>-0.769</v>
       </c>
       <c r="F49" s="1">
-        <v>-0.674</v>
+        <v>-0.665</v>
       </c>
       <c r="G49" s="1">
-        <v>-0.637</v>
+        <v>-0.587</v>
       </c>
       <c r="H49" s="1">
-        <v>-0.629</v>
+        <v>-0.533</v>
       </c>
       <c r="I49" s="1">
-        <v>-0.638</v>
+        <v>-0.543</v>
       </c>
       <c r="J49" s="1">
-        <v>-0.655</v>
+        <v>-0.587</v>
       </c>
       <c r="K49" s="1">
-        <v>-0.722</v>
+        <v>-0.666</v>
       </c>
       <c r="L49" s="1">
-        <v>-0.825</v>
+        <v>-0.769</v>
       </c>
       <c r="M49" s="1">
-        <v>-0.905</v>
+        <v>-0.877</v>
       </c>
       <c r="N49" s="1">
-        <v>-0.931</v>
+        <v>-0.93</v>
       </c>
       <c r="O49" s="1">
-        <v>-0.85</v>
+        <v>-0.852</v>
       </c>
       <c r="P49" s="1">
-        <v>-0.724</v>
+        <v>-0.705</v>
       </c>
       <c r="Q49" s="1">
-        <v>-0.607</v>
+        <v>-0.586</v>
       </c>
       <c r="R49" s="1">
         <v>-0.486</v>
       </c>
       <c r="S49" s="1">
-        <v>-0.347</v>
+        <v>-0.35</v>
       </c>
       <c r="T49" s="1">
-        <v>-0.175</v>
+        <v>-0.161</v>
       </c>
       <c r="U49" s="1">
-        <v>-0.033</v>
+        <v>0.008999999999999999</v>
       </c>
     </row>
     <row r="50" spans="1:21">
@@ -3791,61 +3794,61 @@
         <v>-1.279</v>
       </c>
       <c r="C50" s="1">
-        <v>-1.121</v>
+        <v>-1.119</v>
       </c>
       <c r="D50" s="1">
-        <v>-0.892</v>
+        <v>-0.872</v>
       </c>
       <c r="E50" s="1">
-        <v>-0.74</v>
+        <v>-0.701</v>
       </c>
       <c r="F50" s="1">
-        <v>-0.679</v>
+        <v>-0.612</v>
       </c>
       <c r="G50" s="1">
-        <v>-0.669</v>
+        <v>-0.599</v>
       </c>
       <c r="H50" s="1">
-        <v>-0.68</v>
+        <v>-0.627</v>
       </c>
       <c r="I50" s="1">
-        <v>-0.736</v>
+        <v>-0.656</v>
       </c>
       <c r="J50" s="1">
-        <v>-0.8129999999999999</v>
+        <v>-0.6919999999999999</v>
       </c>
       <c r="K50" s="1">
-        <v>-0.896</v>
+        <v>-0.765</v>
       </c>
       <c r="L50" s="1">
-        <v>-1.002</v>
+        <v>-0.852</v>
       </c>
       <c r="M50" s="1">
-        <v>-1.054</v>
+        <v>-0.895</v>
       </c>
       <c r="N50" s="1">
-        <v>-0.987</v>
+        <v>-0.828</v>
       </c>
       <c r="O50" s="1">
-        <v>-0.853</v>
+        <v>-0.703</v>
       </c>
       <c r="P50" s="1">
-        <v>-0.722</v>
+        <v>-0.598</v>
       </c>
       <c r="Q50" s="1">
-        <v>-0.6</v>
+        <v>-0.501</v>
       </c>
       <c r="R50" s="1">
-        <v>-0.457</v>
+        <v>-0.347</v>
       </c>
       <c r="S50" s="1">
-        <v>-0.288</v>
+        <v>-0.168</v>
       </c>
       <c r="T50" s="1">
-        <v>-0.134</v>
+        <v>-0.018</v>
       </c>
       <c r="U50" s="1">
-        <v>-0.034</v>
+        <v>0.07199999999999999</v>
       </c>
     </row>
     <row r="51" spans="1:21">
@@ -3856,61 +3859,61 @@
         <v>-0.914</v>
       </c>
       <c r="C51" s="1">
-        <v>-0.79</v>
+        <v>-0.772</v>
       </c>
       <c r="D51" s="1">
-        <v>-0.639</v>
+        <v>-0.606</v>
       </c>
       <c r="E51" s="1">
+        <v>-0.5600000000000001</v>
+      </c>
+      <c r="F51" s="1">
+        <v>-0.582</v>
+      </c>
+      <c r="G51" s="1">
+        <v>-0.598</v>
+      </c>
+      <c r="H51" s="1">
         <v>-0.595</v>
       </c>
-      <c r="F51" s="1">
-        <v>-0.602</v>
-      </c>
-      <c r="G51" s="1">
-        <v>-0.621</v>
-      </c>
-      <c r="H51" s="1">
-        <v>-0.639</v>
-      </c>
       <c r="I51" s="1">
-        <v>-0.646</v>
+        <v>-0.605</v>
       </c>
       <c r="J51" s="1">
-        <v>-0.6879999999999999</v>
+        <v>-0.653</v>
       </c>
       <c r="K51" s="1">
-        <v>-0.763</v>
+        <v>-0.741</v>
       </c>
       <c r="L51" s="1">
-        <v>-0.8159999999999999</v>
+        <v>-0.792</v>
       </c>
       <c r="M51" s="1">
-        <v>-0.794</v>
+        <v>-0.745</v>
       </c>
       <c r="N51" s="1">
-        <v>-0.681</v>
+        <v>-0.633</v>
       </c>
       <c r="O51" s="1">
-        <v>-0.5659999999999999</v>
+        <v>-0.521</v>
       </c>
       <c r="P51" s="1">
-        <v>-0.488</v>
+        <v>-0.426</v>
       </c>
       <c r="Q51" s="1">
-        <v>-0.412</v>
+        <v>-0.328</v>
       </c>
       <c r="R51" s="1">
-        <v>-0.289</v>
+        <v>-0.215</v>
       </c>
       <c r="S51" s="1">
-        <v>-0.181</v>
+        <v>-0.099</v>
       </c>
       <c r="T51" s="1">
-        <v>-0.115</v>
+        <v>-0.007</v>
       </c>
       <c r="U51" s="1">
-        <v>-0.08799999999999999</v>
+        <v>0.047</v>
       </c>
     </row>
     <row r="52" spans="1:21">
@@ -3921,61 +3924,61 @@
         <v>-0.346</v>
       </c>
       <c r="C52" s="1">
+        <v>-0.32</v>
+      </c>
+      <c r="D52" s="1">
+        <v>-0.296</v>
+      </c>
+      <c r="E52" s="1">
         <v>-0.31</v>
       </c>
-      <c r="D52" s="1">
-        <v>-0.3</v>
-      </c>
-      <c r="E52" s="1">
-        <v>-0.328</v>
-      </c>
       <c r="F52" s="1">
-        <v>-0.344</v>
+        <v>-0.332</v>
       </c>
       <c r="G52" s="1">
-        <v>-0.344</v>
+        <v>-0.342</v>
       </c>
       <c r="H52" s="1">
         <v>-0.35</v>
       </c>
       <c r="I52" s="1">
-        <v>-0.376</v>
+        <v>-0.373</v>
       </c>
       <c r="J52" s="1">
-        <v>-0.407</v>
+        <v>-0.416</v>
       </c>
       <c r="K52" s="1">
-        <v>-0.41</v>
+        <v>-0.412</v>
       </c>
       <c r="L52" s="1">
-        <v>-0.367</v>
+        <v>-0.359</v>
       </c>
       <c r="M52" s="1">
-        <v>-0.32</v>
+        <v>-0.289</v>
       </c>
       <c r="N52" s="1">
-        <v>-0.28</v>
+        <v>-0.215</v>
       </c>
       <c r="O52" s="1">
-        <v>-0.252</v>
+        <v>-0.183</v>
       </c>
       <c r="P52" s="1">
-        <v>-0.227</v>
+        <v>-0.19</v>
       </c>
       <c r="Q52" s="1">
-        <v>-0.197</v>
+        <v>-0.208</v>
       </c>
       <c r="R52" s="1">
-        <v>-0.165</v>
+        <v>-0.217</v>
       </c>
       <c r="S52" s="1">
-        <v>-0.138</v>
+        <v>-0.205</v>
       </c>
       <c r="T52" s="1">
-        <v>-0.135</v>
+        <v>-0.209</v>
       </c>
       <c r="U52" s="1">
-        <v>-0.165</v>
+        <v>-0.238</v>
       </c>
     </row>
     <row r="53" spans="1:21">
@@ -3986,61 +3989,61 @@
         <v>-0.489</v>
       </c>
       <c r="C53" s="1">
-        <v>-0.448</v>
+        <v>-0.462</v>
       </c>
       <c r="D53" s="1">
-        <v>-0.385</v>
+        <v>-0.426</v>
       </c>
       <c r="E53" s="1">
-        <v>-0.345</v>
+        <v>-0.386</v>
       </c>
       <c r="F53" s="1">
-        <v>-0.339</v>
+        <v>-0.359</v>
       </c>
       <c r="G53" s="1">
-        <v>-0.346</v>
+        <v>-0.348</v>
       </c>
       <c r="H53" s="1">
-        <v>-0.34</v>
+        <v>-0.353</v>
       </c>
       <c r="I53" s="1">
-        <v>-0.348</v>
+        <v>-0.355</v>
       </c>
       <c r="J53" s="1">
-        <v>-0.358</v>
+        <v>-0.301</v>
       </c>
       <c r="K53" s="1">
-        <v>-0.308</v>
+        <v>-0.214</v>
       </c>
       <c r="L53" s="1">
-        <v>-0.241</v>
+        <v>-0.142</v>
       </c>
       <c r="M53" s="1">
-        <v>-0.197</v>
+        <v>-0.126</v>
       </c>
       <c r="N53" s="1">
-        <v>-0.175</v>
+        <v>-0.137</v>
       </c>
       <c r="O53" s="1">
-        <v>-0.153</v>
+        <v>-0.121</v>
       </c>
       <c r="P53" s="1">
-        <v>-0.1</v>
+        <v>-0.075</v>
       </c>
       <c r="Q53" s="1">
+        <v>-0.05</v>
+      </c>
+      <c r="R53" s="1">
         <v>-0.046</v>
       </c>
-      <c r="R53" s="1">
-        <v>-0.01</v>
-      </c>
       <c r="S53" s="1">
-        <v>0.029</v>
+        <v>-0.048</v>
       </c>
       <c r="T53" s="1">
-        <v>0.044</v>
+        <v>-0.054</v>
       </c>
       <c r="U53" s="1">
-        <v>0.061</v>
+        <v>-0.042</v>
       </c>
     </row>
     <row r="54" spans="1:21">
@@ -4051,61 +4054,61 @@
         <v>-0.375</v>
       </c>
       <c r="C54" s="1">
+        <v>-0.374</v>
+      </c>
+      <c r="D54" s="1">
+        <v>-0.377</v>
+      </c>
+      <c r="E54" s="1">
         <v>-0.393</v>
       </c>
-      <c r="D54" s="1">
-        <v>-0.404</v>
-      </c>
-      <c r="E54" s="1">
-        <v>-0.394</v>
-      </c>
       <c r="F54" s="1">
-        <v>-0.41</v>
+        <v>-0.407</v>
       </c>
       <c r="G54" s="1">
-        <v>-0.471</v>
+        <v>-0.431</v>
       </c>
       <c r="H54" s="1">
-        <v>-0.52</v>
+        <v>-0.481</v>
       </c>
       <c r="I54" s="1">
-        <v>-0.52</v>
+        <v>-0.511</v>
       </c>
       <c r="J54" s="1">
-        <v>-0.472</v>
+        <v>-0.457</v>
       </c>
       <c r="K54" s="1">
-        <v>-0.385</v>
+        <v>-0.363</v>
       </c>
       <c r="L54" s="1">
-        <v>-0.301</v>
+        <v>-0.292</v>
       </c>
       <c r="M54" s="1">
-        <v>-0.247</v>
+        <v>-0.248</v>
       </c>
       <c r="N54" s="1">
-        <v>-0.213</v>
+        <v>-0.206</v>
       </c>
       <c r="O54" s="1">
-        <v>-0.177</v>
+        <v>-0.146</v>
       </c>
       <c r="P54" s="1">
-        <v>-0.122</v>
+        <v>-0.093</v>
       </c>
       <c r="Q54" s="1">
-        <v>-0.07099999999999999</v>
+        <v>-0.06</v>
       </c>
       <c r="R54" s="1">
-        <v>-0.05</v>
+        <v>-0.042</v>
       </c>
       <c r="S54" s="1">
-        <v>-0.031</v>
+        <v>-0.039</v>
       </c>
       <c r="T54" s="1">
-        <v>-0.031</v>
+        <v>-0.033</v>
       </c>
       <c r="U54" s="1">
-        <v>-0.025</v>
+        <v>-0.005</v>
       </c>
     </row>
     <row r="55" spans="1:21">
@@ -4116,61 +4119,61 @@
         <v>-0.279</v>
       </c>
       <c r="C55" s="1">
-        <v>-0.335</v>
+        <v>-0.334</v>
       </c>
       <c r="D55" s="1">
-        <v>-0.414</v>
+        <v>-0.398</v>
       </c>
       <c r="E55" s="1">
-        <v>-0.443</v>
+        <v>-0.433</v>
       </c>
       <c r="F55" s="1">
-        <v>-0.451</v>
+        <v>-0.474</v>
       </c>
       <c r="G55" s="1">
-        <v>-0.485</v>
+        <v>-0.496</v>
       </c>
       <c r="H55" s="1">
-        <v>-0.513</v>
+        <v>-0.468</v>
       </c>
       <c r="I55" s="1">
-        <v>-0.482</v>
+        <v>-0.408</v>
       </c>
       <c r="J55" s="1">
-        <v>-0.423</v>
+        <v>-0.338</v>
       </c>
       <c r="K55" s="1">
-        <v>-0.354</v>
+        <v>-0.274</v>
       </c>
       <c r="L55" s="1">
-        <v>-0.288</v>
+        <v>-0.21</v>
       </c>
       <c r="M55" s="1">
-        <v>-0.233</v>
+        <v>-0.147</v>
       </c>
       <c r="N55" s="1">
-        <v>-0.182</v>
+        <v>-0.093</v>
       </c>
       <c r="O55" s="1">
-        <v>-0.113</v>
+        <v>-0.053</v>
       </c>
       <c r="P55" s="1">
-        <v>-0.045</v>
+        <v>-0.026</v>
       </c>
       <c r="Q55" s="1">
-        <v>0.003</v>
+        <v>0.006</v>
       </c>
       <c r="R55" s="1">
-        <v>0.02</v>
+        <v>0.034</v>
       </c>
       <c r="S55" s="1">
-        <v>0.039</v>
+        <v>0.064</v>
       </c>
       <c r="T55" s="1">
-        <v>0.06900000000000001</v>
+        <v>0.083</v>
       </c>
       <c r="U55" s="1">
-        <v>0.104</v>
+        <v>0.092</v>
       </c>
     </row>
     <row r="56" spans="1:21">
@@ -4181,61 +4184,61 @@
         <v>-0.378</v>
       </c>
       <c r="C56" s="1">
-        <v>-0.426</v>
+        <v>-0.428</v>
       </c>
       <c r="D56" s="1">
-        <v>-0.503</v>
+        <v>-0.502</v>
       </c>
       <c r="E56" s="1">
-        <v>-0.583</v>
+        <v>-0.586</v>
       </c>
       <c r="F56" s="1">
-        <v>-0.67</v>
+        <v>-0.677</v>
       </c>
       <c r="G56" s="1">
-        <v>-0.725</v>
+        <v>-0.729</v>
       </c>
       <c r="H56" s="1">
-        <v>-0.6919999999999999</v>
+        <v>-0.695</v>
       </c>
       <c r="I56" s="1">
-        <v>-0.584</v>
+        <v>-0.59</v>
       </c>
       <c r="J56" s="1">
-        <v>-0.478</v>
+        <v>-0.476</v>
       </c>
       <c r="K56" s="1">
-        <v>-0.397</v>
+        <v>-0.391</v>
       </c>
       <c r="L56" s="1">
-        <v>-0.345</v>
+        <v>-0.323</v>
       </c>
       <c r="M56" s="1">
-        <v>-0.317</v>
+        <v>-0.253</v>
       </c>
       <c r="N56" s="1">
-        <v>-0.301</v>
+        <v>-0.198</v>
       </c>
       <c r="O56" s="1">
-        <v>-0.261</v>
+        <v>-0.167</v>
       </c>
       <c r="P56" s="1">
-        <v>-0.246</v>
+        <v>-0.158</v>
       </c>
       <c r="Q56" s="1">
-        <v>-0.303</v>
+        <v>-0.183</v>
       </c>
       <c r="R56" s="1">
-        <v>-0.385</v>
+        <v>-0.198</v>
       </c>
       <c r="S56" s="1">
-        <v>-0.447</v>
+        <v>-0.201</v>
       </c>
       <c r="T56" s="1">
-        <v>-0.461</v>
+        <v>-0.159</v>
       </c>
       <c r="U56" s="1">
-        <v>-0.423</v>
+        <v>-0.117</v>
       </c>
     </row>
     <row r="57" spans="1:21">
@@ -4246,61 +4249,61 @@
         <v>-0.6</v>
       </c>
       <c r="C57" s="1">
-        <v>-0.633</v>
+        <v>-0.624</v>
       </c>
       <c r="D57" s="1">
-        <v>-0.696</v>
+        <v>-0.695</v>
       </c>
       <c r="E57" s="1">
-        <v>-0.792</v>
+        <v>-0.78</v>
       </c>
       <c r="F57" s="1">
-        <v>-0.864</v>
+        <v>-0.846</v>
       </c>
       <c r="G57" s="1">
-        <v>-0.8149999999999999</v>
+        <v>-0.82</v>
       </c>
       <c r="H57" s="1">
-        <v>-0.675</v>
+        <v>-0.697</v>
       </c>
       <c r="I57" s="1">
-        <v>-0.53</v>
+        <v>-0.552</v>
       </c>
       <c r="J57" s="1">
-        <v>-0.416</v>
+        <v>-0.44</v>
       </c>
       <c r="K57" s="1">
-        <v>-0.319</v>
+        <v>-0.36</v>
       </c>
       <c r="L57" s="1">
-        <v>-0.251</v>
+        <v>-0.291</v>
       </c>
       <c r="M57" s="1">
-        <v>-0.195</v>
+        <v>-0.241</v>
       </c>
       <c r="N57" s="1">
-        <v>-0.159</v>
+        <v>-0.2</v>
       </c>
       <c r="O57" s="1">
+        <v>-0.177</v>
+      </c>
+      <c r="P57" s="1">
+        <v>-0.171</v>
+      </c>
+      <c r="Q57" s="1">
+        <v>-0.184</v>
+      </c>
+      <c r="R57" s="1">
+        <v>-0.184</v>
+      </c>
+      <c r="S57" s="1">
         <v>-0.144</v>
       </c>
-      <c r="P57" s="1">
-        <v>-0.155</v>
-      </c>
-      <c r="Q57" s="1">
-        <v>-0.179</v>
-      </c>
-      <c r="R57" s="1">
-        <v>-0.182</v>
-      </c>
-      <c r="S57" s="1">
-        <v>-0.158</v>
-      </c>
       <c r="T57" s="1">
-        <v>-0.131</v>
+        <v>-0.096</v>
       </c>
       <c r="U57" s="1">
-        <v>-0.121</v>
+        <v>-0.06900000000000001</v>
       </c>
     </row>
     <row r="58" spans="1:21">
@@ -4311,61 +4314,61 @@
         <v>-0.732</v>
       </c>
       <c r="C58" s="1">
-        <v>-0.772</v>
+        <v>-0.8</v>
       </c>
       <c r="D58" s="1">
-        <v>-0.887</v>
+        <v>-0.9419999999999999</v>
       </c>
       <c r="E58" s="1">
-        <v>-0.97</v>
+        <v>-1.025</v>
       </c>
       <c r="F58" s="1">
-        <v>-0.92</v>
+        <v>-0.971</v>
       </c>
       <c r="G58" s="1">
-        <v>-0.802</v>
+        <v>-0.82</v>
       </c>
       <c r="H58" s="1">
-        <v>-0.6820000000000001</v>
+        <v>-0.6860000000000001</v>
       </c>
       <c r="I58" s="1">
-        <v>-0.5590000000000001</v>
+        <v>-0.577</v>
       </c>
       <c r="J58" s="1">
-        <v>-0.451</v>
+        <v>-0.463</v>
       </c>
       <c r="K58" s="1">
-        <v>-0.344</v>
+        <v>-0.351</v>
       </c>
       <c r="L58" s="1">
-        <v>-0.257</v>
+        <v>-0.259</v>
       </c>
       <c r="M58" s="1">
-        <v>-0.208</v>
+        <v>-0.215</v>
       </c>
       <c r="N58" s="1">
-        <v>-0.198</v>
+        <v>-0.205</v>
       </c>
       <c r="O58" s="1">
-        <v>-0.209</v>
+        <v>-0.235</v>
       </c>
       <c r="P58" s="1">
-        <v>-0.229</v>
+        <v>-0.259</v>
       </c>
       <c r="Q58" s="1">
-        <v>-0.228</v>
+        <v>-0.233</v>
       </c>
       <c r="R58" s="1">
-        <v>-0.202</v>
+        <v>-0.183</v>
       </c>
       <c r="S58" s="1">
-        <v>-0.167</v>
+        <v>-0.145</v>
       </c>
       <c r="T58" s="1">
-        <v>-0.155</v>
+        <v>-0.134</v>
       </c>
       <c r="U58" s="1">
-        <v>-0.144</v>
+        <v>-0.136</v>
       </c>
     </row>
     <row r="59" spans="1:21">
@@ -4376,61 +4379,61 @@
         <v>-0.826</v>
       </c>
       <c r="C59" s="1">
-        <v>-0.86</v>
+        <v>-0.866</v>
       </c>
       <c r="D59" s="1">
-        <v>-0.883</v>
+        <v>-0.894</v>
       </c>
       <c r="E59" s="1">
-        <v>-0.804</v>
+        <v>-0.8100000000000001</v>
       </c>
       <c r="F59" s="1">
-        <v>-0.67</v>
+        <v>-0.669</v>
       </c>
       <c r="G59" s="1">
-        <v>-0.542</v>
+        <v>-0.537</v>
       </c>
       <c r="H59" s="1">
-        <v>-0.428</v>
+        <v>-0.426</v>
       </c>
       <c r="I59" s="1">
-        <v>-0.283</v>
+        <v>-0.322</v>
       </c>
       <c r="J59" s="1">
-        <v>-0.12</v>
+        <v>-0.222</v>
       </c>
       <c r="K59" s="1">
-        <v>-0.004</v>
+        <v>-0.138</v>
       </c>
       <c r="L59" s="1">
-        <v>0.06900000000000001</v>
+        <v>-0.07199999999999999</v>
       </c>
       <c r="M59" s="1">
-        <v>0.123</v>
+        <v>-0.013</v>
       </c>
       <c r="N59" s="1">
-        <v>0.183</v>
+        <v>0.023</v>
       </c>
       <c r="O59" s="1">
-        <v>0.257</v>
+        <v>0.051</v>
       </c>
       <c r="P59" s="1">
-        <v>0.322</v>
+        <v>0.083</v>
       </c>
       <c r="Q59" s="1">
-        <v>0.338</v>
+        <v>0.122</v>
       </c>
       <c r="R59" s="1">
-        <v>0.326</v>
+        <v>0.117</v>
       </c>
       <c r="S59" s="1">
-        <v>0.302</v>
+        <v>0.067</v>
       </c>
       <c r="T59" s="1">
-        <v>0.225</v>
+        <v>0.023</v>
       </c>
       <c r="U59" s="1">
-        <v>0.153</v>
+        <v>0.006</v>
       </c>
     </row>
     <row r="60" spans="1:21">
@@ -4444,58 +4447,58 @@
         <v>-0.887</v>
       </c>
       <c r="D60" s="1">
-        <v>-0.768</v>
+        <v>-0.749</v>
       </c>
       <c r="E60" s="1">
-        <v>-0.616</v>
+        <v>-0.586</v>
       </c>
       <c r="F60" s="1">
-        <v>-0.485</v>
+        <v>-0.468</v>
       </c>
       <c r="G60" s="1">
-        <v>-0.373</v>
+        <v>-0.356</v>
       </c>
       <c r="H60" s="1">
-        <v>-0.258</v>
+        <v>-0.212</v>
       </c>
       <c r="I60" s="1">
-        <v>-0.107</v>
+        <v>-0.076</v>
       </c>
       <c r="J60" s="1">
-        <v>0.019</v>
+        <v>0.022</v>
       </c>
       <c r="K60" s="1">
-        <v>0.091</v>
+        <v>0.094</v>
       </c>
       <c r="L60" s="1">
-        <v>0.128</v>
+        <v>0.173</v>
       </c>
       <c r="M60" s="1">
-        <v>0.162</v>
+        <v>0.254</v>
       </c>
       <c r="N60" s="1">
-        <v>0.232</v>
+        <v>0.333</v>
       </c>
       <c r="O60" s="1">
-        <v>0.302</v>
+        <v>0.425</v>
       </c>
       <c r="P60" s="1">
-        <v>0.326</v>
+        <v>0.484</v>
       </c>
       <c r="Q60" s="1">
-        <v>0.315</v>
+        <v>0.478</v>
       </c>
       <c r="R60" s="1">
-        <v>0.275</v>
+        <v>0.416</v>
       </c>
       <c r="S60" s="1">
-        <v>0.207</v>
+        <v>0.322</v>
       </c>
       <c r="T60" s="1">
-        <v>0.141</v>
+        <v>0.265</v>
       </c>
       <c r="U60" s="1">
-        <v>0.081</v>
+        <v>0.229</v>
       </c>
     </row>
     <row r="61" spans="1:21">
@@ -4506,61 +4509,61 @@
         <v>-0.903</v>
       </c>
       <c r="C61" s="1">
-        <v>-0.802</v>
+        <v>-0.772</v>
       </c>
       <c r="D61" s="1">
-        <v>-0.631</v>
+        <v>-0.571</v>
       </c>
       <c r="E61" s="1">
-        <v>-0.477</v>
+        <v>-0.426</v>
       </c>
       <c r="F61" s="1">
-        <v>-0.349</v>
+        <v>-0.328</v>
       </c>
       <c r="G61" s="1">
-        <v>-0.214</v>
+        <v>-0.212</v>
       </c>
       <c r="H61" s="1">
-        <v>-0.048</v>
+        <v>-0.065</v>
       </c>
       <c r="I61" s="1">
-        <v>0.109</v>
+        <v>0.057</v>
       </c>
       <c r="J61" s="1">
-        <v>0.229</v>
+        <v>0.134</v>
       </c>
       <c r="K61" s="1">
-        <v>0.323</v>
+        <v>0.214</v>
       </c>
       <c r="L61" s="1">
-        <v>0.397</v>
+        <v>0.289</v>
       </c>
       <c r="M61" s="1">
-        <v>0.521</v>
+        <v>0.362</v>
       </c>
       <c r="N61" s="1">
-        <v>0.648</v>
+        <v>0.441</v>
       </c>
       <c r="O61" s="1">
-        <v>0.709</v>
+        <v>0.48</v>
       </c>
       <c r="P61" s="1">
-        <v>0.675</v>
+        <v>0.468</v>
       </c>
       <c r="Q61" s="1">
-        <v>0.5659999999999999</v>
+        <v>0.399</v>
       </c>
       <c r="R61" s="1">
-        <v>0.429</v>
+        <v>0.296</v>
       </c>
       <c r="S61" s="1">
-        <v>0.303</v>
+        <v>0.195</v>
       </c>
       <c r="T61" s="1">
-        <v>0.205</v>
+        <v>0.11</v>
       </c>
       <c r="U61" s="1">
-        <v>0.148</v>
+        <v>0.046</v>
       </c>
     </row>
     <row r="62" spans="1:21">
@@ -4571,61 +4574,61 @@
         <v>-0.882</v>
       </c>
       <c r="C62" s="1">
-        <v>-0.754</v>
+        <v>-0.739</v>
       </c>
       <c r="D62" s="1">
-        <v>-0.589</v>
+        <v>-0.5679999999999999</v>
       </c>
       <c r="E62" s="1">
-        <v>-0.477</v>
+        <v>-0.447</v>
       </c>
       <c r="F62" s="1">
-        <v>-0.311</v>
+        <v>-0.316</v>
       </c>
       <c r="G62" s="1">
-        <v>-0.117</v>
+        <v>-0.148</v>
       </c>
       <c r="H62" s="1">
-        <v>0.045</v>
+        <v>0.018</v>
       </c>
       <c r="I62" s="1">
-        <v>0.193</v>
+        <v>0.151</v>
       </c>
       <c r="J62" s="1">
-        <v>0.325</v>
+        <v>0.256</v>
       </c>
       <c r="K62" s="1">
-        <v>0.443</v>
+        <v>0.343</v>
       </c>
       <c r="L62" s="1">
-        <v>0.592</v>
+        <v>0.462</v>
       </c>
       <c r="M62" s="1">
-        <v>0.739</v>
+        <v>0.598</v>
       </c>
       <c r="N62" s="1">
-        <v>0.806</v>
+        <v>0.666</v>
       </c>
       <c r="O62" s="1">
-        <v>0.769</v>
+        <v>0.633</v>
       </c>
       <c r="P62" s="1">
-        <v>0.652</v>
+        <v>0.55</v>
       </c>
       <c r="Q62" s="1">
-        <v>0.508</v>
+        <v>0.446</v>
       </c>
       <c r="R62" s="1">
-        <v>0.358</v>
+        <v>0.326</v>
       </c>
       <c r="S62" s="1">
-        <v>0.22</v>
+        <v>0.223</v>
       </c>
       <c r="T62" s="1">
-        <v>0.13</v>
+        <v>0.145</v>
       </c>
       <c r="U62" s="1">
-        <v>0.093</v>
+        <v>0.08599999999999999</v>
       </c>
     </row>
     <row r="63" spans="1:21">
@@ -4636,61 +4639,61 @@
         <v>-0.657</v>
       </c>
       <c r="C63" s="1">
-        <v>-0.579</v>
+        <v>-0.574</v>
       </c>
       <c r="D63" s="1">
-        <v>-0.434</v>
+        <v>-0.429</v>
       </c>
       <c r="E63" s="1">
-        <v>-0.259</v>
+        <v>-0.274</v>
       </c>
       <c r="F63" s="1">
-        <v>-0.055</v>
+        <v>-0.099</v>
       </c>
       <c r="G63" s="1">
-        <v>0.145</v>
+        <v>0.082</v>
       </c>
       <c r="H63" s="1">
-        <v>0.308</v>
+        <v>0.214</v>
       </c>
       <c r="I63" s="1">
-        <v>0.457</v>
+        <v>0.311</v>
       </c>
       <c r="J63" s="1">
-        <v>0.615</v>
+        <v>0.41</v>
       </c>
       <c r="K63" s="1">
-        <v>0.798</v>
+        <v>0.5570000000000001</v>
       </c>
       <c r="L63" s="1">
-        <v>0.948</v>
+        <v>0.703</v>
       </c>
       <c r="M63" s="1">
-        <v>0.986</v>
+        <v>0.764</v>
       </c>
       <c r="N63" s="1">
-        <v>0.923</v>
+        <v>0.732</v>
       </c>
       <c r="O63" s="1">
-        <v>0.783</v>
+        <v>0.623</v>
       </c>
       <c r="P63" s="1">
-        <v>0.587</v>
+        <v>0.469</v>
       </c>
       <c r="Q63" s="1">
-        <v>0.363</v>
+        <v>0.306</v>
       </c>
       <c r="R63" s="1">
-        <v>0.138</v>
+        <v>0.119</v>
       </c>
       <c r="S63" s="1">
-        <v>-0.051</v>
+        <v>-0.031</v>
       </c>
       <c r="T63" s="1">
-        <v>-0.183</v>
+        <v>-0.123</v>
       </c>
       <c r="U63" s="1">
-        <v>-0.274</v>
+        <v>-0.177</v>
       </c>
     </row>
     <row r="64" spans="1:21">
@@ -4701,61 +4704,61 @@
         <v>-0.388</v>
       </c>
       <c r="C64" s="1">
-        <v>-0.269</v>
+        <v>-0.273</v>
       </c>
       <c r="D64" s="1">
-        <v>-0.039</v>
+        <v>-0.056</v>
       </c>
       <c r="E64" s="1">
-        <v>0.202</v>
+        <v>0.182</v>
       </c>
       <c r="F64" s="1">
-        <v>0.423</v>
+        <v>0.401</v>
       </c>
       <c r="G64" s="1">
-        <v>0.599</v>
+        <v>0.59</v>
       </c>
       <c r="H64" s="1">
-        <v>0.783</v>
+        <v>0.786</v>
       </c>
       <c r="I64" s="1">
-        <v>1.028</v>
+        <v>1.034</v>
       </c>
       <c r="J64" s="1">
-        <v>1.314</v>
+        <v>1.301</v>
       </c>
       <c r="K64" s="1">
-        <v>1.553</v>
+        <v>1.516</v>
       </c>
       <c r="L64" s="1">
-        <v>1.627</v>
+        <v>1.609</v>
       </c>
       <c r="M64" s="1">
-        <v>1.541</v>
+        <v>1.516</v>
       </c>
       <c r="N64" s="1">
-        <v>1.317</v>
+        <v>1.279</v>
       </c>
       <c r="O64" s="1">
-        <v>0.971</v>
+        <v>0.957</v>
       </c>
       <c r="P64" s="1">
-        <v>0.591</v>
+        <v>0.608</v>
       </c>
       <c r="Q64" s="1">
-        <v>0.253</v>
+        <v>0.28</v>
       </c>
       <c r="R64" s="1">
-        <v>0.005</v>
+        <v>0.047</v>
       </c>
       <c r="S64" s="1">
-        <v>-0.159</v>
+        <v>-0.066</v>
       </c>
       <c r="T64" s="1">
-        <v>-0.242</v>
+        <v>-0.122</v>
       </c>
       <c r="U64" s="1">
-        <v>-0.293</v>
+        <v>-0.149</v>
       </c>
     </row>
     <row r="65" spans="1:21">
@@ -4766,61 +4769,61 @@
         <v>0.044</v>
       </c>
       <c r="C65" s="1">
-        <v>0.199</v>
+        <v>0.197</v>
       </c>
       <c r="D65" s="1">
-        <v>0.49</v>
+        <v>0.484</v>
       </c>
       <c r="E65" s="1">
-        <v>0.771</v>
+        <v>0.759</v>
       </c>
       <c r="F65" s="1">
-        <v>1.008</v>
+        <v>1.031</v>
       </c>
       <c r="G65" s="1">
-        <v>1.27</v>
+        <v>1.347</v>
       </c>
       <c r="H65" s="1">
-        <v>1.626</v>
+        <v>1.727</v>
       </c>
       <c r="I65" s="1">
-        <v>2.027</v>
+        <v>2.159</v>
       </c>
       <c r="J65" s="1">
-        <v>2.345</v>
+        <v>2.518</v>
       </c>
       <c r="K65" s="1">
-        <v>2.455</v>
+        <v>2.657</v>
       </c>
       <c r="L65" s="1">
-        <v>2.309</v>
+        <v>2.546</v>
       </c>
       <c r="M65" s="1">
-        <v>1.924</v>
+        <v>2.156</v>
       </c>
       <c r="N65" s="1">
-        <v>1.381</v>
+        <v>1.548</v>
       </c>
       <c r="O65" s="1">
-        <v>0.8129999999999999</v>
+        <v>0.909</v>
       </c>
       <c r="P65" s="1">
-        <v>0.293</v>
+        <v>0.363</v>
       </c>
       <c r="Q65" s="1">
-        <v>-0.112</v>
+        <v>-0.039</v>
       </c>
       <c r="R65" s="1">
-        <v>-0.335</v>
+        <v>-0.266</v>
       </c>
       <c r="S65" s="1">
-        <v>-0.436</v>
+        <v>-0.36</v>
       </c>
       <c r="T65" s="1">
-        <v>-0.494</v>
+        <v>-0.41</v>
       </c>
       <c r="U65" s="1">
-        <v>-0.547</v>
+        <v>-0.459</v>
       </c>
     </row>
     <row r="66" spans="1:21">
@@ -4831,61 +4834,61 @@
         <v>0.635</v>
       </c>
       <c r="C66" s="1">
-        <v>0.754</v>
+        <v>0.758</v>
       </c>
       <c r="D66" s="1">
-        <v>0.959</v>
+        <v>0.974</v>
       </c>
       <c r="E66" s="1">
-        <v>1.168</v>
+        <v>1.199</v>
       </c>
       <c r="F66" s="1">
-        <v>1.424</v>
+        <v>1.463</v>
       </c>
       <c r="G66" s="1">
-        <v>1.735</v>
+        <v>1.767</v>
       </c>
       <c r="H66" s="1">
-        <v>2.065</v>
+        <v>2.07</v>
       </c>
       <c r="I66" s="1">
-        <v>2.31</v>
+        <v>2.301</v>
       </c>
       <c r="J66" s="1">
-        <v>2.356</v>
+        <v>2.377</v>
       </c>
       <c r="K66" s="1">
-        <v>2.16</v>
+        <v>2.234</v>
       </c>
       <c r="L66" s="1">
-        <v>1.756</v>
+        <v>1.846</v>
       </c>
       <c r="M66" s="1">
-        <v>1.247</v>
+        <v>1.314</v>
       </c>
       <c r="N66" s="1">
-        <v>0.715</v>
+        <v>0.762</v>
       </c>
       <c r="O66" s="1">
-        <v>0.251</v>
+        <v>0.275</v>
       </c>
       <c r="P66" s="1">
-        <v>-0.096</v>
+        <v>-0.08400000000000001</v>
       </c>
       <c r="Q66" s="1">
-        <v>-0.306</v>
+        <v>-0.302</v>
       </c>
       <c r="R66" s="1">
-        <v>-0.392</v>
+        <v>-0.413</v>
       </c>
       <c r="S66" s="1">
-        <v>-0.437</v>
+        <v>-0.465</v>
       </c>
       <c r="T66" s="1">
-        <v>-0.484</v>
+        <v>-0.52</v>
       </c>
       <c r="U66" s="1">
-        <v>-0.526</v>
+        <v>-0.584</v>
       </c>
     </row>
     <row r="67" spans="1:21">
@@ -4896,61 +4899,61 @@
         <v>0.9429999999999999</v>
       </c>
       <c r="C67" s="1">
-        <v>1.141</v>
+        <v>1.101</v>
       </c>
       <c r="D67" s="1">
-        <v>1.472</v>
+        <v>1.398</v>
       </c>
       <c r="E67" s="1">
-        <v>1.805</v>
+        <v>1.731</v>
       </c>
       <c r="F67" s="1">
-        <v>2.143</v>
+        <v>2.102</v>
       </c>
       <c r="G67" s="1">
-        <v>2.446</v>
+        <v>2.434</v>
       </c>
       <c r="H67" s="1">
-        <v>2.644</v>
+        <v>2.629</v>
       </c>
       <c r="I67" s="1">
-        <v>2.658</v>
+        <v>2.641</v>
       </c>
       <c r="J67" s="1">
-        <v>2.463</v>
+        <v>2.436</v>
       </c>
       <c r="K67" s="1">
-        <v>2.036</v>
+        <v>1.988</v>
       </c>
       <c r="L67" s="1">
-        <v>1.424</v>
+        <v>1.383</v>
       </c>
       <c r="M67" s="1">
-        <v>0.781</v>
+        <v>0.74</v>
       </c>
       <c r="N67" s="1">
-        <v>0.186</v>
+        <v>0.175</v>
       </c>
       <c r="O67" s="1">
-        <v>-0.255</v>
+        <v>-0.237</v>
       </c>
       <c r="P67" s="1">
-        <v>-0.491</v>
+        <v>-0.463</v>
       </c>
       <c r="Q67" s="1">
-        <v>-0.597</v>
+        <v>-0.538</v>
       </c>
       <c r="R67" s="1">
-        <v>-0.653</v>
+        <v>-0.608</v>
       </c>
       <c r="S67" s="1">
-        <v>-0.743</v>
+        <v>-0.724</v>
       </c>
       <c r="T67" s="1">
-        <v>-0.846</v>
+        <v>-0.802</v>
       </c>
       <c r="U67" s="1">
-        <v>-0.8179999999999999</v>
+        <v>-0.77</v>
       </c>
     </row>
     <row r="68" spans="1:21">
@@ -4961,61 +4964,126 @@
         <v>1.429</v>
       </c>
       <c r="C68" s="1">
-        <v>1.676</v>
+        <v>1.666</v>
       </c>
       <c r="D68" s="1">
-        <v>2.138</v>
+        <v>2.118</v>
       </c>
       <c r="E68" s="1">
-        <v>2.626</v>
+        <v>2.606</v>
       </c>
       <c r="F68" s="1">
-        <v>3.032</v>
+        <v>3.011</v>
       </c>
       <c r="G68" s="1">
-        <v>3.28</v>
+        <v>3.241</v>
       </c>
       <c r="H68" s="1">
-        <v>3.299</v>
+        <v>3.255</v>
       </c>
       <c r="I68" s="1">
-        <v>3.004</v>
+        <v>2.983</v>
       </c>
       <c r="J68" s="1">
-        <v>2.366</v>
+        <v>2.381</v>
       </c>
       <c r="K68" s="1">
-        <v>1.548</v>
+        <v>1.572</v>
       </c>
       <c r="L68" s="1">
-        <v>0.757</v>
+        <v>0.744</v>
       </c>
       <c r="M68" s="1">
-        <v>0.037</v>
+        <v>0.034</v>
       </c>
       <c r="N68" s="1">
-        <v>-0.505</v>
+        <v>-0.474</v>
       </c>
       <c r="O68" s="1">
-        <v>-0.777</v>
+        <v>-0.738</v>
       </c>
       <c r="P68" s="1">
-        <v>-0.882</v>
+        <v>-0.843</v>
       </c>
       <c r="Q68" s="1">
-        <v>-0.952</v>
+        <v>-0.92</v>
       </c>
       <c r="R68" s="1">
-        <v>-1.091</v>
+        <v>-1.032</v>
       </c>
       <c r="S68" s="1">
-        <v>-1.243</v>
+        <v>-1.172</v>
       </c>
       <c r="T68" s="1">
-        <v>-1.218</v>
+        <v>-1.179</v>
       </c>
       <c r="U68" s="1">
-        <v>-1.021</v>
+        <v>-0.989</v>
+      </c>
+    </row>
+    <row r="69" spans="1:21">
+      <c r="A69" s="2" t="s">
+        <v>67</v>
+      </c>
+      <c r="B69" s="1">
+        <v>1.963</v>
+      </c>
+      <c r="C69" s="1">
+        <v>2.28</v>
+      </c>
+      <c r="D69" s="1">
+        <v>2.831</v>
+      </c>
+      <c r="E69" s="1">
+        <v>3.253</v>
+      </c>
+      <c r="F69" s="1">
+        <v>3.446</v>
+      </c>
+      <c r="G69" s="1">
+        <v>3.422</v>
+      </c>
+      <c r="H69" s="1">
+        <v>3.119</v>
+      </c>
+      <c r="I69" s="1">
+        <v>2.457</v>
+      </c>
+      <c r="J69" s="1">
+        <v>1.577</v>
+      </c>
+      <c r="K69" s="1">
+        <v>0.703</v>
+      </c>
+      <c r="L69" s="1">
+        <v>-0.052</v>
+      </c>
+      <c r="M69" s="1">
+        <v>-0.592</v>
+      </c>
+      <c r="N69" s="1">
+        <v>-0.877</v>
+      </c>
+      <c r="O69" s="1">
+        <v>-0.989</v>
+      </c>
+      <c r="P69" s="1">
+        <v>-1.08</v>
+      </c>
+      <c r="Q69" s="1">
+        <v>-1.23</v>
+      </c>
+      <c r="R69" s="1">
+        <v>-1.373</v>
+      </c>
+      <c r="S69" s="1">
+        <v>-1.351</v>
+      </c>
+      <c r="T69" s="1">
+        <v>-1.15</v>
+      </c>
+      <c r="U69" s="1">
+        <v>-0.91</v>
       </c>
     </row>
   </sheetData>
@@ -5030,22 +5098,22 @@
   <sheetData>
     <row r="1" spans="1:1">
       <c r="A1" s="2" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
     </row>
     <row r="2" spans="1:1">
       <c r="A2" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
     </row>
     <row r="3" spans="1:1">
       <c r="A3" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
     </row>
     <row r="4" spans="1:1">
       <c r="A4" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
     </row>
   </sheetData>

--- a/content/climate/XRO/XRO_RelENSO_fcst.xlsx
+++ b/content/climate/XRO/XRO_RelENSO_fcst.xlsx
@@ -15,7 +15,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="73" uniqueCount="73">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="74" uniqueCount="74">
   <si>
     <t>2021-01</t>
   </si>
@@ -219,6 +219,9 @@
   </si>
   <si>
     <t>2026-08</t>
+  </si>
+  <si>
+    <t>2026-09</t>
   </si>
   <si>
     <t>Readme</t>
@@ -595,7 +598,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:U69"/>
+  <dimension ref="A1:U70"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="2" max="21" width="10.7109375" style="1" customWidth="1"/>
@@ -603,7 +606,7 @@
   <sheetData>
     <row r="1" spans="1:21">
       <c r="A1" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="B1" s="2">
         <v>0</v>
@@ -671,64 +674,64 @@
         <v>0</v>
       </c>
       <c r="B2" s="1">
-        <v>-1.078</v>
+        <v>-1.068</v>
       </c>
       <c r="C2" s="1">
-        <v>-0.992</v>
+        <v>-0.982</v>
       </c>
       <c r="D2" s="1">
-        <v>-0.866</v>
+        <v>-0.869</v>
       </c>
       <c r="E2" s="1">
-        <v>-0.753</v>
+        <v>-0.78</v>
       </c>
       <c r="F2" s="1">
-        <v>-0.612</v>
+        <v>-0.639</v>
       </c>
       <c r="G2" s="1">
-        <v>-0.446</v>
+        <v>-0.449</v>
       </c>
       <c r="H2" s="1">
-        <v>-0.298</v>
+        <v>-0.3</v>
       </c>
       <c r="I2" s="1">
-        <v>-0.239</v>
+        <v>-0.252</v>
       </c>
       <c r="J2" s="1">
-        <v>-0.276</v>
+        <v>-0.279</v>
       </c>
       <c r="K2" s="1">
-        <v>-0.358</v>
+        <v>-0.333</v>
       </c>
       <c r="L2" s="1">
-        <v>-0.428</v>
+        <v>-0.356</v>
       </c>
       <c r="M2" s="1">
-        <v>-0.429</v>
+        <v>-0.324</v>
       </c>
       <c r="N2" s="1">
-        <v>-0.366</v>
+        <v>-0.26</v>
       </c>
       <c r="O2" s="1">
-        <v>-0.281</v>
+        <v>-0.216</v>
       </c>
       <c r="P2" s="1">
-        <v>-0.26</v>
+        <v>-0.199</v>
       </c>
       <c r="Q2" s="1">
-        <v>-0.242</v>
+        <v>-0.165</v>
       </c>
       <c r="R2" s="1">
-        <v>-0.139</v>
+        <v>-0.091</v>
       </c>
       <c r="S2" s="1">
-        <v>-0.01</v>
+        <v>0.021</v>
       </c>
       <c r="T2" s="1">
-        <v>0.125</v>
+        <v>0.139</v>
       </c>
       <c r="U2" s="1">
-        <v>0.253</v>
+        <v>0.226</v>
       </c>
     </row>
     <row r="3" spans="1:21">
@@ -736,64 +739,64 @@
         <v>1</v>
       </c>
       <c r="B3" s="1">
-        <v>-0.907</v>
+        <v>-0.901</v>
       </c>
       <c r="C3" s="1">
-        <v>-0.863</v>
+        <v>-0.857</v>
       </c>
       <c r="D3" s="1">
-        <v>-0.767</v>
+        <v>-0.739</v>
       </c>
       <c r="E3" s="1">
-        <v>-0.645</v>
+        <v>-0.584</v>
       </c>
       <c r="F3" s="1">
-        <v>-0.493</v>
+        <v>-0.448</v>
       </c>
       <c r="G3" s="1">
-        <v>-0.378</v>
+        <v>-0.358</v>
       </c>
       <c r="H3" s="1">
-        <v>-0.339</v>
+        <v>-0.332</v>
       </c>
       <c r="I3" s="1">
-        <v>-0.367</v>
+        <v>-0.361</v>
       </c>
       <c r="J3" s="1">
-        <v>-0.443</v>
+        <v>-0.451</v>
       </c>
       <c r="K3" s="1">
-        <v>-0.493</v>
+        <v>-0.544</v>
       </c>
       <c r="L3" s="1">
-        <v>-0.488</v>
+        <v>-0.545</v>
       </c>
       <c r="M3" s="1">
-        <v>-0.43</v>
+        <v>-0.479</v>
       </c>
       <c r="N3" s="1">
-        <v>-0.343</v>
+        <v>-0.407</v>
       </c>
       <c r="O3" s="1">
-        <v>-0.309</v>
+        <v>-0.368</v>
       </c>
       <c r="P3" s="1">
-        <v>-0.275</v>
+        <v>-0.316</v>
       </c>
       <c r="Q3" s="1">
-        <v>-0.158</v>
+        <v>-0.199</v>
       </c>
       <c r="R3" s="1">
-        <v>-0.003</v>
+        <v>-0.051</v>
       </c>
       <c r="S3" s="1">
-        <v>0.132</v>
+        <v>0.095</v>
       </c>
       <c r="T3" s="1">
-        <v>0.24</v>
+        <v>0.197</v>
       </c>
       <c r="U3" s="1">
-        <v>0.319</v>
+        <v>0.275</v>
       </c>
     </row>
     <row r="4" spans="1:21">
@@ -801,64 +804,64 @@
         <v>2</v>
       </c>
       <c r="B4" s="1">
-        <v>-0.681</v>
+        <v>-0.674</v>
       </c>
       <c r="C4" s="1">
-        <v>-0.63</v>
+        <v>-0.649</v>
       </c>
       <c r="D4" s="1">
-        <v>-0.525</v>
+        <v>-0.5570000000000001</v>
       </c>
       <c r="E4" s="1">
-        <v>-0.401</v>
+        <v>-0.437</v>
       </c>
       <c r="F4" s="1">
-        <v>-0.29</v>
+        <v>-0.345</v>
       </c>
       <c r="G4" s="1">
-        <v>-0.244</v>
+        <v>-0.303</v>
       </c>
       <c r="H4" s="1">
-        <v>-0.259</v>
+        <v>-0.334</v>
       </c>
       <c r="I4" s="1">
-        <v>-0.337</v>
+        <v>-0.426</v>
       </c>
       <c r="J4" s="1">
-        <v>-0.439</v>
+        <v>-0.523</v>
       </c>
       <c r="K4" s="1">
-        <v>-0.481</v>
+        <v>-0.553</v>
       </c>
       <c r="L4" s="1">
-        <v>-0.46</v>
+        <v>-0.499</v>
       </c>
       <c r="M4" s="1">
-        <v>-0.402</v>
+        <v>-0.441</v>
       </c>
       <c r="N4" s="1">
-        <v>-0.345</v>
+        <v>-0.396</v>
       </c>
       <c r="O4" s="1">
-        <v>-0.291</v>
+        <v>-0.33</v>
       </c>
       <c r="P4" s="1">
-        <v>-0.197</v>
+        <v>-0.199</v>
       </c>
       <c r="Q4" s="1">
-        <v>-0.07000000000000001</v>
+        <v>-0.028</v>
       </c>
       <c r="R4" s="1">
-        <v>0.041</v>
+        <v>0.126</v>
       </c>
       <c r="S4" s="1">
-        <v>0.122</v>
+        <v>0.24</v>
       </c>
       <c r="T4" s="1">
-        <v>0.197</v>
+        <v>0.324</v>
       </c>
       <c r="U4" s="1">
-        <v>0.26</v>
+        <v>0.43</v>
       </c>
     </row>
     <row r="5" spans="1:21">
@@ -866,64 +869,64 @@
         <v>3</v>
       </c>
       <c r="B5" s="1">
-        <v>-0.741</v>
+        <v>-0.738</v>
       </c>
       <c r="C5" s="1">
-        <v>-0.657</v>
+        <v>-0.651</v>
       </c>
       <c r="D5" s="1">
-        <v>-0.49</v>
+        <v>-0.506</v>
       </c>
       <c r="E5" s="1">
-        <v>-0.372</v>
+        <v>-0.404</v>
       </c>
       <c r="F5" s="1">
-        <v>-0.334</v>
+        <v>-0.365</v>
       </c>
       <c r="G5" s="1">
-        <v>-0.37</v>
+        <v>-0.403</v>
       </c>
       <c r="H5" s="1">
-        <v>-0.456</v>
+        <v>-0.503</v>
       </c>
       <c r="I5" s="1">
-        <v>-0.518</v>
+        <v>-0.629</v>
       </c>
       <c r="J5" s="1">
-        <v>-0.527</v>
+        <v>-0.677</v>
       </c>
       <c r="K5" s="1">
-        <v>-0.485</v>
+        <v>-0.63</v>
       </c>
       <c r="L5" s="1">
-        <v>-0.415</v>
+        <v>-0.547</v>
       </c>
       <c r="M5" s="1">
-        <v>-0.363</v>
+        <v>-0.481</v>
       </c>
       <c r="N5" s="1">
-        <v>-0.297</v>
+        <v>-0.419</v>
       </c>
       <c r="O5" s="1">
-        <v>-0.182</v>
+        <v>-0.294</v>
       </c>
       <c r="P5" s="1">
-        <v>-0.022</v>
+        <v>-0.119</v>
       </c>
       <c r="Q5" s="1">
-        <v>0.12</v>
+        <v>0.019</v>
       </c>
       <c r="R5" s="1">
-        <v>0.199</v>
+        <v>0.127</v>
       </c>
       <c r="S5" s="1">
-        <v>0.257</v>
+        <v>0.202</v>
       </c>
       <c r="T5" s="1">
-        <v>0.313</v>
+        <v>0.28</v>
       </c>
       <c r="U5" s="1">
-        <v>0.351</v>
+        <v>0.372</v>
       </c>
     </row>
     <row r="6" spans="1:21">
@@ -931,64 +934,64 @@
         <v>4</v>
       </c>
       <c r="B6" s="1">
-        <v>-0.448</v>
+        <v>-0.447</v>
       </c>
       <c r="C6" s="1">
+        <v>-0.422</v>
+      </c>
+      <c r="D6" s="1">
         <v>-0.393</v>
       </c>
-      <c r="D6" s="1">
-        <v>-0.345</v>
-      </c>
       <c r="E6" s="1">
-        <v>-0.378</v>
+        <v>-0.409</v>
       </c>
       <c r="F6" s="1">
-        <v>-0.451</v>
+        <v>-0.49</v>
       </c>
       <c r="G6" s="1">
-        <v>-0.534</v>
+        <v>-0.591</v>
       </c>
       <c r="H6" s="1">
-        <v>-0.61</v>
+        <v>-0.6919999999999999</v>
       </c>
       <c r="I6" s="1">
-        <v>-0.632</v>
+        <v>-0.741</v>
       </c>
       <c r="J6" s="1">
-        <v>-0.574</v>
+        <v>-0.6899999999999999</v>
       </c>
       <c r="K6" s="1">
-        <v>-0.499</v>
+        <v>-0.584</v>
       </c>
       <c r="L6" s="1">
-        <v>-0.45</v>
+        <v>-0.5</v>
       </c>
       <c r="M6" s="1">
-        <v>-0.383</v>
+        <v>-0.413</v>
       </c>
       <c r="N6" s="1">
-        <v>-0.282</v>
+        <v>-0.266</v>
       </c>
       <c r="O6" s="1">
-        <v>-0.131</v>
+        <v>-0.08799999999999999</v>
       </c>
       <c r="P6" s="1">
-        <v>0.002</v>
+        <v>0.073</v>
       </c>
       <c r="Q6" s="1">
-        <v>0.083</v>
+        <v>0.182</v>
       </c>
       <c r="R6" s="1">
-        <v>0.131</v>
+        <v>0.258</v>
       </c>
       <c r="S6" s="1">
-        <v>0.161</v>
+        <v>0.32</v>
       </c>
       <c r="T6" s="1">
-        <v>0.205</v>
+        <v>0.364</v>
       </c>
       <c r="U6" s="1">
-        <v>0.265</v>
+        <v>0.412</v>
       </c>
     </row>
     <row r="7" spans="1:21">
@@ -996,64 +999,64 @@
         <v>5</v>
       </c>
       <c r="B7" s="1">
-        <v>-0.277</v>
+        <v>-0.272</v>
       </c>
       <c r="C7" s="1">
-        <v>-0.313</v>
+        <v>-0.303</v>
       </c>
       <c r="D7" s="1">
-        <v>-0.383</v>
+        <v>-0.38</v>
       </c>
       <c r="E7" s="1">
-        <v>-0.452</v>
+        <v>-0.461</v>
       </c>
       <c r="F7" s="1">
-        <v>-0.5659999999999999</v>
+        <v>-0.5610000000000001</v>
       </c>
       <c r="G7" s="1">
         <v>-0.704</v>
       </c>
       <c r="H7" s="1">
-        <v>-0.783</v>
+        <v>-0.82</v>
       </c>
       <c r="I7" s="1">
-        <v>-0.754</v>
+        <v>-0.828</v>
       </c>
       <c r="J7" s="1">
-        <v>-0.666</v>
+        <v>-0.743</v>
       </c>
       <c r="K7" s="1">
-        <v>-0.576</v>
+        <v>-0.633</v>
       </c>
       <c r="L7" s="1">
-        <v>-0.487</v>
+        <v>-0.518</v>
       </c>
       <c r="M7" s="1">
-        <v>-0.345</v>
+        <v>-0.38</v>
       </c>
       <c r="N7" s="1">
-        <v>-0.169</v>
+        <v>-0.223</v>
       </c>
       <c r="O7" s="1">
-        <v>-0.024</v>
+        <v>-0.08599999999999999</v>
       </c>
       <c r="P7" s="1">
-        <v>0.081</v>
+        <v>0.006</v>
       </c>
       <c r="Q7" s="1">
-        <v>0.137</v>
+        <v>0.053</v>
       </c>
       <c r="R7" s="1">
-        <v>0.173</v>
+        <v>0.089</v>
       </c>
       <c r="S7" s="1">
-        <v>0.231</v>
+        <v>0.128</v>
       </c>
       <c r="T7" s="1">
-        <v>0.285</v>
+        <v>0.152</v>
       </c>
       <c r="U7" s="1">
-        <v>0.304</v>
+        <v>0.162</v>
       </c>
     </row>
     <row r="8" spans="1:21">
@@ -1061,64 +1064,64 @@
         <v>6</v>
       </c>
       <c r="B8" s="1">
-        <v>-0.452</v>
+        <v>-0.443</v>
       </c>
       <c r="C8" s="1">
-        <v>-0.538</v>
+        <v>-0.511</v>
       </c>
       <c r="D8" s="1">
-        <v>-0.6889999999999999</v>
+        <v>-0.628</v>
       </c>
       <c r="E8" s="1">
-        <v>-0.854</v>
+        <v>-0.79</v>
       </c>
       <c r="F8" s="1">
-        <v>-1.049</v>
+        <v>-0.988</v>
       </c>
       <c r="G8" s="1">
-        <v>-1.214</v>
+        <v>-1.138</v>
       </c>
       <c r="H8" s="1">
-        <v>-1.21</v>
+        <v>-1.139</v>
       </c>
       <c r="I8" s="1">
-        <v>-1.07</v>
+        <v>-1.013</v>
       </c>
       <c r="J8" s="1">
-        <v>-0.914</v>
+        <v>-0.871</v>
       </c>
       <c r="K8" s="1">
-        <v>-0.752</v>
+        <v>-0.719</v>
       </c>
       <c r="L8" s="1">
-        <v>-0.5600000000000001</v>
+        <v>-0.524</v>
       </c>
       <c r="M8" s="1">
-        <v>-0.341</v>
+        <v>-0.322</v>
       </c>
       <c r="N8" s="1">
-        <v>-0.15</v>
+        <v>-0.178</v>
       </c>
       <c r="O8" s="1">
-        <v>-0.031</v>
+        <v>-0.08500000000000001</v>
       </c>
       <c r="P8" s="1">
+        <v>-0.037</v>
+      </c>
+      <c r="Q8" s="1">
+        <v>-0.029</v>
+      </c>
+      <c r="R8" s="1">
+        <v>-0.046</v>
+      </c>
+      <c r="S8" s="1">
+        <v>-0.03</v>
+      </c>
+      <c r="T8" s="1">
         <v>0.031</v>
       </c>
-      <c r="Q8" s="1">
-        <v>0.08</v>
-      </c>
-      <c r="R8" s="1">
-        <v>0.117</v>
-      </c>
-      <c r="S8" s="1">
-        <v>0.153</v>
-      </c>
-      <c r="T8" s="1">
-        <v>0.196</v>
-      </c>
       <c r="U8" s="1">
-        <v>0.212</v>
+        <v>0.06</v>
       </c>
     </row>
     <row r="9" spans="1:21">
@@ -1126,64 +1129,64 @@
         <v>7</v>
       </c>
       <c r="B9" s="1">
-        <v>-0.641</v>
+        <v>-0.634</v>
       </c>
       <c r="C9" s="1">
-        <v>-0.715</v>
+        <v>-0.71</v>
       </c>
       <c r="D9" s="1">
-        <v>-0.897</v>
+        <v>-0.874</v>
       </c>
       <c r="E9" s="1">
-        <v>-1.114</v>
+        <v>-1.08</v>
       </c>
       <c r="F9" s="1">
-        <v>-1.284</v>
+        <v>-1.253</v>
       </c>
       <c r="G9" s="1">
-        <v>-1.278</v>
+        <v>-1.269</v>
       </c>
       <c r="H9" s="1">
-        <v>-1.121</v>
+        <v>-1.144</v>
       </c>
       <c r="I9" s="1">
-        <v>-0.954</v>
+        <v>-0.98</v>
       </c>
       <c r="J9" s="1">
-        <v>-0.8070000000000001</v>
+        <v>-0.8120000000000001</v>
       </c>
       <c r="K9" s="1">
-        <v>-0.619</v>
+        <v>-0.62</v>
       </c>
       <c r="L9" s="1">
-        <v>-0.382</v>
+        <v>-0.411</v>
       </c>
       <c r="M9" s="1">
-        <v>-0.194</v>
+        <v>-0.253</v>
       </c>
       <c r="N9" s="1">
-        <v>-0.089</v>
+        <v>-0.175</v>
       </c>
       <c r="O9" s="1">
-        <v>-0.052</v>
+        <v>-0.153</v>
       </c>
       <c r="P9" s="1">
-        <v>-0.046</v>
+        <v>-0.174</v>
       </c>
       <c r="Q9" s="1">
-        <v>-0.005</v>
+        <v>-0.21</v>
       </c>
       <c r="R9" s="1">
-        <v>0.058</v>
+        <v>-0.192</v>
       </c>
       <c r="S9" s="1">
-        <v>0.112</v>
+        <v>-0.146</v>
       </c>
       <c r="T9" s="1">
-        <v>0.131</v>
+        <v>-0.124</v>
       </c>
       <c r="U9" s="1">
-        <v>0.106</v>
+        <v>-0.11</v>
       </c>
     </row>
     <row r="10" spans="1:21">
@@ -1191,64 +1194,64 @@
         <v>8</v>
       </c>
       <c r="B10" s="1">
-        <v>-0.646</v>
+        <v>-0.644</v>
       </c>
       <c r="C10" s="1">
-        <v>-0.727</v>
+        <v>-0.749</v>
       </c>
       <c r="D10" s="1">
-        <v>-0.924</v>
+        <v>-0.97</v>
       </c>
       <c r="E10" s="1">
-        <v>-1.102</v>
+        <v>-1.149</v>
       </c>
       <c r="F10" s="1">
-        <v>-1.126</v>
+        <v>-1.17</v>
       </c>
       <c r="G10" s="1">
-        <v>-1.037</v>
+        <v>-1.053</v>
       </c>
       <c r="H10" s="1">
-        <v>-0.901</v>
+        <v>-0.894</v>
       </c>
       <c r="I10" s="1">
-        <v>-0.754</v>
+        <v>-0.747</v>
       </c>
       <c r="J10" s="1">
-        <v>-0.618</v>
+        <v>-0.608</v>
       </c>
       <c r="K10" s="1">
-        <v>-0.473</v>
+        <v>-0.453</v>
       </c>
       <c r="L10" s="1">
-        <v>-0.359</v>
+        <v>-0.326</v>
       </c>
       <c r="M10" s="1">
-        <v>-0.309</v>
+        <v>-0.267</v>
       </c>
       <c r="N10" s="1">
-        <v>-0.307</v>
+        <v>-0.261</v>
       </c>
       <c r="O10" s="1">
-        <v>-0.376</v>
+        <v>-0.291</v>
       </c>
       <c r="P10" s="1">
-        <v>-0.46</v>
+        <v>-0.332</v>
       </c>
       <c r="Q10" s="1">
-        <v>-0.482</v>
+        <v>-0.312</v>
       </c>
       <c r="R10" s="1">
-        <v>-0.426</v>
+        <v>-0.239</v>
       </c>
       <c r="S10" s="1">
-        <v>-0.351</v>
+        <v>-0.186</v>
       </c>
       <c r="T10" s="1">
-        <v>-0.294</v>
+        <v>-0.163</v>
       </c>
       <c r="U10" s="1">
-        <v>-0.245</v>
+        <v>-0.149</v>
       </c>
     </row>
     <row r="11" spans="1:21">
@@ -1256,64 +1259,64 @@
         <v>9</v>
       </c>
       <c r="B11" s="1">
-        <v>-1.17</v>
+        <v>-1.164</v>
       </c>
       <c r="C11" s="1">
-        <v>-1.29</v>
+        <v>-1.294</v>
       </c>
       <c r="D11" s="1">
-        <v>-1.455</v>
+        <v>-1.474</v>
       </c>
       <c r="E11" s="1">
-        <v>-1.446</v>
+        <v>-1.477</v>
       </c>
       <c r="F11" s="1">
-        <v>-1.28</v>
+        <v>-1.313</v>
       </c>
       <c r="G11" s="1">
-        <v>-1.09</v>
+        <v>-1.119</v>
       </c>
       <c r="H11" s="1">
-        <v>-0.905</v>
+        <v>-0.9409999999999999</v>
       </c>
       <c r="I11" s="1">
-        <v>-0.6899999999999999</v>
+        <v>-0.741</v>
       </c>
       <c r="J11" s="1">
-        <v>-0.439</v>
+        <v>-0.501</v>
       </c>
       <c r="K11" s="1">
-        <v>-0.225</v>
+        <v>-0.301</v>
       </c>
       <c r="L11" s="1">
-        <v>-0.105</v>
+        <v>-0.195</v>
       </c>
       <c r="M11" s="1">
-        <v>-0.057</v>
+        <v>-0.152</v>
       </c>
       <c r="N11" s="1">
-        <v>-0.039</v>
+        <v>-0.146</v>
       </c>
       <c r="O11" s="1">
-        <v>-0.025</v>
+        <v>-0.142</v>
       </c>
       <c r="P11" s="1">
-        <v>0.042</v>
+        <v>-0.106</v>
       </c>
       <c r="Q11" s="1">
-        <v>0.115</v>
+        <v>-0.033</v>
       </c>
       <c r="R11" s="1">
-        <v>0.137</v>
+        <v>0.017</v>
       </c>
       <c r="S11" s="1">
-        <v>0.107</v>
+        <v>0.022</v>
       </c>
       <c r="T11" s="1">
-        <v>0.063</v>
+        <v>0.034</v>
       </c>
       <c r="U11" s="1">
-        <v>0.057</v>
+        <v>0.094</v>
       </c>
     </row>
     <row r="12" spans="1:21">
@@ -1321,64 +1324,64 @@
         <v>10</v>
       </c>
       <c r="B12" s="1">
-        <v>-1.218</v>
+        <v>-1.21</v>
       </c>
       <c r="C12" s="1">
-        <v>-1.284</v>
+        <v>-1.274</v>
       </c>
       <c r="D12" s="1">
-        <v>-1.305</v>
+        <v>-1.273</v>
       </c>
       <c r="E12" s="1">
-        <v>-1.202</v>
+        <v>-1.133</v>
       </c>
       <c r="F12" s="1">
-        <v>-1.041</v>
+        <v>-0.958</v>
       </c>
       <c r="G12" s="1">
-        <v>-0.867</v>
+        <v>-0.793</v>
       </c>
       <c r="H12" s="1">
-        <v>-0.654</v>
+        <v>-0.594</v>
       </c>
       <c r="I12" s="1">
-        <v>-0.427</v>
+        <v>-0.392</v>
       </c>
       <c r="J12" s="1">
-        <v>-0.244</v>
+        <v>-0.248</v>
       </c>
       <c r="K12" s="1">
-        <v>-0.124</v>
+        <v>-0.175</v>
       </c>
       <c r="L12" s="1">
-        <v>-0.07000000000000001</v>
+        <v>-0.159</v>
       </c>
       <c r="M12" s="1">
-        <v>-0.039</v>
+        <v>-0.169</v>
       </c>
       <c r="N12" s="1">
-        <v>0</v>
+        <v>-0.187</v>
       </c>
       <c r="O12" s="1">
-        <v>0.058</v>
+        <v>-0.139</v>
       </c>
       <c r="P12" s="1">
-        <v>0.105</v>
+        <v>-0.053</v>
       </c>
       <c r="Q12" s="1">
-        <v>0.098</v>
+        <v>-0.018</v>
       </c>
       <c r="R12" s="1">
-        <v>0.078</v>
+        <v>-0.034</v>
       </c>
       <c r="S12" s="1">
-        <v>0.07000000000000001</v>
+        <v>-0.037</v>
       </c>
       <c r="T12" s="1">
-        <v>0.081</v>
+        <v>0.002</v>
       </c>
       <c r="U12" s="1">
-        <v>0.13</v>
+        <v>0.068</v>
       </c>
     </row>
     <row r="13" spans="1:21">
@@ -1386,64 +1389,64 @@
         <v>11</v>
       </c>
       <c r="B13" s="1">
-        <v>-1.227</v>
+        <v>-1.223</v>
       </c>
       <c r="C13" s="1">
-        <v>-1.17</v>
+        <v>-1.147</v>
       </c>
       <c r="D13" s="1">
-        <v>-1.033</v>
+        <v>-0.985</v>
       </c>
       <c r="E13" s="1">
-        <v>-0.879</v>
+        <v>-0.841</v>
       </c>
       <c r="F13" s="1">
         <v>-0.704</v>
       </c>
       <c r="G13" s="1">
-        <v>-0.472</v>
+        <v>-0.502</v>
       </c>
       <c r="H13" s="1">
-        <v>-0.222</v>
+        <v>-0.274</v>
       </c>
       <c r="I13" s="1">
-        <v>-0.012</v>
+        <v>-0.082</v>
       </c>
       <c r="J13" s="1">
-        <v>0.142</v>
+        <v>0.034</v>
       </c>
       <c r="K13" s="1">
-        <v>0.24</v>
+        <v>0.079</v>
       </c>
       <c r="L13" s="1">
-        <v>0.329</v>
+        <v>0.11</v>
       </c>
       <c r="M13" s="1">
-        <v>0.465</v>
+        <v>0.19</v>
       </c>
       <c r="N13" s="1">
-        <v>0.613</v>
+        <v>0.324</v>
       </c>
       <c r="O13" s="1">
-        <v>0.6870000000000001</v>
+        <v>0.427</v>
       </c>
       <c r="P13" s="1">
-        <v>0.667</v>
+        <v>0.457</v>
       </c>
       <c r="Q13" s="1">
-        <v>0.5629999999999999</v>
+        <v>0.411</v>
       </c>
       <c r="R13" s="1">
-        <v>0.442</v>
+        <v>0.318</v>
       </c>
       <c r="S13" s="1">
-        <v>0.332</v>
+        <v>0.257</v>
       </c>
       <c r="T13" s="1">
-        <v>0.265</v>
+        <v>0.252</v>
       </c>
       <c r="U13" s="1">
-        <v>0.232</v>
+        <v>0.268</v>
       </c>
     </row>
     <row r="14" spans="1:21">
@@ -1451,64 +1454,64 @@
         <v>12</v>
       </c>
       <c r="B14" s="1">
-        <v>-1.152</v>
+        <v>-1.148</v>
       </c>
       <c r="C14" s="1">
-        <v>-1.041</v>
+        <v>-1.026</v>
       </c>
       <c r="D14" s="1">
-        <v>-0.905</v>
+        <v>-0.88</v>
       </c>
       <c r="E14" s="1">
-        <v>-0.8110000000000001</v>
+        <v>-0.784</v>
       </c>
       <c r="F14" s="1">
-        <v>-0.637</v>
+        <v>-0.627</v>
       </c>
       <c r="G14" s="1">
-        <v>-0.387</v>
+        <v>-0.411</v>
       </c>
       <c r="H14" s="1">
-        <v>-0.18</v>
+        <v>-0.229</v>
       </c>
       <c r="I14" s="1">
-        <v>-0.062</v>
+        <v>-0.123</v>
       </c>
       <c r="J14" s="1">
-        <v>-0.021</v>
+        <v>-0.096</v>
       </c>
       <c r="K14" s="1">
-        <v>-0.001</v>
+        <v>-0.096</v>
       </c>
       <c r="L14" s="1">
-        <v>0.041</v>
+        <v>-0.037</v>
       </c>
       <c r="M14" s="1">
-        <v>0.108</v>
+        <v>0.08500000000000001</v>
       </c>
       <c r="N14" s="1">
-        <v>0.18</v>
+        <v>0.214</v>
       </c>
       <c r="O14" s="1">
+        <v>0.269</v>
+      </c>
+      <c r="P14" s="1">
+        <v>0.246</v>
+      </c>
+      <c r="Q14" s="1">
         <v>0.205</v>
       </c>
-      <c r="P14" s="1">
-        <v>0.166</v>
-      </c>
-      <c r="Q14" s="1">
-        <v>0.112</v>
-      </c>
       <c r="R14" s="1">
-        <v>0.075</v>
+        <v>0.201</v>
       </c>
       <c r="S14" s="1">
-        <v>0.074</v>
+        <v>0.229</v>
       </c>
       <c r="T14" s="1">
-        <v>0.109</v>
+        <v>0.245</v>
       </c>
       <c r="U14" s="1">
-        <v>0.156</v>
+        <v>0.255</v>
       </c>
     </row>
     <row r="15" spans="1:21">
@@ -1516,64 +1519,64 @@
         <v>13</v>
       </c>
       <c r="B15" s="1">
-        <v>-1.011</v>
+        <v>-1.008</v>
       </c>
       <c r="C15" s="1">
-        <v>-0.956</v>
+        <v>-0.95</v>
       </c>
       <c r="D15" s="1">
-        <v>-0.859</v>
+        <v>-0.879</v>
       </c>
       <c r="E15" s="1">
-        <v>-0.71</v>
+        <v>-0.719</v>
       </c>
       <c r="F15" s="1">
-        <v>-0.448</v>
+        <v>-0.458</v>
       </c>
       <c r="G15" s="1">
-        <v>-0.201</v>
+        <v>-0.209</v>
       </c>
       <c r="H15" s="1">
-        <v>-0.08400000000000001</v>
+        <v>-0.054</v>
       </c>
       <c r="I15" s="1">
-        <v>-0.033</v>
+        <v>-0.005</v>
       </c>
       <c r="J15" s="1">
-        <v>-0.004</v>
+        <v>-0.002</v>
       </c>
       <c r="K15" s="1">
-        <v>0.07199999999999999</v>
+        <v>0.046</v>
       </c>
       <c r="L15" s="1">
-        <v>0.204</v>
+        <v>0.167</v>
       </c>
       <c r="M15" s="1">
-        <v>0.322</v>
+        <v>0.275</v>
       </c>
       <c r="N15" s="1">
-        <v>0.347</v>
+        <v>0.312</v>
       </c>
       <c r="O15" s="1">
-        <v>0.285</v>
+        <v>0.253</v>
       </c>
       <c r="P15" s="1">
-        <v>0.224</v>
+        <v>0.17</v>
       </c>
       <c r="Q15" s="1">
-        <v>0.221</v>
+        <v>0.145</v>
       </c>
       <c r="R15" s="1">
-        <v>0.271</v>
+        <v>0.127</v>
       </c>
       <c r="S15" s="1">
-        <v>0.325</v>
+        <v>0.117</v>
       </c>
       <c r="T15" s="1">
-        <v>0.356</v>
+        <v>0.12</v>
       </c>
       <c r="U15" s="1">
-        <v>0.399</v>
+        <v>0.115</v>
       </c>
     </row>
     <row r="16" spans="1:21">
@@ -1581,64 +1584,64 @@
         <v>14</v>
       </c>
       <c r="B16" s="1">
-        <v>-1.278</v>
+        <v>-1.277</v>
       </c>
       <c r="C16" s="1">
-        <v>-1.216</v>
+        <v>-1.209</v>
       </c>
       <c r="D16" s="1">
-        <v>-1.038</v>
+        <v>-1.017</v>
       </c>
       <c r="E16" s="1">
-        <v>-0.787</v>
+        <v>-0.748</v>
       </c>
       <c r="F16" s="1">
-        <v>-0.546</v>
+        <v>-0.475</v>
       </c>
       <c r="G16" s="1">
-        <v>-0.399</v>
+        <v>-0.307</v>
       </c>
       <c r="H16" s="1">
-        <v>-0.371</v>
+        <v>-0.294</v>
       </c>
       <c r="I16" s="1">
-        <v>-0.435</v>
+        <v>-0.373</v>
       </c>
       <c r="J16" s="1">
-        <v>-0.477</v>
+        <v>-0.43</v>
       </c>
       <c r="K16" s="1">
-        <v>-0.396</v>
+        <v>-0.366</v>
       </c>
       <c r="L16" s="1">
-        <v>-0.221</v>
+        <v>-0.236</v>
       </c>
       <c r="M16" s="1">
-        <v>-0.105</v>
+        <v>-0.159</v>
       </c>
       <c r="N16" s="1">
-        <v>-0.098</v>
+        <v>-0.149</v>
       </c>
       <c r="O16" s="1">
-        <v>-0.065</v>
+        <v>-0.137</v>
       </c>
       <c r="P16" s="1">
-        <v>0.046</v>
+        <v>-0.027</v>
       </c>
       <c r="Q16" s="1">
-        <v>0.222</v>
+        <v>0.134</v>
       </c>
       <c r="R16" s="1">
-        <v>0.408</v>
+        <v>0.271</v>
       </c>
       <c r="S16" s="1">
-        <v>0.54</v>
+        <v>0.377</v>
       </c>
       <c r="T16" s="1">
-        <v>0.659</v>
+        <v>0.481</v>
       </c>
       <c r="U16" s="1">
-        <v>0.785</v>
+        <v>0.607</v>
       </c>
     </row>
     <row r="17" spans="1:21">
@@ -1646,64 +1649,64 @@
         <v>15</v>
       </c>
       <c r="B17" s="1">
-        <v>-1.291</v>
+        <v>-1.292</v>
       </c>
       <c r="C17" s="1">
-        <v>-1.178</v>
+        <v>-1.176</v>
       </c>
       <c r="D17" s="1">
-        <v>-0.915</v>
+        <v>-0.911</v>
       </c>
       <c r="E17" s="1">
-        <v>-0.654</v>
+        <v>-0.659</v>
       </c>
       <c r="F17" s="1">
-        <v>-0.528</v>
+        <v>-0.509</v>
       </c>
       <c r="G17" s="1">
-        <v>-0.548</v>
+        <v>-0.52</v>
       </c>
       <c r="H17" s="1">
-        <v>-0.659</v>
+        <v>-0.661</v>
       </c>
       <c r="I17" s="1">
-        <v>-0.748</v>
+        <v>-0.775</v>
       </c>
       <c r="J17" s="1">
-        <v>-0.6860000000000001</v>
+        <v>-0.714</v>
       </c>
       <c r="K17" s="1">
-        <v>-0.525</v>
+        <v>-0.534</v>
       </c>
       <c r="L17" s="1">
-        <v>-0.411</v>
+        <v>-0.388</v>
       </c>
       <c r="M17" s="1">
-        <v>-0.384</v>
+        <v>-0.329</v>
       </c>
       <c r="N17" s="1">
-        <v>-0.355</v>
+        <v>-0.293</v>
       </c>
       <c r="O17" s="1">
-        <v>-0.228</v>
+        <v>-0.16</v>
       </c>
       <c r="P17" s="1">
-        <v>0.025</v>
+        <v>0.07199999999999999</v>
       </c>
       <c r="Q17" s="1">
-        <v>0.293</v>
+        <v>0.308</v>
       </c>
       <c r="R17" s="1">
-        <v>0.477</v>
+        <v>0.489</v>
       </c>
       <c r="S17" s="1">
-        <v>0.625</v>
+        <v>0.624</v>
       </c>
       <c r="T17" s="1">
-        <v>0.771</v>
+        <v>0.776</v>
       </c>
       <c r="U17" s="1">
-        <v>0.91</v>
+        <v>0.9409999999999999</v>
       </c>
     </row>
     <row r="18" spans="1:21">
@@ -1711,64 +1714,64 @@
         <v>16</v>
       </c>
       <c r="B18" s="1">
-        <v>-1.16</v>
+        <v>-1.157</v>
       </c>
       <c r="C18" s="1">
-        <v>-0.993</v>
+        <v>-0.967</v>
       </c>
       <c r="D18" s="1">
-        <v>-0.75</v>
+        <v>-0.699</v>
       </c>
       <c r="E18" s="1">
-        <v>-0.67</v>
+        <v>-0.587</v>
       </c>
       <c r="F18" s="1">
-        <v>-0.76</v>
+        <v>-0.64</v>
       </c>
       <c r="G18" s="1">
-        <v>-0.965</v>
+        <v>-0.804</v>
       </c>
       <c r="H18" s="1">
-        <v>-1.143</v>
+        <v>-0.961</v>
       </c>
       <c r="I18" s="1">
-        <v>-1.159</v>
+        <v>-0.972</v>
       </c>
       <c r="J18" s="1">
-        <v>-1.012</v>
+        <v>-0.827</v>
       </c>
       <c r="K18" s="1">
-        <v>-0.848</v>
+        <v>-0.694</v>
       </c>
       <c r="L18" s="1">
-        <v>-0.782</v>
+        <v>-0.635</v>
       </c>
       <c r="M18" s="1">
-        <v>-0.711</v>
+        <v>-0.5639999999999999</v>
       </c>
       <c r="N18" s="1">
-        <v>-0.511</v>
+        <v>-0.383</v>
       </c>
       <c r="O18" s="1">
-        <v>-0.169</v>
+        <v>-0.068</v>
       </c>
       <c r="P18" s="1">
-        <v>0.163</v>
+        <v>0.245</v>
       </c>
       <c r="Q18" s="1">
-        <v>0.377</v>
+        <v>0.454</v>
       </c>
       <c r="R18" s="1">
-        <v>0.523</v>
+        <v>0.618</v>
       </c>
       <c r="S18" s="1">
-        <v>0.663</v>
+        <v>0.778</v>
       </c>
       <c r="T18" s="1">
-        <v>0.8110000000000001</v>
+        <v>0.9399999999999999</v>
       </c>
       <c r="U18" s="1">
-        <v>0.947</v>
+        <v>1.074</v>
       </c>
     </row>
     <row r="19" spans="1:21">
@@ -1776,64 +1779,64 @@
         <v>17</v>
       </c>
       <c r="B19" s="1">
-        <v>-0.786</v>
+        <v>-0.78</v>
       </c>
       <c r="C19" s="1">
-        <v>-0.681</v>
+        <v>-0.6850000000000001</v>
       </c>
       <c r="D19" s="1">
-        <v>-0.588</v>
+        <v>-0.608</v>
       </c>
       <c r="E19" s="1">
-        <v>-0.642</v>
+        <v>-0.679</v>
       </c>
       <c r="F19" s="1">
-        <v>-0.803</v>
+        <v>-0.874</v>
       </c>
       <c r="G19" s="1">
-        <v>-0.964</v>
+        <v>-1.1</v>
       </c>
       <c r="H19" s="1">
-        <v>-0.987</v>
+        <v>-1.135</v>
       </c>
       <c r="I19" s="1">
-        <v>-0.844</v>
+        <v>-0.986</v>
       </c>
       <c r="J19" s="1">
-        <v>-0.72</v>
+        <v>-0.836</v>
       </c>
       <c r="K19" s="1">
-        <v>-0.665</v>
+        <v>-0.766</v>
       </c>
       <c r="L19" s="1">
-        <v>-0.578</v>
+        <v>-0.6830000000000001</v>
       </c>
       <c r="M19" s="1">
-        <v>-0.405</v>
+        <v>-0.457</v>
       </c>
       <c r="N19" s="1">
-        <v>-0.124</v>
+        <v>-0.138</v>
       </c>
       <c r="O19" s="1">
-        <v>0.159</v>
+        <v>0.158</v>
       </c>
       <c r="P19" s="1">
-        <v>0.355</v>
+        <v>0.362</v>
       </c>
       <c r="Q19" s="1">
-        <v>0.497</v>
+        <v>0.481</v>
       </c>
       <c r="R19" s="1">
-        <v>0.627</v>
+        <v>0.556</v>
       </c>
       <c r="S19" s="1">
-        <v>0.751</v>
+        <v>0.625</v>
       </c>
       <c r="T19" s="1">
-        <v>0.87</v>
+        <v>0.711</v>
       </c>
       <c r="U19" s="1">
-        <v>0.9360000000000001</v>
+        <v>0.76</v>
       </c>
     </row>
     <row r="20" spans="1:21">
@@ -1841,64 +1844,64 @@
         <v>18</v>
       </c>
       <c r="B20" s="1">
-        <v>-0.644</v>
+        <v>-0.637</v>
       </c>
       <c r="C20" s="1">
-        <v>-0.641</v>
+        <v>-0.662</v>
       </c>
       <c r="D20" s="1">
-        <v>-0.726</v>
+        <v>-0.761</v>
       </c>
       <c r="E20" s="1">
-        <v>-0.921</v>
+        <v>-0.9340000000000001</v>
       </c>
       <c r="F20" s="1">
-        <v>-1.097</v>
+        <v>-1.102</v>
       </c>
       <c r="G20" s="1">
-        <v>-1.098</v>
+        <v>-1.104</v>
       </c>
       <c r="H20" s="1">
-        <v>-0.931</v>
+        <v>-0.954</v>
       </c>
       <c r="I20" s="1">
-        <v>-0.791</v>
+        <v>-0.822</v>
       </c>
       <c r="J20" s="1">
-        <v>-0.739</v>
+        <v>-0.77</v>
       </c>
       <c r="K20" s="1">
-        <v>-0.657</v>
+        <v>-0.695</v>
       </c>
       <c r="L20" s="1">
-        <v>-0.423</v>
+        <v>-0.471</v>
       </c>
       <c r="M20" s="1">
-        <v>-0.036</v>
+        <v>-0.097</v>
       </c>
       <c r="N20" s="1">
-        <v>0.347</v>
+        <v>0.27</v>
       </c>
       <c r="O20" s="1">
-        <v>0.627</v>
+        <v>0.532</v>
       </c>
       <c r="P20" s="1">
-        <v>0.852</v>
+        <v>0.707</v>
       </c>
       <c r="Q20" s="1">
-        <v>1.082</v>
+        <v>0.868</v>
       </c>
       <c r="R20" s="1">
-        <v>1.321</v>
+        <v>1.045</v>
       </c>
       <c r="S20" s="1">
-        <v>1.499</v>
+        <v>1.204</v>
       </c>
       <c r="T20" s="1">
-        <v>1.549</v>
+        <v>1.254</v>
       </c>
       <c r="U20" s="1">
-        <v>1.437</v>
+        <v>1.181</v>
       </c>
     </row>
     <row r="21" spans="1:21">
@@ -1906,64 +1909,64 @@
         <v>19</v>
       </c>
       <c r="B21" s="1">
-        <v>-0.909</v>
+        <v>-0.901</v>
       </c>
       <c r="C21" s="1">
-        <v>-1.006</v>
+        <v>-1.012</v>
       </c>
       <c r="D21" s="1">
-        <v>-1.228</v>
+        <v>-1.258</v>
       </c>
       <c r="E21" s="1">
-        <v>-1.465</v>
+        <v>-1.491</v>
       </c>
       <c r="F21" s="1">
-        <v>-1.498</v>
+        <v>-1.523</v>
       </c>
       <c r="G21" s="1">
-        <v>-1.298</v>
+        <v>-1.328</v>
       </c>
       <c r="H21" s="1">
-        <v>-1.089</v>
+        <v>-1.12</v>
       </c>
       <c r="I21" s="1">
-        <v>-0.962</v>
+        <v>-1.023</v>
       </c>
       <c r="J21" s="1">
-        <v>-0.852</v>
+        <v>-0.927</v>
       </c>
       <c r="K21" s="1">
-        <v>-0.628</v>
+        <v>-0.649</v>
       </c>
       <c r="L21" s="1">
-        <v>-0.222</v>
+        <v>-0.194</v>
       </c>
       <c r="M21" s="1">
-        <v>0.195</v>
+        <v>0.259</v>
       </c>
       <c r="N21" s="1">
-        <v>0.491</v>
+        <v>0.589</v>
       </c>
       <c r="O21" s="1">
-        <v>0.722</v>
+        <v>0.824</v>
       </c>
       <c r="P21" s="1">
-        <v>0.9330000000000001</v>
+        <v>1.064</v>
       </c>
       <c r="Q21" s="1">
-        <v>1.142</v>
+        <v>1.329</v>
       </c>
       <c r="R21" s="1">
-        <v>1.317</v>
+        <v>1.551</v>
       </c>
       <c r="S21" s="1">
-        <v>1.387</v>
+        <v>1.628</v>
       </c>
       <c r="T21" s="1">
-        <v>1.333</v>
+        <v>1.529</v>
       </c>
       <c r="U21" s="1">
-        <v>1.141</v>
+        <v>1.287</v>
       </c>
     </row>
     <row r="22" spans="1:21">
@@ -1971,64 +1974,64 @@
         <v>20</v>
       </c>
       <c r="B22" s="1">
-        <v>-1.019</v>
+        <v>-1.005</v>
       </c>
       <c r="C22" s="1">
-        <v>-1.146</v>
+        <v>-1.147</v>
       </c>
       <c r="D22" s="1">
-        <v>-1.332</v>
+        <v>-1.344</v>
       </c>
       <c r="E22" s="1">
-        <v>-1.348</v>
+        <v>-1.341</v>
       </c>
       <c r="F22" s="1">
-        <v>-1.189</v>
+        <v>-1.144</v>
       </c>
       <c r="G22" s="1">
-        <v>-1.015</v>
+        <v>-0.96</v>
       </c>
       <c r="H22" s="1">
-        <v>-0.923</v>
+        <v>-0.881</v>
       </c>
       <c r="I22" s="1">
-        <v>-0.8159999999999999</v>
+        <v>-0.784</v>
       </c>
       <c r="J22" s="1">
-        <v>-0.554</v>
+        <v>-0.503</v>
       </c>
       <c r="K22" s="1">
-        <v>-0.144</v>
+        <v>-0.056</v>
       </c>
       <c r="L22" s="1">
-        <v>0.254</v>
+        <v>0.344</v>
       </c>
       <c r="M22" s="1">
-        <v>0.5679999999999999</v>
+        <v>0.633</v>
       </c>
       <c r="N22" s="1">
-        <v>0.8070000000000001</v>
+        <v>0.873</v>
       </c>
       <c r="O22" s="1">
-        <v>1.021</v>
+        <v>1.098</v>
       </c>
       <c r="P22" s="1">
-        <v>1.246</v>
+        <v>1.326</v>
       </c>
       <c r="Q22" s="1">
-        <v>1.419</v>
+        <v>1.532</v>
       </c>
       <c r="R22" s="1">
-        <v>1.487</v>
+        <v>1.619</v>
       </c>
       <c r="S22" s="1">
-        <v>1.406</v>
+        <v>1.524</v>
       </c>
       <c r="T22" s="1">
-        <v>1.16</v>
+        <v>1.287</v>
       </c>
       <c r="U22" s="1">
-        <v>0.844</v>
+        <v>0.982</v>
       </c>
     </row>
     <row r="23" spans="1:21">
@@ -2036,64 +2039,64 @@
         <v>21</v>
       </c>
       <c r="B23" s="1">
-        <v>-0.985</v>
+        <v>-0.977</v>
       </c>
       <c r="C23" s="1">
-        <v>-1.032</v>
+        <v>-1.043</v>
       </c>
       <c r="D23" s="1">
-        <v>-1.021</v>
+        <v>-1.054</v>
       </c>
       <c r="E23" s="1">
-        <v>-0.867</v>
+        <v>-0.912</v>
       </c>
       <c r="F23" s="1">
-        <v>-0.699</v>
+        <v>-0.787</v>
       </c>
       <c r="G23" s="1">
-        <v>-0.59</v>
+        <v>-0.733</v>
       </c>
       <c r="H23" s="1">
-        <v>-0.483</v>
+        <v>-0.652</v>
       </c>
       <c r="I23" s="1">
-        <v>-0.263</v>
+        <v>-0.416</v>
       </c>
       <c r="J23" s="1">
-        <v>0.047</v>
+        <v>-0.02</v>
       </c>
       <c r="K23" s="1">
-        <v>0.333</v>
+        <v>0.367</v>
       </c>
       <c r="L23" s="1">
-        <v>0.531</v>
+        <v>0.645</v>
       </c>
       <c r="M23" s="1">
-        <v>0.662</v>
+        <v>0.868</v>
       </c>
       <c r="N23" s="1">
-        <v>0.786</v>
+        <v>1.119</v>
       </c>
       <c r="O23" s="1">
-        <v>0.9360000000000001</v>
+        <v>1.379</v>
       </c>
       <c r="P23" s="1">
-        <v>1.104</v>
+        <v>1.569</v>
       </c>
       <c r="Q23" s="1">
-        <v>1.198</v>
+        <v>1.637</v>
       </c>
       <c r="R23" s="1">
-        <v>1.136</v>
+        <v>1.533</v>
       </c>
       <c r="S23" s="1">
-        <v>0.971</v>
+        <v>1.293</v>
       </c>
       <c r="T23" s="1">
-        <v>0.75</v>
+        <v>0.98</v>
       </c>
       <c r="U23" s="1">
-        <v>0.535</v>
+        <v>0.644</v>
       </c>
     </row>
     <row r="24" spans="1:21">
@@ -2101,64 +2104,64 @@
         <v>22</v>
       </c>
       <c r="B24" s="1">
-        <v>-1.166</v>
+        <v>-1.157</v>
       </c>
       <c r="C24" s="1">
-        <v>-1.094</v>
+        <v>-1.091</v>
       </c>
       <c r="D24" s="1">
-        <v>-0.9</v>
+        <v>-0.929</v>
       </c>
       <c r="E24" s="1">
-        <v>-0.731</v>
+        <v>-0.784</v>
       </c>
       <c r="F24" s="1">
-        <v>-0.639</v>
+        <v>-0.698</v>
       </c>
       <c r="G24" s="1">
-        <v>-0.519</v>
+        <v>-0.588</v>
       </c>
       <c r="H24" s="1">
-        <v>-0.254</v>
+        <v>-0.302</v>
       </c>
       <c r="I24" s="1">
-        <v>0.1</v>
+        <v>0.089</v>
       </c>
       <c r="J24" s="1">
-        <v>0.428</v>
+        <v>0.421</v>
       </c>
       <c r="K24" s="1">
-        <v>0.671</v>
+        <v>0.675</v>
       </c>
       <c r="L24" s="1">
-        <v>0.869</v>
+        <v>0.895</v>
       </c>
       <c r="M24" s="1">
-        <v>1.08</v>
+        <v>1.107</v>
       </c>
       <c r="N24" s="1">
-        <v>1.314</v>
+        <v>1.331</v>
       </c>
       <c r="O24" s="1">
-        <v>1.506</v>
+        <v>1.497</v>
       </c>
       <c r="P24" s="1">
-        <v>1.562</v>
+        <v>1.514</v>
       </c>
       <c r="Q24" s="1">
-        <v>1.467</v>
+        <v>1.385</v>
       </c>
       <c r="R24" s="1">
-        <v>1.232</v>
+        <v>1.143</v>
       </c>
       <c r="S24" s="1">
-        <v>0.926</v>
+        <v>0.85</v>
       </c>
       <c r="T24" s="1">
-        <v>0.608</v>
+        <v>0.554</v>
       </c>
       <c r="U24" s="1">
-        <v>0.343</v>
+        <v>0.277</v>
       </c>
     </row>
     <row r="25" spans="1:21">
@@ -2166,64 +2169,64 @@
         <v>23</v>
       </c>
       <c r="B25" s="1">
-        <v>-1.026</v>
+        <v>-1.021</v>
       </c>
       <c r="C25" s="1">
-        <v>-0.944</v>
+        <v>-0.907</v>
       </c>
       <c r="D25" s="1">
-        <v>-0.8</v>
+        <v>-0.754</v>
       </c>
       <c r="E25" s="1">
-        <v>-0.68</v>
+        <v>-0.648</v>
       </c>
       <c r="F25" s="1">
-        <v>-0.504</v>
+        <v>-0.479</v>
       </c>
       <c r="G25" s="1">
-        <v>-0.215</v>
+        <v>-0.211</v>
       </c>
       <c r="H25" s="1">
-        <v>0.152</v>
+        <v>0.12</v>
       </c>
       <c r="I25" s="1">
-        <v>0.503</v>
+        <v>0.427</v>
       </c>
       <c r="J25" s="1">
-        <v>0.755</v>
+        <v>0.649</v>
       </c>
       <c r="K25" s="1">
-        <v>0.969</v>
+        <v>0.84</v>
       </c>
       <c r="L25" s="1">
-        <v>1.229</v>
+        <v>1.046</v>
       </c>
       <c r="M25" s="1">
-        <v>1.515</v>
+        <v>1.259</v>
       </c>
       <c r="N25" s="1">
-        <v>1.717</v>
+        <v>1.434</v>
       </c>
       <c r="O25" s="1">
-        <v>1.767</v>
+        <v>1.495</v>
       </c>
       <c r="P25" s="1">
-        <v>1.635</v>
+        <v>1.417</v>
       </c>
       <c r="Q25" s="1">
-        <v>1.346</v>
+        <v>1.202</v>
       </c>
       <c r="R25" s="1">
-        <v>0.982</v>
+        <v>0.905</v>
       </c>
       <c r="S25" s="1">
-        <v>0.605</v>
+        <v>0.59</v>
       </c>
       <c r="T25" s="1">
-        <v>0.285</v>
+        <v>0.299</v>
       </c>
       <c r="U25" s="1">
-        <v>0.037</v>
+        <v>0.067</v>
       </c>
     </row>
     <row r="26" spans="1:21">
@@ -2234,61 +2237,61 @@
         <v>-0.848</v>
       </c>
       <c r="C26" s="1">
-        <v>-0.755</v>
+        <v>-0.779</v>
       </c>
       <c r="D26" s="1">
-        <v>-0.619</v>
+        <v>-0.648</v>
       </c>
       <c r="E26" s="1">
-        <v>-0.429</v>
+        <v>-0.466</v>
       </c>
       <c r="F26" s="1">
-        <v>-0.135</v>
+        <v>-0.212</v>
       </c>
       <c r="G26" s="1">
-        <v>0.19</v>
+        <v>0.099</v>
       </c>
       <c r="H26" s="1">
-        <v>0.491</v>
+        <v>0.382</v>
       </c>
       <c r="I26" s="1">
-        <v>0.744</v>
+        <v>0.591</v>
       </c>
       <c r="J26" s="1">
-        <v>0.98</v>
+        <v>0.775</v>
       </c>
       <c r="K26" s="1">
-        <v>1.246</v>
+        <v>0.982</v>
       </c>
       <c r="L26" s="1">
-        <v>1.502</v>
+        <v>1.205</v>
       </c>
       <c r="M26" s="1">
-        <v>1.693</v>
+        <v>1.393</v>
       </c>
       <c r="N26" s="1">
-        <v>1.737</v>
+        <v>1.451</v>
       </c>
       <c r="O26" s="1">
-        <v>1.615</v>
+        <v>1.347</v>
       </c>
       <c r="P26" s="1">
-        <v>1.359</v>
+        <v>1.124</v>
       </c>
       <c r="Q26" s="1">
-        <v>1.004</v>
+        <v>0.841</v>
       </c>
       <c r="R26" s="1">
-        <v>0.643</v>
+        <v>0.55</v>
       </c>
       <c r="S26" s="1">
-        <v>0.322</v>
+        <v>0.289</v>
       </c>
       <c r="T26" s="1">
-        <v>0.07199999999999999</v>
+        <v>0.081</v>
       </c>
       <c r="U26" s="1">
-        <v>-0.08</v>
+        <v>-0.048</v>
       </c>
     </row>
     <row r="27" spans="1:21">
@@ -2299,61 +2302,61 @@
         <v>-0.646</v>
       </c>
       <c r="C27" s="1">
-        <v>-0.577</v>
+        <v>-0.548</v>
       </c>
       <c r="D27" s="1">
-        <v>-0.39</v>
+        <v>-0.36</v>
       </c>
       <c r="E27" s="1">
-        <v>-0.143</v>
+        <v>-0.108</v>
       </c>
       <c r="F27" s="1">
-        <v>0.106</v>
+        <v>0.144</v>
       </c>
       <c r="G27" s="1">
+        <v>0.339</v>
+      </c>
+      <c r="H27" s="1">
+        <v>0.502</v>
+      </c>
+      <c r="I27" s="1">
+        <v>0.627</v>
+      </c>
+      <c r="J27" s="1">
+        <v>0.757</v>
+      </c>
+      <c r="K27" s="1">
+        <v>0.887</v>
+      </c>
+      <c r="L27" s="1">
+        <v>0.969</v>
+      </c>
+      <c r="M27" s="1">
+        <v>0.973</v>
+      </c>
+      <c r="N27" s="1">
+        <v>0.878</v>
+      </c>
+      <c r="O27" s="1">
+        <v>0.702</v>
+      </c>
+      <c r="P27" s="1">
+        <v>0.506</v>
+      </c>
+      <c r="Q27" s="1">
         <v>0.305</v>
       </c>
-      <c r="H27" s="1">
-        <v>0.449</v>
-      </c>
-      <c r="I27" s="1">
-        <v>0.58</v>
-      </c>
-      <c r="J27" s="1">
-        <v>0.741</v>
-      </c>
-      <c r="K27" s="1">
-        <v>0.903</v>
-      </c>
-      <c r="L27" s="1">
-        <v>1.009</v>
-      </c>
-      <c r="M27" s="1">
-        <v>1.015</v>
-      </c>
-      <c r="N27" s="1">
-        <v>0.907</v>
-      </c>
-      <c r="O27" s="1">
-        <v>0.747</v>
-      </c>
-      <c r="P27" s="1">
-        <v>0.5659999999999999</v>
-      </c>
-      <c r="Q27" s="1">
-        <v>0.341</v>
-      </c>
       <c r="R27" s="1">
-        <v>0.1</v>
+        <v>0.09</v>
       </c>
       <c r="S27" s="1">
-        <v>-0.09</v>
+        <v>-0.079</v>
       </c>
       <c r="T27" s="1">
-        <v>-0.198</v>
+        <v>-0.176</v>
       </c>
       <c r="U27" s="1">
-        <v>-0.253</v>
+        <v>-0.229</v>
       </c>
     </row>
     <row r="28" spans="1:21">
@@ -2361,64 +2364,64 @@
         <v>26</v>
       </c>
       <c r="B28" s="1">
-        <v>-0.262</v>
+        <v>-0.268</v>
       </c>
       <c r="C28" s="1">
-        <v>-0.174</v>
+        <v>-0.175</v>
       </c>
       <c r="D28" s="1">
-        <v>0.049</v>
+        <v>0.029</v>
       </c>
       <c r="E28" s="1">
-        <v>0.268</v>
+        <v>0.251</v>
       </c>
       <c r="F28" s="1">
-        <v>0.45</v>
+        <v>0.437</v>
       </c>
       <c r="G28" s="1">
-        <v>0.592</v>
+        <v>0.578</v>
       </c>
       <c r="H28" s="1">
-        <v>0.714</v>
+        <v>0.711</v>
       </c>
       <c r="I28" s="1">
-        <v>0.871</v>
+        <v>0.851</v>
       </c>
       <c r="J28" s="1">
-        <v>1.019</v>
+        <v>0.972</v>
       </c>
       <c r="K28" s="1">
-        <v>1.097</v>
+        <v>1.039</v>
       </c>
       <c r="L28" s="1">
-        <v>1.079</v>
+        <v>1.017</v>
       </c>
       <c r="M28" s="1">
-        <v>0.971</v>
+        <v>0.89</v>
       </c>
       <c r="N28" s="1">
-        <v>0.783</v>
+        <v>0.708</v>
       </c>
       <c r="O28" s="1">
-        <v>0.553</v>
+        <v>0.49</v>
       </c>
       <c r="P28" s="1">
-        <v>0.272</v>
+        <v>0.196</v>
       </c>
       <c r="Q28" s="1">
-        <v>-0.003</v>
+        <v>-0.111</v>
       </c>
       <c r="R28" s="1">
-        <v>-0.233</v>
+        <v>-0.355</v>
       </c>
       <c r="S28" s="1">
-        <v>-0.37</v>
+        <v>-0.496</v>
       </c>
       <c r="T28" s="1">
-        <v>-0.431</v>
+        <v>-0.575</v>
       </c>
       <c r="U28" s="1">
-        <v>-0.518</v>
+        <v>-0.671</v>
       </c>
     </row>
     <row r="29" spans="1:21">
@@ -2426,64 +2429,64 @@
         <v>27</v>
       </c>
       <c r="B29" s="1">
-        <v>-0.299</v>
+        <v>-0.297</v>
       </c>
       <c r="C29" s="1">
         <v>-0.152</v>
       </c>
       <c r="D29" s="1">
-        <v>0.097</v>
+        <v>0.102</v>
       </c>
       <c r="E29" s="1">
-        <v>0.331</v>
+        <v>0.336</v>
       </c>
       <c r="F29" s="1">
-        <v>0.528</v>
+        <v>0.497</v>
       </c>
       <c r="G29" s="1">
-        <v>0.678</v>
+        <v>0.637</v>
       </c>
       <c r="H29" s="1">
-        <v>0.8070000000000001</v>
+        <v>0.768</v>
       </c>
       <c r="I29" s="1">
-        <v>0.891</v>
+        <v>0.847</v>
       </c>
       <c r="J29" s="1">
-        <v>0.914</v>
+        <v>0.884</v>
       </c>
       <c r="K29" s="1">
-        <v>0.857</v>
+        <v>0.821</v>
       </c>
       <c r="L29" s="1">
-        <v>0.754</v>
+        <v>0.6879999999999999</v>
       </c>
       <c r="M29" s="1">
-        <v>0.605</v>
+        <v>0.532</v>
       </c>
       <c r="N29" s="1">
-        <v>0.405</v>
+        <v>0.345</v>
       </c>
       <c r="O29" s="1">
-        <v>0.162</v>
+        <v>0.092</v>
       </c>
       <c r="P29" s="1">
-        <v>-0.138</v>
+        <v>-0.202</v>
       </c>
       <c r="Q29" s="1">
-        <v>-0.394</v>
+        <v>-0.452</v>
       </c>
       <c r="R29" s="1">
-        <v>-0.546</v>
+        <v>-0.591</v>
       </c>
       <c r="S29" s="1">
-        <v>-0.605</v>
+        <v>-0.677</v>
       </c>
       <c r="T29" s="1">
-        <v>-0.66</v>
+        <v>-0.78</v>
       </c>
       <c r="U29" s="1">
-        <v>-0.772</v>
+        <v>-0.947</v>
       </c>
     </row>
     <row r="30" spans="1:21">
@@ -2491,64 +2494,64 @@
         <v>28</v>
       </c>
       <c r="B30" s="1">
-        <v>0.07099999999999999</v>
+        <v>0.075</v>
       </c>
       <c r="C30" s="1">
-        <v>0.202</v>
+        <v>0.185</v>
       </c>
       <c r="D30" s="1">
-        <v>0.386</v>
+        <v>0.361</v>
       </c>
       <c r="E30" s="1">
-        <v>0.499</v>
+        <v>0.472</v>
       </c>
       <c r="F30" s="1">
-        <v>0.576</v>
+        <v>0.5580000000000001</v>
       </c>
       <c r="G30" s="1">
-        <v>0.651</v>
+        <v>0.614</v>
       </c>
       <c r="H30" s="1">
-        <v>0.6899999999999999</v>
+        <v>0.635</v>
       </c>
       <c r="I30" s="1">
-        <v>0.6840000000000001</v>
+        <v>0.65</v>
       </c>
       <c r="J30" s="1">
-        <v>0.64</v>
+        <v>0.604</v>
       </c>
       <c r="K30" s="1">
-        <v>0.538</v>
+        <v>0.486</v>
       </c>
       <c r="L30" s="1">
-        <v>0.402</v>
+        <v>0.361</v>
       </c>
       <c r="M30" s="1">
-        <v>0.249</v>
+        <v>0.229</v>
       </c>
       <c r="N30" s="1">
-        <v>0.078</v>
+        <v>0.028</v>
       </c>
       <c r="O30" s="1">
-        <v>-0.129</v>
+        <v>-0.212</v>
       </c>
       <c r="P30" s="1">
-        <v>-0.326</v>
+        <v>-0.421</v>
       </c>
       <c r="Q30" s="1">
-        <v>-0.475</v>
+        <v>-0.5570000000000001</v>
       </c>
       <c r="R30" s="1">
-        <v>-0.573</v>
+        <v>-0.636</v>
       </c>
       <c r="S30" s="1">
-        <v>-0.648</v>
+        <v>-0.738</v>
       </c>
       <c r="T30" s="1">
-        <v>-0.753</v>
+        <v>-0.886</v>
       </c>
       <c r="U30" s="1">
-        <v>-0.853</v>
+        <v>-1.003</v>
       </c>
     </row>
     <row r="31" spans="1:21">
@@ -2556,64 +2559,64 @@
         <v>29</v>
       </c>
       <c r="B31" s="1">
-        <v>0.378</v>
+        <v>0.386</v>
       </c>
       <c r="C31" s="1">
-        <v>0.527</v>
+        <v>0.511</v>
       </c>
       <c r="D31" s="1">
-        <v>0.717</v>
+        <v>0.665</v>
       </c>
       <c r="E31" s="1">
-        <v>0.832</v>
+        <v>0.787</v>
       </c>
       <c r="F31" s="1">
-        <v>0.931</v>
+        <v>0.917</v>
       </c>
       <c r="G31" s="1">
-        <v>1.021</v>
+        <v>1.007</v>
       </c>
       <c r="H31" s="1">
-        <v>1.071</v>
+        <v>1.013</v>
       </c>
       <c r="I31" s="1">
-        <v>1.03</v>
+        <v>0.9330000000000001</v>
       </c>
       <c r="J31" s="1">
-        <v>0.891</v>
+        <v>0.784</v>
       </c>
       <c r="K31" s="1">
-        <v>0.6860000000000001</v>
+        <v>0.58</v>
       </c>
       <c r="L31" s="1">
-        <v>0.446</v>
+        <v>0.347</v>
       </c>
       <c r="M31" s="1">
-        <v>0.163</v>
+        <v>0.062</v>
       </c>
       <c r="N31" s="1">
-        <v>-0.17</v>
+        <v>-0.268</v>
       </c>
       <c r="O31" s="1">
-        <v>-0.463</v>
+        <v>-0.545</v>
       </c>
       <c r="P31" s="1">
-        <v>-0.653</v>
+        <v>-0.728</v>
       </c>
       <c r="Q31" s="1">
-        <v>-0.781</v>
+        <v>-0.849</v>
       </c>
       <c r="R31" s="1">
-        <v>-0.888</v>
+        <v>-0.961</v>
       </c>
       <c r="S31" s="1">
-        <v>-1.025</v>
+        <v>-1.115</v>
       </c>
       <c r="T31" s="1">
-        <v>-1.159</v>
+        <v>-1.251</v>
       </c>
       <c r="U31" s="1">
-        <v>-1.15</v>
+        <v>-1.223</v>
       </c>
     </row>
     <row r="32" spans="1:21">
@@ -2621,64 +2624,64 @@
         <v>30</v>
       </c>
       <c r="B32" s="1">
-        <v>0.501</v>
+        <v>0.512</v>
       </c>
       <c r="C32" s="1">
-        <v>0.584</v>
+        <v>0.604</v>
       </c>
       <c r="D32" s="1">
-        <v>0.726</v>
+        <v>0.751</v>
       </c>
       <c r="E32" s="1">
-        <v>0.838</v>
+        <v>0.864</v>
       </c>
       <c r="F32" s="1">
-        <v>0.899</v>
+        <v>0.912</v>
       </c>
       <c r="G32" s="1">
-        <v>0.912</v>
+        <v>0.889</v>
       </c>
       <c r="H32" s="1">
-        <v>0.829</v>
+        <v>0.78</v>
       </c>
       <c r="I32" s="1">
-        <v>0.653</v>
+        <v>0.614</v>
       </c>
       <c r="J32" s="1">
-        <v>0.48</v>
+        <v>0.445</v>
       </c>
       <c r="K32" s="1">
-        <v>0.314</v>
+        <v>0.265</v>
       </c>
       <c r="L32" s="1">
-        <v>0.062</v>
+        <v>0.008999999999999999</v>
       </c>
       <c r="M32" s="1">
-        <v>-0.259</v>
+        <v>-0.307</v>
       </c>
       <c r="N32" s="1">
-        <v>-0.538</v>
+        <v>-0.5659999999999999</v>
       </c>
       <c r="O32" s="1">
-        <v>-0.697</v>
+        <v>-0.719</v>
       </c>
       <c r="P32" s="1">
-        <v>-0.782</v>
+        <v>-0.8100000000000001</v>
       </c>
       <c r="Q32" s="1">
-        <v>-0.904</v>
+        <v>-0.901</v>
       </c>
       <c r="R32" s="1">
-        <v>-1.095</v>
+        <v>-1.068</v>
       </c>
       <c r="S32" s="1">
-        <v>-1.26</v>
+        <v>-1.225</v>
       </c>
       <c r="T32" s="1">
-        <v>-1.261</v>
+        <v>-1.219</v>
       </c>
       <c r="U32" s="1">
-        <v>-1.072</v>
+        <v>-1.082</v>
       </c>
     </row>
     <row r="33" spans="1:21">
@@ -2686,61 +2689,61 @@
         <v>31</v>
       </c>
       <c r="B33" s="1">
-        <v>0.785</v>
+        <v>0.794</v>
       </c>
       <c r="C33" s="1">
-        <v>0.874</v>
+        <v>0.888</v>
       </c>
       <c r="D33" s="1">
-        <v>1.018</v>
+        <v>1.038</v>
       </c>
       <c r="E33" s="1">
-        <v>1.121</v>
+        <v>1.147</v>
       </c>
       <c r="F33" s="1">
-        <v>1.138</v>
+        <v>1.171</v>
       </c>
       <c r="G33" s="1">
-        <v>1.039</v>
+        <v>1.067</v>
       </c>
       <c r="H33" s="1">
-        <v>0.865</v>
+        <v>0.878</v>
       </c>
       <c r="I33" s="1">
-        <v>0.649</v>
+        <v>0.657</v>
       </c>
       <c r="J33" s="1">
-        <v>0.374</v>
+        <v>0.391</v>
       </c>
       <c r="K33" s="1">
-        <v>0.023</v>
+        <v>0.033</v>
       </c>
       <c r="L33" s="1">
-        <v>-0.358</v>
+        <v>-0.365</v>
       </c>
       <c r="M33" s="1">
-        <v>-0.6840000000000001</v>
+        <v>-0.703</v>
       </c>
       <c r="N33" s="1">
-        <v>-0.877</v>
+        <v>-0.895</v>
       </c>
       <c r="O33" s="1">
-        <v>-0.971</v>
+        <v>-1.002</v>
       </c>
       <c r="P33" s="1">
-        <v>-1.076</v>
+        <v>-1.128</v>
       </c>
       <c r="Q33" s="1">
-        <v>-1.254</v>
+        <v>-1.32</v>
       </c>
       <c r="R33" s="1">
-        <v>-1.44</v>
+        <v>-1.49</v>
       </c>
       <c r="S33" s="1">
-        <v>-1.452</v>
+        <v>-1.469</v>
       </c>
       <c r="T33" s="1">
-        <v>-1.264</v>
+        <v>-1.266</v>
       </c>
       <c r="U33" s="1">
         <v>-1.02</v>
@@ -2751,64 +2754,64 @@
         <v>32</v>
       </c>
       <c r="B34" s="1">
-        <v>1.057</v>
+        <v>1.063</v>
       </c>
       <c r="C34" s="1">
-        <v>1.142</v>
+        <v>1.15</v>
       </c>
       <c r="D34" s="1">
-        <v>1.259</v>
+        <v>1.269</v>
       </c>
       <c r="E34" s="1">
-        <v>1.279</v>
+        <v>1.289</v>
       </c>
       <c r="F34" s="1">
-        <v>1.162</v>
+        <v>1.165</v>
       </c>
       <c r="G34" s="1">
-        <v>0.948</v>
+        <v>0.9350000000000001</v>
       </c>
       <c r="H34" s="1">
-        <v>0.704</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="I34" s="1">
-        <v>0.422</v>
+        <v>0.417</v>
       </c>
       <c r="J34" s="1">
-        <v>0.08</v>
+        <v>0.057</v>
       </c>
       <c r="K34" s="1">
-        <v>-0.312</v>
+        <v>-0.373</v>
       </c>
       <c r="L34" s="1">
-        <v>-0.664</v>
+        <v>-0.737</v>
       </c>
       <c r="M34" s="1">
-        <v>-0.897</v>
+        <v>-0.929</v>
       </c>
       <c r="N34" s="1">
-        <v>-1.01</v>
+        <v>-1.008</v>
       </c>
       <c r="O34" s="1">
-        <v>-1.109</v>
+        <v>-1.11</v>
       </c>
       <c r="P34" s="1">
-        <v>-1.279</v>
+        <v>-1.292</v>
       </c>
       <c r="Q34" s="1">
-        <v>-1.456</v>
+        <v>-1.504</v>
       </c>
       <c r="R34" s="1">
-        <v>-1.454</v>
+        <v>-1.531</v>
       </c>
       <c r="S34" s="1">
-        <v>-1.253</v>
+        <v>-1.313</v>
       </c>
       <c r="T34" s="1">
-        <v>-1.011</v>
+        <v>-1.059</v>
       </c>
       <c r="U34" s="1">
-        <v>-0.837</v>
+        <v>-0.865</v>
       </c>
     </row>
     <row r="35" spans="1:21">
@@ -2816,64 +2819,64 @@
         <v>33</v>
       </c>
       <c r="B35" s="1">
-        <v>1.079</v>
+        <v>1.088</v>
       </c>
       <c r="C35" s="1">
-        <v>1.171</v>
+        <v>1.187</v>
       </c>
       <c r="D35" s="1">
-        <v>1.25</v>
+        <v>1.309</v>
       </c>
       <c r="E35" s="1">
-        <v>1.203</v>
+        <v>1.281</v>
       </c>
       <c r="F35" s="1">
-        <v>1.047</v>
+        <v>1.11</v>
       </c>
       <c r="G35" s="1">
-        <v>0.8149999999999999</v>
+        <v>0.862</v>
       </c>
       <c r="H35" s="1">
-        <v>0.54</v>
+        <v>0.582</v>
       </c>
       <c r="I35" s="1">
-        <v>0.17</v>
+        <v>0.239</v>
       </c>
       <c r="J35" s="1">
-        <v>-0.237</v>
+        <v>-0.175</v>
       </c>
       <c r="K35" s="1">
-        <v>-0.572</v>
+        <v>-0.53</v>
       </c>
       <c r="L35" s="1">
-        <v>-0.783</v>
+        <v>-0.742</v>
       </c>
       <c r="M35" s="1">
-        <v>-0.906</v>
+        <v>-0.842</v>
       </c>
       <c r="N35" s="1">
-        <v>-1.009</v>
+        <v>-0.944</v>
       </c>
       <c r="O35" s="1">
-        <v>-1.162</v>
+        <v>-1.098</v>
       </c>
       <c r="P35" s="1">
-        <v>-1.326</v>
+        <v>-1.226</v>
       </c>
       <c r="Q35" s="1">
-        <v>-1.337</v>
+        <v>-1.205</v>
       </c>
       <c r="R35" s="1">
-        <v>-1.163</v>
+        <v>-1.028</v>
       </c>
       <c r="S35" s="1">
-        <v>-0.9340000000000001</v>
+        <v>-0.83</v>
       </c>
       <c r="T35" s="1">
-        <v>-0.763</v>
+        <v>-0.6919999999999999</v>
       </c>
       <c r="U35" s="1">
-        <v>-0.649</v>
+        <v>-0.606</v>
       </c>
     </row>
     <row r="36" spans="1:21">
@@ -2881,64 +2884,64 @@
         <v>34</v>
       </c>
       <c r="B36" s="1">
-        <v>1.339</v>
+        <v>1.345</v>
       </c>
       <c r="C36" s="1">
-        <v>1.303</v>
+        <v>1.321</v>
       </c>
       <c r="D36" s="1">
-        <v>1.163</v>
+        <v>1.174</v>
       </c>
       <c r="E36" s="1">
-        <v>0.951</v>
+        <v>0.9370000000000001</v>
       </c>
       <c r="F36" s="1">
-        <v>0.708</v>
+        <v>0.672</v>
       </c>
       <c r="G36" s="1">
-        <v>0.411</v>
+        <v>0.38</v>
       </c>
       <c r="H36" s="1">
-        <v>0.037</v>
+        <v>0.029</v>
       </c>
       <c r="I36" s="1">
-        <v>-0.349</v>
+        <v>-0.366</v>
       </c>
       <c r="J36" s="1">
-        <v>-0.653</v>
+        <v>-0.698</v>
       </c>
       <c r="K36" s="1">
-        <v>-0.839</v>
+        <v>-0.886</v>
       </c>
       <c r="L36" s="1">
-        <v>-0.965</v>
+        <v>-0.981</v>
       </c>
       <c r="M36" s="1">
-        <v>-1.08</v>
+        <v>-1.09</v>
       </c>
       <c r="N36" s="1">
-        <v>-1.249</v>
+        <v>-1.273</v>
       </c>
       <c r="O36" s="1">
-        <v>-1.394</v>
+        <v>-1.455</v>
       </c>
       <c r="P36" s="1">
-        <v>-1.368</v>
+        <v>-1.45</v>
       </c>
       <c r="Q36" s="1">
-        <v>-1.186</v>
+        <v>-1.246</v>
       </c>
       <c r="R36" s="1">
-        <v>-0.967</v>
+        <v>-1</v>
       </c>
       <c r="S36" s="1">
-        <v>-0.775</v>
+        <v>-0.8100000000000001</v>
       </c>
       <c r="T36" s="1">
-        <v>-0.644</v>
+        <v>-0.681</v>
       </c>
       <c r="U36" s="1">
-        <v>-0.575</v>
+        <v>-0.584</v>
       </c>
     </row>
     <row r="37" spans="1:21">
@@ -2946,64 +2949,64 @@
         <v>35</v>
       </c>
       <c r="B37" s="1">
-        <v>1.432</v>
+        <v>1.433</v>
       </c>
       <c r="C37" s="1">
-        <v>1.325</v>
+        <v>1.328</v>
       </c>
       <c r="D37" s="1">
-        <v>1.087</v>
+        <v>1.078</v>
       </c>
       <c r="E37" s="1">
-        <v>0.788</v>
+        <v>0.765</v>
       </c>
       <c r="F37" s="1">
-        <v>0.434</v>
+        <v>0.397</v>
       </c>
       <c r="G37" s="1">
-        <v>0.029</v>
+        <v>-0.015</v>
       </c>
       <c r="H37" s="1">
-        <v>-0.431</v>
+        <v>-0.465</v>
       </c>
       <c r="I37" s="1">
-        <v>-0.841</v>
+        <v>-0.83</v>
       </c>
       <c r="J37" s="1">
-        <v>-1.068</v>
+        <v>-1.026</v>
       </c>
       <c r="K37" s="1">
-        <v>-1.179</v>
+        <v>-1.133</v>
       </c>
       <c r="L37" s="1">
-        <v>-1.292</v>
+        <v>-1.267</v>
       </c>
       <c r="M37" s="1">
-        <v>-1.506</v>
+        <v>-1.491</v>
       </c>
       <c r="N37" s="1">
-        <v>-1.736</v>
+        <v>-1.684</v>
       </c>
       <c r="O37" s="1">
-        <v>-1.726</v>
+        <v>-1.644</v>
       </c>
       <c r="P37" s="1">
-        <v>-1.496</v>
+        <v>-1.406</v>
       </c>
       <c r="Q37" s="1">
-        <v>-1.223</v>
+        <v>-1.142</v>
       </c>
       <c r="R37" s="1">
-        <v>-0.989</v>
+        <v>-0.9350000000000001</v>
       </c>
       <c r="S37" s="1">
-        <v>-0.826</v>
+        <v>-0.783</v>
       </c>
       <c r="T37" s="1">
-        <v>-0.714</v>
+        <v>-0.677</v>
       </c>
       <c r="U37" s="1">
-        <v>-0.639</v>
+        <v>-0.596</v>
       </c>
     </row>
     <row r="38" spans="1:21">
@@ -3011,64 +3014,64 @@
         <v>36</v>
       </c>
       <c r="B38" s="1">
-        <v>1.107</v>
+        <v>1.11</v>
       </c>
       <c r="C38" s="1">
-        <v>1.02</v>
+        <v>1.017</v>
       </c>
       <c r="D38" s="1">
-        <v>0.767</v>
+        <v>0.755</v>
       </c>
       <c r="E38" s="1">
-        <v>0.419</v>
+        <v>0.4</v>
       </c>
       <c r="F38" s="1">
-        <v>-0.007</v>
+        <v>-0.021</v>
       </c>
       <c r="G38" s="1">
-        <v>-0.442</v>
+        <v>-0.441</v>
       </c>
       <c r="H38" s="1">
-        <v>-0.785</v>
+        <v>-0.779</v>
       </c>
       <c r="I38" s="1">
-        <v>-0.999</v>
+        <v>-0.985</v>
       </c>
       <c r="J38" s="1">
-        <v>-1.127</v>
+        <v>-1.104</v>
       </c>
       <c r="K38" s="1">
-        <v>-1.249</v>
+        <v>-1.243</v>
       </c>
       <c r="L38" s="1">
-        <v>-1.438</v>
+        <v>-1.449</v>
       </c>
       <c r="M38" s="1">
-        <v>-1.645</v>
+        <v>-1.619</v>
       </c>
       <c r="N38" s="1">
-        <v>-1.632</v>
+        <v>-1.579</v>
       </c>
       <c r="O38" s="1">
-        <v>-1.381</v>
+        <v>-1.321</v>
       </c>
       <c r="P38" s="1">
-        <v>-1.108</v>
+        <v>-1.046</v>
       </c>
       <c r="Q38" s="1">
-        <v>-0.916</v>
+        <v>-0.853</v>
       </c>
       <c r="R38" s="1">
-        <v>-0.778</v>
+        <v>-0.706</v>
       </c>
       <c r="S38" s="1">
-        <v>-0.6889999999999999</v>
+        <v>-0.612</v>
       </c>
       <c r="T38" s="1">
-        <v>-0.653</v>
+        <v>-0.547</v>
       </c>
       <c r="U38" s="1">
-        <v>-0.653</v>
+        <v>-0.475</v>
       </c>
     </row>
     <row r="39" spans="1:21">
@@ -3079,61 +3082,61 @@
         <v>0.907</v>
       </c>
       <c r="C39" s="1">
-        <v>0.771</v>
+        <v>0.767</v>
       </c>
       <c r="D39" s="1">
-        <v>0.464</v>
+        <v>0.459</v>
       </c>
       <c r="E39" s="1">
-        <v>0.06</v>
+        <v>0.042</v>
       </c>
       <c r="F39" s="1">
-        <v>-0.404</v>
+        <v>-0.425</v>
       </c>
       <c r="G39" s="1">
-        <v>-0.8080000000000001</v>
+        <v>-0.805</v>
       </c>
       <c r="H39" s="1">
-        <v>-1.059</v>
+        <v>-1.028</v>
       </c>
       <c r="I39" s="1">
-        <v>-1.18</v>
+        <v>-1.142</v>
       </c>
       <c r="J39" s="1">
-        <v>-1.304</v>
+        <v>-1.295</v>
       </c>
       <c r="K39" s="1">
-        <v>-1.501</v>
+        <v>-1.521</v>
       </c>
       <c r="L39" s="1">
-        <v>-1.673</v>
+        <v>-1.702</v>
       </c>
       <c r="M39" s="1">
-        <v>-1.648</v>
+        <v>-1.679</v>
       </c>
       <c r="N39" s="1">
-        <v>-1.423</v>
+        <v>-1.444</v>
       </c>
       <c r="O39" s="1">
-        <v>-1.152</v>
+        <v>-1.158</v>
       </c>
       <c r="P39" s="1">
-        <v>-0.954</v>
+        <v>-0.9350000000000001</v>
       </c>
       <c r="Q39" s="1">
-        <v>-0.844</v>
+        <v>-0.8110000000000001</v>
       </c>
       <c r="R39" s="1">
-        <v>-0.771</v>
+        <v>-0.77</v>
       </c>
       <c r="S39" s="1">
-        <v>-0.725</v>
+        <v>-0.751</v>
       </c>
       <c r="T39" s="1">
-        <v>-0.723</v>
+        <v>-0.753</v>
       </c>
       <c r="U39" s="1">
-        <v>-0.764</v>
+        <v>-0.8070000000000001</v>
       </c>
     </row>
     <row r="40" spans="1:21">
@@ -3141,64 +3144,64 @@
         <v>38</v>
       </c>
       <c r="B40" s="1">
-        <v>0.713</v>
+        <v>0.71</v>
       </c>
       <c r="C40" s="1">
-        <v>0.524</v>
+        <v>0.517</v>
       </c>
       <c r="D40" s="1">
-        <v>0.123</v>
+        <v>0.133</v>
       </c>
       <c r="E40" s="1">
-        <v>-0.335</v>
+        <v>-0.324</v>
       </c>
       <c r="F40" s="1">
-        <v>-0.722</v>
+        <v>-0.74</v>
       </c>
       <c r="G40" s="1">
-        <v>-0.959</v>
+        <v>-0.991</v>
       </c>
       <c r="H40" s="1">
-        <v>-1.07</v>
+        <v>-1.11</v>
       </c>
       <c r="I40" s="1">
-        <v>-1.198</v>
+        <v>-1.239</v>
       </c>
       <c r="J40" s="1">
-        <v>-1.407</v>
+        <v>-1.446</v>
       </c>
       <c r="K40" s="1">
-        <v>-1.602</v>
+        <v>-1.621</v>
       </c>
       <c r="L40" s="1">
-        <v>-1.595</v>
+        <v>-1.604</v>
       </c>
       <c r="M40" s="1">
-        <v>-1.366</v>
+        <v>-1.38</v>
       </c>
       <c r="N40" s="1">
-        <v>-1.089</v>
+        <v>-1.119</v>
       </c>
       <c r="O40" s="1">
-        <v>-0.879</v>
+        <v>-0.918</v>
       </c>
       <c r="P40" s="1">
-        <v>-0.786</v>
+        <v>-0.788</v>
       </c>
       <c r="Q40" s="1">
-        <v>-0.757</v>
+        <v>-0.733</v>
       </c>
       <c r="R40" s="1">
-        <v>-0.734</v>
+        <v>-0.723</v>
       </c>
       <c r="S40" s="1">
-        <v>-0.732</v>
+        <v>-0.731</v>
       </c>
       <c r="T40" s="1">
-        <v>-0.753</v>
+        <v>-0.766</v>
       </c>
       <c r="U40" s="1">
-        <v>-0.8110000000000001</v>
+        <v>-0.856</v>
       </c>
     </row>
     <row r="41" spans="1:21">
@@ -3206,64 +3209,64 @@
         <v>39</v>
       </c>
       <c r="B41" s="1">
-        <v>0.257</v>
+        <v>0.254</v>
       </c>
       <c r="C41" s="1">
-        <v>0.051</v>
+        <v>0.037</v>
       </c>
       <c r="D41" s="1">
-        <v>-0.333</v>
+        <v>-0.37</v>
       </c>
       <c r="E41" s="1">
-        <v>-0.673</v>
+        <v>-0.733</v>
       </c>
       <c r="F41" s="1">
-        <v>-0.869</v>
+        <v>-0.948</v>
       </c>
       <c r="G41" s="1">
-        <v>-0.968</v>
+        <v>-1.051</v>
       </c>
       <c r="H41" s="1">
-        <v>-1.069</v>
+        <v>-1.172</v>
       </c>
       <c r="I41" s="1">
-        <v>-1.243</v>
+        <v>-1.356</v>
       </c>
       <c r="J41" s="1">
-        <v>-1.406</v>
+        <v>-1.517</v>
       </c>
       <c r="K41" s="1">
-        <v>-1.397</v>
+        <v>-1.487</v>
       </c>
       <c r="L41" s="1">
-        <v>-1.208</v>
+        <v>-1.252</v>
       </c>
       <c r="M41" s="1">
-        <v>-0.987</v>
+        <v>-1.01</v>
       </c>
       <c r="N41" s="1">
-        <v>-0.829</v>
+        <v>-0.843</v>
       </c>
       <c r="O41" s="1">
-        <v>-0.73</v>
+        <v>-0.769</v>
       </c>
       <c r="P41" s="1">
-        <v>-0.678</v>
+        <v>-0.739</v>
       </c>
       <c r="Q41" s="1">
-        <v>-0.681</v>
+        <v>-0.734</v>
       </c>
       <c r="R41" s="1">
-        <v>-0.708</v>
+        <v>-0.748</v>
       </c>
       <c r="S41" s="1">
-        <v>-0.76</v>
+        <v>-0.804</v>
       </c>
       <c r="T41" s="1">
-        <v>-0.869</v>
+        <v>-0.9409999999999999</v>
       </c>
       <c r="U41" s="1">
-        <v>-1.012</v>
+        <v>-1.11</v>
       </c>
     </row>
     <row r="42" spans="1:21">
@@ -3271,64 +3274,64 @@
         <v>40</v>
       </c>
       <c r="B42" s="1">
-        <v>-0.42</v>
+        <v>-0.423</v>
       </c>
       <c r="C42" s="1">
-        <v>-0.61</v>
+        <v>-0.637</v>
       </c>
       <c r="D42" s="1">
-        <v>-0.887</v>
+        <v>-0.9419999999999999</v>
       </c>
       <c r="E42" s="1">
-        <v>-1.068</v>
+        <v>-1.113</v>
       </c>
       <c r="F42" s="1">
-        <v>-1.184</v>
+        <v>-1.224</v>
       </c>
       <c r="G42" s="1">
-        <v>-1.337</v>
+        <v>-1.366</v>
       </c>
       <c r="H42" s="1">
-        <v>-1.532</v>
+        <v>-1.546</v>
       </c>
       <c r="I42" s="1">
-        <v>-1.665</v>
+        <v>-1.678</v>
       </c>
       <c r="J42" s="1">
-        <v>-1.601</v>
+        <v>-1.605</v>
       </c>
       <c r="K42" s="1">
-        <v>-1.36</v>
+        <v>-1.356</v>
       </c>
       <c r="L42" s="1">
-        <v>-1.128</v>
+        <v>-1.096</v>
       </c>
       <c r="M42" s="1">
-        <v>-0.959</v>
+        <v>-0.904</v>
       </c>
       <c r="N42" s="1">
-        <v>-0.825</v>
+        <v>-0.783</v>
       </c>
       <c r="O42" s="1">
-        <v>-0.712</v>
+        <v>-0.715</v>
       </c>
       <c r="P42" s="1">
-        <v>-0.652</v>
+        <v>-0.67</v>
       </c>
       <c r="Q42" s="1">
-        <v>-0.648</v>
+        <v>-0.641</v>
       </c>
       <c r="R42" s="1">
-        <v>-0.678</v>
+        <v>-0.669</v>
       </c>
       <c r="S42" s="1">
-        <v>-0.771</v>
+        <v>-0.763</v>
       </c>
       <c r="T42" s="1">
-        <v>-0.898</v>
+        <v>-0.882</v>
       </c>
       <c r="U42" s="1">
-        <v>-0.9320000000000001</v>
+        <v>-0.9409999999999999</v>
       </c>
     </row>
     <row r="43" spans="1:21">
@@ -3336,64 +3339,64 @@
         <v>41</v>
       </c>
       <c r="B43" s="1">
-        <v>-0.289</v>
+        <v>-0.292</v>
       </c>
       <c r="C43" s="1">
-        <v>-0.435</v>
+        <v>-0.433</v>
       </c>
       <c r="D43" s="1">
-        <v>-0.63</v>
+        <v>-0.636</v>
       </c>
       <c r="E43" s="1">
-        <v>-0.735</v>
+        <v>-0.777</v>
       </c>
       <c r="F43" s="1">
-        <v>-0.835</v>
+        <v>-0.887</v>
       </c>
       <c r="G43" s="1">
-        <v>-0.965</v>
+        <v>-1.031</v>
       </c>
       <c r="H43" s="1">
-        <v>-1.073</v>
+        <v>-1.143</v>
       </c>
       <c r="I43" s="1">
-        <v>-1.043</v>
+        <v>-1.089</v>
       </c>
       <c r="J43" s="1">
-        <v>-0.862</v>
+        <v>-0.925</v>
       </c>
       <c r="K43" s="1">
-        <v>-0.701</v>
+        <v>-0.765</v>
       </c>
       <c r="L43" s="1">
-        <v>-0.616</v>
+        <v>-0.656</v>
       </c>
       <c r="M43" s="1">
-        <v>-0.574</v>
+        <v>-0.573</v>
       </c>
       <c r="N43" s="1">
-        <v>-0.58</v>
+        <v>-0.54</v>
       </c>
       <c r="O43" s="1">
-        <v>-0.614</v>
+        <v>-0.5590000000000001</v>
       </c>
       <c r="P43" s="1">
-        <v>-0.646</v>
+        <v>-0.581</v>
       </c>
       <c r="Q43" s="1">
-        <v>-0.697</v>
+        <v>-0.634</v>
       </c>
       <c r="R43" s="1">
-        <v>-0.788</v>
+        <v>-0.733</v>
       </c>
       <c r="S43" s="1">
-        <v>-0.901</v>
+        <v>-0.863</v>
       </c>
       <c r="T43" s="1">
-        <v>-0.978</v>
+        <v>-0.9350000000000001</v>
       </c>
       <c r="U43" s="1">
-        <v>-0.928</v>
+        <v>-0.878</v>
       </c>
     </row>
     <row r="44" spans="1:21">
@@ -3401,64 +3404,64 @@
         <v>42</v>
       </c>
       <c r="B44" s="1">
-        <v>-0.374</v>
+        <v>-0.377</v>
       </c>
       <c r="C44" s="1">
-        <v>-0.414</v>
+        <v>-0.437</v>
       </c>
       <c r="D44" s="1">
-        <v>-0.493</v>
+        <v>-0.536</v>
       </c>
       <c r="E44" s="1">
-        <v>-0.59</v>
+        <v>-0.639</v>
       </c>
       <c r="F44" s="1">
-        <v>-0.706</v>
+        <v>-0.756</v>
       </c>
       <c r="G44" s="1">
-        <v>-0.793</v>
+        <v>-0.828</v>
       </c>
       <c r="H44" s="1">
-        <v>-0.753</v>
+        <v>-0.787</v>
       </c>
       <c r="I44" s="1">
-        <v>-0.611</v>
+        <v>-0.647</v>
       </c>
       <c r="J44" s="1">
-        <v>-0.48</v>
+        <v>-0.51</v>
       </c>
       <c r="K44" s="1">
-        <v>-0.437</v>
+        <v>-0.449</v>
       </c>
       <c r="L44" s="1">
-        <v>-0.456</v>
+        <v>-0.443</v>
       </c>
       <c r="M44" s="1">
-        <v>-0.487</v>
+        <v>-0.462</v>
       </c>
       <c r="N44" s="1">
-        <v>-0.513</v>
+        <v>-0.495</v>
       </c>
       <c r="O44" s="1">
-        <v>-0.512</v>
+        <v>-0.525</v>
       </c>
       <c r="P44" s="1">
-        <v>-0.532</v>
+        <v>-0.5679999999999999</v>
       </c>
       <c r="Q44" s="1">
-        <v>-0.612</v>
+        <v>-0.643</v>
       </c>
       <c r="R44" s="1">
-        <v>-0.711</v>
+        <v>-0.724</v>
       </c>
       <c r="S44" s="1">
-        <v>-0.753</v>
+        <v>-0.754</v>
       </c>
       <c r="T44" s="1">
-        <v>-0.6899999999999999</v>
+        <v>-0.6820000000000001</v>
       </c>
       <c r="U44" s="1">
-        <v>-0.588</v>
+        <v>-0.544</v>
       </c>
     </row>
     <row r="45" spans="1:21">
@@ -3466,64 +3469,64 @@
         <v>43</v>
       </c>
       <c r="B45" s="1">
-        <v>-0.515</v>
+        <v>-0.516</v>
       </c>
       <c r="C45" s="1">
-        <v>-0.5649999999999999</v>
+        <v>-0.554</v>
       </c>
       <c r="D45" s="1">
-        <v>-0.659</v>
+        <v>-0.678</v>
       </c>
       <c r="E45" s="1">
+        <v>-0.839</v>
+      </c>
+      <c r="F45" s="1">
+        <v>-0.9389999999999999</v>
+      </c>
+      <c r="G45" s="1">
+        <v>-0.91</v>
+      </c>
+      <c r="H45" s="1">
+        <v>-0.773</v>
+      </c>
+      <c r="I45" s="1">
+        <v>-0.635</v>
+      </c>
+      <c r="J45" s="1">
+        <v>-0.5639999999999999</v>
+      </c>
+      <c r="K45" s="1">
+        <v>-0.552</v>
+      </c>
+      <c r="L45" s="1">
+        <v>-0.58</v>
+      </c>
+      <c r="M45" s="1">
+        <v>-0.628</v>
+      </c>
+      <c r="N45" s="1">
+        <v>-0.654</v>
+      </c>
+      <c r="O45" s="1">
+        <v>-0.6929999999999999</v>
+      </c>
+      <c r="P45" s="1">
         <v>-0.786</v>
       </c>
-      <c r="F45" s="1">
-        <v>-0.89</v>
-      </c>
-      <c r="G45" s="1">
-        <v>-0.852</v>
-      </c>
-      <c r="H45" s="1">
-        <v>-0.7</v>
-      </c>
-      <c r="I45" s="1">
-        <v>-0.586</v>
-      </c>
-      <c r="J45" s="1">
-        <v>-0.537</v>
-      </c>
-      <c r="K45" s="1">
-        <v>-0.538</v>
-      </c>
-      <c r="L45" s="1">
-        <v>-0.585</v>
-      </c>
-      <c r="M45" s="1">
-        <v>-0.631</v>
-      </c>
-      <c r="N45" s="1">
-        <v>-0.668</v>
-      </c>
-      <c r="O45" s="1">
-        <v>-0.739</v>
-      </c>
-      <c r="P45" s="1">
-        <v>-0.847</v>
-      </c>
       <c r="Q45" s="1">
-        <v>-0.986</v>
+        <v>-0.899</v>
       </c>
       <c r="R45" s="1">
-        <v>-1.077</v>
+        <v>-0.972</v>
       </c>
       <c r="S45" s="1">
-        <v>-1.02</v>
+        <v>-0.9320000000000001</v>
       </c>
       <c r="T45" s="1">
-        <v>-0.864</v>
+        <v>-0.782</v>
       </c>
       <c r="U45" s="1">
-        <v>-0.734</v>
+        <v>-0.639</v>
       </c>
     </row>
     <row r="46" spans="1:21">
@@ -3531,64 +3534,64 @@
         <v>44</v>
       </c>
       <c r="B46" s="1">
-        <v>-0.82</v>
+        <v>-0.824</v>
       </c>
       <c r="C46" s="1">
-        <v>-0.919</v>
+        <v>-0.899</v>
       </c>
       <c r="D46" s="1">
-        <v>-1.085</v>
+        <v>-1.047</v>
       </c>
       <c r="E46" s="1">
-        <v>-1.204</v>
+        <v>-1.166</v>
       </c>
       <c r="F46" s="1">
-        <v>-1.168</v>
+        <v>-1.126</v>
       </c>
       <c r="G46" s="1">
-        <v>-0.996</v>
+        <v>-0.946</v>
       </c>
       <c r="H46" s="1">
-        <v>-0.796</v>
+        <v>-0.774</v>
       </c>
       <c r="I46" s="1">
+        <v>-0.668</v>
+      </c>
+      <c r="J46" s="1">
+        <v>-0.62</v>
+      </c>
+      <c r="K46" s="1">
+        <v>-0.631</v>
+      </c>
+      <c r="L46" s="1">
+        <v>-0.648</v>
+      </c>
+      <c r="M46" s="1">
         <v>-0.665</v>
       </c>
-      <c r="J46" s="1">
-        <v>-0.609</v>
-      </c>
-      <c r="K46" s="1">
-        <v>-0.582</v>
-      </c>
-      <c r="L46" s="1">
-        <v>-0.578</v>
-      </c>
-      <c r="M46" s="1">
-        <v>-0.587</v>
-      </c>
       <c r="N46" s="1">
-        <v>-0.626</v>
+        <v>-0.725</v>
       </c>
       <c r="O46" s="1">
-        <v>-0.698</v>
+        <v>-0.819</v>
       </c>
       <c r="P46" s="1">
-        <v>-0.795</v>
+        <v>-0.9409999999999999</v>
       </c>
       <c r="Q46" s="1">
-        <v>-0.825</v>
+        <v>-1.028</v>
       </c>
       <c r="R46" s="1">
-        <v>-0.745</v>
+        <v>-0.984</v>
       </c>
       <c r="S46" s="1">
-        <v>-0.641</v>
+        <v>-0.858</v>
       </c>
       <c r="T46" s="1">
-        <v>-0.5570000000000001</v>
+        <v>-0.723</v>
       </c>
       <c r="U46" s="1">
-        <v>-0.499</v>
+        <v>-0.602</v>
       </c>
     </row>
     <row r="47" spans="1:21">
@@ -3596,64 +3599,64 @@
         <v>45</v>
       </c>
       <c r="B47" s="1">
-        <v>-1.017</v>
+        <v>-1.019</v>
       </c>
       <c r="C47" s="1">
-        <v>-1.061</v>
+        <v>-1.075</v>
       </c>
       <c r="D47" s="1">
-        <v>-1.117</v>
+        <v>-1.141</v>
       </c>
       <c r="E47" s="1">
-        <v>-1.041</v>
+        <v>-1.08</v>
       </c>
       <c r="F47" s="1">
-        <v>-0.865</v>
+        <v>-0.895</v>
       </c>
       <c r="G47" s="1">
-        <v>-0.6909999999999999</v>
+        <v>-0.708</v>
       </c>
       <c r="H47" s="1">
-        <v>-0.569</v>
+        <v>-0.587</v>
       </c>
       <c r="I47" s="1">
-        <v>-0.521</v>
+        <v>-0.512</v>
       </c>
       <c r="J47" s="1">
-        <v>-0.502</v>
+        <v>-0.463</v>
       </c>
       <c r="K47" s="1">
-        <v>-0.486</v>
+        <v>-0.456</v>
       </c>
       <c r="L47" s="1">
-        <v>-0.494</v>
+        <v>-0.456</v>
       </c>
       <c r="M47" s="1">
-        <v>-0.527</v>
+        <v>-0.465</v>
       </c>
       <c r="N47" s="1">
-        <v>-0.595</v>
+        <v>-0.516</v>
       </c>
       <c r="O47" s="1">
-        <v>-0.66</v>
+        <v>-0.57</v>
       </c>
       <c r="P47" s="1">
-        <v>-0.655</v>
+        <v>-0.5659999999999999</v>
       </c>
       <c r="Q47" s="1">
-        <v>-0.581</v>
+        <v>-0.485</v>
       </c>
       <c r="R47" s="1">
-        <v>-0.491</v>
+        <v>-0.381</v>
       </c>
       <c r="S47" s="1">
-        <v>-0.436</v>
+        <v>-0.317</v>
       </c>
       <c r="T47" s="1">
-        <v>-0.376</v>
+        <v>-0.273</v>
       </c>
       <c r="U47" s="1">
-        <v>-0.261</v>
+        <v>-0.199</v>
       </c>
     </row>
     <row r="48" spans="1:21">
@@ -3661,64 +3664,64 @@
         <v>46</v>
       </c>
       <c r="B48" s="1">
-        <v>-0.8</v>
+        <v>-0.792</v>
       </c>
       <c r="C48" s="1">
-        <v>-0.841</v>
+        <v>-0.821</v>
       </c>
       <c r="D48" s="1">
-        <v>-0.821</v>
+        <v>-0.793</v>
       </c>
       <c r="E48" s="1">
-        <v>-0.6909999999999999</v>
+        <v>-0.671</v>
       </c>
       <c r="F48" s="1">
-        <v>-0.54</v>
+        <v>-0.528</v>
       </c>
       <c r="G48" s="1">
-        <v>-0.45</v>
+        <v>-0.446</v>
       </c>
       <c r="H48" s="1">
-        <v>-0.438</v>
+        <v>-0.467</v>
       </c>
       <c r="I48" s="1">
-        <v>-0.479</v>
+        <v>-0.554</v>
       </c>
       <c r="J48" s="1">
-        <v>-0.521</v>
+        <v>-0.616</v>
       </c>
       <c r="K48" s="1">
-        <v>-0.579</v>
+        <v>-0.637</v>
       </c>
       <c r="L48" s="1">
-        <v>-0.653</v>
+        <v>-0.666</v>
       </c>
       <c r="M48" s="1">
-        <v>-0.747</v>
+        <v>-0.733</v>
       </c>
       <c r="N48" s="1">
-        <v>-0.853</v>
+        <v>-0.836</v>
       </c>
       <c r="O48" s="1">
-        <v>-0.928</v>
+        <v>-0.897</v>
       </c>
       <c r="P48" s="1">
-        <v>-0.894</v>
+        <v>-0.835</v>
       </c>
       <c r="Q48" s="1">
-        <v>-0.772</v>
+        <v>-0.6840000000000001</v>
       </c>
       <c r="R48" s="1">
-        <v>-0.664</v>
+        <v>-0.55</v>
       </c>
       <c r="S48" s="1">
-        <v>-0.578</v>
+        <v>-0.456</v>
       </c>
       <c r="T48" s="1">
-        <v>-0.466</v>
+        <v>-0.344</v>
       </c>
       <c r="U48" s="1">
-        <v>-0.305</v>
+        <v>-0.192</v>
       </c>
     </row>
     <row r="49" spans="1:21">
@@ -3726,64 +3729,64 @@
         <v>47</v>
       </c>
       <c r="B49" s="1">
-        <v>-1.138</v>
+        <v>-1.134</v>
       </c>
       <c r="C49" s="1">
-        <v>-1.083</v>
+        <v>-1.076</v>
       </c>
       <c r="D49" s="1">
-        <v>-0.9340000000000001</v>
+        <v>-0.921</v>
       </c>
       <c r="E49" s="1">
-        <v>-0.769</v>
+        <v>-0.756</v>
       </c>
       <c r="F49" s="1">
         <v>-0.665</v>
       </c>
       <c r="G49" s="1">
-        <v>-0.587</v>
+        <v>-0.634</v>
       </c>
       <c r="H49" s="1">
-        <v>-0.533</v>
+        <v>-0.631</v>
       </c>
       <c r="I49" s="1">
-        <v>-0.543</v>
+        <v>-0.637</v>
       </c>
       <c r="J49" s="1">
-        <v>-0.587</v>
+        <v>-0.65</v>
       </c>
       <c r="K49" s="1">
-        <v>-0.666</v>
+        <v>-0.717</v>
       </c>
       <c r="L49" s="1">
-        <v>-0.769</v>
+        <v>-0.861</v>
       </c>
       <c r="M49" s="1">
-        <v>-0.877</v>
+        <v>-0.987</v>
       </c>
       <c r="N49" s="1">
-        <v>-0.93</v>
+        <v>-1.005</v>
       </c>
       <c r="O49" s="1">
-        <v>-0.852</v>
+        <v>-0.902</v>
       </c>
       <c r="P49" s="1">
-        <v>-0.705</v>
+        <v>-0.758</v>
       </c>
       <c r="Q49" s="1">
-        <v>-0.586</v>
+        <v>-0.661</v>
       </c>
       <c r="R49" s="1">
-        <v>-0.486</v>
+        <v>-0.583</v>
       </c>
       <c r="S49" s="1">
-        <v>-0.35</v>
+        <v>-0.444</v>
       </c>
       <c r="T49" s="1">
-        <v>-0.161</v>
+        <v>-0.258</v>
       </c>
       <c r="U49" s="1">
-        <v>0.008999999999999999</v>
+        <v>-0.07000000000000001</v>
       </c>
     </row>
     <row r="50" spans="1:21">
@@ -3794,61 +3797,61 @@
         <v>-1.279</v>
       </c>
       <c r="C50" s="1">
-        <v>-1.119</v>
+        <v>-1.106</v>
       </c>
       <c r="D50" s="1">
-        <v>-0.872</v>
+        <v>-0.856</v>
       </c>
       <c r="E50" s="1">
-        <v>-0.701</v>
+        <v>-0.72</v>
       </c>
       <c r="F50" s="1">
-        <v>-0.612</v>
+        <v>-0.654</v>
       </c>
       <c r="G50" s="1">
-        <v>-0.599</v>
+        <v>-0.626</v>
       </c>
       <c r="H50" s="1">
-        <v>-0.627</v>
+        <v>-0.636</v>
       </c>
       <c r="I50" s="1">
-        <v>-0.656</v>
+        <v>-0.676</v>
       </c>
       <c r="J50" s="1">
-        <v>-0.6919999999999999</v>
+        <v>-0.756</v>
       </c>
       <c r="K50" s="1">
-        <v>-0.765</v>
+        <v>-0.865</v>
       </c>
       <c r="L50" s="1">
-        <v>-0.852</v>
+        <v>-0.977</v>
       </c>
       <c r="M50" s="1">
-        <v>-0.895</v>
+        <v>-1.014</v>
       </c>
       <c r="N50" s="1">
-        <v>-0.828</v>
+        <v>-0.927</v>
       </c>
       <c r="O50" s="1">
-        <v>-0.703</v>
+        <v>-0.774</v>
       </c>
       <c r="P50" s="1">
-        <v>-0.598</v>
+        <v>-0.641</v>
       </c>
       <c r="Q50" s="1">
-        <v>-0.501</v>
+        <v>-0.529</v>
       </c>
       <c r="R50" s="1">
-        <v>-0.347</v>
+        <v>-0.392</v>
       </c>
       <c r="S50" s="1">
-        <v>-0.168</v>
+        <v>-0.239</v>
       </c>
       <c r="T50" s="1">
-        <v>-0.018</v>
+        <v>-0.096</v>
       </c>
       <c r="U50" s="1">
-        <v>0.07199999999999999</v>
+        <v>0.012</v>
       </c>
     </row>
     <row r="51" spans="1:21">
@@ -3856,64 +3859,64 @@
         <v>49</v>
       </c>
       <c r="B51" s="1">
-        <v>-0.914</v>
+        <v>-0.913</v>
       </c>
       <c r="C51" s="1">
-        <v>-0.772</v>
+        <v>-0.779</v>
       </c>
       <c r="D51" s="1">
-        <v>-0.606</v>
+        <v>-0.618</v>
       </c>
       <c r="E51" s="1">
-        <v>-0.5600000000000001</v>
+        <v>-0.571</v>
       </c>
       <c r="F51" s="1">
-        <v>-0.582</v>
+        <v>-0.61</v>
       </c>
       <c r="G51" s="1">
-        <v>-0.598</v>
+        <v>-0.641</v>
       </c>
       <c r="H51" s="1">
-        <v>-0.595</v>
+        <v>-0.625</v>
       </c>
       <c r="I51" s="1">
-        <v>-0.605</v>
+        <v>-0.629</v>
       </c>
       <c r="J51" s="1">
-        <v>-0.653</v>
+        <v>-0.696</v>
       </c>
       <c r="K51" s="1">
-        <v>-0.741</v>
+        <v>-0.776</v>
       </c>
       <c r="L51" s="1">
-        <v>-0.792</v>
+        <v>-0.8080000000000001</v>
       </c>
       <c r="M51" s="1">
-        <v>-0.745</v>
+        <v>-0.746</v>
       </c>
       <c r="N51" s="1">
-        <v>-0.633</v>
+        <v>-0.624</v>
       </c>
       <c r="O51" s="1">
-        <v>-0.521</v>
+        <v>-0.525</v>
       </c>
       <c r="P51" s="1">
-        <v>-0.426</v>
+        <v>-0.465</v>
       </c>
       <c r="Q51" s="1">
-        <v>-0.328</v>
+        <v>-0.372</v>
       </c>
       <c r="R51" s="1">
-        <v>-0.215</v>
+        <v>-0.232</v>
       </c>
       <c r="S51" s="1">
-        <v>-0.099</v>
+        <v>-0.12</v>
       </c>
       <c r="T51" s="1">
-        <v>-0.007</v>
+        <v>-0.031</v>
       </c>
       <c r="U51" s="1">
-        <v>0.047</v>
+        <v>0.031</v>
       </c>
     </row>
     <row r="52" spans="1:21">
@@ -3921,64 +3924,64 @@
         <v>50</v>
       </c>
       <c r="B52" s="1">
-        <v>-0.346</v>
+        <v>-0.341</v>
       </c>
       <c r="C52" s="1">
-        <v>-0.32</v>
+        <v>-0.321</v>
       </c>
       <c r="D52" s="1">
-        <v>-0.296</v>
+        <v>-0.306</v>
       </c>
       <c r="E52" s="1">
-        <v>-0.31</v>
+        <v>-0.306</v>
       </c>
       <c r="F52" s="1">
-        <v>-0.332</v>
+        <v>-0.295</v>
       </c>
       <c r="G52" s="1">
-        <v>-0.342</v>
+        <v>-0.272</v>
       </c>
       <c r="H52" s="1">
-        <v>-0.35</v>
+        <v>-0.266</v>
       </c>
       <c r="I52" s="1">
-        <v>-0.373</v>
+        <v>-0.299</v>
       </c>
       <c r="J52" s="1">
-        <v>-0.416</v>
+        <v>-0.355</v>
       </c>
       <c r="K52" s="1">
-        <v>-0.412</v>
+        <v>-0.371</v>
       </c>
       <c r="L52" s="1">
-        <v>-0.359</v>
+        <v>-0.36</v>
       </c>
       <c r="M52" s="1">
-        <v>-0.289</v>
+        <v>-0.307</v>
       </c>
       <c r="N52" s="1">
-        <v>-0.215</v>
+        <v>-0.241</v>
       </c>
       <c r="O52" s="1">
+        <v>-0.213</v>
+      </c>
+      <c r="P52" s="1">
         <v>-0.183</v>
       </c>
-      <c r="P52" s="1">
-        <v>-0.19</v>
-      </c>
       <c r="Q52" s="1">
-        <v>-0.208</v>
+        <v>-0.151</v>
       </c>
       <c r="R52" s="1">
-        <v>-0.217</v>
+        <v>-0.139</v>
       </c>
       <c r="S52" s="1">
-        <v>-0.205</v>
+        <v>-0.139</v>
       </c>
       <c r="T52" s="1">
-        <v>-0.209</v>
+        <v>-0.145</v>
       </c>
       <c r="U52" s="1">
-        <v>-0.238</v>
+        <v>-0.151</v>
       </c>
     </row>
     <row r="53" spans="1:21">
@@ -3986,64 +3989,64 @@
         <v>51</v>
       </c>
       <c r="B53" s="1">
-        <v>-0.489</v>
+        <v>-0.491</v>
       </c>
       <c r="C53" s="1">
-        <v>-0.462</v>
+        <v>-0.453</v>
       </c>
       <c r="D53" s="1">
-        <v>-0.426</v>
+        <v>-0.405</v>
       </c>
       <c r="E53" s="1">
-        <v>-0.386</v>
+        <v>-0.377</v>
       </c>
       <c r="F53" s="1">
-        <v>-0.359</v>
+        <v>-0.348</v>
       </c>
       <c r="G53" s="1">
         <v>-0.348</v>
       </c>
       <c r="H53" s="1">
-        <v>-0.353</v>
+        <v>-0.381</v>
       </c>
       <c r="I53" s="1">
-        <v>-0.355</v>
+        <v>-0.4</v>
       </c>
       <c r="J53" s="1">
-        <v>-0.301</v>
+        <v>-0.376</v>
       </c>
       <c r="K53" s="1">
-        <v>-0.214</v>
+        <v>-0.287</v>
       </c>
       <c r="L53" s="1">
-        <v>-0.142</v>
+        <v>-0.191</v>
       </c>
       <c r="M53" s="1">
-        <v>-0.126</v>
+        <v>-0.136</v>
       </c>
       <c r="N53" s="1">
-        <v>-0.137</v>
+        <v>-0.112</v>
       </c>
       <c r="O53" s="1">
-        <v>-0.121</v>
+        <v>-0.081</v>
       </c>
       <c r="P53" s="1">
-        <v>-0.075</v>
+        <v>-0.032</v>
       </c>
       <c r="Q53" s="1">
-        <v>-0.05</v>
+        <v>0.022</v>
       </c>
       <c r="R53" s="1">
-        <v>-0.046</v>
+        <v>0.063</v>
       </c>
       <c r="S53" s="1">
-        <v>-0.048</v>
+        <v>0.08400000000000001</v>
       </c>
       <c r="T53" s="1">
-        <v>-0.054</v>
+        <v>0.097</v>
       </c>
       <c r="U53" s="1">
-        <v>-0.042</v>
+        <v>0.128</v>
       </c>
     </row>
     <row r="54" spans="1:21">
@@ -4051,64 +4054,64 @@
         <v>52</v>
       </c>
       <c r="B54" s="1">
-        <v>-0.375</v>
+        <v>-0.372</v>
       </c>
       <c r="C54" s="1">
-        <v>-0.374</v>
+        <v>-0.366</v>
       </c>
       <c r="D54" s="1">
-        <v>-0.377</v>
+        <v>-0.382</v>
       </c>
       <c r="E54" s="1">
-        <v>-0.393</v>
+        <v>-0.408</v>
       </c>
       <c r="F54" s="1">
-        <v>-0.407</v>
+        <v>-0.436</v>
       </c>
       <c r="G54" s="1">
-        <v>-0.431</v>
+        <v>-0.48</v>
       </c>
       <c r="H54" s="1">
-        <v>-0.481</v>
+        <v>-0.516</v>
       </c>
       <c r="I54" s="1">
-        <v>-0.511</v>
+        <v>-0.51</v>
       </c>
       <c r="J54" s="1">
         <v>-0.457</v>
       </c>
       <c r="K54" s="1">
-        <v>-0.363</v>
+        <v>-0.388</v>
       </c>
       <c r="L54" s="1">
-        <v>-0.292</v>
+        <v>-0.329</v>
       </c>
       <c r="M54" s="1">
-        <v>-0.248</v>
+        <v>-0.269</v>
       </c>
       <c r="N54" s="1">
-        <v>-0.206</v>
+        <v>-0.198</v>
       </c>
       <c r="O54" s="1">
-        <v>-0.146</v>
+        <v>-0.133</v>
       </c>
       <c r="P54" s="1">
-        <v>-0.093</v>
+        <v>-0.062</v>
       </c>
       <c r="Q54" s="1">
-        <v>-0.06</v>
+        <v>-0</v>
       </c>
       <c r="R54" s="1">
-        <v>-0.042</v>
+        <v>0.018</v>
       </c>
       <c r="S54" s="1">
-        <v>-0.039</v>
+        <v>0.01</v>
       </c>
       <c r="T54" s="1">
-        <v>-0.033</v>
+        <v>0.034</v>
       </c>
       <c r="U54" s="1">
-        <v>-0.005</v>
+        <v>0.08500000000000001</v>
       </c>
     </row>
     <row r="55" spans="1:21">
@@ -4116,64 +4119,64 @@
         <v>53</v>
       </c>
       <c r="B55" s="1">
-        <v>-0.279</v>
+        <v>-0.276</v>
       </c>
       <c r="C55" s="1">
-        <v>-0.334</v>
+        <v>-0.328</v>
       </c>
       <c r="D55" s="1">
-        <v>-0.398</v>
+        <v>-0.399</v>
       </c>
       <c r="E55" s="1">
-        <v>-0.433</v>
+        <v>-0.447</v>
       </c>
       <c r="F55" s="1">
-        <v>-0.474</v>
+        <v>-0.466</v>
       </c>
       <c r="G55" s="1">
-        <v>-0.496</v>
+        <v>-0.511</v>
       </c>
       <c r="H55" s="1">
-        <v>-0.468</v>
+        <v>-0.5629999999999999</v>
       </c>
       <c r="I55" s="1">
-        <v>-0.408</v>
+        <v>-0.534</v>
       </c>
       <c r="J55" s="1">
-        <v>-0.338</v>
+        <v>-0.456</v>
       </c>
       <c r="K55" s="1">
-        <v>-0.274</v>
+        <v>-0.381</v>
       </c>
       <c r="L55" s="1">
-        <v>-0.21</v>
+        <v>-0.307</v>
       </c>
       <c r="M55" s="1">
-        <v>-0.147</v>
+        <v>-0.235</v>
       </c>
       <c r="N55" s="1">
-        <v>-0.093</v>
+        <v>-0.18</v>
       </c>
       <c r="O55" s="1">
-        <v>-0.053</v>
+        <v>-0.135</v>
       </c>
       <c r="P55" s="1">
-        <v>-0.026</v>
+        <v>-0.108</v>
       </c>
       <c r="Q55" s="1">
-        <v>0.006</v>
+        <v>-0.092</v>
       </c>
       <c r="R55" s="1">
-        <v>0.034</v>
+        <v>-0.11</v>
       </c>
       <c r="S55" s="1">
-        <v>0.064</v>
+        <v>-0.16</v>
       </c>
       <c r="T55" s="1">
-        <v>0.083</v>
+        <v>-0.19</v>
       </c>
       <c r="U55" s="1">
-        <v>0.092</v>
+        <v>-0.18</v>
       </c>
     </row>
     <row r="56" spans="1:21">
@@ -4181,64 +4184,64 @@
         <v>54</v>
       </c>
       <c r="B56" s="1">
-        <v>-0.378</v>
+        <v>-0.376</v>
       </c>
       <c r="C56" s="1">
-        <v>-0.428</v>
+        <v>-0.433</v>
       </c>
       <c r="D56" s="1">
-        <v>-0.502</v>
+        <v>-0.495</v>
       </c>
       <c r="E56" s="1">
-        <v>-0.586</v>
+        <v>-0.553</v>
       </c>
       <c r="F56" s="1">
-        <v>-0.677</v>
+        <v>-0.631</v>
       </c>
       <c r="G56" s="1">
-        <v>-0.729</v>
+        <v>-0.676</v>
       </c>
       <c r="H56" s="1">
-        <v>-0.695</v>
+        <v>-0.635</v>
       </c>
       <c r="I56" s="1">
-        <v>-0.59</v>
+        <v>-0.546</v>
       </c>
       <c r="J56" s="1">
-        <v>-0.476</v>
+        <v>-0.46</v>
       </c>
       <c r="K56" s="1">
-        <v>-0.391</v>
+        <v>-0.394</v>
       </c>
       <c r="L56" s="1">
-        <v>-0.323</v>
+        <v>-0.342</v>
       </c>
       <c r="M56" s="1">
-        <v>-0.253</v>
+        <v>-0.308</v>
       </c>
       <c r="N56" s="1">
-        <v>-0.198</v>
+        <v>-0.281</v>
       </c>
       <c r="O56" s="1">
-        <v>-0.167</v>
+        <v>-0.248</v>
       </c>
       <c r="P56" s="1">
-        <v>-0.158</v>
+        <v>-0.231</v>
       </c>
       <c r="Q56" s="1">
-        <v>-0.183</v>
+        <v>-0.235</v>
       </c>
       <c r="R56" s="1">
-        <v>-0.198</v>
+        <v>-0.267</v>
       </c>
       <c r="S56" s="1">
-        <v>-0.201</v>
+        <v>-0.308</v>
       </c>
       <c r="T56" s="1">
-        <v>-0.159</v>
+        <v>-0.316</v>
       </c>
       <c r="U56" s="1">
-        <v>-0.117</v>
+        <v>-0.288</v>
       </c>
     </row>
     <row r="57" spans="1:21">
@@ -4246,64 +4249,64 @@
         <v>55</v>
       </c>
       <c r="B57" s="1">
-        <v>-0.6</v>
+        <v>-0.598</v>
       </c>
       <c r="C57" s="1">
-        <v>-0.624</v>
+        <v>-0.629</v>
       </c>
       <c r="D57" s="1">
-        <v>-0.695</v>
+        <v>-0.706</v>
       </c>
       <c r="E57" s="1">
-        <v>-0.78</v>
+        <v>-0.834</v>
       </c>
       <c r="F57" s="1">
-        <v>-0.846</v>
+        <v>-0.9419999999999999</v>
       </c>
       <c r="G57" s="1">
-        <v>-0.82</v>
+        <v>-0.917</v>
       </c>
       <c r="H57" s="1">
-        <v>-0.697</v>
+        <v>-0.788</v>
       </c>
       <c r="I57" s="1">
-        <v>-0.552</v>
+        <v>-0.638</v>
       </c>
       <c r="J57" s="1">
-        <v>-0.44</v>
+        <v>-0.512</v>
       </c>
       <c r="K57" s="1">
-        <v>-0.36</v>
+        <v>-0.411</v>
       </c>
       <c r="L57" s="1">
-        <v>-0.291</v>
+        <v>-0.322</v>
       </c>
       <c r="M57" s="1">
-        <v>-0.241</v>
+        <v>-0.249</v>
       </c>
       <c r="N57" s="1">
-        <v>-0.2</v>
+        <v>-0.215</v>
       </c>
       <c r="O57" s="1">
-        <v>-0.177</v>
+        <v>-0.221</v>
       </c>
       <c r="P57" s="1">
-        <v>-0.171</v>
+        <v>-0.246</v>
       </c>
       <c r="Q57" s="1">
-        <v>-0.184</v>
+        <v>-0.297</v>
       </c>
       <c r="R57" s="1">
-        <v>-0.184</v>
+        <v>-0.344</v>
       </c>
       <c r="S57" s="1">
-        <v>-0.144</v>
+        <v>-0.325</v>
       </c>
       <c r="T57" s="1">
-        <v>-0.096</v>
+        <v>-0.264</v>
       </c>
       <c r="U57" s="1">
-        <v>-0.06900000000000001</v>
+        <v>-0.231</v>
       </c>
     </row>
     <row r="58" spans="1:21">
@@ -4311,64 +4314,64 @@
         <v>56</v>
       </c>
       <c r="B58" s="1">
-        <v>-0.732</v>
+        <v>-0.73</v>
       </c>
       <c r="C58" s="1">
-        <v>-0.8</v>
+        <v>-0.777</v>
       </c>
       <c r="D58" s="1">
-        <v>-0.9419999999999999</v>
+        <v>-0.89</v>
       </c>
       <c r="E58" s="1">
-        <v>-1.025</v>
+        <v>-0.979</v>
       </c>
       <c r="F58" s="1">
-        <v>-0.971</v>
+        <v>-0.9350000000000001</v>
       </c>
       <c r="G58" s="1">
-        <v>-0.82</v>
+        <v>-0.8080000000000001</v>
       </c>
       <c r="H58" s="1">
-        <v>-0.6860000000000001</v>
+        <v>-0.654</v>
       </c>
       <c r="I58" s="1">
-        <v>-0.577</v>
+        <v>-0.515</v>
       </c>
       <c r="J58" s="1">
-        <v>-0.463</v>
+        <v>-0.394</v>
       </c>
       <c r="K58" s="1">
-        <v>-0.351</v>
+        <v>-0.298</v>
       </c>
       <c r="L58" s="1">
-        <v>-0.259</v>
+        <v>-0.233</v>
       </c>
       <c r="M58" s="1">
-        <v>-0.215</v>
+        <v>-0.188</v>
       </c>
       <c r="N58" s="1">
-        <v>-0.205</v>
+        <v>-0.173</v>
       </c>
       <c r="O58" s="1">
-        <v>-0.235</v>
+        <v>-0.192</v>
       </c>
       <c r="P58" s="1">
-        <v>-0.259</v>
+        <v>-0.207</v>
       </c>
       <c r="Q58" s="1">
-        <v>-0.233</v>
+        <v>-0.196</v>
       </c>
       <c r="R58" s="1">
-        <v>-0.183</v>
+        <v>-0.162</v>
       </c>
       <c r="S58" s="1">
-        <v>-0.145</v>
+        <v>-0.115</v>
       </c>
       <c r="T58" s="1">
-        <v>-0.134</v>
+        <v>-0.097</v>
       </c>
       <c r="U58" s="1">
-        <v>-0.136</v>
+        <v>-0.103</v>
       </c>
     </row>
     <row r="59" spans="1:21">
@@ -4376,64 +4379,64 @@
         <v>57</v>
       </c>
       <c r="B59" s="1">
-        <v>-0.826</v>
+        <v>-0.8169999999999999</v>
       </c>
       <c r="C59" s="1">
-        <v>-0.866</v>
+        <v>-0.861</v>
       </c>
       <c r="D59" s="1">
-        <v>-0.894</v>
+        <v>-0.897</v>
       </c>
       <c r="E59" s="1">
-        <v>-0.8100000000000001</v>
+        <v>-0.837</v>
       </c>
       <c r="F59" s="1">
-        <v>-0.669</v>
+        <v>-0.6830000000000001</v>
       </c>
       <c r="G59" s="1">
-        <v>-0.537</v>
+        <v>-0.531</v>
       </c>
       <c r="H59" s="1">
-        <v>-0.426</v>
+        <v>-0.424</v>
       </c>
       <c r="I59" s="1">
-        <v>-0.322</v>
+        <v>-0.315</v>
       </c>
       <c r="J59" s="1">
-        <v>-0.222</v>
+        <v>-0.196</v>
       </c>
       <c r="K59" s="1">
-        <v>-0.138</v>
+        <v>-0.092</v>
       </c>
       <c r="L59" s="1">
-        <v>-0.07199999999999999</v>
+        <v>-0.017</v>
       </c>
       <c r="M59" s="1">
-        <v>-0.013</v>
+        <v>0.03</v>
       </c>
       <c r="N59" s="1">
-        <v>0.023</v>
+        <v>0.067</v>
       </c>
       <c r="O59" s="1">
-        <v>0.051</v>
+        <v>0.128</v>
       </c>
       <c r="P59" s="1">
-        <v>0.083</v>
+        <v>0.209</v>
       </c>
       <c r="Q59" s="1">
-        <v>0.122</v>
+        <v>0.258</v>
       </c>
       <c r="R59" s="1">
-        <v>0.117</v>
+        <v>0.239</v>
       </c>
       <c r="S59" s="1">
-        <v>0.067</v>
+        <v>0.201</v>
       </c>
       <c r="T59" s="1">
-        <v>0.023</v>
+        <v>0.154</v>
       </c>
       <c r="U59" s="1">
-        <v>0.006</v>
+        <v>0.127</v>
       </c>
     </row>
     <row r="60" spans="1:21">
@@ -4441,64 +4444,64 @@
         <v>58</v>
       </c>
       <c r="B60" s="1">
-        <v>-0.914</v>
+        <v>-0.913</v>
       </c>
       <c r="C60" s="1">
-        <v>-0.887</v>
+        <v>-0.878</v>
       </c>
       <c r="D60" s="1">
-        <v>-0.749</v>
+        <v>-0.741</v>
       </c>
       <c r="E60" s="1">
-        <v>-0.586</v>
+        <v>-0.596</v>
       </c>
       <c r="F60" s="1">
-        <v>-0.468</v>
+        <v>-0.477</v>
       </c>
       <c r="G60" s="1">
-        <v>-0.356</v>
+        <v>-0.352</v>
       </c>
       <c r="H60" s="1">
-        <v>-0.212</v>
+        <v>-0.223</v>
       </c>
       <c r="I60" s="1">
-        <v>-0.076</v>
+        <v>-0.104</v>
       </c>
       <c r="J60" s="1">
-        <v>0.022</v>
+        <v>-0.017</v>
       </c>
       <c r="K60" s="1">
-        <v>0.094</v>
+        <v>0.056</v>
       </c>
       <c r="L60" s="1">
-        <v>0.173</v>
+        <v>0.097</v>
       </c>
       <c r="M60" s="1">
-        <v>0.254</v>
+        <v>0.123</v>
       </c>
       <c r="N60" s="1">
-        <v>0.333</v>
+        <v>0.169</v>
       </c>
       <c r="O60" s="1">
-        <v>0.425</v>
+        <v>0.228</v>
       </c>
       <c r="P60" s="1">
-        <v>0.484</v>
+        <v>0.263</v>
       </c>
       <c r="Q60" s="1">
-        <v>0.478</v>
+        <v>0.248</v>
       </c>
       <c r="R60" s="1">
-        <v>0.416</v>
+        <v>0.204</v>
       </c>
       <c r="S60" s="1">
-        <v>0.322</v>
+        <v>0.148</v>
       </c>
       <c r="T60" s="1">
-        <v>0.265</v>
+        <v>0.09</v>
       </c>
       <c r="U60" s="1">
-        <v>0.229</v>
+        <v>0.058</v>
       </c>
     </row>
     <row r="61" spans="1:21">
@@ -4506,64 +4509,64 @@
         <v>59</v>
       </c>
       <c r="B61" s="1">
-        <v>-0.903</v>
+        <v>-0.907</v>
       </c>
       <c r="C61" s="1">
-        <v>-0.772</v>
+        <v>-0.78</v>
       </c>
       <c r="D61" s="1">
-        <v>-0.571</v>
+        <v>-0.569</v>
       </c>
       <c r="E61" s="1">
-        <v>-0.426</v>
+        <v>-0.42</v>
       </c>
       <c r="F61" s="1">
-        <v>-0.328</v>
+        <v>-0.302</v>
       </c>
       <c r="G61" s="1">
-        <v>-0.212</v>
+        <v>-0.167</v>
       </c>
       <c r="H61" s="1">
-        <v>-0.065</v>
+        <v>-0.018</v>
       </c>
       <c r="I61" s="1">
-        <v>0.057</v>
+        <v>0.112</v>
       </c>
       <c r="J61" s="1">
-        <v>0.134</v>
+        <v>0.225</v>
       </c>
       <c r="K61" s="1">
-        <v>0.214</v>
+        <v>0.337</v>
       </c>
       <c r="L61" s="1">
-        <v>0.289</v>
+        <v>0.456</v>
       </c>
       <c r="M61" s="1">
-        <v>0.362</v>
+        <v>0.584</v>
       </c>
       <c r="N61" s="1">
-        <v>0.441</v>
+        <v>0.6830000000000001</v>
       </c>
       <c r="O61" s="1">
-        <v>0.48</v>
+        <v>0.726</v>
       </c>
       <c r="P61" s="1">
-        <v>0.468</v>
+        <v>0.6909999999999999</v>
       </c>
       <c r="Q61" s="1">
-        <v>0.399</v>
+        <v>0.605</v>
       </c>
       <c r="R61" s="1">
-        <v>0.296</v>
+        <v>0.502</v>
       </c>
       <c r="S61" s="1">
-        <v>0.195</v>
+        <v>0.374</v>
       </c>
       <c r="T61" s="1">
-        <v>0.11</v>
+        <v>0.245</v>
       </c>
       <c r="U61" s="1">
-        <v>0.046</v>
+        <v>0.164</v>
       </c>
     </row>
     <row r="62" spans="1:21">
@@ -4571,64 +4574,64 @@
         <v>60</v>
       </c>
       <c r="B62" s="1">
-        <v>-0.882</v>
+        <v>-0.888</v>
       </c>
       <c r="C62" s="1">
-        <v>-0.739</v>
+        <v>-0.749</v>
       </c>
       <c r="D62" s="1">
-        <v>-0.5679999999999999</v>
+        <v>-0.574</v>
       </c>
       <c r="E62" s="1">
-        <v>-0.447</v>
+        <v>-0.464</v>
       </c>
       <c r="F62" s="1">
-        <v>-0.316</v>
+        <v>-0.335</v>
       </c>
       <c r="G62" s="1">
-        <v>-0.148</v>
+        <v>-0.162</v>
       </c>
       <c r="H62" s="1">
-        <v>0.018</v>
+        <v>0.026</v>
       </c>
       <c r="I62" s="1">
-        <v>0.151</v>
+        <v>0.177</v>
       </c>
       <c r="J62" s="1">
-        <v>0.256</v>
+        <v>0.304</v>
       </c>
       <c r="K62" s="1">
-        <v>0.343</v>
+        <v>0.456</v>
       </c>
       <c r="L62" s="1">
-        <v>0.462</v>
+        <v>0.618</v>
       </c>
       <c r="M62" s="1">
-        <v>0.598</v>
+        <v>0.738</v>
       </c>
       <c r="N62" s="1">
-        <v>0.666</v>
+        <v>0.788</v>
       </c>
       <c r="O62" s="1">
-        <v>0.633</v>
+        <v>0.755</v>
       </c>
       <c r="P62" s="1">
-        <v>0.55</v>
+        <v>0.667</v>
       </c>
       <c r="Q62" s="1">
-        <v>0.446</v>
+        <v>0.532</v>
       </c>
       <c r="R62" s="1">
-        <v>0.326</v>
+        <v>0.394</v>
       </c>
       <c r="S62" s="1">
-        <v>0.223</v>
+        <v>0.272</v>
       </c>
       <c r="T62" s="1">
-        <v>0.145</v>
+        <v>0.174</v>
       </c>
       <c r="U62" s="1">
-        <v>0.08599999999999999</v>
+        <v>0.124</v>
       </c>
     </row>
     <row r="63" spans="1:21">
@@ -4636,64 +4639,64 @@
         <v>61</v>
       </c>
       <c r="B63" s="1">
-        <v>-0.657</v>
+        <v>-0.664</v>
       </c>
       <c r="C63" s="1">
-        <v>-0.574</v>
+        <v>-0.575</v>
       </c>
       <c r="D63" s="1">
-        <v>-0.429</v>
+        <v>-0.423</v>
       </c>
       <c r="E63" s="1">
-        <v>-0.274</v>
+        <v>-0.242</v>
       </c>
       <c r="F63" s="1">
-        <v>-0.099</v>
+        <v>-0.04</v>
       </c>
       <c r="G63" s="1">
-        <v>0.082</v>
+        <v>0.11</v>
       </c>
       <c r="H63" s="1">
-        <v>0.214</v>
+        <v>0.213</v>
       </c>
       <c r="I63" s="1">
-        <v>0.311</v>
+        <v>0.289</v>
       </c>
       <c r="J63" s="1">
-        <v>0.41</v>
+        <v>0.381</v>
       </c>
       <c r="K63" s="1">
-        <v>0.5570000000000001</v>
+        <v>0.524</v>
       </c>
       <c r="L63" s="1">
-        <v>0.703</v>
+        <v>0.665</v>
       </c>
       <c r="M63" s="1">
-        <v>0.764</v>
+        <v>0.72</v>
       </c>
       <c r="N63" s="1">
-        <v>0.732</v>
+        <v>0.695</v>
       </c>
       <c r="O63" s="1">
-        <v>0.623</v>
+        <v>0.573</v>
       </c>
       <c r="P63" s="1">
-        <v>0.469</v>
+        <v>0.408</v>
       </c>
       <c r="Q63" s="1">
-        <v>0.306</v>
+        <v>0.263</v>
       </c>
       <c r="R63" s="1">
-        <v>0.119</v>
+        <v>0.097</v>
       </c>
       <c r="S63" s="1">
-        <v>-0.031</v>
+        <v>-0.053</v>
       </c>
       <c r="T63" s="1">
-        <v>-0.123</v>
+        <v>-0.141</v>
       </c>
       <c r="U63" s="1">
-        <v>-0.177</v>
+        <v>-0.192</v>
       </c>
     </row>
     <row r="64" spans="1:21">
@@ -4701,64 +4704,64 @@
         <v>62</v>
       </c>
       <c r="B64" s="1">
-        <v>-0.388</v>
+        <v>-0.4</v>
       </c>
       <c r="C64" s="1">
-        <v>-0.273</v>
+        <v>-0.286</v>
       </c>
       <c r="D64" s="1">
-        <v>-0.056</v>
+        <v>-0.06900000000000001</v>
       </c>
       <c r="E64" s="1">
-        <v>0.182</v>
+        <v>0.164</v>
       </c>
       <c r="F64" s="1">
-        <v>0.401</v>
+        <v>0.377</v>
       </c>
       <c r="G64" s="1">
-        <v>0.59</v>
+        <v>0.545</v>
       </c>
       <c r="H64" s="1">
-        <v>0.786</v>
+        <v>0.718</v>
       </c>
       <c r="I64" s="1">
-        <v>1.034</v>
+        <v>0.951</v>
       </c>
       <c r="J64" s="1">
-        <v>1.301</v>
+        <v>1.237</v>
       </c>
       <c r="K64" s="1">
-        <v>1.516</v>
+        <v>1.489</v>
       </c>
       <c r="L64" s="1">
-        <v>1.609</v>
+        <v>1.586</v>
       </c>
       <c r="M64" s="1">
-        <v>1.516</v>
+        <v>1.501</v>
       </c>
       <c r="N64" s="1">
-        <v>1.279</v>
+        <v>1.269</v>
       </c>
       <c r="O64" s="1">
-        <v>0.957</v>
+        <v>0.95</v>
       </c>
       <c r="P64" s="1">
-        <v>0.608</v>
+        <v>0.619</v>
       </c>
       <c r="Q64" s="1">
-        <v>0.28</v>
+        <v>0.322</v>
       </c>
       <c r="R64" s="1">
-        <v>0.047</v>
+        <v>0.07099999999999999</v>
       </c>
       <c r="S64" s="1">
-        <v>-0.066</v>
+        <v>-0.092</v>
       </c>
       <c r="T64" s="1">
-        <v>-0.122</v>
+        <v>-0.163</v>
       </c>
       <c r="U64" s="1">
-        <v>-0.149</v>
+        <v>-0.216</v>
       </c>
     </row>
     <row r="65" spans="1:21">
@@ -4766,64 +4769,64 @@
         <v>63</v>
       </c>
       <c r="B65" s="1">
-        <v>0.044</v>
+        <v>0.036</v>
       </c>
       <c r="C65" s="1">
-        <v>0.197</v>
+        <v>0.188</v>
       </c>
       <c r="D65" s="1">
-        <v>0.484</v>
+        <v>0.48</v>
       </c>
       <c r="E65" s="1">
-        <v>0.759</v>
+        <v>0.772</v>
       </c>
       <c r="F65" s="1">
-        <v>1.031</v>
+        <v>1.034</v>
       </c>
       <c r="G65" s="1">
-        <v>1.347</v>
+        <v>1.33</v>
       </c>
       <c r="H65" s="1">
-        <v>1.727</v>
+        <v>1.703</v>
       </c>
       <c r="I65" s="1">
-        <v>2.159</v>
+        <v>2.118</v>
       </c>
       <c r="J65" s="1">
-        <v>2.518</v>
+        <v>2.453</v>
       </c>
       <c r="K65" s="1">
-        <v>2.657</v>
+        <v>2.595</v>
       </c>
       <c r="L65" s="1">
-        <v>2.546</v>
+        <v>2.473</v>
       </c>
       <c r="M65" s="1">
-        <v>2.156</v>
+        <v>2.068</v>
       </c>
       <c r="N65" s="1">
-        <v>1.548</v>
+        <v>1.493</v>
       </c>
       <c r="O65" s="1">
-        <v>0.909</v>
+        <v>0.912</v>
       </c>
       <c r="P65" s="1">
-        <v>0.363</v>
+        <v>0.398</v>
       </c>
       <c r="Q65" s="1">
-        <v>-0.039</v>
+        <v>0.013</v>
       </c>
       <c r="R65" s="1">
-        <v>-0.266</v>
+        <v>-0.23</v>
       </c>
       <c r="S65" s="1">
-        <v>-0.36</v>
+        <v>-0.367</v>
       </c>
       <c r="T65" s="1">
-        <v>-0.41</v>
+        <v>-0.434</v>
       </c>
       <c r="U65" s="1">
-        <v>-0.459</v>
+        <v>-0.468</v>
       </c>
     </row>
     <row r="66" spans="1:21">
@@ -4831,64 +4834,64 @@
         <v>64</v>
       </c>
       <c r="B66" s="1">
-        <v>0.635</v>
+        <v>0.632</v>
       </c>
       <c r="C66" s="1">
-        <v>0.758</v>
+        <v>0.766</v>
       </c>
       <c r="D66" s="1">
-        <v>0.974</v>
+        <v>0.984</v>
       </c>
       <c r="E66" s="1">
-        <v>1.199</v>
+        <v>1.197</v>
       </c>
       <c r="F66" s="1">
-        <v>1.463</v>
+        <v>1.439</v>
       </c>
       <c r="G66" s="1">
-        <v>1.767</v>
+        <v>1.731</v>
       </c>
       <c r="H66" s="1">
-        <v>2.07</v>
+        <v>2.039</v>
       </c>
       <c r="I66" s="1">
-        <v>2.301</v>
+        <v>2.273</v>
       </c>
       <c r="J66" s="1">
-        <v>2.377</v>
+        <v>2.342</v>
       </c>
       <c r="K66" s="1">
-        <v>2.234</v>
+        <v>2.182</v>
       </c>
       <c r="L66" s="1">
-        <v>1.846</v>
+        <v>1.8</v>
       </c>
       <c r="M66" s="1">
-        <v>1.314</v>
+        <v>1.264</v>
       </c>
       <c r="N66" s="1">
-        <v>0.762</v>
+        <v>0.698</v>
       </c>
       <c r="O66" s="1">
-        <v>0.275</v>
+        <v>0.242</v>
       </c>
       <c r="P66" s="1">
-        <v>-0.08400000000000001</v>
+        <v>-0.11</v>
       </c>
       <c r="Q66" s="1">
-        <v>-0.302</v>
+        <v>-0.334</v>
       </c>
       <c r="R66" s="1">
-        <v>-0.413</v>
+        <v>-0.436</v>
       </c>
       <c r="S66" s="1">
-        <v>-0.465</v>
+        <v>-0.51</v>
       </c>
       <c r="T66" s="1">
-        <v>-0.52</v>
+        <v>-0.608</v>
       </c>
       <c r="U66" s="1">
-        <v>-0.584</v>
+        <v>-0.6879999999999999</v>
       </c>
     </row>
     <row r="67" spans="1:21">
@@ -4896,64 +4899,64 @@
         <v>65</v>
       </c>
       <c r="B67" s="1">
-        <v>0.9429999999999999</v>
+        <v>0.948</v>
       </c>
       <c r="C67" s="1">
-        <v>1.101</v>
+        <v>1.116</v>
       </c>
       <c r="D67" s="1">
-        <v>1.398</v>
+        <v>1.425</v>
       </c>
       <c r="E67" s="1">
-        <v>1.731</v>
+        <v>1.738</v>
       </c>
       <c r="F67" s="1">
-        <v>2.102</v>
+        <v>2.049</v>
       </c>
       <c r="G67" s="1">
-        <v>2.434</v>
+        <v>2.325</v>
       </c>
       <c r="H67" s="1">
-        <v>2.629</v>
+        <v>2.5</v>
       </c>
       <c r="I67" s="1">
-        <v>2.641</v>
+        <v>2.488</v>
       </c>
       <c r="J67" s="1">
-        <v>2.436</v>
+        <v>2.272</v>
       </c>
       <c r="K67" s="1">
-        <v>1.988</v>
+        <v>1.84</v>
       </c>
       <c r="L67" s="1">
-        <v>1.383</v>
+        <v>1.267</v>
       </c>
       <c r="M67" s="1">
-        <v>0.74</v>
+        <v>0.667</v>
       </c>
       <c r="N67" s="1">
-        <v>0.175</v>
+        <v>0.122</v>
       </c>
       <c r="O67" s="1">
-        <v>-0.237</v>
+        <v>-0.284</v>
       </c>
       <c r="P67" s="1">
-        <v>-0.463</v>
+        <v>-0.485</v>
       </c>
       <c r="Q67" s="1">
-        <v>-0.538</v>
+        <v>-0.5659999999999999</v>
       </c>
       <c r="R67" s="1">
-        <v>-0.608</v>
+        <v>-0.612</v>
       </c>
       <c r="S67" s="1">
-        <v>-0.724</v>
+        <v>-0.679</v>
       </c>
       <c r="T67" s="1">
-        <v>-0.802</v>
+        <v>-0.761</v>
       </c>
       <c r="U67" s="1">
-        <v>-0.77</v>
+        <v>-0.759</v>
       </c>
     </row>
     <row r="68" spans="1:21">
@@ -4961,64 +4964,64 @@
         <v>66</v>
       </c>
       <c r="B68" s="1">
-        <v>1.429</v>
+        <v>1.435</v>
       </c>
       <c r="C68" s="1">
-        <v>1.666</v>
+        <v>1.675</v>
       </c>
       <c r="D68" s="1">
-        <v>2.118</v>
+        <v>2.117</v>
       </c>
       <c r="E68" s="1">
-        <v>2.606</v>
+        <v>2.561</v>
       </c>
       <c r="F68" s="1">
-        <v>3.011</v>
+        <v>2.95</v>
       </c>
       <c r="G68" s="1">
-        <v>3.241</v>
+        <v>3.186</v>
       </c>
       <c r="H68" s="1">
-        <v>3.255</v>
+        <v>3.206</v>
       </c>
       <c r="I68" s="1">
-        <v>2.983</v>
+        <v>2.953</v>
       </c>
       <c r="J68" s="1">
-        <v>2.381</v>
+        <v>2.356</v>
       </c>
       <c r="K68" s="1">
-        <v>1.572</v>
+        <v>1.543</v>
       </c>
       <c r="L68" s="1">
-        <v>0.744</v>
+        <v>0.726</v>
       </c>
       <c r="M68" s="1">
-        <v>0.034</v>
+        <v>0.024</v>
       </c>
       <c r="N68" s="1">
-        <v>-0.474</v>
+        <v>-0.473</v>
       </c>
       <c r="O68" s="1">
-        <v>-0.738</v>
+        <v>-0.732</v>
       </c>
       <c r="P68" s="1">
-        <v>-0.843</v>
+        <v>-0.847</v>
       </c>
       <c r="Q68" s="1">
-        <v>-0.92</v>
+        <v>-0.93</v>
       </c>
       <c r="R68" s="1">
-        <v>-1.032</v>
+        <v>-1.037</v>
       </c>
       <c r="S68" s="1">
-        <v>-1.172</v>
+        <v>-1.151</v>
       </c>
       <c r="T68" s="1">
-        <v>-1.179</v>
+        <v>-1.147</v>
       </c>
       <c r="U68" s="1">
-        <v>-0.989</v>
+        <v>-0.966</v>
       </c>
     </row>
     <row r="69" spans="1:21">
@@ -5026,64 +5029,129 @@
         <v>67</v>
       </c>
       <c r="B69" s="1">
-        <v>1.963</v>
+        <v>1.97</v>
       </c>
       <c r="C69" s="1">
-        <v>2.28</v>
+        <v>2.272</v>
       </c>
       <c r="D69" s="1">
-        <v>2.831</v>
+        <v>2.786</v>
       </c>
       <c r="E69" s="1">
-        <v>3.253</v>
+        <v>3.184</v>
       </c>
       <c r="F69" s="1">
-        <v>3.446</v>
+        <v>3.401</v>
       </c>
       <c r="G69" s="1">
-        <v>3.422</v>
+        <v>3.419</v>
       </c>
       <c r="H69" s="1">
-        <v>3.119</v>
+        <v>3.143</v>
       </c>
       <c r="I69" s="1">
-        <v>2.457</v>
+        <v>2.487</v>
       </c>
       <c r="J69" s="1">
-        <v>1.577</v>
+        <v>1.612</v>
       </c>
       <c r="K69" s="1">
-        <v>0.703</v>
+        <v>0.74</v>
       </c>
       <c r="L69" s="1">
-        <v>-0.052</v>
+        <v>-0.046</v>
       </c>
       <c r="M69" s="1">
-        <v>-0.592</v>
+        <v>-0.611</v>
       </c>
       <c r="N69" s="1">
-        <v>-0.877</v>
+        <v>-0.896</v>
       </c>
       <c r="O69" s="1">
-        <v>-0.989</v>
+        <v>-1.012</v>
       </c>
       <c r="P69" s="1">
-        <v>-1.08</v>
+        <v>-1.095</v>
       </c>
       <c r="Q69" s="1">
-        <v>-1.23</v>
+        <v>-1.233</v>
       </c>
       <c r="R69" s="1">
-        <v>-1.373</v>
+        <v>-1.375</v>
       </c>
       <c r="S69" s="1">
-        <v>-1.351</v>
+        <v>-1.336</v>
       </c>
       <c r="T69" s="1">
-        <v>-1.15</v>
+        <v>-1.101</v>
       </c>
       <c r="U69" s="1">
-        <v>-0.91</v>
+        <v>-0.854</v>
+      </c>
+    </row>
+    <row r="70" spans="1:21">
+      <c r="A70" s="2" t="s">
+        <v>68</v>
+      </c>
+      <c r="B70" s="1">
+        <v>2.345</v>
+      </c>
+      <c r="C70" s="1">
+        <v>2.618</v>
+      </c>
+      <c r="D70" s="1">
+        <v>3.016</v>
+      </c>
+      <c r="E70" s="1">
+        <v>3.225</v>
+      </c>
+      <c r="F70" s="1">
+        <v>3.241</v>
+      </c>
+      <c r="G70" s="1">
+        <v>2.985</v>
+      </c>
+      <c r="H70" s="1">
+        <v>2.376</v>
+      </c>
+      <c r="I70" s="1">
+        <v>1.546</v>
+      </c>
+      <c r="J70" s="1">
+        <v>0.717</v>
+      </c>
+      <c r="K70" s="1">
+        <v>-0.024</v>
+      </c>
+      <c r="L70" s="1">
+        <v>-0.5669999999999999</v>
+      </c>
+      <c r="M70" s="1">
+        <v>-0.857</v>
+      </c>
+      <c r="N70" s="1">
+        <v>-0.973</v>
+      </c>
+      <c r="O70" s="1">
+        <v>-1.059</v>
+      </c>
+      <c r="P70" s="1">
+        <v>-1.212</v>
+      </c>
+      <c r="Q70" s="1">
+        <v>-1.35</v>
+      </c>
+      <c r="R70" s="1">
+        <v>-1.318</v>
+      </c>
+      <c r="S70" s="1">
+        <v>-1.116</v>
+      </c>
+      <c r="T70" s="1">
+        <v>-0.878</v>
+      </c>
+      <c r="U70" s="1">
+        <v>-0.706</v>
       </c>
     </row>
   </sheetData>
@@ -5098,22 +5166,22 @@
   <sheetData>
     <row r="1" spans="1:1">
       <c r="A1" s="2" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
     </row>
     <row r="2" spans="1:1">
       <c r="A2" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
     </row>
     <row r="3" spans="1:1">
       <c r="A3" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
     </row>
     <row r="4" spans="1:1">
       <c r="A4" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
     </row>
   </sheetData>
